--- a/data/OP1/case33_2/case33_2_operational_data.xlsx
+++ b/data/OP1/case33_2/case33_2_operational_data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/micaelsimoes/PycharmProjects/shared-resources-planning/data/CS7/case33_2/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/micaelsimoes/PycharmProjects/shared-resources-planning/data/OP1/case33_2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22A33D5E-48B4-484F-BD94-44F8DCA9BB97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E208676C-69A3-CB40-9126-1BB62723DAA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1120" yWindow="620" windowWidth="29400" windowHeight="19120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1120" yWindow="620" windowWidth="50080" windowHeight="28180" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Characterization" sheetId="2" r:id="rId1"/>
@@ -473,12 +473,12 @@
         <v>1</v>
       </c>
       <c r="B2" s="1">
-        <f>E2*1</f>
-        <v>4</v>
+        <f>E2*1.5</f>
+        <v>6</v>
       </c>
       <c r="C2" s="1">
-        <f>-F2*1</f>
-        <v>-2.4</v>
+        <f>F2*1.5</f>
+        <v>-3.5999999999999996</v>
       </c>
       <c r="D2" s="2">
         <v>2.6917900403768499E-2</v>
@@ -487,7 +487,7 @@
         <v>4</v>
       </c>
       <c r="F2" s="4">
-        <v>2.4</v>
+        <v>-2.4</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
@@ -495,12 +495,12 @@
         <v>2</v>
       </c>
       <c r="B3" s="1">
-        <f t="shared" ref="B3:B33" si="0">E3*1</f>
-        <v>3.5999999999999996</v>
+        <f t="shared" ref="B3:B33" si="0">E3*1.5</f>
+        <v>5.3999999999999995</v>
       </c>
       <c r="C3" s="1">
-        <f t="shared" ref="C3:C33" si="1">-F3*1</f>
-        <v>-1.6</v>
+        <f t="shared" ref="C3:C33" si="1">F3*1.5</f>
+        <v>-2.4000000000000004</v>
       </c>
       <c r="D3" s="2">
         <v>2.4226110363391645E-2</v>
@@ -509,7 +509,7 @@
         <v>3.5999999999999996</v>
       </c>
       <c r="F3" s="4">
-        <v>1.6</v>
+        <v>-1.6</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
@@ -518,11 +518,11 @@
       </c>
       <c r="B4" s="1">
         <f t="shared" si="0"/>
-        <v>4.8</v>
+        <v>7.1999999999999993</v>
       </c>
       <c r="C4" s="1">
         <f t="shared" si="1"/>
-        <v>-3.2</v>
+        <v>-4.8000000000000007</v>
       </c>
       <c r="D4" s="2">
         <v>3.2301480484522194E-2</v>
@@ -531,7 +531,7 @@
         <v>4.8</v>
       </c>
       <c r="F4" s="4">
-        <v>3.2</v>
+        <v>-3.2</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
@@ -540,11 +540,11 @@
       </c>
       <c r="B5" s="1">
         <f t="shared" si="0"/>
-        <v>2.4</v>
+        <v>3.5999999999999996</v>
       </c>
       <c r="C5" s="1">
         <f t="shared" si="1"/>
-        <v>-1.2</v>
+        <v>-1.7999999999999998</v>
       </c>
       <c r="D5" s="2">
         <v>1.6150740242261097E-2</v>
@@ -553,7 +553,7 @@
         <v>2.4</v>
       </c>
       <c r="F5" s="4">
-        <v>1.2</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
@@ -562,11 +562,11 @@
       </c>
       <c r="B6" s="1">
         <f t="shared" si="0"/>
-        <v>2.4</v>
+        <v>3.5999999999999996</v>
       </c>
       <c r="C6" s="1">
         <f t="shared" si="1"/>
-        <v>-0.8</v>
+        <v>-1.2000000000000002</v>
       </c>
       <c r="D6" s="2">
         <v>1.6150740242261097E-2</v>
@@ -575,7 +575,7 @@
         <v>2.4</v>
       </c>
       <c r="F6" s="4">
-        <v>0.8</v>
+        <v>-0.8</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
@@ -584,11 +584,11 @@
       </c>
       <c r="B7" s="1">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C7" s="1">
         <f t="shared" si="1"/>
-        <v>-4</v>
+        <v>-6</v>
       </c>
       <c r="D7" s="2">
         <v>5.3835800807536999E-2</v>
@@ -597,7 +597,7 @@
         <v>8</v>
       </c>
       <c r="F7" s="4">
-        <v>4</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
@@ -606,11 +606,11 @@
       </c>
       <c r="B8" s="1">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C8" s="1">
         <f t="shared" si="1"/>
-        <v>-4</v>
+        <v>-6</v>
       </c>
       <c r="D8" s="2">
         <v>5.3835800807536999E-2</v>
@@ -619,7 +619,7 @@
         <v>8</v>
       </c>
       <c r="F8" s="4">
-        <v>4</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
@@ -628,11 +628,11 @@
       </c>
       <c r="B9" s="1">
         <f t="shared" si="0"/>
-        <v>2.4</v>
+        <v>3.5999999999999996</v>
       </c>
       <c r="C9" s="1">
         <f t="shared" si="1"/>
-        <v>-0.8</v>
+        <v>-1.2000000000000002</v>
       </c>
       <c r="D9" s="2">
         <v>1.6150740242261097E-2</v>
@@ -641,7 +641,7 @@
         <v>2.4</v>
       </c>
       <c r="F9" s="4">
-        <v>0.8</v>
+        <v>-0.8</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
@@ -650,11 +650,11 @@
       </c>
       <c r="B10" s="1">
         <f t="shared" si="0"/>
-        <v>2.4</v>
+        <v>3.5999999999999996</v>
       </c>
       <c r="C10" s="1">
         <f t="shared" si="1"/>
-        <v>-0.8</v>
+        <v>-1.2000000000000002</v>
       </c>
       <c r="D10" s="2">
         <v>1.6150740242261097E-2</v>
@@ -663,7 +663,7 @@
         <v>2.4</v>
       </c>
       <c r="F10" s="4">
-        <v>0.8</v>
+        <v>-0.8</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
@@ -672,11 +672,11 @@
       </c>
       <c r="B11" s="1">
         <f t="shared" si="0"/>
-        <v>1.7999999999999998</v>
+        <v>2.6999999999999997</v>
       </c>
       <c r="C11" s="1">
         <f t="shared" si="1"/>
-        <v>-1.2</v>
+        <v>-1.7999999999999998</v>
       </c>
       <c r="D11" s="2">
         <v>1.2113055181695823E-2</v>
@@ -685,7 +685,7 @@
         <v>1.7999999999999998</v>
       </c>
       <c r="F11" s="4">
-        <v>1.2</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
@@ -694,11 +694,11 @@
       </c>
       <c r="B12" s="1">
         <f t="shared" si="0"/>
-        <v>2.4</v>
+        <v>3.5999999999999996</v>
       </c>
       <c r="C12" s="1">
         <f t="shared" si="1"/>
-        <v>-1.4000000000000001</v>
+        <v>-2.1</v>
       </c>
       <c r="D12" s="2">
         <v>1.6150740242261097E-2</v>
@@ -707,7 +707,7 @@
         <v>2.4</v>
       </c>
       <c r="F12" s="4">
-        <v>1.4000000000000001</v>
+        <v>-1.4000000000000001</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
@@ -716,11 +716,11 @@
       </c>
       <c r="B13" s="1">
         <f t="shared" si="0"/>
-        <v>2.4</v>
+        <v>3.5999999999999996</v>
       </c>
       <c r="C13" s="1">
         <f t="shared" si="1"/>
-        <v>-1.4000000000000001</v>
+        <v>-2.1</v>
       </c>
       <c r="D13" s="2">
         <v>1.6150740242261097E-2</v>
@@ -729,7 +729,7 @@
         <v>2.4</v>
       </c>
       <c r="F13" s="4">
-        <v>1.4000000000000001</v>
+        <v>-1.4000000000000001</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
@@ -738,11 +738,11 @@
       </c>
       <c r="B14" s="1">
         <f t="shared" si="0"/>
-        <v>4.8</v>
+        <v>7.1999999999999993</v>
       </c>
       <c r="C14" s="1">
         <f t="shared" si="1"/>
-        <v>-3.2</v>
+        <v>-4.8000000000000007</v>
       </c>
       <c r="D14" s="2">
         <v>3.2301480484522194E-2</v>
@@ -751,7 +751,7 @@
         <v>4.8</v>
       </c>
       <c r="F14" s="4">
-        <v>3.2</v>
+        <v>-3.2</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
@@ -760,11 +760,11 @@
       </c>
       <c r="B15" s="1">
         <f t="shared" si="0"/>
-        <v>2.4</v>
+        <v>3.5999999999999996</v>
       </c>
       <c r="C15" s="1">
         <f t="shared" si="1"/>
-        <v>-0.4</v>
+        <v>-0.60000000000000009</v>
       </c>
       <c r="D15" s="2">
         <v>1.6150740242261097E-2</v>
@@ -773,7 +773,7 @@
         <v>2.4</v>
       </c>
       <c r="F15" s="4">
-        <v>0.4</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.2">
@@ -782,11 +782,11 @@
       </c>
       <c r="B16" s="1">
         <f t="shared" si="0"/>
-        <v>2.4</v>
+        <v>3.5999999999999996</v>
       </c>
       <c r="C16" s="1">
         <f t="shared" si="1"/>
-        <v>-0.8</v>
+        <v>-1.2000000000000002</v>
       </c>
       <c r="D16" s="2">
         <v>1.6150740242261097E-2</v>
@@ -795,7 +795,7 @@
         <v>2.4</v>
       </c>
       <c r="F16" s="4">
-        <v>0.8</v>
+        <v>-0.8</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.2">
@@ -804,11 +804,11 @@
       </c>
       <c r="B17" s="1">
         <f t="shared" si="0"/>
-        <v>2.4</v>
+        <v>3.5999999999999996</v>
       </c>
       <c r="C17" s="1">
         <f t="shared" si="1"/>
-        <v>-0.8</v>
+        <v>-1.2000000000000002</v>
       </c>
       <c r="D17" s="2">
         <v>1.6150740242261097E-2</v>
@@ -817,7 +817,7 @@
         <v>2.4</v>
       </c>
       <c r="F17" s="4">
-        <v>0.8</v>
+        <v>-0.8</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.2">
@@ -826,11 +826,11 @@
       </c>
       <c r="B18" s="1">
         <f t="shared" si="0"/>
-        <v>3.5999999999999996</v>
+        <v>5.3999999999999995</v>
       </c>
       <c r="C18" s="1">
         <f t="shared" si="1"/>
-        <v>-1.6</v>
+        <v>-2.4000000000000004</v>
       </c>
       <c r="D18" s="2">
         <v>2.4226110363391645E-2</v>
@@ -839,7 +839,7 @@
         <v>3.5999999999999996</v>
       </c>
       <c r="F18" s="4">
-        <v>1.6</v>
+        <v>-1.6</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.2">
@@ -848,11 +848,11 @@
       </c>
       <c r="B19" s="1">
         <f t="shared" si="0"/>
-        <v>3.5999999999999996</v>
+        <v>5.3999999999999995</v>
       </c>
       <c r="C19" s="1">
         <f t="shared" si="1"/>
-        <v>-1.6</v>
+        <v>-2.4000000000000004</v>
       </c>
       <c r="D19" s="2">
         <v>2.4226110363391645E-2</v>
@@ -861,7 +861,7 @@
         <v>3.5999999999999996</v>
       </c>
       <c r="F19" s="4">
-        <v>1.6</v>
+        <v>-1.6</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.2">
@@ -870,11 +870,11 @@
       </c>
       <c r="B20" s="1">
         <f t="shared" si="0"/>
-        <v>3.5999999999999996</v>
+        <v>5.3999999999999995</v>
       </c>
       <c r="C20" s="1">
         <f t="shared" si="1"/>
-        <v>-1.6</v>
+        <v>-2.4000000000000004</v>
       </c>
       <c r="D20" s="2">
         <v>2.4226110363391645E-2</v>
@@ -883,7 +883,7 @@
         <v>3.5999999999999996</v>
       </c>
       <c r="F20" s="4">
-        <v>1.6</v>
+        <v>-1.6</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.2">
@@ -892,11 +892,11 @@
       </c>
       <c r="B21" s="1">
         <f t="shared" si="0"/>
-        <v>3.5999999999999996</v>
+        <v>5.3999999999999995</v>
       </c>
       <c r="C21" s="1">
         <f t="shared" si="1"/>
-        <v>-1.6</v>
+        <v>-2.4000000000000004</v>
       </c>
       <c r="D21" s="2">
         <v>2.4226110363391645E-2</v>
@@ -905,7 +905,7 @@
         <v>3.5999999999999996</v>
       </c>
       <c r="F21" s="4">
-        <v>1.6</v>
+        <v>-1.6</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.2">
@@ -914,11 +914,11 @@
       </c>
       <c r="B22" s="1">
         <f t="shared" si="0"/>
-        <v>3.5999999999999996</v>
+        <v>5.3999999999999995</v>
       </c>
       <c r="C22" s="1">
         <f t="shared" si="1"/>
-        <v>-1.6</v>
+        <v>-2.4000000000000004</v>
       </c>
       <c r="D22" s="2">
         <v>2.4226110363391645E-2</v>
@@ -927,7 +927,7 @@
         <v>3.5999999999999996</v>
       </c>
       <c r="F22" s="4">
-        <v>1.6</v>
+        <v>-1.6</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.2">
@@ -936,11 +936,11 @@
       </c>
       <c r="B23" s="1">
         <f t="shared" si="0"/>
-        <v>3.5999999999999996</v>
+        <v>5.3999999999999995</v>
       </c>
       <c r="C23" s="1">
         <f t="shared" si="1"/>
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="D23" s="2">
         <v>2.4226110363391645E-2</v>
@@ -949,7 +949,7 @@
         <v>3.5999999999999996</v>
       </c>
       <c r="F23" s="4">
-        <v>2</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.2">
@@ -958,11 +958,11 @@
       </c>
       <c r="B24" s="1">
         <f t="shared" si="0"/>
-        <v>16.8</v>
+        <v>25.200000000000003</v>
       </c>
       <c r="C24" s="1">
         <f t="shared" si="1"/>
-        <v>-8</v>
+        <v>-12</v>
       </c>
       <c r="D24" s="2">
         <v>0.11305518169582769</v>
@@ -971,7 +971,7 @@
         <v>16.8</v>
       </c>
       <c r="F24" s="4">
-        <v>8</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.2">
@@ -980,11 +980,11 @@
       </c>
       <c r="B25" s="1">
         <f t="shared" si="0"/>
-        <v>16.8</v>
+        <v>25.200000000000003</v>
       </c>
       <c r="C25" s="1">
         <f t="shared" si="1"/>
-        <v>-8</v>
+        <v>-12</v>
       </c>
       <c r="D25" s="2">
         <v>0.11305518169582769</v>
@@ -993,7 +993,7 @@
         <v>16.8</v>
       </c>
       <c r="F25" s="4">
-        <v>8</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.2">
@@ -1002,20 +1002,20 @@
       </c>
       <c r="B26" s="1">
         <f t="shared" si="0"/>
-        <v>2.4</v>
+        <v>1.7999999999999998</v>
       </c>
       <c r="C26" s="1">
         <f t="shared" si="1"/>
-        <v>-1</v>
+        <v>-0.75</v>
       </c>
       <c r="D26" s="2">
         <v>1.6150740242261097E-2</v>
       </c>
       <c r="E26" s="4">
-        <v>2.4</v>
+        <v>1.2</v>
       </c>
       <c r="F26" s="4">
-        <v>1</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.2">
@@ -1024,20 +1024,20 @@
       </c>
       <c r="B27" s="1">
         <f t="shared" si="0"/>
-        <v>2.4</v>
+        <v>1.7999999999999998</v>
       </c>
       <c r="C27" s="1">
         <f t="shared" si="1"/>
-        <v>-1</v>
+        <v>-0.75</v>
       </c>
       <c r="D27" s="2">
         <v>1.6150740242261097E-2</v>
       </c>
       <c r="E27" s="4">
-        <v>2.4</v>
+        <v>1.2</v>
       </c>
       <c r="F27" s="4">
-        <v>1</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.2">
@@ -1046,20 +1046,20 @@
       </c>
       <c r="B28" s="1">
         <f t="shared" si="0"/>
-        <v>2.4</v>
+        <v>1.7999999999999998</v>
       </c>
       <c r="C28" s="1">
         <f t="shared" si="1"/>
-        <v>-0.8</v>
+        <v>-0.60000000000000009</v>
       </c>
       <c r="D28" s="2">
         <v>1.6150740242261097E-2</v>
       </c>
       <c r="E28" s="4">
-        <v>2.4</v>
+        <v>1.2</v>
       </c>
       <c r="F28" s="4">
-        <v>0.8</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.2">
@@ -1068,20 +1068,20 @@
       </c>
       <c r="B29" s="1">
         <f t="shared" si="0"/>
-        <v>4.8</v>
+        <v>3.5999999999999996</v>
       </c>
       <c r="C29" s="1">
         <f t="shared" si="1"/>
-        <v>-2.8000000000000003</v>
+        <v>-2.0999999999999996</v>
       </c>
       <c r="D29" s="2">
         <v>3.2301480484522194E-2</v>
       </c>
       <c r="E29" s="4">
-        <v>4.8</v>
+        <v>2.4</v>
       </c>
       <c r="F29" s="4">
-        <v>2.8000000000000003</v>
+        <v>-1.4</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.2">
@@ -1090,20 +1090,20 @@
       </c>
       <c r="B30" s="1">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C30" s="1">
         <f t="shared" si="1"/>
-        <v>-24</v>
+        <v>-3.1500000000000004</v>
       </c>
       <c r="D30" s="2">
         <v>5.3835800807536999E-2</v>
       </c>
       <c r="E30" s="4">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F30" s="4">
-        <v>24</v>
+        <v>-2.1</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.2">
@@ -1112,20 +1112,20 @@
       </c>
       <c r="B31" s="1">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="C31" s="1">
         <f t="shared" si="1"/>
-        <v>-2.8000000000000003</v>
+        <v>-2.0999999999999996</v>
       </c>
       <c r="D31" s="2">
         <v>4.0376850605652742E-2</v>
       </c>
       <c r="E31" s="4">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F31" s="4">
-        <v>2.8000000000000003</v>
+        <v>-1.4</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.2">
@@ -1134,20 +1134,20 @@
       </c>
       <c r="B32" s="1">
         <f t="shared" si="0"/>
-        <v>8.4</v>
+        <v>6.3000000000000007</v>
       </c>
       <c r="C32" s="1">
         <f t="shared" si="1"/>
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="D32" s="2">
         <v>5.6527590847913846E-2</v>
       </c>
       <c r="E32" s="4">
-        <v>8.4</v>
+        <v>4.2</v>
       </c>
       <c r="F32" s="4">
-        <v>4</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.2">
@@ -1156,20 +1156,20 @@
       </c>
       <c r="B33" s="1">
         <f t="shared" si="0"/>
-        <v>2.4</v>
+        <v>1.7999999999999998</v>
       </c>
       <c r="C33" s="1">
         <f t="shared" si="1"/>
-        <v>-1.6</v>
+        <v>-1.9500000000000002</v>
       </c>
       <c r="D33" s="2">
         <v>1.6150740242261097E-2</v>
       </c>
       <c r="E33" s="4">
-        <v>2.4</v>
+        <v>1.2</v>
       </c>
       <c r="F33" s="4">
-        <v>1.6</v>
+        <v>-1.3</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.2">
@@ -69432,76 +69432,76 @@
         <v>1</v>
       </c>
       <c r="D2" s="1">
-        <v>4.9164000000000012</v>
+        <v>9.8328000000000024</v>
       </c>
       <c r="E2" s="1">
-        <v>5.0804000000000009</v>
+        <v>10.160800000000002</v>
       </c>
       <c r="F2" s="1">
-        <v>4.5491999999999999</v>
+        <v>9.0983999999999998</v>
       </c>
       <c r="G2" s="1">
-        <v>4.3119999999999994</v>
+        <v>8.6239999999999988</v>
       </c>
       <c r="H2" s="1">
-        <v>3.5328000000000004</v>
+        <v>7.0656000000000008</v>
       </c>
       <c r="I2" s="1">
-        <v>2.9984000000000006</v>
+        <v>5.9968000000000012</v>
       </c>
       <c r="J2" s="1">
-        <v>3.6668000000000003</v>
+        <v>7.3336000000000006</v>
       </c>
       <c r="K2" s="1">
-        <v>0.63680000000000003</v>
+        <v>1.2736000000000001</v>
       </c>
       <c r="L2" s="1">
-        <v>0.56000000000000005</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="M2" s="1">
-        <v>0.8163999999999999</v>
+        <v>1.6327999999999998</v>
       </c>
       <c r="N2" s="1">
-        <v>0.48080000000000006</v>
+        <v>0.96160000000000012</v>
       </c>
       <c r="O2" s="1">
-        <v>0.6008</v>
+        <v>1.2016</v>
       </c>
       <c r="P2" s="1">
-        <v>0.95720000000000027</v>
+        <v>1.9144000000000005</v>
       </c>
       <c r="Q2" s="1">
-        <v>1.7636000000000003</v>
+        <v>3.5272000000000006</v>
       </c>
       <c r="R2" s="1">
-        <v>1.8815999999999999</v>
+        <v>3.7631999999999999</v>
       </c>
       <c r="S2" s="1">
-        <v>1.8503999999999998</v>
+        <v>3.7007999999999996</v>
       </c>
       <c r="T2" s="1">
-        <v>1.038</v>
+        <v>2.0760000000000001</v>
       </c>
       <c r="U2" s="1">
-        <v>2.1143999999999998</v>
+        <v>4.2287999999999997</v>
       </c>
       <c r="V2" s="1">
-        <v>1.2408000000000001</v>
+        <v>2.4816000000000003</v>
       </c>
       <c r="W2" s="1">
-        <v>0.87239999999999984</v>
+        <v>1.7447999999999997</v>
       </c>
       <c r="X2" s="1">
-        <v>1.3248000000000002</v>
+        <v>2.6496000000000004</v>
       </c>
       <c r="Y2" s="1">
-        <v>0.81880000000000008</v>
+        <v>1.6376000000000002</v>
       </c>
       <c r="Z2" s="1">
-        <v>3.7372000000000005</v>
+        <v>7.474400000000001</v>
       </c>
       <c r="AA2" s="1">
-        <v>4.5052000000000003</v>
+        <v>9.0104000000000006</v>
       </c>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.2">
@@ -69515,76 +69515,76 @@
         <v>1</v>
       </c>
       <c r="D3" s="1">
-        <v>-11.100000000000001</v>
+        <v>-22.200000000000003</v>
       </c>
       <c r="E3" s="1">
-        <v>-11.8696</v>
+        <v>-23.7392</v>
       </c>
       <c r="F3" s="1">
-        <v>-13.349600000000002</v>
+        <v>-26.699200000000005</v>
       </c>
       <c r="G3" s="1">
-        <v>-14.400400000000001</v>
+        <v>-28.800800000000002</v>
       </c>
       <c r="H3" s="1">
-        <v>-15.392000000000001</v>
+        <v>-30.784000000000002</v>
       </c>
       <c r="I3" s="1">
-        <v>-16.798000000000002</v>
+        <v>-33.596000000000004</v>
       </c>
       <c r="J3" s="1">
-        <v>-16.028400000000001</v>
+        <v>-32.056800000000003</v>
       </c>
       <c r="K3" s="1">
-        <v>-17.979759999999999</v>
+        <v>-35.959519999999998</v>
       </c>
       <c r="L3" s="1">
-        <v>-16.307359999999996</v>
+        <v>-32.614719999999991</v>
       </c>
       <c r="M3" s="1">
-        <v>-23.952839999999998</v>
+        <v>-47.905679999999997</v>
       </c>
       <c r="N3" s="1">
-        <v>-23.707360000000005</v>
+        <v>-47.41472000000001</v>
       </c>
       <c r="O3" s="1">
-        <v>-21.672160000000002</v>
+        <v>-43.344320000000003</v>
       </c>
       <c r="P3" s="1">
-        <v>-20.774560000000001</v>
+        <v>-41.549120000000002</v>
       </c>
       <c r="Q3" s="1">
-        <v>-20.057480000000002</v>
+        <v>-40.114960000000004</v>
       </c>
       <c r="R3" s="1">
-        <v>-18.905680000000004</v>
+        <v>-37.811360000000008</v>
       </c>
       <c r="S3" s="1">
-        <v>-17.204239999999999</v>
+        <v>-34.408479999999997</v>
       </c>
       <c r="T3" s="1">
-        <v>-16.086960000000001</v>
+        <v>-32.173920000000003</v>
       </c>
       <c r="U3" s="1">
-        <v>-14.396240000000002</v>
+        <v>-28.792480000000005</v>
       </c>
       <c r="V3" s="1">
-        <v>-9.1377199999999998</v>
+        <v>-18.27544</v>
       </c>
       <c r="W3" s="1">
-        <v>-10.226479999999999</v>
+        <v>-20.452959999999997</v>
       </c>
       <c r="X3" s="1">
-        <v>-10.809839999999999</v>
+        <v>-21.619679999999999</v>
       </c>
       <c r="Y3" s="1">
-        <v>-11.605399999999999</v>
+        <v>-23.210799999999999</v>
       </c>
       <c r="Z3" s="1">
-        <v>-9.2204000000000015</v>
+        <v>-18.440800000000003</v>
       </c>
       <c r="AA3" s="1">
-        <v>-9.797600000000001</v>
+        <v>-19.595200000000002</v>
       </c>
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.2">
@@ -69598,76 +69598,76 @@
         <v>1</v>
       </c>
       <c r="D4" s="1">
-        <v>10.69356</v>
+        <v>21.387119999999999</v>
       </c>
       <c r="E4" s="1">
-        <v>11.440319999999996</v>
+        <v>22.880639999999993</v>
       </c>
       <c r="F4" s="1">
-        <v>12.82724</v>
+        <v>25.65448</v>
       </c>
       <c r="G4" s="1">
-        <v>13.802440000000002</v>
+        <v>27.604880000000005</v>
       </c>
       <c r="H4" s="1">
-        <v>14.691399999999998</v>
+        <v>29.382799999999996</v>
       </c>
       <c r="I4" s="1">
-        <v>16.042000000000002</v>
+        <v>32.084000000000003</v>
       </c>
       <c r="J4" s="1">
-        <v>15.293999999999999</v>
+        <v>30.587999999999997</v>
       </c>
       <c r="K4" s="1">
-        <v>17.259160000000001</v>
+        <v>34.518320000000003</v>
       </c>
       <c r="L4" s="1">
-        <v>15.809160000000002</v>
+        <v>31.618320000000004</v>
       </c>
       <c r="M4" s="1">
-        <v>18.039439999999999</v>
+        <v>36.078879999999998</v>
       </c>
       <c r="N4" s="1">
-        <v>18.181480000000001</v>
+        <v>36.362960000000001</v>
       </c>
       <c r="O4" s="1">
-        <v>17.019639999999999</v>
+        <v>34.039279999999998</v>
       </c>
       <c r="P4" s="1">
-        <v>16.446000000000002</v>
+        <v>32.892000000000003</v>
       </c>
       <c r="Q4" s="1">
-        <v>16.02328</v>
+        <v>32.046559999999999</v>
       </c>
       <c r="R4" s="1">
-        <v>15.016320000000004</v>
+        <v>30.032640000000008</v>
       </c>
       <c r="S4" s="1">
-        <v>13.671480000000003</v>
+        <v>27.342960000000005</v>
       </c>
       <c r="T4" s="1">
-        <v>12.736039999999997</v>
+        <v>25.472079999999995</v>
       </c>
       <c r="U4" s="1">
-        <v>11.38288</v>
+        <v>22.76576</v>
       </c>
       <c r="V4" s="1">
-        <v>8.9093599999999995</v>
+        <v>17.818719999999999</v>
       </c>
       <c r="W4" s="1">
-        <v>9.9721600000000006</v>
+        <v>19.944320000000001</v>
       </c>
       <c r="X4" s="1">
-        <v>10.596560000000002</v>
+        <v>21.193120000000004</v>
       </c>
       <c r="Y4" s="1">
-        <v>11.414560000000002</v>
+        <v>22.829120000000003</v>
       </c>
       <c r="Z4" s="1">
-        <v>8.8819999999999997</v>
+        <v>17.763999999999999</v>
       </c>
       <c r="AA4" s="1">
-        <v>9.4448000000000025</v>
+        <v>18.889600000000005</v>
       </c>
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.2">
@@ -69681,76 +69681,76 @@
         <v>2</v>
       </c>
       <c r="D5" s="1">
-        <v>4.8672360000000019</v>
+        <v>9.7344720000000038</v>
       </c>
       <c r="E5" s="1">
-        <v>5.0804000000000009</v>
+        <v>10.160800000000002</v>
       </c>
       <c r="F5" s="1">
-        <v>4.7311680000000003</v>
+        <v>9.4623360000000005</v>
       </c>
       <c r="G5" s="1">
-        <v>4.3982399999999995</v>
+        <v>8.796479999999999</v>
       </c>
       <c r="H5" s="1">
-        <v>3.4621440000000003</v>
+        <v>6.9242880000000007</v>
       </c>
       <c r="I5" s="1">
-        <v>2.8784640000000006</v>
+        <v>5.7569280000000012</v>
       </c>
       <c r="J5" s="1">
-        <v>3.7034680000000004</v>
+        <v>7.4069360000000009</v>
       </c>
       <c r="K5" s="1">
-        <v>0.62406400000000006</v>
+        <v>1.2481280000000001</v>
       </c>
       <c r="L5" s="1">
-        <v>0.58240000000000014</v>
+        <v>1.1648000000000003</v>
       </c>
       <c r="M5" s="1">
-        <v>0.85721999999999998</v>
+        <v>1.71444</v>
       </c>
       <c r="N5" s="1">
-        <v>0.4711840000000001</v>
+        <v>0.94236800000000021</v>
       </c>
       <c r="O5" s="1">
-        <v>0.60680800000000001</v>
+        <v>1.213616</v>
       </c>
       <c r="P5" s="1">
-        <v>0.95720000000000027</v>
+        <v>1.9144000000000005</v>
       </c>
       <c r="Q5" s="1">
-        <v>1.8517800000000002</v>
+        <v>3.7035600000000004</v>
       </c>
       <c r="R5" s="1">
-        <v>1.8815999999999999</v>
+        <v>3.7631999999999999</v>
       </c>
       <c r="S5" s="1">
-        <v>1.8874079999999998</v>
+        <v>3.7748159999999995</v>
       </c>
       <c r="T5" s="1">
-        <v>0.98609999999999998</v>
+        <v>1.9722</v>
       </c>
       <c r="U5" s="1">
-        <v>2.2201199999999996</v>
+        <v>4.4402399999999993</v>
       </c>
       <c r="V5" s="1">
-        <v>1.2532080000000001</v>
+        <v>2.5064160000000002</v>
       </c>
       <c r="W5" s="1">
-        <v>0.89857199999999982</v>
+        <v>1.7971439999999996</v>
       </c>
       <c r="X5" s="1">
-        <v>1.3380480000000003</v>
+        <v>2.6760960000000007</v>
       </c>
       <c r="Y5" s="1">
-        <v>0.77786</v>
+        <v>1.55572</v>
       </c>
       <c r="Z5" s="1">
-        <v>3.8119440000000004</v>
+        <v>7.6238880000000009</v>
       </c>
       <c r="AA5" s="1">
-        <v>4.5052000000000003</v>
+        <v>9.0104000000000006</v>
       </c>
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.2">
@@ -69764,76 +69764,76 @@
         <v>2</v>
       </c>
       <c r="D6" s="1">
-        <v>-11.100000000000001</v>
+        <v>-22.200000000000003</v>
       </c>
       <c r="E6" s="1">
-        <v>-11.750904</v>
+        <v>-23.501808</v>
       </c>
       <c r="F6" s="1">
-        <v>-13.349600000000002</v>
+        <v>-26.699200000000005</v>
       </c>
       <c r="G6" s="1">
-        <v>-13.68038</v>
+        <v>-27.360759999999999</v>
       </c>
       <c r="H6" s="1">
-        <v>-14.930240000000001</v>
+        <v>-29.860480000000003</v>
       </c>
       <c r="I6" s="1">
-        <v>-16.126080000000002</v>
+        <v>-32.252160000000003</v>
       </c>
       <c r="J6" s="1">
-        <v>-16.188684000000002</v>
+        <v>-32.377368000000004</v>
       </c>
       <c r="K6" s="1">
-        <v>-17.979759999999999</v>
+        <v>-35.959519999999998</v>
       </c>
       <c r="L6" s="1">
-        <v>-16.307359999999996</v>
+        <v>-32.614719999999991</v>
       </c>
       <c r="M6" s="1">
-        <v>-23.713311599999997</v>
+        <v>-47.426623199999995</v>
       </c>
       <c r="N6" s="1">
-        <v>-24.181507200000006</v>
+        <v>-48.363014400000012</v>
       </c>
       <c r="O6" s="1">
-        <v>-21.238716800000002</v>
+        <v>-42.477433600000005</v>
       </c>
       <c r="P6" s="1">
-        <v>-21.605542400000001</v>
+        <v>-43.211084800000002</v>
       </c>
       <c r="Q6" s="1">
-        <v>-19.8569052</v>
+        <v>-39.7138104</v>
       </c>
       <c r="R6" s="1">
-        <v>-19.661907200000005</v>
+        <v>-39.32381440000001</v>
       </c>
       <c r="S6" s="1">
-        <v>-17.204239999999999</v>
+        <v>-34.408479999999997</v>
       </c>
       <c r="T6" s="1">
-        <v>-15.765220800000002</v>
+        <v>-31.530441600000003</v>
       </c>
       <c r="U6" s="1">
-        <v>-13.820390400000001</v>
+        <v>-27.640780800000002</v>
       </c>
       <c r="V6" s="1">
-        <v>-9.1377199999999998</v>
+        <v>-18.27544</v>
       </c>
       <c r="W6" s="1">
-        <v>-10.124215199999998</v>
+        <v>-20.248430399999997</v>
       </c>
       <c r="X6" s="1">
-        <v>-10.593643199999999</v>
+        <v>-21.187286399999998</v>
       </c>
       <c r="Y6" s="1">
-        <v>-11.257237999999999</v>
+        <v>-22.514475999999998</v>
       </c>
       <c r="Z6" s="1">
-        <v>-9.5892160000000004</v>
+        <v>-19.178432000000001</v>
       </c>
       <c r="AA6" s="1">
-        <v>-9.4056960000000007</v>
+        <v>-18.811392000000001</v>
       </c>
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.2">
@@ -69847,76 +69847,76 @@
         <v>2</v>
       </c>
       <c r="D7" s="1">
-        <v>10.158882</v>
+        <v>20.317764</v>
       </c>
       <c r="E7" s="1">
-        <v>11.783529599999998</v>
+        <v>23.567059199999996</v>
       </c>
       <c r="F7" s="1">
-        <v>12.314150399999999</v>
+        <v>24.628300799999998</v>
       </c>
       <c r="G7" s="1">
-        <v>13.112318000000002</v>
+        <v>26.224636000000004</v>
       </c>
       <c r="H7" s="1">
-        <v>14.250657999999998</v>
+        <v>28.501315999999996</v>
       </c>
       <c r="I7" s="1">
-        <v>16.523260000000004</v>
+        <v>33.046520000000008</v>
       </c>
       <c r="J7" s="1">
-        <v>14.68224</v>
+        <v>29.36448</v>
       </c>
       <c r="K7" s="1">
-        <v>16.568793600000003</v>
+        <v>33.137587200000006</v>
       </c>
       <c r="L7" s="1">
-        <v>15.967251600000003</v>
+        <v>31.934503200000005</v>
       </c>
       <c r="M7" s="1">
-        <v>17.4982568</v>
+        <v>34.9965136</v>
       </c>
       <c r="N7" s="1">
-        <v>18.181480000000001</v>
+        <v>36.362960000000001</v>
       </c>
       <c r="O7" s="1">
-        <v>17.360032799999999</v>
+        <v>34.720065599999998</v>
       </c>
       <c r="P7" s="1">
-        <v>15.788160000000003</v>
+        <v>31.576320000000006</v>
       </c>
       <c r="Q7" s="1">
-        <v>16.343745599999998</v>
+        <v>32.687491199999997</v>
       </c>
       <c r="R7" s="1">
-        <v>15.767136000000004</v>
+        <v>31.534272000000009</v>
       </c>
       <c r="S7" s="1">
-        <v>14.081624400000003</v>
+        <v>28.163248800000005</v>
       </c>
       <c r="T7" s="1">
-        <v>12.353958799999997</v>
+        <v>24.707917599999995</v>
       </c>
       <c r="U7" s="1">
-        <v>11.838195199999999</v>
+        <v>23.676390399999999</v>
       </c>
       <c r="V7" s="1">
-        <v>9.3548279999999995</v>
+        <v>18.709655999999999</v>
       </c>
       <c r="W7" s="1">
-        <v>9.9721600000000006</v>
+        <v>19.944320000000001</v>
       </c>
       <c r="X7" s="1">
-        <v>10.066732000000002</v>
+        <v>20.133464000000004</v>
       </c>
       <c r="Y7" s="1">
-        <v>11.985288000000002</v>
+        <v>23.970576000000005</v>
       </c>
       <c r="Z7" s="1">
-        <v>8.7931799999999996</v>
+        <v>17.586359999999999</v>
       </c>
       <c r="AA7" s="1">
-        <v>9.4448000000000025</v>
+        <v>18.889600000000005</v>
       </c>
     </row>
     <row r="8" spans="1:27" x14ac:dyDescent="0.2">
@@ -69930,76 +69930,76 @@
         <v>3</v>
       </c>
       <c r="D8" s="1">
-        <v>4.7698912800000013</v>
+        <v>9.5397825600000026</v>
       </c>
       <c r="E8" s="1">
-        <v>5.1820080000000006</v>
+        <v>10.364016000000001</v>
       </c>
       <c r="F8" s="1">
-        <v>4.7784796800000002</v>
+        <v>9.5569593600000005</v>
       </c>
       <c r="G8" s="1">
-        <v>4.2223103999999996</v>
+        <v>8.4446207999999992</v>
       </c>
       <c r="H8" s="1">
-        <v>3.2890367999999999</v>
+        <v>6.5780735999999997</v>
       </c>
       <c r="I8" s="1">
-        <v>2.9072486400000006</v>
+        <v>5.8144972800000012</v>
       </c>
       <c r="J8" s="1">
-        <v>3.6664333200000003</v>
+        <v>7.3328666400000007</v>
       </c>
       <c r="K8" s="1">
-        <v>0.64902656000000003</v>
+        <v>1.2980531200000001</v>
       </c>
       <c r="L8" s="1">
-        <v>0.58240000000000014</v>
+        <v>1.1648000000000003</v>
       </c>
       <c r="M8" s="1">
-        <v>0.81435900000000006</v>
+        <v>1.6287180000000001</v>
       </c>
       <c r="N8" s="1">
-        <v>0.47589584000000007</v>
+        <v>0.95179168000000014</v>
       </c>
       <c r="O8" s="1">
-        <v>0.60680800000000001</v>
+        <v>1.213616</v>
       </c>
       <c r="P8" s="1">
-        <v>0.94762800000000025</v>
+        <v>1.8952560000000005</v>
       </c>
       <c r="Q8" s="1">
-        <v>1.7591910000000002</v>
+        <v>3.5183820000000003</v>
       </c>
       <c r="R8" s="1">
-        <v>1.8251519999999999</v>
+        <v>3.6503039999999998</v>
       </c>
       <c r="S8" s="1">
-        <v>1.8307857599999997</v>
+        <v>3.6615715199999994</v>
       </c>
       <c r="T8" s="1">
-        <v>0.98609999999999998</v>
+        <v>1.9722</v>
       </c>
       <c r="U8" s="1">
-        <v>2.1535163999999996</v>
+        <v>4.3070327999999991</v>
       </c>
       <c r="V8" s="1">
-        <v>1.22814384</v>
+        <v>2.45628768</v>
       </c>
       <c r="W8" s="1">
-        <v>0.9435005999999998</v>
+        <v>1.8870011999999996</v>
       </c>
       <c r="X8" s="1">
-        <v>1.3380480000000003</v>
+        <v>2.6760960000000007</v>
       </c>
       <c r="Y8" s="1">
-        <v>0.80897439999999998</v>
+        <v>1.6179488</v>
       </c>
       <c r="Z8" s="1">
-        <v>3.7357051200000004</v>
+        <v>7.4714102400000009</v>
       </c>
       <c r="AA8" s="1">
-        <v>4.3249919999999999</v>
+        <v>8.6499839999999999</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.2">
@@ -70013,76 +70013,76 @@
         <v>3</v>
       </c>
       <c r="D9" s="1">
-        <v>-10.545000000000002</v>
+        <v>-21.090000000000003</v>
       </c>
       <c r="E9" s="1">
-        <v>-11.750904</v>
+        <v>-23.501808</v>
       </c>
       <c r="F9" s="1">
-        <v>-12.682120000000003</v>
+        <v>-25.364240000000006</v>
       </c>
       <c r="G9" s="1">
-        <v>-13.68038</v>
+        <v>-27.360759999999999</v>
       </c>
       <c r="H9" s="1">
-        <v>-15.527449600000002</v>
+        <v>-31.054899200000005</v>
       </c>
       <c r="I9" s="1">
-        <v>-15.803558400000002</v>
+        <v>-31.607116800000004</v>
       </c>
       <c r="J9" s="1">
-        <v>-16.674344520000002</v>
+        <v>-33.348689040000004</v>
       </c>
       <c r="K9" s="1">
-        <v>-17.620164799999998</v>
+        <v>-35.240329599999995</v>
       </c>
       <c r="L9" s="1">
-        <v>-17.122727999999995</v>
+        <v>-34.24545599999999</v>
       </c>
       <c r="M9" s="1">
-        <v>-23.950444715999996</v>
+        <v>-47.900889431999992</v>
       </c>
       <c r="N9" s="1">
-        <v>-23.456061984000009</v>
+        <v>-46.912123968000017</v>
       </c>
       <c r="O9" s="1">
-        <v>-21.875878304000004</v>
+        <v>-43.751756608000008</v>
       </c>
       <c r="P9" s="1">
-        <v>-21.389486976000004</v>
+        <v>-42.778973952000008</v>
       </c>
       <c r="Q9" s="1">
-        <v>-20.849750459999999</v>
+        <v>-41.699500919999998</v>
       </c>
       <c r="R9" s="1">
-        <v>-19.465288128000005</v>
+        <v>-38.930576256000009</v>
       </c>
       <c r="S9" s="1">
-        <v>-17.204239999999999</v>
+        <v>-34.408479999999997</v>
       </c>
       <c r="T9" s="1">
-        <v>-15.607568592000002</v>
+        <v>-31.215137184000003</v>
       </c>
       <c r="U9" s="1">
-        <v>-14.373206016000001</v>
+        <v>-28.746412032000002</v>
       </c>
       <c r="V9" s="1">
-        <v>-9.4118516000000003</v>
+        <v>-18.823703200000001</v>
       </c>
       <c r="W9" s="1">
-        <v>-10.022973047999997</v>
+        <v>-20.045946095999994</v>
       </c>
       <c r="X9" s="1">
-        <v>-10.593643199999999</v>
+        <v>-21.187286399999998</v>
       </c>
       <c r="Y9" s="1">
-        <v>-10.694376099999999</v>
+        <v>-21.388752199999999</v>
       </c>
       <c r="Z9" s="1">
-        <v>-9.4933238400000004</v>
+        <v>-18.986647680000001</v>
       </c>
       <c r="AA9" s="1">
-        <v>-9.8759808000000007</v>
+        <v>-19.751961600000001</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.2">
@@ -70096,76 +70096,76 @@
         <v>3</v>
       </c>
       <c r="D10" s="1">
-        <v>10.36205964</v>
+        <v>20.72411928</v>
       </c>
       <c r="E10" s="1">
-        <v>11.194353119999999</v>
+        <v>22.388706239999998</v>
       </c>
       <c r="F10" s="1">
-        <v>12.314150399999999</v>
+        <v>24.628300799999998</v>
       </c>
       <c r="G10" s="1">
-        <v>12.718948460000002</v>
+        <v>25.437896920000004</v>
       </c>
       <c r="H10" s="1">
-        <v>13.538125099999997</v>
+        <v>27.076250199999993</v>
       </c>
       <c r="I10" s="1">
-        <v>15.697097000000003</v>
+        <v>31.394194000000006</v>
       </c>
       <c r="J10" s="1">
-        <v>13.948127999999999</v>
+        <v>27.896255999999997</v>
       </c>
       <c r="K10" s="1">
-        <v>15.740353920000002</v>
+        <v>31.480707840000004</v>
       </c>
       <c r="L10" s="1">
-        <v>15.647906568000003</v>
+        <v>31.295813136000007</v>
       </c>
       <c r="M10" s="1">
-        <v>17.848221936000002</v>
+        <v>35.696443872000003</v>
       </c>
       <c r="N10" s="1">
-        <v>18.5451096</v>
+        <v>37.0902192</v>
       </c>
       <c r="O10" s="1">
-        <v>16.49203116</v>
+        <v>32.98406232</v>
       </c>
       <c r="P10" s="1">
-        <v>16.419686400000003</v>
+        <v>32.839372800000007</v>
       </c>
       <c r="Q10" s="1">
-        <v>16.507183055999999</v>
+        <v>33.014366111999998</v>
       </c>
       <c r="R10" s="1">
-        <v>16.082478720000005</v>
+        <v>32.164957440000009</v>
       </c>
       <c r="S10" s="1">
-        <v>13.518359424000003</v>
+        <v>27.036718848000007</v>
       </c>
       <c r="T10" s="1">
-        <v>12.848117151999997</v>
+        <v>25.696234303999994</v>
       </c>
       <c r="U10" s="1">
-        <v>11.364667391999999</v>
+        <v>22.729334783999999</v>
       </c>
       <c r="V10" s="1">
-        <v>9.822569399999999</v>
+        <v>19.645138799999998</v>
       </c>
       <c r="W10" s="1">
-        <v>10.071881600000001</v>
+        <v>20.143763200000002</v>
       </c>
       <c r="X10" s="1">
-        <v>10.469401280000001</v>
+        <v>20.938802560000003</v>
       </c>
       <c r="Y10" s="1">
-        <v>12.344846640000004</v>
+        <v>24.689693280000007</v>
       </c>
       <c r="Z10" s="1">
-        <v>8.8811117999999993</v>
+        <v>17.762223599999999</v>
       </c>
       <c r="AA10" s="1">
-        <v>9.9170400000000036</v>
+        <v>19.834080000000007</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.2">
@@ -70179,76 +70179,76 @@
         <v>1</v>
       </c>
       <c r="D11" s="1">
-        <v>4.6705800000000011</v>
+        <v>9.3411600000000021</v>
       </c>
       <c r="E11" s="1">
-        <v>4.8263800000000003</v>
+        <v>9.6527600000000007</v>
       </c>
       <c r="F11" s="1">
-        <v>4.3217400000000001</v>
+        <v>8.6434800000000003</v>
       </c>
       <c r="G11" s="1">
-        <v>4.0963999999999992</v>
+        <v>8.1927999999999983</v>
       </c>
       <c r="H11" s="1">
-        <v>3.35616</v>
+        <v>6.7123200000000001</v>
       </c>
       <c r="I11" s="1">
-        <v>2.8484800000000003</v>
+        <v>5.6969600000000007</v>
       </c>
       <c r="J11" s="1">
-        <v>3.48346</v>
+        <v>6.96692</v>
       </c>
       <c r="K11" s="1">
-        <v>0.60496000000000005</v>
+        <v>1.2099200000000001</v>
       </c>
       <c r="L11" s="1">
-        <v>0.53200000000000003</v>
+        <v>1.0640000000000001</v>
       </c>
       <c r="M11" s="1">
-        <v>0.77557999999999983</v>
+        <v>1.5511599999999997</v>
       </c>
       <c r="N11" s="1">
-        <v>0.45676000000000005</v>
+        <v>0.91352000000000011</v>
       </c>
       <c r="O11" s="1">
-        <v>0.57075999999999993</v>
+        <v>1.1415199999999999</v>
       </c>
       <c r="P11" s="1">
-        <v>0.90934000000000026</v>
+        <v>1.8186800000000005</v>
       </c>
       <c r="Q11" s="1">
-        <v>1.6754200000000001</v>
+        <v>3.3508400000000003</v>
       </c>
       <c r="R11" s="1">
-        <v>1.7875199999999998</v>
+        <v>3.5750399999999996</v>
       </c>
       <c r="S11" s="1">
-        <v>1.7578799999999997</v>
+        <v>3.5157599999999993</v>
       </c>
       <c r="T11" s="1">
-        <v>0.98609999999999998</v>
+        <v>1.9722</v>
       </c>
       <c r="U11" s="1">
-        <v>2.0086799999999996</v>
+        <v>4.0173599999999992</v>
       </c>
       <c r="V11" s="1">
-        <v>1.17876</v>
+        <v>2.3575200000000001</v>
       </c>
       <c r="W11" s="1">
-        <v>0.82877999999999985</v>
+        <v>1.6575599999999997</v>
       </c>
       <c r="X11" s="1">
-        <v>1.2585600000000001</v>
+        <v>2.5171200000000002</v>
       </c>
       <c r="Y11" s="1">
-        <v>0.77786</v>
+        <v>1.55572</v>
       </c>
       <c r="Z11" s="1">
-        <v>3.5503400000000003</v>
+        <v>7.1006800000000005</v>
       </c>
       <c r="AA11" s="1">
-        <v>4.2799399999999999</v>
+        <v>8.5598799999999997</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.2">
@@ -70262,76 +70262,76 @@
         <v>1</v>
       </c>
       <c r="D12" s="1">
-        <v>-10.966800000000003</v>
+        <v>-21.933600000000006</v>
       </c>
       <c r="E12" s="1">
-        <v>-11.750904</v>
+        <v>-23.501808</v>
       </c>
       <c r="F12" s="1">
-        <v>-12.048014000000002</v>
+        <v>-24.096028000000004</v>
       </c>
       <c r="G12" s="1">
-        <v>-13.68038</v>
+        <v>-27.360759999999999</v>
       </c>
       <c r="H12" s="1">
-        <v>-15.372175104000002</v>
+        <v>-30.744350208000004</v>
       </c>
       <c r="I12" s="1">
-        <v>-16.435700736000001</v>
+        <v>-32.871401472000002</v>
       </c>
       <c r="J12" s="1">
-        <v>-16.174114184400004</v>
+        <v>-32.348228368800008</v>
       </c>
       <c r="K12" s="1">
-        <v>-17.443963151999995</v>
+        <v>-34.88792630399999</v>
       </c>
       <c r="L12" s="1">
-        <v>-17.465182559999995</v>
+        <v>-34.93036511999999</v>
       </c>
       <c r="M12" s="1">
-        <v>-22.992426927359997</v>
+        <v>-45.984853854719994</v>
       </c>
       <c r="N12" s="1">
-        <v>-23.690622603840012</v>
+        <v>-47.381245207680024</v>
       </c>
       <c r="O12" s="1">
-        <v>-22.532154653120006</v>
+        <v>-45.064309306240013</v>
       </c>
       <c r="P12" s="1">
-        <v>-20.747802366720002</v>
+        <v>-41.495604733440004</v>
       </c>
       <c r="Q12" s="1">
-        <v>-19.807262936999997</v>
+        <v>-39.614525873999995</v>
       </c>
       <c r="R12" s="1">
-        <v>-19.270635246720005</v>
+        <v>-38.54127049344001</v>
       </c>
       <c r="S12" s="1">
-        <v>-17.204239999999999</v>
+        <v>-34.408479999999997</v>
       </c>
       <c r="T12" s="1">
-        <v>-16.231871335680001</v>
+        <v>-32.463742671360002</v>
       </c>
       <c r="U12" s="1">
-        <v>-14.08574189568</v>
+        <v>-28.17148379136</v>
       </c>
       <c r="V12" s="1">
-        <v>-9.0353775360000004</v>
+        <v>-18.070755072000001</v>
       </c>
       <c r="W12" s="1">
-        <v>-10.123202778479998</v>
+        <v>-20.246405556959996</v>
       </c>
       <c r="X12" s="1">
-        <v>-11.123325359999999</v>
+        <v>-22.246650719999998</v>
       </c>
       <c r="Y12" s="1">
-        <v>-10.694376099999999</v>
+        <v>-21.388752199999999</v>
       </c>
       <c r="Z12" s="1">
-        <v>-9.2085241248000003</v>
+        <v>-18.417048249600001</v>
       </c>
       <c r="AA12" s="1">
-        <v>-9.6784611839999997</v>
+        <v>-19.356922367999999</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.2">
@@ -70345,76 +70345,76 @@
         <v>1</v>
       </c>
       <c r="D13" s="1">
-        <v>9.8439566579999997</v>
+        <v>19.687913315999999</v>
       </c>
       <c r="E13" s="1">
-        <v>10.8585225264</v>
+        <v>21.7170450528</v>
       </c>
       <c r="F13" s="1">
-        <v>12.437291903999999</v>
+        <v>24.874583807999997</v>
       </c>
       <c r="G13" s="1">
-        <v>12.464569490800002</v>
+        <v>24.929138981600005</v>
       </c>
       <c r="H13" s="1">
-        <v>13.402743848999997</v>
+        <v>26.805487697999993</v>
       </c>
       <c r="I13" s="1">
-        <v>15.854067970000003</v>
+        <v>31.708135940000005</v>
       </c>
       <c r="J13" s="1">
-        <v>13.948127999999999</v>
+        <v>27.896255999999997</v>
       </c>
       <c r="K13" s="1">
-        <v>15.897757459200001</v>
+        <v>31.795514918400002</v>
       </c>
       <c r="L13" s="1">
-        <v>15.647906568000003</v>
+        <v>31.295813136000007</v>
       </c>
       <c r="M13" s="1">
-        <v>18.383668594080003</v>
+        <v>36.767337188160006</v>
       </c>
       <c r="N13" s="1">
-        <v>17.617854120000001</v>
+        <v>35.235708240000001</v>
       </c>
       <c r="O13" s="1">
-        <v>15.667429602</v>
+        <v>31.334859204000001</v>
       </c>
       <c r="P13" s="1">
-        <v>16.912276992000002</v>
+        <v>33.824553984000005</v>
       </c>
       <c r="Q13" s="1">
-        <v>16.34211122544</v>
+        <v>32.68422245088</v>
       </c>
       <c r="R13" s="1">
-        <v>15.760829145600006</v>
+        <v>31.521658291200012</v>
       </c>
       <c r="S13" s="1">
-        <v>12.842441452800003</v>
+        <v>25.684882905600006</v>
       </c>
       <c r="T13" s="1">
-        <v>13.490523009599997</v>
+        <v>26.981046019199994</v>
       </c>
       <c r="U13" s="1">
-        <v>11.819254087679999</v>
+        <v>23.638508175359998</v>
       </c>
       <c r="V13" s="1">
-        <v>9.9207950939999989</v>
+        <v>19.841590187999998</v>
       </c>
       <c r="W13" s="1">
-        <v>10.374038048000003</v>
+        <v>20.748076096000005</v>
       </c>
       <c r="X13" s="1">
-        <v>10.364707267200002</v>
+        <v>20.729414534400004</v>
       </c>
       <c r="Y13" s="1">
-        <v>12.838640505600004</v>
+        <v>25.677281011200009</v>
       </c>
       <c r="Z13" s="1">
-        <v>8.8811117999999993</v>
+        <v>17.762223599999999</v>
       </c>
       <c r="AA13" s="1">
-        <v>10.115380800000004</v>
+        <v>20.230761600000008</v>
       </c>
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.2">
@@ -70428,76 +70428,76 @@
         <v>2</v>
       </c>
       <c r="D14" s="1">
-        <v>4.8574032000000011</v>
+        <v>9.7148064000000023</v>
       </c>
       <c r="E14" s="1">
-        <v>4.8746438000000003</v>
+        <v>9.7492876000000006</v>
       </c>
       <c r="F14" s="1">
-        <v>4.3217400000000001</v>
+        <v>8.6434800000000003</v>
       </c>
       <c r="G14" s="1">
-        <v>4.1783279999999987</v>
+        <v>8.3566559999999974</v>
       </c>
       <c r="H14" s="1">
-        <v>3.3897216000000001</v>
+        <v>6.7794432000000002</v>
       </c>
       <c r="I14" s="1">
-        <v>2.7630256000000002</v>
+        <v>5.5260512000000004</v>
       </c>
       <c r="J14" s="1">
-        <v>3.6227983999999998</v>
+        <v>7.2455967999999995</v>
       </c>
       <c r="K14" s="1">
-        <v>0.59891040000000006</v>
+        <v>1.1978208000000001</v>
       </c>
       <c r="L14" s="1">
-        <v>0.54796000000000011</v>
+        <v>1.0959200000000002</v>
       </c>
       <c r="M14" s="1">
-        <v>0.76782419999999985</v>
+        <v>1.5356483999999997</v>
       </c>
       <c r="N14" s="1">
-        <v>0.47046280000000001</v>
+        <v>0.94092560000000003</v>
       </c>
       <c r="O14" s="1">
-        <v>0.54222199999999998</v>
+        <v>1.084444</v>
       </c>
       <c r="P14" s="1">
-        <v>0.90934000000000026</v>
+        <v>1.8186800000000005</v>
       </c>
       <c r="Q14" s="1">
-        <v>1.7256826000000001</v>
+        <v>3.4513652000000001</v>
       </c>
       <c r="R14" s="1">
-        <v>1.7517695999999998</v>
+        <v>3.5035391999999996</v>
       </c>
       <c r="S14" s="1">
-        <v>1.7930375999999995</v>
+        <v>3.5860751999999989</v>
       </c>
       <c r="T14" s="1">
-        <v>0.94665599999999994</v>
+        <v>1.8933119999999999</v>
       </c>
       <c r="U14" s="1">
-        <v>1.9283327999999995</v>
+        <v>3.856665599999999</v>
       </c>
       <c r="V14" s="1">
-        <v>1.1316096</v>
+        <v>2.2632192</v>
       </c>
       <c r="W14" s="1">
-        <v>0.87021899999999985</v>
+        <v>1.7404379999999997</v>
       </c>
       <c r="X14" s="1">
-        <v>1.2208032000000002</v>
+        <v>2.4416064000000004</v>
       </c>
       <c r="Y14" s="1">
-        <v>0.80119580000000001</v>
+        <v>1.6023916</v>
       </c>
       <c r="Z14" s="1">
-        <v>3.5858434000000003</v>
+        <v>7.1716868000000007</v>
       </c>
       <c r="AA14" s="1">
-        <v>4.1943412000000002</v>
+        <v>8.3886824000000004</v>
       </c>
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.2">
@@ -70511,76 +70511,76 @@
         <v>2</v>
       </c>
       <c r="D15" s="1">
-        <v>-11.076468000000002</v>
+        <v>-22.152936000000004</v>
       </c>
       <c r="E15" s="1">
-        <v>-11.515885920000001</v>
+        <v>-23.031771840000001</v>
       </c>
       <c r="F15" s="1">
-        <v>-11.566093440000001</v>
+        <v>-23.132186880000003</v>
       </c>
       <c r="G15" s="1">
-        <v>-13.133164799999999</v>
+        <v>-26.266329599999999</v>
       </c>
       <c r="H15" s="1">
-        <v>-15.987062108160004</v>
+        <v>-31.974124216320007</v>
       </c>
       <c r="I15" s="1">
-        <v>-16.106986721279998</v>
+        <v>-32.213973442559997</v>
       </c>
       <c r="J15" s="1">
-        <v>-15.850631900712003</v>
+        <v>-31.701263801424005</v>
       </c>
       <c r="K15" s="1">
-        <v>-16.746204625919994</v>
+        <v>-33.492409251839987</v>
       </c>
       <c r="L15" s="1">
-        <v>-17.639834385599997</v>
+        <v>-35.279668771199994</v>
       </c>
       <c r="M15" s="1">
-        <v>-22.762502658086397</v>
+        <v>-45.525005316172795</v>
       </c>
       <c r="N15" s="1">
-        <v>-24.638247507993611</v>
+        <v>-49.276495015987223</v>
       </c>
       <c r="O15" s="1">
-        <v>-22.081511560057606</v>
+        <v>-44.163023120115213</v>
       </c>
       <c r="P15" s="1">
-        <v>-20.540324343052802</v>
+        <v>-41.080648686105604</v>
       </c>
       <c r="Q15" s="1">
-        <v>-19.014972419519996</v>
+        <v>-38.029944839039992</v>
       </c>
       <c r="R15" s="1">
-        <v>-18.885222541785605</v>
+        <v>-37.770445083571211</v>
       </c>
       <c r="S15" s="1">
-        <v>-16.344027999999998</v>
+        <v>-32.688055999999996</v>
       </c>
       <c r="T15" s="1">
-        <v>-16.231871335680001</v>
+        <v>-32.463742671360002</v>
       </c>
       <c r="U15" s="1">
-        <v>-13.9448844767232</v>
+        <v>-27.889768953446399</v>
       </c>
       <c r="V15" s="1">
-        <v>-9.0353775360000004</v>
+        <v>-18.070755072000001</v>
       </c>
       <c r="W15" s="1">
-        <v>-10.325666834049597</v>
+        <v>-20.651333668099195</v>
       </c>
       <c r="X15" s="1">
-        <v>-11.234558613599999</v>
+        <v>-22.469117227199998</v>
       </c>
       <c r="Y15" s="1">
-        <v>-10.801319861</v>
+        <v>-21.602639721999999</v>
       </c>
       <c r="Z15" s="1">
-        <v>-8.8401831598079994</v>
+        <v>-17.680366319615999</v>
       </c>
       <c r="AA15" s="1">
-        <v>-10.06559963136</v>
+        <v>-20.131199262719999</v>
       </c>
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.2">
@@ -70594,76 +70594,76 @@
         <v>2</v>
       </c>
       <c r="D16" s="1">
-        <v>9.3517588250999992</v>
+        <v>18.703517650199998</v>
       </c>
       <c r="E16" s="1">
-        <v>10.424181625344</v>
+        <v>20.848363250687999</v>
       </c>
       <c r="F16" s="1">
-        <v>13.059156499199998</v>
+        <v>26.118312998399997</v>
       </c>
       <c r="G16" s="1">
-        <v>11.965986711168002</v>
+        <v>23.931973422336004</v>
       </c>
       <c r="H16" s="1">
-        <v>14.072881041449996</v>
+        <v>28.145762082899992</v>
       </c>
       <c r="I16" s="1">
-        <v>15.219905251200002</v>
+        <v>30.439810502400004</v>
       </c>
       <c r="J16" s="1">
-        <v>14.087609279999999</v>
+        <v>28.175218559999998</v>
       </c>
       <c r="K16" s="1">
-        <v>15.897757459200001</v>
+        <v>31.795514918400002</v>
       </c>
       <c r="L16" s="1">
-        <v>14.865511239600004</v>
+        <v>29.731022479200007</v>
       </c>
       <c r="M16" s="1">
-        <v>18.751341965961604</v>
+        <v>37.502683931923208</v>
       </c>
       <c r="N16" s="1">
-        <v>17.265497037599999</v>
+        <v>34.530994075199999</v>
       </c>
       <c r="O16" s="1">
-        <v>16.29412678608</v>
+        <v>32.588253572159999</v>
       </c>
       <c r="P16" s="1">
-        <v>16.235785912320001</v>
+        <v>32.471571824640002</v>
       </c>
       <c r="Q16" s="1">
-        <v>16.832374562203199</v>
+        <v>33.664749124406399</v>
       </c>
       <c r="R16" s="1">
-        <v>16.076045728512007</v>
+        <v>32.152091457024014</v>
       </c>
       <c r="S16" s="1">
-        <v>12.970865867328003</v>
+        <v>25.941731734656006</v>
       </c>
       <c r="T16" s="1">
-        <v>13.760333469791997</v>
+        <v>27.520666939583993</v>
       </c>
       <c r="U16" s="1">
-        <v>11.582869005926399</v>
+        <v>23.165738011852799</v>
       </c>
       <c r="V16" s="1">
-        <v>10.020003044939999</v>
+        <v>20.040006089879999</v>
       </c>
       <c r="W16" s="1">
-        <v>10.374038048000003</v>
+        <v>20.748076096000005</v>
       </c>
       <c r="X16" s="1">
-        <v>10.779295557888002</v>
+        <v>21.558591115776004</v>
       </c>
       <c r="Y16" s="1">
-        <v>13.095413315712005</v>
+        <v>26.190826631424009</v>
       </c>
       <c r="Z16" s="1">
-        <v>8.969922918</v>
+        <v>17.939845836</v>
       </c>
       <c r="AA16" s="1">
-        <v>9.7107655680000047</v>
+        <v>19.421531136000009</v>
       </c>
     </row>
     <row r="17" spans="1:27" x14ac:dyDescent="0.2">
@@ -70677,76 +70677,76 @@
         <v>3</v>
       </c>
       <c r="D17" s="1">
-        <v>4.6145330400000013</v>
+        <v>9.2290660800000026</v>
       </c>
       <c r="E17" s="1">
-        <v>5.0696295520000003</v>
+        <v>10.139259104000001</v>
       </c>
       <c r="F17" s="1">
-        <v>4.2785225999999996</v>
+        <v>8.5570451999999992</v>
       </c>
       <c r="G17" s="1">
-        <v>4.3872443999999984</v>
+        <v>8.7744887999999968</v>
       </c>
       <c r="H17" s="1">
-        <v>3.4236188159999998</v>
+        <v>6.8472376319999997</v>
       </c>
       <c r="I17" s="1">
-        <v>2.7353953440000005</v>
+        <v>5.470790688000001</v>
       </c>
       <c r="J17" s="1">
-        <v>3.5141144479999995</v>
+        <v>7.028228895999999</v>
       </c>
       <c r="K17" s="1">
-        <v>0.60489950400000003</v>
+        <v>1.2097990080000001</v>
       </c>
       <c r="L17" s="1">
-        <v>0.54796000000000011</v>
+        <v>1.0959200000000002</v>
       </c>
       <c r="M17" s="1">
-        <v>0.74478947399999984</v>
+        <v>1.4895789479999997</v>
       </c>
       <c r="N17" s="1">
-        <v>0.46575817200000003</v>
+        <v>0.93151634400000005</v>
       </c>
       <c r="O17" s="1">
-        <v>0.53679977999999995</v>
+        <v>1.0735995599999999</v>
       </c>
       <c r="P17" s="1">
-        <v>0.90934000000000026</v>
+        <v>1.8186800000000005</v>
       </c>
       <c r="Q17" s="1">
-        <v>1.7429394260000002</v>
+        <v>3.4858788520000004</v>
       </c>
       <c r="R17" s="1">
-        <v>1.8393580799999998</v>
+        <v>3.6787161599999996</v>
       </c>
       <c r="S17" s="1">
-        <v>1.7033857199999993</v>
+        <v>3.4067714399999987</v>
       </c>
       <c r="T17" s="1">
-        <v>0.91825632000000001</v>
+        <v>1.83651264</v>
       </c>
       <c r="U17" s="1">
-        <v>1.9090494719999995</v>
+        <v>3.8180989439999991</v>
       </c>
       <c r="V17" s="1">
-        <v>1.1542417919999999</v>
+        <v>2.3084835839999998</v>
       </c>
       <c r="W17" s="1">
-        <v>0.87021899999999985</v>
+        <v>1.7404379999999997</v>
       </c>
       <c r="X17" s="1">
-        <v>1.1963871360000002</v>
+        <v>2.3927742720000005</v>
       </c>
       <c r="Y17" s="1">
-        <v>0.80119580000000001</v>
+        <v>1.6023916</v>
       </c>
       <c r="Z17" s="1">
-        <v>3.4424096640000004</v>
+        <v>6.8848193280000007</v>
       </c>
       <c r="AA17" s="1">
-        <v>4.1104543759999999</v>
+        <v>8.2209087519999997</v>
       </c>
     </row>
     <row r="18" spans="1:27" x14ac:dyDescent="0.2">
@@ -70760,76 +70760,76 @@
         <v>3</v>
       </c>
       <c r="D18" s="1">
-        <v>-10.965703320000003</v>
+        <v>-21.931406640000006</v>
       </c>
       <c r="E18" s="1">
-        <v>-11.976521356800001</v>
+        <v>-23.953042713600002</v>
       </c>
       <c r="F18" s="1">
-        <v>-10.987788768</v>
+        <v>-21.975577535999999</v>
       </c>
       <c r="G18" s="1">
-        <v>-13.264496447999999</v>
+        <v>-26.528992895999998</v>
       </c>
       <c r="H18" s="1">
-        <v>-16.466673971404802</v>
+        <v>-32.933347942809604</v>
       </c>
       <c r="I18" s="1">
-        <v>-16.268056588492797</v>
+        <v>-32.536113176985594</v>
       </c>
       <c r="J18" s="1">
-        <v>-15.216606624683523</v>
+        <v>-30.433213249367046</v>
       </c>
       <c r="K18" s="1">
-        <v>-17.081128718438393</v>
+        <v>-34.162257436876786</v>
       </c>
       <c r="L18" s="1">
-        <v>-17.816232729455997</v>
+        <v>-35.632465458911994</v>
       </c>
       <c r="M18" s="1">
-        <v>-21.852002551762943</v>
+        <v>-43.704005103525887</v>
       </c>
       <c r="N18" s="1">
-        <v>-25.131012458153482</v>
+        <v>-50.262024916306963</v>
       </c>
       <c r="O18" s="1">
-        <v>-21.86069644445703</v>
+        <v>-43.72139288891406</v>
       </c>
       <c r="P18" s="1">
-        <v>-21.156534073344389</v>
+        <v>-42.313068146688778</v>
       </c>
       <c r="Q18" s="1">
-        <v>-19.585421592105593</v>
+        <v>-39.170843184211186</v>
       </c>
       <c r="R18" s="1">
-        <v>-19.829483668874886</v>
+        <v>-39.658967337749772</v>
       </c>
       <c r="S18" s="1">
-        <v>-16.997789119999997</v>
+        <v>-33.995578239999993</v>
       </c>
       <c r="T18" s="1">
-        <v>-15.7449151956096</v>
+        <v>-31.489830391219201</v>
       </c>
       <c r="U18" s="1">
-        <v>-14.363231011024896</v>
+        <v>-28.726462022049791</v>
       </c>
       <c r="V18" s="1">
-        <v>-8.5836086592000012</v>
+        <v>-17.167217318400002</v>
       </c>
       <c r="W18" s="1">
-        <v>-10.119153497368606</v>
+        <v>-20.238306994737211</v>
       </c>
       <c r="X18" s="1">
-        <v>-11.122213027463999</v>
+        <v>-22.244426054927999</v>
       </c>
       <c r="Y18" s="1">
-        <v>-10.47728026517</v>
+        <v>-20.95456053034</v>
       </c>
       <c r="Z18" s="1">
-        <v>-8.6633794966118405</v>
+        <v>-17.326758993223681</v>
       </c>
       <c r="AA18" s="1">
-        <v>-10.06559963136</v>
+        <v>-20.131199262719999</v>
       </c>
     </row>
     <row r="19" spans="1:27" x14ac:dyDescent="0.2">
@@ -70843,76 +70843,76 @@
         <v>3</v>
       </c>
       <c r="D19" s="1">
-        <v>8.884170883845</v>
+        <v>17.76834176769</v>
       </c>
       <c r="E19" s="1">
-        <v>10.63266525785088</v>
+        <v>21.265330515701759</v>
       </c>
       <c r="F19" s="1">
-        <v>13.581522759167999</v>
+        <v>27.163045518335998</v>
       </c>
       <c r="G19" s="1">
-        <v>12.564286046726401</v>
+        <v>25.128572093452803</v>
       </c>
       <c r="H19" s="1">
-        <v>14.635796283107995</v>
+        <v>29.27159256621599</v>
       </c>
       <c r="I19" s="1">
-        <v>14.763308093664001</v>
+        <v>29.526616187328003</v>
       </c>
       <c r="J19" s="1">
-        <v>14.791989743999999</v>
+        <v>29.583979487999997</v>
       </c>
       <c r="K19" s="1">
-        <v>16.692645332160001</v>
+        <v>33.385290664320003</v>
       </c>
       <c r="L19" s="1">
-        <v>14.419545902412004</v>
+        <v>28.839091804824008</v>
       </c>
       <c r="M19" s="1">
-        <v>18.751341965961604</v>
+        <v>37.502683931923208</v>
       </c>
       <c r="N19" s="1">
-        <v>17.438152007976001</v>
+        <v>34.876304015952002</v>
       </c>
       <c r="O19" s="1">
-        <v>15.968244250358401</v>
+        <v>31.936488500716802</v>
       </c>
       <c r="P19" s="1">
-        <v>17.047575207936003</v>
+        <v>34.095150415872006</v>
       </c>
       <c r="Q19" s="1">
-        <v>16.327403325337105</v>
+        <v>32.65480665067421</v>
       </c>
       <c r="R19" s="1">
-        <v>15.272243442086406</v>
+        <v>30.544486884172812</v>
       </c>
       <c r="S19" s="1">
-        <v>12.841157208654723</v>
+        <v>25.682314417309446</v>
       </c>
       <c r="T19" s="1">
-        <v>13.760333469791997</v>
+        <v>27.520666939583993</v>
       </c>
       <c r="U19" s="1">
-        <v>11.814526386044927</v>
+        <v>23.629052772089853</v>
       </c>
       <c r="V19" s="1">
-        <v>10.420803166737599</v>
+        <v>20.841606333475198</v>
       </c>
       <c r="W19" s="1">
-        <v>10.685259189440004</v>
+        <v>21.370518378880007</v>
       </c>
       <c r="X19" s="1">
-        <v>10.779295557888002</v>
+        <v>21.558591115776004</v>
       </c>
       <c r="Y19" s="1">
-        <v>12.833505049397765</v>
+        <v>25.667010098795529</v>
       </c>
       <c r="Z19" s="1">
-        <v>8.6111260012799988</v>
+        <v>17.222252002559998</v>
       </c>
       <c r="AA19" s="1">
-        <v>9.4194426009600036</v>
+        <v>18.838885201920007</v>
       </c>
     </row>
     <row r="20" spans="1:27" x14ac:dyDescent="0.2">
@@ -70926,76 +70926,76 @@
         <v>1</v>
       </c>
       <c r="D20" s="1">
-        <v>5.1376380000000017</v>
+        <v>10.275276000000003</v>
       </c>
       <c r="E20" s="1">
-        <v>5.3090180000000009</v>
+        <v>10.618036000000002</v>
       </c>
       <c r="F20" s="1">
-        <v>4.7539140000000009</v>
+        <v>9.5078280000000017</v>
       </c>
       <c r="G20" s="1">
-        <v>4.5060399999999996</v>
+        <v>9.0120799999999992</v>
       </c>
       <c r="H20" s="1">
-        <v>3.6917760000000004</v>
+        <v>7.3835520000000008</v>
       </c>
       <c r="I20" s="1">
-        <v>3.1333280000000006</v>
+        <v>6.2666560000000011</v>
       </c>
       <c r="J20" s="1">
-        <v>3.8318060000000003</v>
+        <v>7.6636120000000005</v>
       </c>
       <c r="K20" s="1">
-        <v>0.66545600000000016</v>
+        <v>1.3309120000000003</v>
       </c>
       <c r="L20" s="1">
-        <v>0.58520000000000005</v>
+        <v>1.1704000000000001</v>
       </c>
       <c r="M20" s="1">
-        <v>0.85313799999999984</v>
+        <v>1.7062759999999997</v>
       </c>
       <c r="N20" s="1">
-        <v>0.5024360000000001</v>
+        <v>1.0048720000000002</v>
       </c>
       <c r="O20" s="1">
-        <v>0.62783599999999995</v>
+        <v>1.2556719999999999</v>
       </c>
       <c r="P20" s="1">
-        <v>1.0002740000000003</v>
+        <v>2.0005480000000007</v>
       </c>
       <c r="Q20" s="1">
-        <v>1.8429620000000002</v>
+        <v>3.6859240000000004</v>
       </c>
       <c r="R20" s="1">
-        <v>1.966272</v>
+        <v>3.932544</v>
       </c>
       <c r="S20" s="1">
-        <v>1.9336679999999997</v>
+        <v>3.8673359999999994</v>
       </c>
       <c r="T20" s="1">
-        <v>1.0847100000000001</v>
+        <v>2.1694200000000001</v>
       </c>
       <c r="U20" s="1">
-        <v>2.2095479999999998</v>
+        <v>4.4190959999999997</v>
       </c>
       <c r="V20" s="1">
-        <v>1.2966360000000001</v>
+        <v>2.5932720000000002</v>
       </c>
       <c r="W20" s="1">
-        <v>0.91165799999999986</v>
+        <v>1.8233159999999997</v>
       </c>
       <c r="X20" s="1">
-        <v>1.3844160000000003</v>
+        <v>2.7688320000000006</v>
       </c>
       <c r="Y20" s="1">
-        <v>0.85564600000000002</v>
+        <v>1.711292</v>
       </c>
       <c r="Z20" s="1">
-        <v>3.9053740000000006</v>
+        <v>7.8107480000000011</v>
       </c>
       <c r="AA20" s="1">
-        <v>4.7079339999999998</v>
+        <v>9.4158679999999997</v>
       </c>
     </row>
     <row r="21" spans="1:27" x14ac:dyDescent="0.2">
@@ -71009,76 +71009,76 @@
         <v>1</v>
       </c>
       <c r="D21" s="1">
-        <v>-10.636732220400004</v>
+        <v>-21.273464440800009</v>
       </c>
       <c r="E21" s="1">
-        <v>-12.575347424640002</v>
+        <v>-25.150694849280004</v>
       </c>
       <c r="F21" s="1">
-        <v>-10.658155104959999</v>
+        <v>-21.316310209919997</v>
       </c>
       <c r="G21" s="1">
-        <v>-13.529786376959999</v>
+        <v>-27.059572753919998</v>
       </c>
       <c r="H21" s="1">
-        <v>-17.125340930260997</v>
+        <v>-34.250681860521993</v>
       </c>
       <c r="I21" s="1">
-        <v>-16.268056588492797</v>
+        <v>-32.536113176985594</v>
       </c>
       <c r="J21" s="1">
-        <v>-15.36877269093036</v>
+        <v>-30.73754538186072</v>
       </c>
       <c r="K21" s="1">
-        <v>-16.910317431254008</v>
+        <v>-33.820634862508015</v>
       </c>
       <c r="L21" s="1">
-        <v>-17.994395056750555</v>
+        <v>-35.988790113501111</v>
       </c>
       <c r="M21" s="1">
-        <v>-21.852002551762943</v>
+        <v>-43.704005103525887</v>
       </c>
       <c r="N21" s="1">
-        <v>-24.879702333571945</v>
+        <v>-49.75940466714389</v>
       </c>
       <c r="O21" s="1">
-        <v>-22.735124302235313</v>
+        <v>-45.470248604470626</v>
       </c>
       <c r="P21" s="1">
-        <v>-21.156534073344389</v>
+        <v>-42.313068146688778</v>
       </c>
       <c r="Q21" s="1">
-        <v>-20.172984239868761</v>
+        <v>-40.345968479737522</v>
       </c>
       <c r="R21" s="1">
-        <v>-19.234599158808638</v>
+        <v>-38.469198317617277</v>
       </c>
       <c r="S21" s="1">
-        <v>-16.657833337599996</v>
+        <v>-33.315666675199992</v>
       </c>
       <c r="T21" s="1">
-        <v>-14.957669435829121</v>
+        <v>-29.915338871658243</v>
       </c>
       <c r="U21" s="1">
-        <v>-14.363231011024896</v>
+        <v>-28.726462022049791</v>
       </c>
       <c r="V21" s="1">
-        <v>-8.7552808323840008</v>
+        <v>-17.510561664768002</v>
       </c>
       <c r="W21" s="1">
-        <v>-10.422728102289664</v>
+        <v>-20.845456204579328</v>
       </c>
       <c r="X21" s="1">
-        <v>-11.56710154856256</v>
+        <v>-23.13420309712512</v>
       </c>
       <c r="Y21" s="1">
-        <v>-10.267734659866601</v>
+        <v>-20.535469319733203</v>
       </c>
       <c r="Z21" s="1">
-        <v>-8.6633794966118405</v>
+        <v>-17.326758993223681</v>
       </c>
       <c r="AA21" s="1">
-        <v>-10.367567620300798</v>
+        <v>-20.735135240601597</v>
       </c>
     </row>
     <row r="22" spans="1:27" x14ac:dyDescent="0.2">
@@ -71092,76 +71092,76 @@
         <v>1</v>
       </c>
       <c r="D22" s="1">
-        <v>8.4399623396527499</v>
+        <v>16.8799246793055</v>
       </c>
       <c r="E22" s="1">
-        <v>10.845318563007897</v>
+        <v>21.690637126015794</v>
       </c>
       <c r="F22" s="1">
-        <v>13.988968441943038</v>
+        <v>27.977936883886077</v>
       </c>
       <c r="G22" s="1">
-        <v>12.313000325791872</v>
+        <v>24.626000651583745</v>
       </c>
       <c r="H22" s="1">
-        <v>14.928512208770155</v>
+        <v>29.857024417540309</v>
       </c>
       <c r="I22" s="1">
-        <v>14.61567501272736</v>
+        <v>29.23135002545472</v>
       </c>
       <c r="J22" s="1">
-        <v>14.348230051679998</v>
+        <v>28.696460103359996</v>
       </c>
       <c r="K22" s="1">
-        <v>17.1934246921248</v>
+        <v>34.386849384249601</v>
       </c>
       <c r="L22" s="1">
-        <v>15.140523197532605</v>
+        <v>30.281046395065211</v>
       </c>
       <c r="M22" s="1">
-        <v>19.313882224940453</v>
+        <v>38.627764449880907</v>
       </c>
       <c r="N22" s="1">
-        <v>17.089388967816479</v>
+        <v>34.178777935632958</v>
       </c>
       <c r="O22" s="1">
-        <v>16.287609135365571</v>
+        <v>32.575218270731142</v>
       </c>
       <c r="P22" s="1">
-        <v>17.72947821625344</v>
+        <v>35.458956432506881</v>
       </c>
       <c r="Q22" s="1">
-        <v>16.817225425097217</v>
+        <v>33.634450850194433</v>
       </c>
       <c r="R22" s="1">
-        <v>14.814076138823815</v>
+        <v>29.628152277647629</v>
       </c>
       <c r="S22" s="1">
-        <v>12.712745636568174</v>
+        <v>25.425491273136348</v>
       </c>
       <c r="T22" s="1">
-        <v>14.035540139187836</v>
+        <v>28.071080278375671</v>
       </c>
       <c r="U22" s="1">
-        <v>11.46009059446358</v>
+        <v>22.92018118892716</v>
       </c>
       <c r="V22" s="1">
-        <v>10.733427261739727</v>
+        <v>21.466854523479455</v>
       </c>
       <c r="W22" s="1">
-        <v>11.112669557017602</v>
+        <v>22.225339114035204</v>
       </c>
       <c r="X22" s="1">
-        <v>10.671502602309122</v>
+        <v>21.343005204618244</v>
       </c>
       <c r="Y22" s="1">
-        <v>12.705169998903786</v>
+        <v>25.410339997807572</v>
       </c>
       <c r="Z22" s="1">
-        <v>8.783348521305598</v>
+        <v>17.566697042611196</v>
       </c>
       <c r="AA22" s="1">
-        <v>9.5136370269696027</v>
+        <v>19.027274053939205</v>
       </c>
     </row>
     <row r="23" spans="1:27" x14ac:dyDescent="0.2">
@@ -71175,76 +71175,76 @@
         <v>2</v>
       </c>
       <c r="D23" s="1">
-        <v>5.3945199000000015</v>
+        <v>10.789039800000003</v>
       </c>
       <c r="E23" s="1">
-        <v>5.5744689000000003</v>
+        <v>11.148937800000001</v>
       </c>
       <c r="F23" s="1">
-        <v>4.5637574400000007</v>
+        <v>9.1275148800000014</v>
       </c>
       <c r="G23" s="1">
-        <v>4.3708587999999997</v>
+        <v>8.7417175999999994</v>
       </c>
       <c r="H23" s="1">
-        <v>3.6548582400000003</v>
+        <v>7.3097164800000005</v>
       </c>
       <c r="I23" s="1">
-        <v>3.0706614400000007</v>
+        <v>6.1413228800000015</v>
       </c>
       <c r="J23" s="1">
-        <v>3.7934879399999999</v>
+        <v>7.5869758799999998</v>
       </c>
       <c r="K23" s="1">
-        <v>0.67211056000000013</v>
+        <v>1.3442211200000003</v>
       </c>
       <c r="L23" s="1">
-        <v>0.57349600000000001</v>
+        <v>1.146992</v>
       </c>
       <c r="M23" s="1">
-        <v>0.86166937999999993</v>
+        <v>1.7233387599999999</v>
       </c>
       <c r="N23" s="1">
-        <v>0.52253344000000013</v>
+        <v>1.0450668800000003</v>
       </c>
       <c r="O23" s="1">
-        <v>0.65294943999999999</v>
+        <v>1.30589888</v>
       </c>
       <c r="P23" s="1">
-        <v>0.98026852000000031</v>
+        <v>1.9605370400000006</v>
       </c>
       <c r="Q23" s="1">
-        <v>1.9166804800000004</v>
+        <v>3.8333609600000007</v>
       </c>
       <c r="R23" s="1">
-        <v>2.0645856</v>
+        <v>4.1291712</v>
       </c>
       <c r="S23" s="1">
-        <v>1.8369845999999999</v>
+        <v>3.6739691999999997</v>
       </c>
       <c r="T23" s="1">
-        <v>1.1172513000000002</v>
+        <v>2.2345026000000003</v>
       </c>
       <c r="U23" s="1">
-        <v>2.2979299199999996</v>
+        <v>4.5958598399999993</v>
       </c>
       <c r="V23" s="1">
-        <v>1.2707032800000002</v>
+        <v>2.5414065600000004</v>
       </c>
       <c r="W23" s="1">
-        <v>0.90254141999999993</v>
+        <v>1.8050828399999999</v>
       </c>
       <c r="X23" s="1">
-        <v>1.3844160000000003</v>
+        <v>2.7688320000000006</v>
       </c>
       <c r="Y23" s="1">
-        <v>0.88131538000000009</v>
+        <v>1.7626307600000002</v>
       </c>
       <c r="Z23" s="1">
-        <v>4.1006427000000008</v>
+        <v>8.2012854000000015</v>
       </c>
       <c r="AA23" s="1">
-        <v>4.8020926800000003</v>
+        <v>9.6041853600000007</v>
       </c>
     </row>
     <row r="24" spans="1:27" x14ac:dyDescent="0.2">
@@ -71258,76 +71258,76 @@
         <v>2</v>
       </c>
       <c r="D24" s="1">
-        <v>-10.743099542604005</v>
+        <v>-21.48619908520801</v>
       </c>
       <c r="E24" s="1">
-        <v>-12.952607847379202</v>
+        <v>-25.905215694758404</v>
       </c>
       <c r="F24" s="1">
-        <v>-10.444992002860799</v>
+        <v>-20.889984005721598</v>
       </c>
       <c r="G24" s="1">
-        <v>-13.259190649420798</v>
+        <v>-26.518381298841597</v>
       </c>
       <c r="H24" s="1">
-        <v>-17.296594339563608</v>
+        <v>-34.593188679127216</v>
       </c>
       <c r="I24" s="1">
-        <v>-15.780014890838013</v>
+        <v>-31.560029781676025</v>
       </c>
       <c r="J24" s="1">
-        <v>-15.061397237111754</v>
+        <v>-30.122794474223507</v>
       </c>
       <c r="K24" s="1">
-        <v>-17.248523779879086</v>
+        <v>-34.497047559758172</v>
       </c>
       <c r="L24" s="1">
-        <v>-18.714170859020577</v>
+        <v>-37.428341718041153</v>
       </c>
       <c r="M24" s="1">
-        <v>-22.507562628315831</v>
+        <v>-45.015125256631663</v>
       </c>
       <c r="N24" s="1">
-        <v>-23.88451424022907</v>
+        <v>-47.76902848045814</v>
       </c>
       <c r="O24" s="1">
-        <v>-23.417178031302374</v>
+        <v>-46.834356062604748</v>
       </c>
       <c r="P24" s="1">
-        <v>-20.521838051144059</v>
+        <v>-41.043676102288117</v>
       </c>
       <c r="Q24" s="1">
-        <v>-19.769524555071385</v>
+        <v>-39.53904911014277</v>
       </c>
       <c r="R24" s="1">
-        <v>-19.234599158808638</v>
+        <v>-38.469198317617277</v>
       </c>
       <c r="S24" s="1">
-        <v>-15.991520004095996</v>
+        <v>-31.983040008191992</v>
       </c>
       <c r="T24" s="1">
-        <v>-15.107246130187413</v>
+        <v>-30.214492260374826</v>
       </c>
       <c r="U24" s="1">
-        <v>-13.645069460473652</v>
+        <v>-27.290138920947303</v>
       </c>
       <c r="V24" s="1">
-        <v>-8.405069599088641</v>
+        <v>-16.810139198177282</v>
       </c>
       <c r="W24" s="1">
-        <v>-10.422728102289664</v>
+        <v>-20.845456204579328</v>
       </c>
       <c r="X24" s="1">
-        <v>-12.029785610505062</v>
+        <v>-24.059571221010124</v>
       </c>
       <c r="Y24" s="1">
-        <v>-9.9597026200706029</v>
+        <v>-19.919405240141206</v>
       </c>
       <c r="Z24" s="1">
-        <v>-8.8366470865440778</v>
+        <v>-17.673294173088156</v>
       </c>
       <c r="AA24" s="1">
-        <v>-10.263891944097791</v>
+        <v>-20.527783888195582</v>
       </c>
     </row>
     <row r="25" spans="1:27" x14ac:dyDescent="0.2">
@@ -71341,76 +71341,76 @@
         <v>2</v>
       </c>
       <c r="D25" s="1">
-        <v>8.3555627162562232</v>
+        <v>16.711125432512446</v>
       </c>
       <c r="E25" s="1">
-        <v>10.845318563007897</v>
+        <v>21.690637126015794</v>
       </c>
       <c r="F25" s="1">
-        <v>13.289520019845886</v>
+        <v>26.579040039691773</v>
       </c>
       <c r="G25" s="1">
-        <v>12.55926033230771</v>
+        <v>25.118520664615421</v>
       </c>
       <c r="H25" s="1">
-        <v>15.227082452945558</v>
+        <v>30.454164905891115</v>
       </c>
       <c r="I25" s="1">
-        <v>15.054145263109181</v>
+        <v>30.108290526218362</v>
       </c>
       <c r="J25" s="1">
-        <v>14.491712352196798</v>
+        <v>28.983424704393595</v>
       </c>
       <c r="K25" s="1">
-        <v>17.1934246921248</v>
+        <v>34.386849384249601</v>
       </c>
       <c r="L25" s="1">
-        <v>14.383497037655975</v>
+        <v>28.766994075311949</v>
       </c>
       <c r="M25" s="1">
-        <v>20.086437513938073</v>
+        <v>40.172875027876145</v>
       </c>
       <c r="N25" s="1">
-        <v>17.602070636850975</v>
+        <v>35.20414127370195</v>
       </c>
       <c r="O25" s="1">
-        <v>16.450485226719227</v>
+        <v>32.900970453438454</v>
       </c>
       <c r="P25" s="1">
-        <v>17.72947821625344</v>
+        <v>35.458956432506881</v>
       </c>
       <c r="Q25" s="1">
-        <v>16.649053170846244</v>
+        <v>33.298106341692488</v>
       </c>
       <c r="R25" s="1">
-        <v>14.073372331882624</v>
+        <v>28.146744663765247</v>
       </c>
       <c r="S25" s="1">
-        <v>12.077108354739764</v>
+        <v>24.154216709479527</v>
       </c>
       <c r="T25" s="1">
-        <v>13.614473935012199</v>
+        <v>27.228947870024399</v>
       </c>
       <c r="U25" s="1">
-        <v>11.23088878257431</v>
+        <v>22.461777565148619</v>
       </c>
       <c r="V25" s="1">
-        <v>10.733427261739727</v>
+        <v>21.466854523479455</v>
       </c>
       <c r="W25" s="1">
-        <v>11.446049643728131</v>
+        <v>22.892099287456261</v>
       </c>
       <c r="X25" s="1">
-        <v>10.137927472193665</v>
+        <v>20.27585494438733</v>
       </c>
       <c r="Y25" s="1">
-        <v>13.340428498848976</v>
+        <v>26.680856997697951</v>
       </c>
       <c r="Z25" s="1">
-        <v>8.6076815508794855</v>
+        <v>17.215363101758971</v>
       </c>
       <c r="AA25" s="1">
-        <v>9.7990461377786904</v>
+        <v>19.598092275557381</v>
       </c>
     </row>
     <row r="26" spans="1:27" x14ac:dyDescent="0.2">
@@ -71424,76 +71424,76 @@
         <v>3</v>
       </c>
       <c r="D26" s="1">
-        <v>5.556355497000002</v>
+        <v>11.112710994000004</v>
       </c>
       <c r="E26" s="1">
-        <v>5.6302135890000002</v>
+        <v>11.260427178</v>
       </c>
       <c r="F26" s="1">
-        <v>4.518119865600001</v>
+        <v>9.036239731200002</v>
       </c>
       <c r="G26" s="1">
-        <v>4.5894017399999996</v>
+        <v>9.1788034799999991</v>
       </c>
       <c r="H26" s="1">
-        <v>3.6914068224000003</v>
+        <v>7.3828136448000006</v>
       </c>
       <c r="I26" s="1">
-        <v>3.0706614400000007</v>
+        <v>6.1413228800000015</v>
       </c>
       <c r="J26" s="1">
-        <v>3.6038135429999998</v>
+        <v>7.2076270859999996</v>
       </c>
       <c r="K26" s="1">
-        <v>0.63850503200000008</v>
+        <v>1.2770100640000002</v>
       </c>
       <c r="L26" s="1">
-        <v>0.54482120000000001</v>
+        <v>1.0896424</v>
       </c>
       <c r="M26" s="1">
-        <v>0.83581929859999993</v>
+        <v>1.6716385971999999</v>
       </c>
       <c r="N26" s="1">
-        <v>0.51730810560000007</v>
+        <v>1.0346162112000001</v>
       </c>
       <c r="O26" s="1">
-        <v>0.6660084288</v>
+        <v>1.3320168576</v>
       </c>
       <c r="P26" s="1">
-        <v>0.96066314960000032</v>
+        <v>1.9213262992000006</v>
       </c>
       <c r="Q26" s="1">
-        <v>2.0125145040000003</v>
+        <v>4.0250290080000006</v>
       </c>
       <c r="R26" s="1">
-        <v>2.1678148799999999</v>
+        <v>4.3356297599999998</v>
       </c>
       <c r="S26" s="1">
-        <v>1.9288338299999999</v>
+        <v>3.8576676599999997</v>
       </c>
       <c r="T26" s="1">
-        <v>1.1284238130000002</v>
+        <v>2.2568476260000003</v>
       </c>
       <c r="U26" s="1">
-        <v>2.2979299199999996</v>
+        <v>4.5958598399999993</v>
       </c>
       <c r="V26" s="1">
-        <v>1.2707032800000002</v>
+        <v>2.5414065600000004</v>
       </c>
       <c r="W26" s="1">
-        <v>0.86643976319999993</v>
+        <v>1.7328795263999999</v>
       </c>
       <c r="X26" s="1">
-        <v>1.3428835200000002</v>
+        <v>2.6857670400000004</v>
       </c>
       <c r="Y26" s="1">
-        <v>0.89012853380000012</v>
+        <v>1.7802570676000002</v>
       </c>
       <c r="Z26" s="1">
-        <v>3.9776234190000008</v>
+        <v>7.9552468380000017</v>
       </c>
       <c r="AA26" s="1">
-        <v>4.9461554604</v>
+        <v>9.8923109208</v>
       </c>
     </row>
     <row r="27" spans="1:27" x14ac:dyDescent="0.2">
@@ -71507,76 +71507,76 @@
         <v>3</v>
       </c>
       <c r="D27" s="1">
-        <v>-11.280254519734205</v>
+        <v>-22.56050903946841</v>
       </c>
       <c r="E27" s="1">
-        <v>-12.823081768905411</v>
+        <v>-25.646163537810821</v>
       </c>
       <c r="F27" s="1">
-        <v>-10.340542082832192</v>
+        <v>-20.681084165664384</v>
       </c>
       <c r="G27" s="1">
-        <v>-12.861414929938173</v>
+        <v>-25.722829859876345</v>
       </c>
       <c r="H27" s="1">
-        <v>-17.123628396167973</v>
+        <v>-34.247256792335946</v>
       </c>
       <c r="I27" s="1">
-        <v>-16.253415337563155</v>
+        <v>-32.506830675126309</v>
       </c>
       <c r="J27" s="1">
-        <v>-14.308327375256164</v>
+        <v>-28.616654750512328</v>
       </c>
       <c r="K27" s="1">
-        <v>-17.076038542080298</v>
+        <v>-34.152077084160595</v>
       </c>
       <c r="L27" s="1">
-        <v>-18.152745733249962</v>
+        <v>-36.305491466499923</v>
       </c>
       <c r="M27" s="1">
-        <v>-23.182789507165307</v>
+        <v>-46.365579014330613</v>
       </c>
       <c r="N27" s="1">
-        <v>-23.88451424022907</v>
+        <v>-47.76902848045814</v>
       </c>
       <c r="O27" s="1">
-        <v>-23.417178031302374</v>
+        <v>-46.834356062604748</v>
       </c>
       <c r="P27" s="1">
-        <v>-20.111401290121179</v>
+        <v>-40.222802580242359</v>
       </c>
       <c r="Q27" s="1">
-        <v>-19.769524555071385</v>
+        <v>-39.53904911014277</v>
       </c>
       <c r="R27" s="1">
-        <v>-19.61929114198481</v>
+        <v>-39.23858228396962</v>
       </c>
       <c r="S27" s="1">
-        <v>-16.311350404177915</v>
+        <v>-32.62270080835583</v>
       </c>
       <c r="T27" s="1">
-        <v>-15.560463514093035</v>
+        <v>-31.12092702818607</v>
       </c>
       <c r="U27" s="1">
-        <v>-13.645069460473652</v>
+        <v>-27.290138920947303</v>
       </c>
       <c r="V27" s="1">
-        <v>-8.5731709910704144</v>
+        <v>-17.146341982140829</v>
       </c>
       <c r="W27" s="1">
-        <v>-10.839637226381251</v>
+        <v>-21.679274452762503</v>
       </c>
       <c r="X27" s="1">
-        <v>-11.66889204218991</v>
+        <v>-23.33778408437982</v>
       </c>
       <c r="Y27" s="1">
-        <v>-10.059299646271308</v>
+        <v>-20.118599292542616</v>
       </c>
       <c r="Z27" s="1">
-        <v>-8.394814732216874</v>
+        <v>-16.789629464433748</v>
       </c>
       <c r="AA27" s="1">
-        <v>-10.469169782979748</v>
+        <v>-20.938339565959495</v>
       </c>
     </row>
     <row r="28" spans="1:27" x14ac:dyDescent="0.2">
@@ -71590,76 +71590,76 @@
         <v>3</v>
       </c>
       <c r="D28" s="1">
-        <v>8.104895834768536</v>
+        <v>16.209791669537072</v>
       </c>
       <c r="E28" s="1">
-        <v>10.519959006117661</v>
+        <v>21.039918012235322</v>
       </c>
       <c r="F28" s="1">
-        <v>13.289520019845886</v>
+        <v>26.579040039691773</v>
       </c>
       <c r="G28" s="1">
-        <v>12.93603814227694</v>
+        <v>25.872076284553881</v>
       </c>
       <c r="H28" s="1">
-        <v>15.988436575592836</v>
+        <v>31.976873151185671</v>
       </c>
       <c r="I28" s="1">
-        <v>14.903603810478089</v>
+        <v>29.807207620956177</v>
       </c>
       <c r="J28" s="1">
-        <v>15.216297969806638</v>
+        <v>30.432595939613275</v>
       </c>
       <c r="K28" s="1">
-        <v>16.849556198282304</v>
+        <v>33.699112396564608</v>
       </c>
       <c r="L28" s="1">
-        <v>14.239662067279415</v>
+        <v>28.47932413455883</v>
       </c>
       <c r="M28" s="1">
-        <v>21.090759389634979</v>
+        <v>42.181518779269958</v>
       </c>
       <c r="N28" s="1">
-        <v>18.306153462325014</v>
+        <v>36.612306924650028</v>
       </c>
       <c r="O28" s="1">
-        <v>15.95697066991765</v>
+        <v>31.913941339835301</v>
       </c>
       <c r="P28" s="1">
-        <v>17.72947821625344</v>
+        <v>35.458956432506881</v>
       </c>
       <c r="Q28" s="1">
-        <v>17.315015297680091</v>
+        <v>34.630030595360182</v>
       </c>
       <c r="R28" s="1">
-        <v>14.073372331882624</v>
+        <v>28.146744663765247</v>
       </c>
       <c r="S28" s="1">
-        <v>11.835566187644968</v>
+        <v>23.671132375289936</v>
       </c>
       <c r="T28" s="1">
-        <v>13.206039716961834</v>
+        <v>26.412079433923669</v>
       </c>
       <c r="U28" s="1">
-        <v>11.792433221703025</v>
+        <v>23.58486644340605</v>
       </c>
       <c r="V28" s="1">
-        <v>10.733427261739727</v>
+        <v>21.466854523479455</v>
       </c>
       <c r="W28" s="1">
-        <v>11.331589147290849</v>
+        <v>22.663178294581698</v>
       </c>
       <c r="X28" s="1">
-        <v>10.543444571081411</v>
+        <v>21.086889142162821</v>
       </c>
       <c r="Y28" s="1">
-        <v>12.940215643883507</v>
+        <v>25.880431287767014</v>
       </c>
       <c r="Z28" s="1">
-        <v>8.8659119974058704</v>
+        <v>17.731823994811741</v>
       </c>
       <c r="AA28" s="1">
-        <v>9.5050747536453297</v>
+        <v>19.010149507290659</v>
       </c>
     </row>
     <row r="29" spans="1:27" x14ac:dyDescent="0.2">
@@ -71673,76 +71673,76 @@
         <v>1</v>
       </c>
       <c r="D29" s="1">
-        <v>4.880756100000001</v>
+        <v>9.7615122000000021</v>
       </c>
       <c r="E29" s="1">
-        <v>5.0435671000000006</v>
+        <v>10.087134200000001</v>
       </c>
       <c r="F29" s="1">
-        <v>4.5162183000000002</v>
+        <v>9.0324366000000005</v>
       </c>
       <c r="G29" s="1">
-        <v>4.2807379999999995</v>
+        <v>8.561475999999999</v>
       </c>
       <c r="H29" s="1">
-        <v>3.5071872000000002</v>
+        <v>7.0143744000000003</v>
       </c>
       <c r="I29" s="1">
-        <v>2.9766616000000004</v>
+        <v>5.9533232000000007</v>
       </c>
       <c r="J29" s="1">
-        <v>3.6402157000000002</v>
+        <v>7.2804314000000003</v>
       </c>
       <c r="K29" s="1">
-        <v>0.63218320000000017</v>
+        <v>1.2643664000000003</v>
       </c>
       <c r="L29" s="1">
-        <v>0.55593999999999999</v>
+        <v>1.11188</v>
       </c>
       <c r="M29" s="1">
-        <v>0.81048109999999984</v>
+        <v>1.6209621999999997</v>
       </c>
       <c r="N29" s="1">
-        <v>0.47731420000000008</v>
+        <v>0.95462840000000015</v>
       </c>
       <c r="O29" s="1">
-        <v>0.59644419999999987</v>
+        <v>1.1928883999999997</v>
       </c>
       <c r="P29" s="1">
-        <v>0.95026030000000028</v>
+        <v>1.9005206000000006</v>
       </c>
       <c r="Q29" s="1">
-        <v>1.7508139</v>
+        <v>3.5016278000000001</v>
       </c>
       <c r="R29" s="1">
-        <v>1.8679584</v>
+        <v>3.7359168</v>
       </c>
       <c r="S29" s="1">
-        <v>1.8369845999999996</v>
+        <v>3.6739691999999993</v>
       </c>
       <c r="T29" s="1">
-        <v>1.0304745</v>
+        <v>2.0609489999999999</v>
       </c>
       <c r="U29" s="1">
-        <v>2.0990705999999997</v>
+        <v>4.1981411999999994</v>
       </c>
       <c r="V29" s="1">
-        <v>1.2318042</v>
+        <v>2.4636084</v>
       </c>
       <c r="W29" s="1">
-        <v>0.86607509999999988</v>
+        <v>1.7321501999999998</v>
       </c>
       <c r="X29" s="1">
-        <v>1.3151952000000002</v>
+        <v>2.6303904000000005</v>
       </c>
       <c r="Y29" s="1">
-        <v>0.81286369999999997</v>
+        <v>1.6257273999999999</v>
       </c>
       <c r="Z29" s="1">
-        <v>3.7101053000000004</v>
+        <v>7.4202106000000008</v>
       </c>
       <c r="AA29" s="1">
-        <v>4.4725372999999999</v>
+        <v>8.9450745999999999</v>
       </c>
     </row>
     <row r="30" spans="1:27" x14ac:dyDescent="0.2">
@@ -71756,76 +71756,76 @@
         <v>1</v>
       </c>
       <c r="D30" s="1">
-        <v>-11.167451974536863</v>
+        <v>-22.334903949073727</v>
       </c>
       <c r="E30" s="1">
-        <v>-12.823081768905411</v>
+        <v>-25.646163537810821</v>
       </c>
       <c r="F30" s="1">
-        <v>-10.030325820347226</v>
+        <v>-20.060651640694452</v>
       </c>
       <c r="G30" s="1">
-        <v>-13.3758715271357</v>
+        <v>-26.751743054271401</v>
       </c>
       <c r="H30" s="1">
-        <v>-17.808573532014695</v>
+        <v>-35.617147064029389</v>
       </c>
       <c r="I30" s="1">
-        <v>-16.90355195106568</v>
+        <v>-33.80710390213136</v>
       </c>
       <c r="J30" s="1">
-        <v>-15.023743744018972</v>
+        <v>-30.047487488037945</v>
       </c>
       <c r="K30" s="1">
-        <v>-17.759080083763511</v>
+        <v>-35.518160167527022</v>
       </c>
       <c r="L30" s="1">
-        <v>-18.697328105247461</v>
+        <v>-37.394656210494922</v>
       </c>
       <c r="M30" s="1">
-        <v>-23.646445297308613</v>
+        <v>-47.292890594617226</v>
       </c>
       <c r="N30" s="1">
-        <v>-24.12335938263136</v>
+        <v>-48.24671876526272</v>
       </c>
       <c r="O30" s="1">
-        <v>-23.651349811615397</v>
+        <v>-47.302699623230794</v>
       </c>
       <c r="P30" s="1">
-        <v>-19.306945238516331</v>
+        <v>-38.613890477032662</v>
       </c>
       <c r="Q30" s="1">
-        <v>-18.978743572868531</v>
+        <v>-37.957487145737062</v>
       </c>
       <c r="R30" s="1">
-        <v>-20.011676964824506</v>
+        <v>-40.023353929649012</v>
       </c>
       <c r="S30" s="1">
-        <v>-16.474463908219697</v>
+        <v>-32.948927816439394</v>
       </c>
       <c r="T30" s="1">
-        <v>-15.716068149233966</v>
+        <v>-31.432136298467931</v>
       </c>
       <c r="U30" s="1">
-        <v>-14.054421544287861</v>
+        <v>-28.108843088575721</v>
       </c>
       <c r="V30" s="1">
-        <v>-8.144512441516893</v>
+        <v>-16.289024883033786</v>
       </c>
       <c r="W30" s="1">
-        <v>-10.948033598645063</v>
+        <v>-21.896067197290126</v>
       </c>
       <c r="X30" s="1">
-        <v>-11.202136360502314</v>
+        <v>-22.404272721004627</v>
       </c>
       <c r="Y30" s="1">
-        <v>-10.361078635659446</v>
+        <v>-20.722157271318892</v>
       </c>
       <c r="Z30" s="1">
-        <v>-8.5627110268612121</v>
+        <v>-17.125422053722424</v>
       </c>
       <c r="AA30" s="1">
-        <v>-10.992628272128735</v>
+        <v>-21.985256544257471</v>
       </c>
     </row>
     <row r="31" spans="1:27" x14ac:dyDescent="0.2">
@@ -71839,76 +71839,76 @@
         <v>1</v>
       </c>
       <c r="D31" s="1">
-        <v>8.4290916681592769</v>
+        <v>16.858183336318554</v>
       </c>
       <c r="E31" s="1">
-        <v>10.625158596178837</v>
+        <v>21.250317192357674</v>
       </c>
       <c r="F31" s="1">
-        <v>13.821100820639721</v>
+        <v>27.642201641279442</v>
       </c>
       <c r="G31" s="1">
-        <v>13.194758905122479</v>
+        <v>26.389517810244957</v>
       </c>
       <c r="H31" s="1">
-        <v>16.468089672860621</v>
+        <v>32.936179345721243</v>
       </c>
       <c r="I31" s="1">
-        <v>14.605531734268528</v>
+        <v>29.211063468537056</v>
       </c>
       <c r="J31" s="1">
-        <v>14.455483071316305</v>
+        <v>28.91096614263261</v>
       </c>
       <c r="K31" s="1">
-        <v>16.849556198282304</v>
+        <v>33.699112396564608</v>
       </c>
       <c r="L31" s="1">
-        <v>14.524455308625004</v>
+        <v>29.048910617250009</v>
       </c>
       <c r="M31" s="1">
-        <v>22.145297359116725</v>
+        <v>44.29059471823345</v>
       </c>
       <c r="N31" s="1">
-        <v>17.940030393078516</v>
+        <v>35.880060786157031</v>
       </c>
       <c r="O31" s="1">
-        <v>15.95697066991765</v>
+        <v>31.913941339835301</v>
       </c>
       <c r="P31" s="1">
-        <v>18.438657344903575</v>
+        <v>36.87731468980715</v>
       </c>
       <c r="Q31" s="1">
-        <v>16.449264532796086</v>
+        <v>32.898529065592172</v>
       </c>
       <c r="R31" s="1">
-        <v>14.073372331882624</v>
+        <v>28.146744663765247</v>
       </c>
       <c r="S31" s="1">
-        <v>12.427344497027216</v>
+        <v>24.854688994054431</v>
       </c>
       <c r="T31" s="1">
-        <v>13.073979319792215</v>
+        <v>26.147958639584431</v>
       </c>
       <c r="U31" s="1">
-        <v>11.556584557268964</v>
+        <v>23.113169114537929</v>
       </c>
       <c r="V31" s="1">
-        <v>10.948095806974523</v>
+        <v>21.896191613949046</v>
       </c>
       <c r="W31" s="1">
-        <v>11.671536821709573</v>
+        <v>23.343073643419146</v>
       </c>
       <c r="X31" s="1">
-        <v>10.75431346250304</v>
+        <v>21.50862692500608</v>
       </c>
       <c r="Y31" s="1">
-        <v>12.552009174567001</v>
+        <v>25.104018349134002</v>
       </c>
       <c r="Z31" s="1">
-        <v>8.9545711173799294</v>
+        <v>17.909142234759859</v>
       </c>
       <c r="AA31" s="1">
-        <v>9.6001255011817825</v>
+        <v>19.200251002363565</v>
       </c>
     </row>
     <row r="32" spans="1:27" x14ac:dyDescent="0.2">
@@ -71922,76 +71922,76 @@
         <v>2</v>
       </c>
       <c r="D32" s="1">
-        <v>4.8319485390000008</v>
+        <v>9.6638970780000015</v>
       </c>
       <c r="E32" s="1">
-        <v>5.2957454550000014</v>
+        <v>10.591490910000003</v>
       </c>
       <c r="F32" s="1">
-        <v>4.5162183000000002</v>
+        <v>9.0324366000000005</v>
       </c>
       <c r="G32" s="1">
-        <v>4.0667010999999995</v>
+        <v>8.133402199999999</v>
       </c>
       <c r="H32" s="1">
-        <v>3.4721153280000006</v>
+        <v>6.9442306560000011</v>
       </c>
       <c r="I32" s="1">
-        <v>2.8278285200000006</v>
+        <v>5.6556570400000012</v>
       </c>
       <c r="J32" s="1">
-        <v>3.494607072</v>
+        <v>6.989214144</v>
       </c>
       <c r="K32" s="1">
-        <v>0.65114869600000025</v>
+        <v>1.3022973920000005</v>
       </c>
       <c r="L32" s="1">
-        <v>0.55593999999999999</v>
+        <v>1.11188</v>
       </c>
       <c r="M32" s="1">
-        <v>0.79427147799999986</v>
+        <v>1.5885429559999997</v>
       </c>
       <c r="N32" s="1">
-        <v>0.47254105800000007</v>
+        <v>0.94508211600000014</v>
       </c>
       <c r="O32" s="1">
-        <v>0.60240864199999988</v>
+        <v>1.2048172839999998</v>
       </c>
       <c r="P32" s="1">
-        <v>0.94075769700000023</v>
+        <v>1.8815153940000005</v>
       </c>
       <c r="Q32" s="1">
-        <v>1.733305761</v>
+        <v>3.466611522</v>
       </c>
       <c r="R32" s="1">
-        <v>1.8866379839999998</v>
+        <v>3.7732759679999996</v>
       </c>
       <c r="S32" s="1">
-        <v>1.7635052159999998</v>
+        <v>3.5270104319999995</v>
       </c>
       <c r="T32" s="1">
-        <v>1.0304745</v>
+        <v>2.0609489999999999</v>
       </c>
       <c r="U32" s="1">
-        <v>2.2040241299999996</v>
+        <v>4.4080482599999993</v>
       </c>
       <c r="V32" s="1">
-        <v>1.1825320320000001</v>
+        <v>2.3650640640000002</v>
       </c>
       <c r="W32" s="1">
-        <v>0.88339660199999981</v>
+        <v>1.7667932039999996</v>
       </c>
       <c r="X32" s="1">
-        <v>1.2625873920000001</v>
+        <v>2.5251747840000003</v>
       </c>
       <c r="Y32" s="1">
-        <v>0.78034915199999999</v>
+        <v>1.560698304</v>
       </c>
       <c r="Z32" s="1">
-        <v>3.6730042470000006</v>
+        <v>7.3460084940000012</v>
       </c>
       <c r="AA32" s="1">
-        <v>4.4725372999999999</v>
+        <v>8.9450745999999999</v>
       </c>
     </row>
     <row r="33" spans="1:27" x14ac:dyDescent="0.2">
@@ -72005,76 +72005,76 @@
         <v>2</v>
       </c>
       <c r="D33" s="1">
-        <v>-10.944102935046125</v>
+        <v>-21.88820587009225</v>
       </c>
       <c r="E33" s="1">
-        <v>-12.566620133527303</v>
+        <v>-25.133240267054607</v>
       </c>
       <c r="F33" s="1">
-        <v>-9.8297193039402817</v>
+        <v>-19.659438607880563</v>
       </c>
       <c r="G33" s="1">
-        <v>-12.974595381321627</v>
+        <v>-25.949190762643255</v>
       </c>
       <c r="H33" s="1">
-        <v>-18.699002208615429</v>
+        <v>-37.398004417230858</v>
       </c>
       <c r="I33" s="1">
-        <v>-16.39644539253371</v>
+        <v>-32.792890785067421</v>
       </c>
       <c r="J33" s="1">
-        <v>-15.324218618899351</v>
+        <v>-30.648437237798703</v>
       </c>
       <c r="K33" s="1">
-        <v>-17.581489282925876</v>
+        <v>-35.162978565851752</v>
       </c>
       <c r="L33" s="1">
-        <v>-18.136408262090036</v>
+        <v>-36.272816524180072</v>
       </c>
       <c r="M33" s="1">
-        <v>-22.937051938389356</v>
+        <v>-45.874103876778712</v>
       </c>
       <c r="N33" s="1">
-        <v>-22.91719141349979</v>
+        <v>-45.83438282699958</v>
       </c>
       <c r="O33" s="1">
-        <v>-24.83391730219617</v>
+        <v>-49.66783460439234</v>
       </c>
       <c r="P33" s="1">
-        <v>-19.886153595671821</v>
+        <v>-39.772307191343643</v>
       </c>
       <c r="Q33" s="1">
-        <v>-19.358318444325899</v>
+        <v>-38.716636888651799</v>
       </c>
       <c r="R33" s="1">
-        <v>-20.81214404341749</v>
+        <v>-41.62428808683498</v>
       </c>
       <c r="S33" s="1">
-        <v>-17.133442464548484</v>
+        <v>-34.266884929096967</v>
       </c>
       <c r="T33" s="1">
-        <v>-15.558907467741626</v>
+        <v>-31.117814935483253</v>
       </c>
       <c r="U33" s="1">
-        <v>-13.913877328844983</v>
+        <v>-27.827754657689965</v>
       </c>
       <c r="V33" s="1">
-        <v>-8.2259575659320614</v>
+        <v>-16.451915131864123</v>
       </c>
       <c r="W33" s="1">
-        <v>-10.948033598645063</v>
+        <v>-21.896067197290126</v>
       </c>
       <c r="X33" s="1">
-        <v>-11.426179087712359</v>
+        <v>-22.852358175424719</v>
       </c>
       <c r="Y33" s="1">
-        <v>-10.879132567442419</v>
+        <v>-21.758265134884837</v>
       </c>
       <c r="Z33" s="1">
-        <v>-8.9908465782042732</v>
+        <v>-17.981693156408546</v>
       </c>
       <c r="AA33" s="1">
-        <v>-10.552923141243587</v>
+        <v>-21.105846282487175</v>
       </c>
     </row>
     <row r="34" spans="1:27" x14ac:dyDescent="0.2">
@@ -72088,76 +72088,76 @@
         <v>2</v>
       </c>
       <c r="D34" s="1">
-        <v>8.0076370847513143</v>
+        <v>16.015274169502629</v>
       </c>
       <c r="E34" s="1">
-        <v>10.943913354064202</v>
+        <v>21.887826708128404</v>
       </c>
       <c r="F34" s="1">
-        <v>13.130045779607736</v>
+        <v>26.260091559215471</v>
       </c>
       <c r="G34" s="1">
-        <v>12.666968548917581</v>
+        <v>25.333937097835161</v>
       </c>
       <c r="H34" s="1">
-        <v>15.644685189217592</v>
+        <v>31.289370378435184</v>
       </c>
       <c r="I34" s="1">
-        <v>15.043697686296584</v>
+        <v>30.087395372593168</v>
       </c>
       <c r="J34" s="1">
-        <v>13.877263748463651</v>
+        <v>27.754527496927302</v>
       </c>
       <c r="K34" s="1">
-        <v>16.007078388368189</v>
+        <v>32.014156776736378</v>
       </c>
       <c r="L34" s="1">
-        <v>15.105433520970005</v>
+        <v>30.210867041940009</v>
       </c>
       <c r="M34" s="1">
-        <v>21.038032491160887</v>
+        <v>42.076064982321775</v>
       </c>
       <c r="N34" s="1">
-        <v>17.043028873424589</v>
+        <v>34.086057746849178</v>
       </c>
       <c r="O34" s="1">
-        <v>16.754819203413533</v>
+        <v>33.509638406827065</v>
       </c>
       <c r="P34" s="1">
-        <v>18.807430491801647</v>
+        <v>37.614860983603293</v>
       </c>
       <c r="Q34" s="1">
-        <v>16.778249823452008</v>
+        <v>33.556499646904015</v>
       </c>
       <c r="R34" s="1">
-        <v>14.354839778520278</v>
+        <v>28.709679557040555</v>
       </c>
       <c r="S34" s="1">
-        <v>12.427344497027216</v>
+        <v>24.854688994054431</v>
       </c>
       <c r="T34" s="1">
-        <v>13.204719112990137</v>
+        <v>26.409438225980274</v>
       </c>
       <c r="U34" s="1">
-        <v>11.209887020550896</v>
+        <v>22.419774041101793</v>
       </c>
       <c r="V34" s="1">
-        <v>11.276538681183759</v>
+        <v>22.553077362367517</v>
       </c>
       <c r="W34" s="1">
-        <v>11.904967558143765</v>
+        <v>23.80993511628753</v>
       </c>
       <c r="X34" s="1">
-        <v>10.216597789377888</v>
+        <v>20.433195578755775</v>
       </c>
       <c r="Y34" s="1">
-        <v>12.42648908282133</v>
+        <v>24.852978165642661</v>
       </c>
       <c r="Z34" s="1">
-        <v>8.5068425615109327</v>
+        <v>17.013685123021865</v>
       </c>
       <c r="AA34" s="1">
-        <v>9.888129266217236</v>
+        <v>19.776258532434472</v>
       </c>
     </row>
     <row r="35" spans="1:27" x14ac:dyDescent="0.2">
@@ -72171,76 +72171,76 @@
         <v>3</v>
       </c>
       <c r="D35" s="1">
-        <v>4.8319485390000008</v>
+        <v>9.6638970780000015</v>
       </c>
       <c r="E35" s="1">
-        <v>5.5075752732000014</v>
+        <v>11.015150546400003</v>
       </c>
       <c r="F35" s="1">
-        <v>4.5162183000000002</v>
+        <v>9.0324366000000005</v>
       </c>
       <c r="G35" s="1">
-        <v>3.9853670779999995</v>
+        <v>7.9707341559999989</v>
       </c>
       <c r="H35" s="1">
-        <v>3.2985095616000009</v>
+        <v>6.5970191232000017</v>
       </c>
       <c r="I35" s="1">
-        <v>2.7712719496000005</v>
+        <v>5.5425438992000009</v>
       </c>
       <c r="J35" s="1">
-        <v>3.3198767184000002</v>
+        <v>6.6397534368000004</v>
       </c>
       <c r="K35" s="1">
-        <v>0.63812572208000029</v>
+        <v>1.2762514441600006</v>
       </c>
       <c r="L35" s="1">
-        <v>0.55593999999999999</v>
+        <v>1.11188</v>
       </c>
       <c r="M35" s="1">
-        <v>0.80221419277999984</v>
+        <v>1.6044283855599997</v>
       </c>
       <c r="N35" s="1">
-        <v>0.49616811090000007</v>
+        <v>0.99233622180000014</v>
       </c>
       <c r="O35" s="1">
-        <v>0.59638455557999992</v>
+        <v>1.1927691111599998</v>
       </c>
       <c r="P35" s="1">
-        <v>0.98779558185000027</v>
+        <v>1.9755911637000005</v>
       </c>
       <c r="Q35" s="1">
-        <v>1.7679718762199998</v>
+        <v>3.5359437524399997</v>
       </c>
       <c r="R35" s="1">
-        <v>1.9243707436799997</v>
+        <v>3.8487414873599994</v>
       </c>
       <c r="S35" s="1">
-        <v>1.7106000595199999</v>
+        <v>3.4212001190399999</v>
       </c>
       <c r="T35" s="1">
-        <v>1.061388735</v>
+        <v>2.1227774699999999</v>
       </c>
       <c r="U35" s="1">
-        <v>2.1379034060999995</v>
+        <v>4.275806812199999</v>
       </c>
       <c r="V35" s="1">
-        <v>1.2298333132800001</v>
+        <v>2.4596666265600002</v>
       </c>
       <c r="W35" s="1">
-        <v>0.85689470393999978</v>
+        <v>1.7137894078799996</v>
       </c>
       <c r="X35" s="1">
-        <v>1.1994580224000002</v>
+        <v>2.3989160448000004</v>
       </c>
       <c r="Y35" s="1">
-        <v>0.77254566048000006</v>
+        <v>1.5450913209600001</v>
       </c>
       <c r="Z35" s="1">
-        <v>3.7464643319400004</v>
+        <v>7.4929286638800008</v>
       </c>
       <c r="AA35" s="1">
-        <v>4.4278119270000005</v>
+        <v>8.855623854000001</v>
       </c>
     </row>
     <row r="36" spans="1:27" x14ac:dyDescent="0.2">
@@ -72254,76 +72254,76 @@
         <v>3</v>
       </c>
       <c r="D36" s="1">
-        <v>-11.491308081798431</v>
+        <v>-22.982616163596862</v>
       </c>
       <c r="E36" s="1">
-        <v>-13.194951140203669</v>
+        <v>-26.389902280407338</v>
       </c>
       <c r="F36" s="1">
-        <v>-10.124610883058489</v>
+        <v>-20.249221766116978</v>
       </c>
       <c r="G36" s="1">
-        <v>-13.234087288948061</v>
+        <v>-26.468174577896121</v>
       </c>
       <c r="H36" s="1">
-        <v>-19.072982252787739</v>
+        <v>-38.145964505575478</v>
       </c>
       <c r="I36" s="1">
-        <v>-17.216267662160398</v>
+        <v>-34.432535324320796</v>
       </c>
       <c r="J36" s="1">
-        <v>-14.86449206033237</v>
+        <v>-29.728984120664741</v>
       </c>
       <c r="K36" s="1">
-        <v>-17.933119068584393</v>
+        <v>-35.866238137168786</v>
       </c>
       <c r="L36" s="1">
-        <v>-17.955044179469137</v>
+        <v>-35.910088358938275</v>
       </c>
       <c r="M36" s="1">
-        <v>-22.248940380237677</v>
+        <v>-44.497880760475354</v>
       </c>
       <c r="N36" s="1">
-        <v>-21.771331842824804</v>
+        <v>-43.542663685649607</v>
       </c>
       <c r="O36" s="1">
-        <v>-24.337238956152245</v>
+        <v>-48.674477912304489</v>
       </c>
       <c r="P36" s="1">
-        <v>-18.891845915888229</v>
+        <v>-37.783691831776459</v>
       </c>
       <c r="Q36" s="1">
-        <v>-19.16473525988264</v>
+        <v>-38.32947051976528</v>
       </c>
       <c r="R36" s="1">
-        <v>-21.852751245588365</v>
+        <v>-43.70550249117673</v>
       </c>
       <c r="S36" s="1">
-        <v>-17.64744573848494</v>
+        <v>-35.29489147696988</v>
       </c>
       <c r="T36" s="1">
-        <v>-14.780962094354544</v>
+        <v>-29.561924188709089</v>
       </c>
       <c r="U36" s="1">
-        <v>-14.609571195287231</v>
+        <v>-29.219142390574461</v>
       </c>
       <c r="V36" s="1">
-        <v>-8.3082171415913812</v>
+        <v>-16.616434283182762</v>
       </c>
       <c r="W36" s="1">
-        <v>-11.166994270617963</v>
+        <v>-22.333988541235925</v>
       </c>
       <c r="X36" s="1">
-        <v>-11.083393715080987</v>
+        <v>-22.166787430161975</v>
       </c>
       <c r="Y36" s="1">
-        <v>-10.443967264744721</v>
+        <v>-20.887934529489442</v>
       </c>
       <c r="Z36" s="1">
-        <v>-9.3504804413324436</v>
+        <v>-18.700960882664887</v>
       </c>
       <c r="AA36" s="1">
-        <v>-10.341864678418714</v>
+        <v>-20.683729356837429</v>
       </c>
     </row>
     <row r="37" spans="1:27" x14ac:dyDescent="0.2">
@@ -72337,76 +72337,76 @@
         <v>3</v>
       </c>
       <c r="D37" s="1">
-        <v>8.0076370847513143</v>
+        <v>16.015274169502629</v>
       </c>
       <c r="E37" s="1">
-        <v>10.725035086982919</v>
+        <v>21.450070173965837</v>
       </c>
       <c r="F37" s="1">
-        <v>13.130045779607736</v>
+        <v>26.260091559215471</v>
       </c>
       <c r="G37" s="1">
-        <v>12.033620121471701</v>
+        <v>24.067240242943402</v>
       </c>
       <c r="H37" s="1">
-        <v>16.114025744894121</v>
+        <v>32.228051489788243</v>
       </c>
       <c r="I37" s="1">
-        <v>15.795882570611413</v>
+        <v>31.591765141222826</v>
       </c>
       <c r="J37" s="1">
-        <v>14.432354298402197</v>
+        <v>28.864708596804395</v>
       </c>
       <c r="K37" s="1">
-        <v>16.327219956135551</v>
+        <v>32.654439912271101</v>
       </c>
       <c r="L37" s="1">
-        <v>15.105433520970005</v>
+        <v>30.210867041940009</v>
       </c>
       <c r="M37" s="1">
-        <v>21.458793140984103</v>
+        <v>42.917586281968205</v>
       </c>
       <c r="N37" s="1">
-        <v>17.724750028361573</v>
+        <v>35.449500056723146</v>
       </c>
       <c r="O37" s="1">
-        <v>17.257463779515938</v>
+        <v>34.514927559031875</v>
       </c>
       <c r="P37" s="1">
-        <v>17.867058967211566</v>
+        <v>35.734117934423132</v>
       </c>
       <c r="Q37" s="1">
-        <v>15.939337332279408</v>
+        <v>31.878674664558815</v>
       </c>
       <c r="R37" s="1">
-        <v>14.641936574090682</v>
+        <v>29.283873148181364</v>
       </c>
       <c r="S37" s="1">
-        <v>12.178797607086672</v>
+        <v>24.357595214173344</v>
       </c>
       <c r="T37" s="1">
-        <v>13.46881349524994</v>
+        <v>26.937626990499879</v>
       </c>
       <c r="U37" s="1">
-        <v>10.873590409934371</v>
+        <v>21.747180819868742</v>
       </c>
       <c r="V37" s="1">
-        <v>11.727600228431108</v>
+        <v>23.455200456862215</v>
       </c>
       <c r="W37" s="1">
-        <v>11.666868206980888</v>
+        <v>23.333736413961777</v>
       </c>
       <c r="X37" s="1">
-        <v>10.114431811484108</v>
+        <v>20.228863622968216</v>
       </c>
       <c r="Y37" s="1">
-        <v>12.42648908282133</v>
+        <v>24.852978165642661</v>
       </c>
       <c r="Z37" s="1">
-        <v>8.1665688590504946</v>
+        <v>16.333137718100989</v>
       </c>
       <c r="AA37" s="1">
-        <v>9.888129266217236</v>
+        <v>19.776258532434472</v>
       </c>
     </row>
   </sheetData>

--- a/data/OP1/case33_2/case33_2_operational_data.xlsx
+++ b/data/OP1/case33_2/case33_2_operational_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/micaelsimoes/PycharmProjects/shared-resources-planning/data/OP1/case33_2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E208676C-69A3-CB40-9126-1BB62723DAA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2788A26D-BA04-CC46-B662-018A0B04770D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1120" yWindow="620" windowWidth="50080" windowHeight="28180" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1120" yWindow="620" windowWidth="50080" windowHeight="28180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Characterization" sheetId="2" r:id="rId1"/>
@@ -473,12 +473,12 @@
         <v>1</v>
       </c>
       <c r="B2" s="1">
-        <f>E2*1.5</f>
-        <v>6</v>
+        <f>E2*3</f>
+        <v>12</v>
       </c>
       <c r="C2" s="1">
-        <f>F2*1.5</f>
-        <v>-3.5999999999999996</v>
+        <f>F2*3</f>
+        <v>-7.1999999999999993</v>
       </c>
       <c r="D2" s="2">
         <v>2.6917900403768499E-2</v>
@@ -495,12 +495,12 @@
         <v>2</v>
       </c>
       <c r="B3" s="1">
-        <f t="shared" ref="B3:B33" si="0">E3*1.5</f>
-        <v>5.3999999999999995</v>
+        <f t="shared" ref="B3:B33" si="0">E3*3</f>
+        <v>10.799999999999999</v>
       </c>
       <c r="C3" s="1">
-        <f t="shared" ref="C3:C33" si="1">F3*1.5</f>
-        <v>-2.4000000000000004</v>
+        <f t="shared" ref="C3:C33" si="1">F3*3</f>
+        <v>-4.8000000000000007</v>
       </c>
       <c r="D3" s="2">
         <v>2.4226110363391645E-2</v>
@@ -518,11 +518,11 @@
       </c>
       <c r="B4" s="1">
         <f t="shared" si="0"/>
-        <v>7.1999999999999993</v>
+        <v>14.399999999999999</v>
       </c>
       <c r="C4" s="1">
         <f t="shared" si="1"/>
-        <v>-4.8000000000000007</v>
+        <v>-9.6000000000000014</v>
       </c>
       <c r="D4" s="2">
         <v>3.2301480484522194E-2</v>
@@ -540,11 +540,11 @@
       </c>
       <c r="B5" s="1">
         <f t="shared" si="0"/>
-        <v>3.5999999999999996</v>
+        <v>7.1999999999999993</v>
       </c>
       <c r="C5" s="1">
         <f t="shared" si="1"/>
-        <v>-1.7999999999999998</v>
+        <v>-3.5999999999999996</v>
       </c>
       <c r="D5" s="2">
         <v>1.6150740242261097E-2</v>
@@ -562,11 +562,11 @@
       </c>
       <c r="B6" s="1">
         <f t="shared" si="0"/>
-        <v>3.5999999999999996</v>
+        <v>7.1999999999999993</v>
       </c>
       <c r="C6" s="1">
         <f t="shared" si="1"/>
-        <v>-1.2000000000000002</v>
+        <v>-2.4000000000000004</v>
       </c>
       <c r="D6" s="2">
         <v>1.6150740242261097E-2</v>
@@ -584,20 +584,20 @@
       </c>
       <c r="B7" s="1">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C7" s="1">
         <f t="shared" si="1"/>
-        <v>-6</v>
+        <v>-9</v>
       </c>
       <c r="D7" s="2">
         <v>5.3835800807536999E-2</v>
       </c>
       <c r="E7" s="4">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F7" s="4">
-        <v>-4</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
@@ -606,20 +606,20 @@
       </c>
       <c r="B8" s="1">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C8" s="1">
         <f t="shared" si="1"/>
-        <v>-6</v>
+        <v>-9</v>
       </c>
       <c r="D8" s="2">
         <v>5.3835800807536999E-2</v>
       </c>
       <c r="E8" s="4">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F8" s="4">
-        <v>-4</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
@@ -628,11 +628,11 @@
       </c>
       <c r="B9" s="1">
         <f t="shared" si="0"/>
-        <v>3.5999999999999996</v>
+        <v>7.1999999999999993</v>
       </c>
       <c r="C9" s="1">
         <f t="shared" si="1"/>
-        <v>-1.2000000000000002</v>
+        <v>-2.4000000000000004</v>
       </c>
       <c r="D9" s="2">
         <v>1.6150740242261097E-2</v>
@@ -650,11 +650,11 @@
       </c>
       <c r="B10" s="1">
         <f t="shared" si="0"/>
-        <v>3.5999999999999996</v>
+        <v>7.1999999999999993</v>
       </c>
       <c r="C10" s="1">
         <f t="shared" si="1"/>
-        <v>-1.2000000000000002</v>
+        <v>-2.4000000000000004</v>
       </c>
       <c r="D10" s="2">
         <v>1.6150740242261097E-2</v>
@@ -672,11 +672,11 @@
       </c>
       <c r="B11" s="1">
         <f t="shared" si="0"/>
-        <v>2.6999999999999997</v>
+        <v>5.3999999999999995</v>
       </c>
       <c r="C11" s="1">
         <f t="shared" si="1"/>
-        <v>-1.7999999999999998</v>
+        <v>-3.5999999999999996</v>
       </c>
       <c r="D11" s="2">
         <v>1.2113055181695823E-2</v>
@@ -694,11 +694,11 @@
       </c>
       <c r="B12" s="1">
         <f t="shared" si="0"/>
-        <v>3.5999999999999996</v>
+        <v>7.1999999999999993</v>
       </c>
       <c r="C12" s="1">
         <f t="shared" si="1"/>
-        <v>-2.1</v>
+        <v>-4.2</v>
       </c>
       <c r="D12" s="2">
         <v>1.6150740242261097E-2</v>
@@ -716,11 +716,11 @@
       </c>
       <c r="B13" s="1">
         <f t="shared" si="0"/>
-        <v>3.5999999999999996</v>
+        <v>7.1999999999999993</v>
       </c>
       <c r="C13" s="1">
         <f t="shared" si="1"/>
-        <v>-2.1</v>
+        <v>-4.2</v>
       </c>
       <c r="D13" s="2">
         <v>1.6150740242261097E-2</v>
@@ -738,11 +738,11 @@
       </c>
       <c r="B14" s="1">
         <f t="shared" si="0"/>
-        <v>7.1999999999999993</v>
+        <v>14.399999999999999</v>
       </c>
       <c r="C14" s="1">
         <f t="shared" si="1"/>
-        <v>-4.8000000000000007</v>
+        <v>-9.6000000000000014</v>
       </c>
       <c r="D14" s="2">
         <v>3.2301480484522194E-2</v>
@@ -760,11 +760,11 @@
       </c>
       <c r="B15" s="1">
         <f t="shared" si="0"/>
-        <v>3.5999999999999996</v>
+        <v>7.1999999999999993</v>
       </c>
       <c r="C15" s="1">
         <f t="shared" si="1"/>
-        <v>-0.60000000000000009</v>
+        <v>-1.2000000000000002</v>
       </c>
       <c r="D15" s="2">
         <v>1.6150740242261097E-2</v>
@@ -782,11 +782,11 @@
       </c>
       <c r="B16" s="1">
         <f t="shared" si="0"/>
-        <v>3.5999999999999996</v>
+        <v>7.1999999999999993</v>
       </c>
       <c r="C16" s="1">
         <f t="shared" si="1"/>
-        <v>-1.2000000000000002</v>
+        <v>-2.4000000000000004</v>
       </c>
       <c r="D16" s="2">
         <v>1.6150740242261097E-2</v>
@@ -804,11 +804,11 @@
       </c>
       <c r="B17" s="1">
         <f t="shared" si="0"/>
-        <v>3.5999999999999996</v>
+        <v>7.1999999999999993</v>
       </c>
       <c r="C17" s="1">
         <f t="shared" si="1"/>
-        <v>-1.2000000000000002</v>
+        <v>-2.4000000000000004</v>
       </c>
       <c r="D17" s="2">
         <v>1.6150740242261097E-2</v>
@@ -826,11 +826,11 @@
       </c>
       <c r="B18" s="1">
         <f t="shared" si="0"/>
-        <v>5.3999999999999995</v>
+        <v>10.799999999999999</v>
       </c>
       <c r="C18" s="1">
         <f t="shared" si="1"/>
-        <v>-2.4000000000000004</v>
+        <v>-4.8000000000000007</v>
       </c>
       <c r="D18" s="2">
         <v>2.4226110363391645E-2</v>
@@ -848,11 +848,11 @@
       </c>
       <c r="B19" s="1">
         <f t="shared" si="0"/>
-        <v>5.3999999999999995</v>
+        <v>10.799999999999999</v>
       </c>
       <c r="C19" s="1">
         <f t="shared" si="1"/>
-        <v>-2.4000000000000004</v>
+        <v>-4.8000000000000007</v>
       </c>
       <c r="D19" s="2">
         <v>2.4226110363391645E-2</v>
@@ -870,11 +870,11 @@
       </c>
       <c r="B20" s="1">
         <f t="shared" si="0"/>
-        <v>5.3999999999999995</v>
+        <v>10.799999999999999</v>
       </c>
       <c r="C20" s="1">
         <f t="shared" si="1"/>
-        <v>-2.4000000000000004</v>
+        <v>-4.8000000000000007</v>
       </c>
       <c r="D20" s="2">
         <v>2.4226110363391645E-2</v>
@@ -892,11 +892,11 @@
       </c>
       <c r="B21" s="1">
         <f t="shared" si="0"/>
-        <v>5.3999999999999995</v>
+        <v>10.799999999999999</v>
       </c>
       <c r="C21" s="1">
         <f t="shared" si="1"/>
-        <v>-2.4000000000000004</v>
+        <v>-4.8000000000000007</v>
       </c>
       <c r="D21" s="2">
         <v>2.4226110363391645E-2</v>
@@ -914,11 +914,11 @@
       </c>
       <c r="B22" s="1">
         <f t="shared" si="0"/>
-        <v>5.3999999999999995</v>
+        <v>10.799999999999999</v>
       </c>
       <c r="C22" s="1">
         <f t="shared" si="1"/>
-        <v>-2.4000000000000004</v>
+        <v>-4.8000000000000007</v>
       </c>
       <c r="D22" s="2">
         <v>2.4226110363391645E-2</v>
@@ -936,11 +936,11 @@
       </c>
       <c r="B23" s="1">
         <f t="shared" si="0"/>
-        <v>5.3999999999999995</v>
+        <v>10.799999999999999</v>
       </c>
       <c r="C23" s="1">
         <f t="shared" si="1"/>
-        <v>-3</v>
+        <v>-6</v>
       </c>
       <c r="D23" s="2">
         <v>2.4226110363391645E-2</v>
@@ -958,7 +958,7 @@
       </c>
       <c r="B24" s="1">
         <f t="shared" si="0"/>
-        <v>25.200000000000003</v>
+        <v>27</v>
       </c>
       <c r="C24" s="1">
         <f t="shared" si="1"/>
@@ -968,10 +968,10 @@
         <v>0.11305518169582769</v>
       </c>
       <c r="E24" s="4">
-        <v>16.8</v>
+        <v>9</v>
       </c>
       <c r="F24" s="4">
-        <v>-8</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.2">
@@ -980,7 +980,7 @@
       </c>
       <c r="B25" s="1">
         <f t="shared" si="0"/>
-        <v>25.200000000000003</v>
+        <v>27</v>
       </c>
       <c r="C25" s="1">
         <f t="shared" si="1"/>
@@ -990,10 +990,10 @@
         <v>0.11305518169582769</v>
       </c>
       <c r="E25" s="4">
-        <v>16.8</v>
+        <v>9</v>
       </c>
       <c r="F25" s="4">
-        <v>-8</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.2">
@@ -1002,11 +1002,11 @@
       </c>
       <c r="B26" s="1">
         <f t="shared" si="0"/>
-        <v>1.7999999999999998</v>
+        <v>3.5999999999999996</v>
       </c>
       <c r="C26" s="1">
         <f t="shared" si="1"/>
-        <v>-0.75</v>
+        <v>-1.5</v>
       </c>
       <c r="D26" s="2">
         <v>1.6150740242261097E-2</v>
@@ -1024,11 +1024,11 @@
       </c>
       <c r="B27" s="1">
         <f t="shared" si="0"/>
-        <v>1.7999999999999998</v>
+        <v>3.5999999999999996</v>
       </c>
       <c r="C27" s="1">
         <f t="shared" si="1"/>
-        <v>-0.75</v>
+        <v>-1.5</v>
       </c>
       <c r="D27" s="2">
         <v>1.6150740242261097E-2</v>
@@ -1046,11 +1046,11 @@
       </c>
       <c r="B28" s="1">
         <f t="shared" si="0"/>
-        <v>1.7999999999999998</v>
+        <v>3.5999999999999996</v>
       </c>
       <c r="C28" s="1">
         <f t="shared" si="1"/>
-        <v>-0.60000000000000009</v>
+        <v>-1.2000000000000002</v>
       </c>
       <c r="D28" s="2">
         <v>1.6150740242261097E-2</v>
@@ -1068,11 +1068,11 @@
       </c>
       <c r="B29" s="1">
         <f t="shared" si="0"/>
-        <v>3.5999999999999996</v>
+        <v>7.1999999999999993</v>
       </c>
       <c r="C29" s="1">
         <f t="shared" si="1"/>
-        <v>-2.0999999999999996</v>
+        <v>-4.1999999999999993</v>
       </c>
       <c r="D29" s="2">
         <v>3.2301480484522194E-2</v>
@@ -1090,11 +1090,11 @@
       </c>
       <c r="B30" s="1">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C30" s="1">
         <f t="shared" si="1"/>
-        <v>-3.1500000000000004</v>
+        <v>-6.3000000000000007</v>
       </c>
       <c r="D30" s="2">
         <v>5.3835800807536999E-2</v>
@@ -1112,11 +1112,11 @@
       </c>
       <c r="B31" s="1">
         <f t="shared" si="0"/>
-        <v>4.5</v>
+        <v>9</v>
       </c>
       <c r="C31" s="1">
         <f t="shared" si="1"/>
-        <v>-2.0999999999999996</v>
+        <v>-4.1999999999999993</v>
       </c>
       <c r="D31" s="2">
         <v>4.0376850605652742E-2</v>
@@ -1134,11 +1134,11 @@
       </c>
       <c r="B32" s="1">
         <f t="shared" si="0"/>
-        <v>6.3000000000000007</v>
+        <v>12.600000000000001</v>
       </c>
       <c r="C32" s="1">
         <f t="shared" si="1"/>
-        <v>-3</v>
+        <v>-6</v>
       </c>
       <c r="D32" s="2">
         <v>5.6527590847913846E-2</v>
@@ -1156,11 +1156,11 @@
       </c>
       <c r="B33" s="1">
         <f t="shared" si="0"/>
-        <v>1.7999999999999998</v>
+        <v>3.5999999999999996</v>
       </c>
       <c r="C33" s="1">
         <f t="shared" si="1"/>
-        <v>-1.9500000000000002</v>
+        <v>-3.9000000000000004</v>
       </c>
       <c r="D33" s="2">
         <v>1.6150740242261097E-2</v>

--- a/data/OP1/case33_2/case33_2_operational_data.xlsx
+++ b/data/OP1/case33_2/case33_2_operational_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/micaelsimoes/PycharmProjects/shared-resources-planning/data/OP1/case33_2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2788A26D-BA04-CC46-B662-018A0B04770D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C57F9C9-A728-BF4B-8792-5B05B89F3AEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1120" yWindow="620" windowWidth="50080" windowHeight="28180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -473,12 +473,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1">
-        <f>E2*3</f>
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C2" s="1">
-        <f>F2*3</f>
-        <v>-7.1999999999999993</v>
+        <v>-2.4</v>
       </c>
       <c r="D2" s="2">
         <v>2.6917900403768499E-2</v>
@@ -495,12 +493,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1">
-        <f t="shared" ref="B3:B33" si="0">E3*3</f>
-        <v>10.799999999999999</v>
+        <v>3.5999999999999996</v>
       </c>
       <c r="C3" s="1">
-        <f t="shared" ref="C3:C33" si="1">F3*3</f>
-        <v>-4.8000000000000007</v>
+        <v>-1.6</v>
       </c>
       <c r="D3" s="2">
         <v>2.4226110363391645E-2</v>
@@ -517,12 +513,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1">
-        <f t="shared" si="0"/>
-        <v>14.399999999999999</v>
+        <v>4.8</v>
       </c>
       <c r="C4" s="1">
-        <f t="shared" si="1"/>
-        <v>-9.6000000000000014</v>
+        <v>-3.2</v>
       </c>
       <c r="D4" s="2">
         <v>3.2301480484522194E-2</v>
@@ -539,12 +533,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1">
-        <f t="shared" si="0"/>
-        <v>7.1999999999999993</v>
+        <v>2.4</v>
       </c>
       <c r="C5" s="1">
-        <f t="shared" si="1"/>
-        <v>-3.5999999999999996</v>
+        <v>-1.2</v>
       </c>
       <c r="D5" s="2">
         <v>1.6150740242261097E-2</v>
@@ -561,12 +553,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1">
-        <f t="shared" si="0"/>
-        <v>7.1999999999999993</v>
+        <v>2.4</v>
       </c>
       <c r="C6" s="1">
-        <f t="shared" si="1"/>
-        <v>-2.4000000000000004</v>
+        <v>-0.8</v>
       </c>
       <c r="D6" s="2">
         <v>1.6150740242261097E-2</v>
@@ -583,12 +573,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1">
-        <f t="shared" si="0"/>
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="C7" s="1">
-        <f t="shared" si="1"/>
-        <v>-9</v>
+        <v>-3</v>
       </c>
       <c r="D7" s="2">
         <v>5.3835800807536999E-2</v>
@@ -605,12 +593,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1">
-        <f t="shared" si="0"/>
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="C8" s="1">
-        <f t="shared" si="1"/>
-        <v>-9</v>
+        <v>-3</v>
       </c>
       <c r="D8" s="2">
         <v>5.3835800807536999E-2</v>
@@ -627,12 +613,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1">
-        <f t="shared" si="0"/>
-        <v>7.1999999999999993</v>
+        <v>2.4</v>
       </c>
       <c r="C9" s="1">
-        <f t="shared" si="1"/>
-        <v>-2.4000000000000004</v>
+        <v>-0.8</v>
       </c>
       <c r="D9" s="2">
         <v>1.6150740242261097E-2</v>
@@ -649,12 +633,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1">
-        <f t="shared" si="0"/>
-        <v>7.1999999999999993</v>
+        <v>2.4</v>
       </c>
       <c r="C10" s="1">
-        <f t="shared" si="1"/>
-        <v>-2.4000000000000004</v>
+        <v>-0.8</v>
       </c>
       <c r="D10" s="2">
         <v>1.6150740242261097E-2</v>
@@ -671,12 +653,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1">
-        <f t="shared" si="0"/>
-        <v>5.3999999999999995</v>
+        <v>1.7999999999999998</v>
       </c>
       <c r="C11" s="1">
-        <f t="shared" si="1"/>
-        <v>-3.5999999999999996</v>
+        <v>-1.2</v>
       </c>
       <c r="D11" s="2">
         <v>1.2113055181695823E-2</v>
@@ -693,12 +673,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1">
-        <f t="shared" si="0"/>
-        <v>7.1999999999999993</v>
+        <v>2.4</v>
       </c>
       <c r="C12" s="1">
-        <f t="shared" si="1"/>
-        <v>-4.2</v>
+        <v>-1.4000000000000001</v>
       </c>
       <c r="D12" s="2">
         <v>1.6150740242261097E-2</v>
@@ -715,12 +693,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1">
-        <f t="shared" si="0"/>
-        <v>7.1999999999999993</v>
+        <v>2.4</v>
       </c>
       <c r="C13" s="1">
-        <f t="shared" si="1"/>
-        <v>-4.2</v>
+        <v>-1.4000000000000001</v>
       </c>
       <c r="D13" s="2">
         <v>1.6150740242261097E-2</v>
@@ -737,12 +713,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1">
-        <f t="shared" si="0"/>
-        <v>14.399999999999999</v>
+        <v>4.8</v>
       </c>
       <c r="C14" s="1">
-        <f t="shared" si="1"/>
-        <v>-9.6000000000000014</v>
+        <v>-3.2</v>
       </c>
       <c r="D14" s="2">
         <v>3.2301480484522194E-2</v>
@@ -759,12 +733,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1">
-        <f t="shared" si="0"/>
-        <v>7.1999999999999993</v>
+        <v>2.4</v>
       </c>
       <c r="C15" s="1">
-        <f t="shared" si="1"/>
-        <v>-1.2000000000000002</v>
+        <v>-0.4</v>
       </c>
       <c r="D15" s="2">
         <v>1.6150740242261097E-2</v>
@@ -781,12 +753,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="1">
-        <f t="shared" si="0"/>
-        <v>7.1999999999999993</v>
+        <v>2.4</v>
       </c>
       <c r="C16" s="1">
-        <f t="shared" si="1"/>
-        <v>-2.4000000000000004</v>
+        <v>-0.8</v>
       </c>
       <c r="D16" s="2">
         <v>1.6150740242261097E-2</v>
@@ -803,12 +773,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="1">
-        <f t="shared" si="0"/>
-        <v>7.1999999999999993</v>
+        <v>2.4</v>
       </c>
       <c r="C17" s="1">
-        <f t="shared" si="1"/>
-        <v>-2.4000000000000004</v>
+        <v>-0.8</v>
       </c>
       <c r="D17" s="2">
         <v>1.6150740242261097E-2</v>
@@ -825,12 +793,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="1">
-        <f t="shared" si="0"/>
-        <v>10.799999999999999</v>
+        <v>3.5999999999999996</v>
       </c>
       <c r="C18" s="1">
-        <f t="shared" si="1"/>
-        <v>-4.8000000000000007</v>
+        <v>-1.6</v>
       </c>
       <c r="D18" s="2">
         <v>2.4226110363391645E-2</v>
@@ -847,12 +813,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="1">
-        <f t="shared" si="0"/>
-        <v>10.799999999999999</v>
+        <v>3.5999999999999996</v>
       </c>
       <c r="C19" s="1">
-        <f t="shared" si="1"/>
-        <v>-4.8000000000000007</v>
+        <v>-1.6</v>
       </c>
       <c r="D19" s="2">
         <v>2.4226110363391645E-2</v>
@@ -869,12 +833,10 @@
         <v>19</v>
       </c>
       <c r="B20" s="1">
-        <f t="shared" si="0"/>
-        <v>10.799999999999999</v>
+        <v>3.5999999999999996</v>
       </c>
       <c r="C20" s="1">
-        <f t="shared" si="1"/>
-        <v>-4.8000000000000007</v>
+        <v>-1.6</v>
       </c>
       <c r="D20" s="2">
         <v>2.4226110363391645E-2</v>
@@ -891,12 +853,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="1">
-        <f t="shared" si="0"/>
-        <v>10.799999999999999</v>
+        <v>3.5999999999999996</v>
       </c>
       <c r="C21" s="1">
-        <f t="shared" si="1"/>
-        <v>-4.8000000000000007</v>
+        <v>-1.6</v>
       </c>
       <c r="D21" s="2">
         <v>2.4226110363391645E-2</v>
@@ -913,12 +873,10 @@
         <v>21</v>
       </c>
       <c r="B22" s="1">
-        <f t="shared" si="0"/>
-        <v>10.799999999999999</v>
+        <v>3.5999999999999996</v>
       </c>
       <c r="C22" s="1">
-        <f t="shared" si="1"/>
-        <v>-4.8000000000000007</v>
+        <v>-1.6</v>
       </c>
       <c r="D22" s="2">
         <v>2.4226110363391645E-2</v>
@@ -935,12 +893,10 @@
         <v>22</v>
       </c>
       <c r="B23" s="1">
-        <f t="shared" si="0"/>
-        <v>10.799999999999999</v>
+        <v>3.5999999999999996</v>
       </c>
       <c r="C23" s="1">
-        <f t="shared" si="1"/>
-        <v>-6</v>
+        <v>-2</v>
       </c>
       <c r="D23" s="2">
         <v>2.4226110363391645E-2</v>
@@ -957,12 +913,10 @@
         <v>23</v>
       </c>
       <c r="B24" s="1">
-        <f t="shared" si="0"/>
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="C24" s="1">
-        <f t="shared" si="1"/>
-        <v>-12</v>
+        <v>-4</v>
       </c>
       <c r="D24" s="2">
         <v>0.11305518169582769</v>
@@ -979,12 +933,10 @@
         <v>24</v>
       </c>
       <c r="B25" s="1">
-        <f t="shared" si="0"/>
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="C25" s="1">
-        <f t="shared" si="1"/>
-        <v>-12</v>
+        <v>-4</v>
       </c>
       <c r="D25" s="2">
         <v>0.11305518169582769</v>
@@ -1001,12 +953,10 @@
         <v>25</v>
       </c>
       <c r="B26" s="1">
-        <f t="shared" si="0"/>
-        <v>3.5999999999999996</v>
+        <v>1.2</v>
       </c>
       <c r="C26" s="1">
-        <f t="shared" si="1"/>
-        <v>-1.5</v>
+        <v>-0.5</v>
       </c>
       <c r="D26" s="2">
         <v>1.6150740242261097E-2</v>
@@ -1023,12 +973,10 @@
         <v>26</v>
       </c>
       <c r="B27" s="1">
-        <f t="shared" si="0"/>
-        <v>3.5999999999999996</v>
+        <v>1.2</v>
       </c>
       <c r="C27" s="1">
-        <f t="shared" si="1"/>
-        <v>-1.5</v>
+        <v>-0.5</v>
       </c>
       <c r="D27" s="2">
         <v>1.6150740242261097E-2</v>
@@ -1045,12 +993,10 @@
         <v>27</v>
       </c>
       <c r="B28" s="1">
-        <f t="shared" si="0"/>
-        <v>3.5999999999999996</v>
+        <v>1.2</v>
       </c>
       <c r="C28" s="1">
-        <f t="shared" si="1"/>
-        <v>-1.2000000000000002</v>
+        <v>-0.4</v>
       </c>
       <c r="D28" s="2">
         <v>1.6150740242261097E-2</v>
@@ -1067,12 +1013,10 @@
         <v>28</v>
       </c>
       <c r="B29" s="1">
-        <f t="shared" si="0"/>
-        <v>7.1999999999999993</v>
+        <v>2.4</v>
       </c>
       <c r="C29" s="1">
-        <f t="shared" si="1"/>
-        <v>-4.1999999999999993</v>
+        <v>-1.4</v>
       </c>
       <c r="D29" s="2">
         <v>3.2301480484522194E-2</v>
@@ -1089,12 +1033,10 @@
         <v>29</v>
       </c>
       <c r="B30" s="1">
-        <f t="shared" si="0"/>
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C30" s="1">
-        <f t="shared" si="1"/>
-        <v>-6.3000000000000007</v>
+        <v>-2.1</v>
       </c>
       <c r="D30" s="2">
         <v>5.3835800807536999E-2</v>
@@ -1111,12 +1053,10 @@
         <v>30</v>
       </c>
       <c r="B31" s="1">
-        <f t="shared" si="0"/>
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C31" s="1">
-        <f t="shared" si="1"/>
-        <v>-4.1999999999999993</v>
+        <v>-1.4</v>
       </c>
       <c r="D31" s="2">
         <v>4.0376850605652742E-2</v>
@@ -1133,12 +1073,10 @@
         <v>31</v>
       </c>
       <c r="B32" s="1">
-        <f t="shared" si="0"/>
-        <v>12.600000000000001</v>
+        <v>4.2</v>
       </c>
       <c r="C32" s="1">
-        <f t="shared" si="1"/>
-        <v>-6</v>
+        <v>-2</v>
       </c>
       <c r="D32" s="2">
         <v>5.6527590847913846E-2</v>
@@ -1155,12 +1093,10 @@
         <v>32</v>
       </c>
       <c r="B33" s="1">
-        <f t="shared" si="0"/>
-        <v>3.5999999999999996</v>
+        <v>1.2</v>
       </c>
       <c r="C33" s="1">
-        <f t="shared" si="1"/>
-        <v>-3.9000000000000004</v>
+        <v>-1.3</v>
       </c>
       <c r="D33" s="2">
         <v>1.6150740242261097E-2</v>

--- a/data/OP1/case33_2/case33_2_operational_data.xlsx
+++ b/data/OP1/case33_2/case33_2_operational_data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/micaelsimoes/PycharmProjects/shared-resources-planning/data/OP1/case33_2/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/micaelsimoes/PycharmProjects/shared-resources-planning/data/CS7/case33_2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C57F9C9-A728-BF4B-8792-5B05B89F3AEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22A33D5E-48B4-484F-BD94-44F8DCA9BB97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1120" yWindow="620" windowWidth="50080" windowHeight="28180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1120" yWindow="620" windowWidth="29400" windowHeight="19120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Characterization" sheetId="2" r:id="rId1"/>
@@ -473,9 +473,11 @@
         <v>1</v>
       </c>
       <c r="B2" s="1">
+        <f>E2*1</f>
         <v>4</v>
       </c>
       <c r="C2" s="1">
+        <f>-F2*1</f>
         <v>-2.4</v>
       </c>
       <c r="D2" s="2">
@@ -485,7 +487,7 @@
         <v>4</v>
       </c>
       <c r="F2" s="4">
-        <v>-2.4</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
@@ -493,9 +495,11 @@
         <v>2</v>
       </c>
       <c r="B3" s="1">
+        <f t="shared" ref="B3:B33" si="0">E3*1</f>
         <v>3.5999999999999996</v>
       </c>
       <c r="C3" s="1">
+        <f t="shared" ref="C3:C33" si="1">-F3*1</f>
         <v>-1.6</v>
       </c>
       <c r="D3" s="2">
@@ -505,7 +509,7 @@
         <v>3.5999999999999996</v>
       </c>
       <c r="F3" s="4">
-        <v>-1.6</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
@@ -513,9 +517,11 @@
         <v>3</v>
       </c>
       <c r="B4" s="1">
+        <f t="shared" si="0"/>
         <v>4.8</v>
       </c>
       <c r="C4" s="1">
+        <f t="shared" si="1"/>
         <v>-3.2</v>
       </c>
       <c r="D4" s="2">
@@ -525,7 +531,7 @@
         <v>4.8</v>
       </c>
       <c r="F4" s="4">
-        <v>-3.2</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
@@ -533,9 +539,11 @@
         <v>4</v>
       </c>
       <c r="B5" s="1">
+        <f t="shared" si="0"/>
         <v>2.4</v>
       </c>
       <c r="C5" s="1">
+        <f t="shared" si="1"/>
         <v>-1.2</v>
       </c>
       <c r="D5" s="2">
@@ -545,7 +553,7 @@
         <v>2.4</v>
       </c>
       <c r="F5" s="4">
-        <v>-1.2</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
@@ -553,9 +561,11 @@
         <v>5</v>
       </c>
       <c r="B6" s="1">
+        <f t="shared" si="0"/>
         <v>2.4</v>
       </c>
       <c r="C6" s="1">
+        <f t="shared" si="1"/>
         <v>-0.8</v>
       </c>
       <c r="D6" s="2">
@@ -565,7 +575,7 @@
         <v>2.4</v>
       </c>
       <c r="F6" s="4">
-        <v>-0.8</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
@@ -573,19 +583,21 @@
         <v>6</v>
       </c>
       <c r="B7" s="1">
-        <v>6</v>
+        <f t="shared" si="0"/>
+        <v>8</v>
       </c>
       <c r="C7" s="1">
-        <v>-3</v>
+        <f t="shared" si="1"/>
+        <v>-4</v>
       </c>
       <c r="D7" s="2">
         <v>5.3835800807536999E-2</v>
       </c>
       <c r="E7" s="4">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F7" s="4">
-        <v>-3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
@@ -593,19 +605,21 @@
         <v>7</v>
       </c>
       <c r="B8" s="1">
-        <v>6</v>
+        <f t="shared" si="0"/>
+        <v>8</v>
       </c>
       <c r="C8" s="1">
-        <v>-3</v>
+        <f t="shared" si="1"/>
+        <v>-4</v>
       </c>
       <c r="D8" s="2">
         <v>5.3835800807536999E-2</v>
       </c>
       <c r="E8" s="4">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F8" s="4">
-        <v>-3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
@@ -613,9 +627,11 @@
         <v>8</v>
       </c>
       <c r="B9" s="1">
+        <f t="shared" si="0"/>
         <v>2.4</v>
       </c>
       <c r="C9" s="1">
+        <f t="shared" si="1"/>
         <v>-0.8</v>
       </c>
       <c r="D9" s="2">
@@ -625,7 +641,7 @@
         <v>2.4</v>
       </c>
       <c r="F9" s="4">
-        <v>-0.8</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
@@ -633,9 +649,11 @@
         <v>9</v>
       </c>
       <c r="B10" s="1">
+        <f t="shared" si="0"/>
         <v>2.4</v>
       </c>
       <c r="C10" s="1">
+        <f t="shared" si="1"/>
         <v>-0.8</v>
       </c>
       <c r="D10" s="2">
@@ -645,7 +663,7 @@
         <v>2.4</v>
       </c>
       <c r="F10" s="4">
-        <v>-0.8</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
@@ -653,9 +671,11 @@
         <v>10</v>
       </c>
       <c r="B11" s="1">
+        <f t="shared" si="0"/>
         <v>1.7999999999999998</v>
       </c>
       <c r="C11" s="1">
+        <f t="shared" si="1"/>
         <v>-1.2</v>
       </c>
       <c r="D11" s="2">
@@ -665,7 +685,7 @@
         <v>1.7999999999999998</v>
       </c>
       <c r="F11" s="4">
-        <v>-1.2</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
@@ -673,9 +693,11 @@
         <v>11</v>
       </c>
       <c r="B12" s="1">
+        <f t="shared" si="0"/>
         <v>2.4</v>
       </c>
       <c r="C12" s="1">
+        <f t="shared" si="1"/>
         <v>-1.4000000000000001</v>
       </c>
       <c r="D12" s="2">
@@ -685,7 +707,7 @@
         <v>2.4</v>
       </c>
       <c r="F12" s="4">
-        <v>-1.4000000000000001</v>
+        <v>1.4000000000000001</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
@@ -693,9 +715,11 @@
         <v>12</v>
       </c>
       <c r="B13" s="1">
+        <f t="shared" si="0"/>
         <v>2.4</v>
       </c>
       <c r="C13" s="1">
+        <f t="shared" si="1"/>
         <v>-1.4000000000000001</v>
       </c>
       <c r="D13" s="2">
@@ -705,7 +729,7 @@
         <v>2.4</v>
       </c>
       <c r="F13" s="4">
-        <v>-1.4000000000000001</v>
+        <v>1.4000000000000001</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
@@ -713,9 +737,11 @@
         <v>13</v>
       </c>
       <c r="B14" s="1">
+        <f t="shared" si="0"/>
         <v>4.8</v>
       </c>
       <c r="C14" s="1">
+        <f t="shared" si="1"/>
         <v>-3.2</v>
       </c>
       <c r="D14" s="2">
@@ -725,7 +751,7 @@
         <v>4.8</v>
       </c>
       <c r="F14" s="4">
-        <v>-3.2</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
@@ -733,9 +759,11 @@
         <v>14</v>
       </c>
       <c r="B15" s="1">
+        <f t="shared" si="0"/>
         <v>2.4</v>
       </c>
       <c r="C15" s="1">
+        <f t="shared" si="1"/>
         <v>-0.4</v>
       </c>
       <c r="D15" s="2">
@@ -745,7 +773,7 @@
         <v>2.4</v>
       </c>
       <c r="F15" s="4">
-        <v>-0.4</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.2">
@@ -753,9 +781,11 @@
         <v>15</v>
       </c>
       <c r="B16" s="1">
+        <f t="shared" si="0"/>
         <v>2.4</v>
       </c>
       <c r="C16" s="1">
+        <f t="shared" si="1"/>
         <v>-0.8</v>
       </c>
       <c r="D16" s="2">
@@ -765,7 +795,7 @@
         <v>2.4</v>
       </c>
       <c r="F16" s="4">
-        <v>-0.8</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.2">
@@ -773,9 +803,11 @@
         <v>16</v>
       </c>
       <c r="B17" s="1">
+        <f t="shared" si="0"/>
         <v>2.4</v>
       </c>
       <c r="C17" s="1">
+        <f t="shared" si="1"/>
         <v>-0.8</v>
       </c>
       <c r="D17" s="2">
@@ -785,7 +817,7 @@
         <v>2.4</v>
       </c>
       <c r="F17" s="4">
-        <v>-0.8</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.2">
@@ -793,9 +825,11 @@
         <v>17</v>
       </c>
       <c r="B18" s="1">
+        <f t="shared" si="0"/>
         <v>3.5999999999999996</v>
       </c>
       <c r="C18" s="1">
+        <f t="shared" si="1"/>
         <v>-1.6</v>
       </c>
       <c r="D18" s="2">
@@ -805,7 +839,7 @@
         <v>3.5999999999999996</v>
       </c>
       <c r="F18" s="4">
-        <v>-1.6</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.2">
@@ -813,9 +847,11 @@
         <v>18</v>
       </c>
       <c r="B19" s="1">
+        <f t="shared" si="0"/>
         <v>3.5999999999999996</v>
       </c>
       <c r="C19" s="1">
+        <f t="shared" si="1"/>
         <v>-1.6</v>
       </c>
       <c r="D19" s="2">
@@ -825,7 +861,7 @@
         <v>3.5999999999999996</v>
       </c>
       <c r="F19" s="4">
-        <v>-1.6</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.2">
@@ -833,9 +869,11 @@
         <v>19</v>
       </c>
       <c r="B20" s="1">
+        <f t="shared" si="0"/>
         <v>3.5999999999999996</v>
       </c>
       <c r="C20" s="1">
+        <f t="shared" si="1"/>
         <v>-1.6</v>
       </c>
       <c r="D20" s="2">
@@ -845,7 +883,7 @@
         <v>3.5999999999999996</v>
       </c>
       <c r="F20" s="4">
-        <v>-1.6</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.2">
@@ -853,9 +891,11 @@
         <v>20</v>
       </c>
       <c r="B21" s="1">
+        <f t="shared" si="0"/>
         <v>3.5999999999999996</v>
       </c>
       <c r="C21" s="1">
+        <f t="shared" si="1"/>
         <v>-1.6</v>
       </c>
       <c r="D21" s="2">
@@ -865,7 +905,7 @@
         <v>3.5999999999999996</v>
       </c>
       <c r="F21" s="4">
-        <v>-1.6</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.2">
@@ -873,9 +913,11 @@
         <v>21</v>
       </c>
       <c r="B22" s="1">
+        <f t="shared" si="0"/>
         <v>3.5999999999999996</v>
       </c>
       <c r="C22" s="1">
+        <f t="shared" si="1"/>
         <v>-1.6</v>
       </c>
       <c r="D22" s="2">
@@ -885,7 +927,7 @@
         <v>3.5999999999999996</v>
       </c>
       <c r="F22" s="4">
-        <v>-1.6</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.2">
@@ -893,9 +935,11 @@
         <v>22</v>
       </c>
       <c r="B23" s="1">
+        <f t="shared" si="0"/>
         <v>3.5999999999999996</v>
       </c>
       <c r="C23" s="1">
+        <f t="shared" si="1"/>
         <v>-2</v>
       </c>
       <c r="D23" s="2">
@@ -905,7 +949,7 @@
         <v>3.5999999999999996</v>
       </c>
       <c r="F23" s="4">
-        <v>-2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.2">
@@ -913,19 +957,21 @@
         <v>23</v>
       </c>
       <c r="B24" s="1">
-        <v>9</v>
+        <f t="shared" si="0"/>
+        <v>16.8</v>
       </c>
       <c r="C24" s="1">
-        <v>-4</v>
+        <f t="shared" si="1"/>
+        <v>-8</v>
       </c>
       <c r="D24" s="2">
         <v>0.11305518169582769</v>
       </c>
       <c r="E24" s="4">
-        <v>9</v>
+        <v>16.8</v>
       </c>
       <c r="F24" s="4">
-        <v>-4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.2">
@@ -933,19 +979,21 @@
         <v>24</v>
       </c>
       <c r="B25" s="1">
-        <v>9</v>
+        <f t="shared" si="0"/>
+        <v>16.8</v>
       </c>
       <c r="C25" s="1">
-        <v>-4</v>
+        <f t="shared" si="1"/>
+        <v>-8</v>
       </c>
       <c r="D25" s="2">
         <v>0.11305518169582769</v>
       </c>
       <c r="E25" s="4">
-        <v>9</v>
+        <v>16.8</v>
       </c>
       <c r="F25" s="4">
-        <v>-4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.2">
@@ -953,19 +1001,21 @@
         <v>25</v>
       </c>
       <c r="B26" s="1">
-        <v>1.2</v>
+        <f t="shared" si="0"/>
+        <v>2.4</v>
       </c>
       <c r="C26" s="1">
-        <v>-0.5</v>
+        <f t="shared" si="1"/>
+        <v>-1</v>
       </c>
       <c r="D26" s="2">
         <v>1.6150740242261097E-2</v>
       </c>
       <c r="E26" s="4">
-        <v>1.2</v>
+        <v>2.4</v>
       </c>
       <c r="F26" s="4">
-        <v>-0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.2">
@@ -973,19 +1023,21 @@
         <v>26</v>
       </c>
       <c r="B27" s="1">
-        <v>1.2</v>
+        <f t="shared" si="0"/>
+        <v>2.4</v>
       </c>
       <c r="C27" s="1">
-        <v>-0.5</v>
+        <f t="shared" si="1"/>
+        <v>-1</v>
       </c>
       <c r="D27" s="2">
         <v>1.6150740242261097E-2</v>
       </c>
       <c r="E27" s="4">
-        <v>1.2</v>
+        <v>2.4</v>
       </c>
       <c r="F27" s="4">
-        <v>-0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.2">
@@ -993,19 +1045,21 @@
         <v>27</v>
       </c>
       <c r="B28" s="1">
-        <v>1.2</v>
+        <f t="shared" si="0"/>
+        <v>2.4</v>
       </c>
       <c r="C28" s="1">
-        <v>-0.4</v>
+        <f t="shared" si="1"/>
+        <v>-0.8</v>
       </c>
       <c r="D28" s="2">
         <v>1.6150740242261097E-2</v>
       </c>
       <c r="E28" s="4">
-        <v>1.2</v>
+        <v>2.4</v>
       </c>
       <c r="F28" s="4">
-        <v>-0.4</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.2">
@@ -1013,19 +1067,21 @@
         <v>28</v>
       </c>
       <c r="B29" s="1">
-        <v>2.4</v>
+        <f t="shared" si="0"/>
+        <v>4.8</v>
       </c>
       <c r="C29" s="1">
-        <v>-1.4</v>
+        <f t="shared" si="1"/>
+        <v>-2.8000000000000003</v>
       </c>
       <c r="D29" s="2">
         <v>3.2301480484522194E-2</v>
       </c>
       <c r="E29" s="4">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="F29" s="4">
-        <v>-1.4</v>
+        <v>2.8000000000000003</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.2">
@@ -1033,19 +1089,21 @@
         <v>29</v>
       </c>
       <c r="B30" s="1">
-        <v>4</v>
+        <f t="shared" si="0"/>
+        <v>8</v>
       </c>
       <c r="C30" s="1">
-        <v>-2.1</v>
+        <f t="shared" si="1"/>
+        <v>-24</v>
       </c>
       <c r="D30" s="2">
         <v>5.3835800807536999E-2</v>
       </c>
       <c r="E30" s="4">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F30" s="4">
-        <v>-2.1</v>
+        <v>24</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.2">
@@ -1053,19 +1111,21 @@
         <v>30</v>
       </c>
       <c r="B31" s="1">
-        <v>3</v>
+        <f t="shared" si="0"/>
+        <v>6</v>
       </c>
       <c r="C31" s="1">
-        <v>-1.4</v>
+        <f t="shared" si="1"/>
+        <v>-2.8000000000000003</v>
       </c>
       <c r="D31" s="2">
         <v>4.0376850605652742E-2</v>
       </c>
       <c r="E31" s="4">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F31" s="4">
-        <v>-1.4</v>
+        <v>2.8000000000000003</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.2">
@@ -1073,19 +1133,21 @@
         <v>31</v>
       </c>
       <c r="B32" s="1">
-        <v>4.2</v>
+        <f t="shared" si="0"/>
+        <v>8.4</v>
       </c>
       <c r="C32" s="1">
-        <v>-2</v>
+        <f t="shared" si="1"/>
+        <v>-4</v>
       </c>
       <c r="D32" s="2">
         <v>5.6527590847913846E-2</v>
       </c>
       <c r="E32" s="4">
-        <v>4.2</v>
+        <v>8.4</v>
       </c>
       <c r="F32" s="4">
-        <v>-2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.2">
@@ -1093,19 +1155,21 @@
         <v>32</v>
       </c>
       <c r="B33" s="1">
-        <v>1.2</v>
+        <f t="shared" si="0"/>
+        <v>2.4</v>
       </c>
       <c r="C33" s="1">
-        <v>-1.3</v>
+        <f t="shared" si="1"/>
+        <v>-1.6</v>
       </c>
       <c r="D33" s="2">
         <v>1.6150740242261097E-2</v>
       </c>
       <c r="E33" s="4">
-        <v>1.2</v>
+        <v>2.4</v>
       </c>
       <c r="F33" s="4">
-        <v>-1.3</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.2">
@@ -69368,76 +69432,76 @@
         <v>1</v>
       </c>
       <c r="D2" s="1">
-        <v>9.8328000000000024</v>
+        <v>4.9164000000000012</v>
       </c>
       <c r="E2" s="1">
-        <v>10.160800000000002</v>
+        <v>5.0804000000000009</v>
       </c>
       <c r="F2" s="1">
-        <v>9.0983999999999998</v>
+        <v>4.5491999999999999</v>
       </c>
       <c r="G2" s="1">
-        <v>8.6239999999999988</v>
+        <v>4.3119999999999994</v>
       </c>
       <c r="H2" s="1">
-        <v>7.0656000000000008</v>
+        <v>3.5328000000000004</v>
       </c>
       <c r="I2" s="1">
-        <v>5.9968000000000012</v>
+        <v>2.9984000000000006</v>
       </c>
       <c r="J2" s="1">
-        <v>7.3336000000000006</v>
+        <v>3.6668000000000003</v>
       </c>
       <c r="K2" s="1">
-        <v>1.2736000000000001</v>
+        <v>0.63680000000000003</v>
       </c>
       <c r="L2" s="1">
-        <v>1.1200000000000001</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="M2" s="1">
-        <v>1.6327999999999998</v>
+        <v>0.8163999999999999</v>
       </c>
       <c r="N2" s="1">
-        <v>0.96160000000000012</v>
+        <v>0.48080000000000006</v>
       </c>
       <c r="O2" s="1">
-        <v>1.2016</v>
+        <v>0.6008</v>
       </c>
       <c r="P2" s="1">
-        <v>1.9144000000000005</v>
+        <v>0.95720000000000027</v>
       </c>
       <c r="Q2" s="1">
-        <v>3.5272000000000006</v>
+        <v>1.7636000000000003</v>
       </c>
       <c r="R2" s="1">
-        <v>3.7631999999999999</v>
+        <v>1.8815999999999999</v>
       </c>
       <c r="S2" s="1">
-        <v>3.7007999999999996</v>
+        <v>1.8503999999999998</v>
       </c>
       <c r="T2" s="1">
-        <v>2.0760000000000001</v>
+        <v>1.038</v>
       </c>
       <c r="U2" s="1">
-        <v>4.2287999999999997</v>
+        <v>2.1143999999999998</v>
       </c>
       <c r="V2" s="1">
-        <v>2.4816000000000003</v>
+        <v>1.2408000000000001</v>
       </c>
       <c r="W2" s="1">
-        <v>1.7447999999999997</v>
+        <v>0.87239999999999984</v>
       </c>
       <c r="X2" s="1">
-        <v>2.6496000000000004</v>
+        <v>1.3248000000000002</v>
       </c>
       <c r="Y2" s="1">
-        <v>1.6376000000000002</v>
+        <v>0.81880000000000008</v>
       </c>
       <c r="Z2" s="1">
-        <v>7.474400000000001</v>
+        <v>3.7372000000000005</v>
       </c>
       <c r="AA2" s="1">
-        <v>9.0104000000000006</v>
+        <v>4.5052000000000003</v>
       </c>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.2">
@@ -69451,76 +69515,76 @@
         <v>1</v>
       </c>
       <c r="D3" s="1">
-        <v>-22.200000000000003</v>
+        <v>-11.100000000000001</v>
       </c>
       <c r="E3" s="1">
-        <v>-23.7392</v>
+        <v>-11.8696</v>
       </c>
       <c r="F3" s="1">
-        <v>-26.699200000000005</v>
+        <v>-13.349600000000002</v>
       </c>
       <c r="G3" s="1">
-        <v>-28.800800000000002</v>
+        <v>-14.400400000000001</v>
       </c>
       <c r="H3" s="1">
-        <v>-30.784000000000002</v>
+        <v>-15.392000000000001</v>
       </c>
       <c r="I3" s="1">
-        <v>-33.596000000000004</v>
+        <v>-16.798000000000002</v>
       </c>
       <c r="J3" s="1">
-        <v>-32.056800000000003</v>
+        <v>-16.028400000000001</v>
       </c>
       <c r="K3" s="1">
-        <v>-35.959519999999998</v>
+        <v>-17.979759999999999</v>
       </c>
       <c r="L3" s="1">
-        <v>-32.614719999999991</v>
+        <v>-16.307359999999996</v>
       </c>
       <c r="M3" s="1">
-        <v>-47.905679999999997</v>
+        <v>-23.952839999999998</v>
       </c>
       <c r="N3" s="1">
-        <v>-47.41472000000001</v>
+        <v>-23.707360000000005</v>
       </c>
       <c r="O3" s="1">
-        <v>-43.344320000000003</v>
+        <v>-21.672160000000002</v>
       </c>
       <c r="P3" s="1">
-        <v>-41.549120000000002</v>
+        <v>-20.774560000000001</v>
       </c>
       <c r="Q3" s="1">
-        <v>-40.114960000000004</v>
+        <v>-20.057480000000002</v>
       </c>
       <c r="R3" s="1">
-        <v>-37.811360000000008</v>
+        <v>-18.905680000000004</v>
       </c>
       <c r="S3" s="1">
-        <v>-34.408479999999997</v>
+        <v>-17.204239999999999</v>
       </c>
       <c r="T3" s="1">
-        <v>-32.173920000000003</v>
+        <v>-16.086960000000001</v>
       </c>
       <c r="U3" s="1">
-        <v>-28.792480000000005</v>
+        <v>-14.396240000000002</v>
       </c>
       <c r="V3" s="1">
-        <v>-18.27544</v>
+        <v>-9.1377199999999998</v>
       </c>
       <c r="W3" s="1">
-        <v>-20.452959999999997</v>
+        <v>-10.226479999999999</v>
       </c>
       <c r="X3" s="1">
-        <v>-21.619679999999999</v>
+        <v>-10.809839999999999</v>
       </c>
       <c r="Y3" s="1">
-        <v>-23.210799999999999</v>
+        <v>-11.605399999999999</v>
       </c>
       <c r="Z3" s="1">
-        <v>-18.440800000000003</v>
+        <v>-9.2204000000000015</v>
       </c>
       <c r="AA3" s="1">
-        <v>-19.595200000000002</v>
+        <v>-9.797600000000001</v>
       </c>
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.2">
@@ -69534,76 +69598,76 @@
         <v>1</v>
       </c>
       <c r="D4" s="1">
-        <v>21.387119999999999</v>
+        <v>10.69356</v>
       </c>
       <c r="E4" s="1">
-        <v>22.880639999999993</v>
+        <v>11.440319999999996</v>
       </c>
       <c r="F4" s="1">
-        <v>25.65448</v>
+        <v>12.82724</v>
       </c>
       <c r="G4" s="1">
-        <v>27.604880000000005</v>
+        <v>13.802440000000002</v>
       </c>
       <c r="H4" s="1">
-        <v>29.382799999999996</v>
+        <v>14.691399999999998</v>
       </c>
       <c r="I4" s="1">
-        <v>32.084000000000003</v>
+        <v>16.042000000000002</v>
       </c>
       <c r="J4" s="1">
-        <v>30.587999999999997</v>
+        <v>15.293999999999999</v>
       </c>
       <c r="K4" s="1">
-        <v>34.518320000000003</v>
+        <v>17.259160000000001</v>
       </c>
       <c r="L4" s="1">
-        <v>31.618320000000004</v>
+        <v>15.809160000000002</v>
       </c>
       <c r="M4" s="1">
-        <v>36.078879999999998</v>
+        <v>18.039439999999999</v>
       </c>
       <c r="N4" s="1">
-        <v>36.362960000000001</v>
+        <v>18.181480000000001</v>
       </c>
       <c r="O4" s="1">
-        <v>34.039279999999998</v>
+        <v>17.019639999999999</v>
       </c>
       <c r="P4" s="1">
-        <v>32.892000000000003</v>
+        <v>16.446000000000002</v>
       </c>
       <c r="Q4" s="1">
-        <v>32.046559999999999</v>
+        <v>16.02328</v>
       </c>
       <c r="R4" s="1">
-        <v>30.032640000000008</v>
+        <v>15.016320000000004</v>
       </c>
       <c r="S4" s="1">
-        <v>27.342960000000005</v>
+        <v>13.671480000000003</v>
       </c>
       <c r="T4" s="1">
-        <v>25.472079999999995</v>
+        <v>12.736039999999997</v>
       </c>
       <c r="U4" s="1">
-        <v>22.76576</v>
+        <v>11.38288</v>
       </c>
       <c r="V4" s="1">
-        <v>17.818719999999999</v>
+        <v>8.9093599999999995</v>
       </c>
       <c r="W4" s="1">
-        <v>19.944320000000001</v>
+        <v>9.9721600000000006</v>
       </c>
       <c r="X4" s="1">
-        <v>21.193120000000004</v>
+        <v>10.596560000000002</v>
       </c>
       <c r="Y4" s="1">
-        <v>22.829120000000003</v>
+        <v>11.414560000000002</v>
       </c>
       <c r="Z4" s="1">
-        <v>17.763999999999999</v>
+        <v>8.8819999999999997</v>
       </c>
       <c r="AA4" s="1">
-        <v>18.889600000000005</v>
+        <v>9.4448000000000025</v>
       </c>
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.2">
@@ -69617,76 +69681,76 @@
         <v>2</v>
       </c>
       <c r="D5" s="1">
-        <v>9.7344720000000038</v>
+        <v>4.8672360000000019</v>
       </c>
       <c r="E5" s="1">
-        <v>10.160800000000002</v>
+        <v>5.0804000000000009</v>
       </c>
       <c r="F5" s="1">
-        <v>9.4623360000000005</v>
+        <v>4.7311680000000003</v>
       </c>
       <c r="G5" s="1">
-        <v>8.796479999999999</v>
+        <v>4.3982399999999995</v>
       </c>
       <c r="H5" s="1">
-        <v>6.9242880000000007</v>
+        <v>3.4621440000000003</v>
       </c>
       <c r="I5" s="1">
-        <v>5.7569280000000012</v>
+        <v>2.8784640000000006</v>
       </c>
       <c r="J5" s="1">
-        <v>7.4069360000000009</v>
+        <v>3.7034680000000004</v>
       </c>
       <c r="K5" s="1">
-        <v>1.2481280000000001</v>
+        <v>0.62406400000000006</v>
       </c>
       <c r="L5" s="1">
-        <v>1.1648000000000003</v>
+        <v>0.58240000000000014</v>
       </c>
       <c r="M5" s="1">
-        <v>1.71444</v>
+        <v>0.85721999999999998</v>
       </c>
       <c r="N5" s="1">
-        <v>0.94236800000000021</v>
+        <v>0.4711840000000001</v>
       </c>
       <c r="O5" s="1">
-        <v>1.213616</v>
+        <v>0.60680800000000001</v>
       </c>
       <c r="P5" s="1">
-        <v>1.9144000000000005</v>
+        <v>0.95720000000000027</v>
       </c>
       <c r="Q5" s="1">
-        <v>3.7035600000000004</v>
+        <v>1.8517800000000002</v>
       </c>
       <c r="R5" s="1">
-        <v>3.7631999999999999</v>
+        <v>1.8815999999999999</v>
       </c>
       <c r="S5" s="1">
-        <v>3.7748159999999995</v>
+        <v>1.8874079999999998</v>
       </c>
       <c r="T5" s="1">
-        <v>1.9722</v>
+        <v>0.98609999999999998</v>
       </c>
       <c r="U5" s="1">
-        <v>4.4402399999999993</v>
+        <v>2.2201199999999996</v>
       </c>
       <c r="V5" s="1">
-        <v>2.5064160000000002</v>
+        <v>1.2532080000000001</v>
       </c>
       <c r="W5" s="1">
-        <v>1.7971439999999996</v>
+        <v>0.89857199999999982</v>
       </c>
       <c r="X5" s="1">
-        <v>2.6760960000000007</v>
+        <v>1.3380480000000003</v>
       </c>
       <c r="Y5" s="1">
-        <v>1.55572</v>
+        <v>0.77786</v>
       </c>
       <c r="Z5" s="1">
-        <v>7.6238880000000009</v>
+        <v>3.8119440000000004</v>
       </c>
       <c r="AA5" s="1">
-        <v>9.0104000000000006</v>
+        <v>4.5052000000000003</v>
       </c>
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.2">
@@ -69700,76 +69764,76 @@
         <v>2</v>
       </c>
       <c r="D6" s="1">
-        <v>-22.200000000000003</v>
+        <v>-11.100000000000001</v>
       </c>
       <c r="E6" s="1">
-        <v>-23.501808</v>
+        <v>-11.750904</v>
       </c>
       <c r="F6" s="1">
-        <v>-26.699200000000005</v>
+        <v>-13.349600000000002</v>
       </c>
       <c r="G6" s="1">
-        <v>-27.360759999999999</v>
+        <v>-13.68038</v>
       </c>
       <c r="H6" s="1">
-        <v>-29.860480000000003</v>
+        <v>-14.930240000000001</v>
       </c>
       <c r="I6" s="1">
-        <v>-32.252160000000003</v>
+        <v>-16.126080000000002</v>
       </c>
       <c r="J6" s="1">
-        <v>-32.377368000000004</v>
+        <v>-16.188684000000002</v>
       </c>
       <c r="K6" s="1">
-        <v>-35.959519999999998</v>
+        <v>-17.979759999999999</v>
       </c>
       <c r="L6" s="1">
-        <v>-32.614719999999991</v>
+        <v>-16.307359999999996</v>
       </c>
       <c r="M6" s="1">
-        <v>-47.426623199999995</v>
+        <v>-23.713311599999997</v>
       </c>
       <c r="N6" s="1">
-        <v>-48.363014400000012</v>
+        <v>-24.181507200000006</v>
       </c>
       <c r="O6" s="1">
-        <v>-42.477433600000005</v>
+        <v>-21.238716800000002</v>
       </c>
       <c r="P6" s="1">
-        <v>-43.211084800000002</v>
+        <v>-21.605542400000001</v>
       </c>
       <c r="Q6" s="1">
-        <v>-39.7138104</v>
+        <v>-19.8569052</v>
       </c>
       <c r="R6" s="1">
-        <v>-39.32381440000001</v>
+        <v>-19.661907200000005</v>
       </c>
       <c r="S6" s="1">
-        <v>-34.408479999999997</v>
+        <v>-17.204239999999999</v>
       </c>
       <c r="T6" s="1">
-        <v>-31.530441600000003</v>
+        <v>-15.765220800000002</v>
       </c>
       <c r="U6" s="1">
-        <v>-27.640780800000002</v>
+        <v>-13.820390400000001</v>
       </c>
       <c r="V6" s="1">
-        <v>-18.27544</v>
+        <v>-9.1377199999999998</v>
       </c>
       <c r="W6" s="1">
-        <v>-20.248430399999997</v>
+        <v>-10.124215199999998</v>
       </c>
       <c r="X6" s="1">
-        <v>-21.187286399999998</v>
+        <v>-10.593643199999999</v>
       </c>
       <c r="Y6" s="1">
-        <v>-22.514475999999998</v>
+        <v>-11.257237999999999</v>
       </c>
       <c r="Z6" s="1">
-        <v>-19.178432000000001</v>
+        <v>-9.5892160000000004</v>
       </c>
       <c r="AA6" s="1">
-        <v>-18.811392000000001</v>
+        <v>-9.4056960000000007</v>
       </c>
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.2">
@@ -69783,76 +69847,76 @@
         <v>2</v>
       </c>
       <c r="D7" s="1">
-        <v>20.317764</v>
+        <v>10.158882</v>
       </c>
       <c r="E7" s="1">
-        <v>23.567059199999996</v>
+        <v>11.783529599999998</v>
       </c>
       <c r="F7" s="1">
-        <v>24.628300799999998</v>
+        <v>12.314150399999999</v>
       </c>
       <c r="G7" s="1">
-        <v>26.224636000000004</v>
+        <v>13.112318000000002</v>
       </c>
       <c r="H7" s="1">
-        <v>28.501315999999996</v>
+        <v>14.250657999999998</v>
       </c>
       <c r="I7" s="1">
-        <v>33.046520000000008</v>
+        <v>16.523260000000004</v>
       </c>
       <c r="J7" s="1">
-        <v>29.36448</v>
+        <v>14.68224</v>
       </c>
       <c r="K7" s="1">
-        <v>33.137587200000006</v>
+        <v>16.568793600000003</v>
       </c>
       <c r="L7" s="1">
-        <v>31.934503200000005</v>
+        <v>15.967251600000003</v>
       </c>
       <c r="M7" s="1">
-        <v>34.9965136</v>
+        <v>17.4982568</v>
       </c>
       <c r="N7" s="1">
-        <v>36.362960000000001</v>
+        <v>18.181480000000001</v>
       </c>
       <c r="O7" s="1">
-        <v>34.720065599999998</v>
+        <v>17.360032799999999</v>
       </c>
       <c r="P7" s="1">
-        <v>31.576320000000006</v>
+        <v>15.788160000000003</v>
       </c>
       <c r="Q7" s="1">
-        <v>32.687491199999997</v>
+        <v>16.343745599999998</v>
       </c>
       <c r="R7" s="1">
-        <v>31.534272000000009</v>
+        <v>15.767136000000004</v>
       </c>
       <c r="S7" s="1">
-        <v>28.163248800000005</v>
+        <v>14.081624400000003</v>
       </c>
       <c r="T7" s="1">
-        <v>24.707917599999995</v>
+        <v>12.353958799999997</v>
       </c>
       <c r="U7" s="1">
-        <v>23.676390399999999</v>
+        <v>11.838195199999999</v>
       </c>
       <c r="V7" s="1">
-        <v>18.709655999999999</v>
+        <v>9.3548279999999995</v>
       </c>
       <c r="W7" s="1">
-        <v>19.944320000000001</v>
+        <v>9.9721600000000006</v>
       </c>
       <c r="X7" s="1">
-        <v>20.133464000000004</v>
+        <v>10.066732000000002</v>
       </c>
       <c r="Y7" s="1">
-        <v>23.970576000000005</v>
+        <v>11.985288000000002</v>
       </c>
       <c r="Z7" s="1">
-        <v>17.586359999999999</v>
+        <v>8.7931799999999996</v>
       </c>
       <c r="AA7" s="1">
-        <v>18.889600000000005</v>
+        <v>9.4448000000000025</v>
       </c>
     </row>
     <row r="8" spans="1:27" x14ac:dyDescent="0.2">
@@ -69866,76 +69930,76 @@
         <v>3</v>
       </c>
       <c r="D8" s="1">
-        <v>9.5397825600000026</v>
+        <v>4.7698912800000013</v>
       </c>
       <c r="E8" s="1">
-        <v>10.364016000000001</v>
+        <v>5.1820080000000006</v>
       </c>
       <c r="F8" s="1">
-        <v>9.5569593600000005</v>
+        <v>4.7784796800000002</v>
       </c>
       <c r="G8" s="1">
-        <v>8.4446207999999992</v>
+        <v>4.2223103999999996</v>
       </c>
       <c r="H8" s="1">
-        <v>6.5780735999999997</v>
+        <v>3.2890367999999999</v>
       </c>
       <c r="I8" s="1">
-        <v>5.8144972800000012</v>
+        <v>2.9072486400000006</v>
       </c>
       <c r="J8" s="1">
-        <v>7.3328666400000007</v>
+        <v>3.6664333200000003</v>
       </c>
       <c r="K8" s="1">
-        <v>1.2980531200000001</v>
+        <v>0.64902656000000003</v>
       </c>
       <c r="L8" s="1">
-        <v>1.1648000000000003</v>
+        <v>0.58240000000000014</v>
       </c>
       <c r="M8" s="1">
-        <v>1.6287180000000001</v>
+        <v>0.81435900000000006</v>
       </c>
       <c r="N8" s="1">
-        <v>0.95179168000000014</v>
+        <v>0.47589584000000007</v>
       </c>
       <c r="O8" s="1">
-        <v>1.213616</v>
+        <v>0.60680800000000001</v>
       </c>
       <c r="P8" s="1">
-        <v>1.8952560000000005</v>
+        <v>0.94762800000000025</v>
       </c>
       <c r="Q8" s="1">
-        <v>3.5183820000000003</v>
+        <v>1.7591910000000002</v>
       </c>
       <c r="R8" s="1">
-        <v>3.6503039999999998</v>
+        <v>1.8251519999999999</v>
       </c>
       <c r="S8" s="1">
-        <v>3.6615715199999994</v>
+        <v>1.8307857599999997</v>
       </c>
       <c r="T8" s="1">
-        <v>1.9722</v>
+        <v>0.98609999999999998</v>
       </c>
       <c r="U8" s="1">
-        <v>4.3070327999999991</v>
+        <v>2.1535163999999996</v>
       </c>
       <c r="V8" s="1">
-        <v>2.45628768</v>
+        <v>1.22814384</v>
       </c>
       <c r="W8" s="1">
-        <v>1.8870011999999996</v>
+        <v>0.9435005999999998</v>
       </c>
       <c r="X8" s="1">
-        <v>2.6760960000000007</v>
+        <v>1.3380480000000003</v>
       </c>
       <c r="Y8" s="1">
-        <v>1.6179488</v>
+        <v>0.80897439999999998</v>
       </c>
       <c r="Z8" s="1">
-        <v>7.4714102400000009</v>
+        <v>3.7357051200000004</v>
       </c>
       <c r="AA8" s="1">
-        <v>8.6499839999999999</v>
+        <v>4.3249919999999999</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.2">
@@ -69949,76 +70013,76 @@
         <v>3</v>
       </c>
       <c r="D9" s="1">
-        <v>-21.090000000000003</v>
+        <v>-10.545000000000002</v>
       </c>
       <c r="E9" s="1">
-        <v>-23.501808</v>
+        <v>-11.750904</v>
       </c>
       <c r="F9" s="1">
-        <v>-25.364240000000006</v>
+        <v>-12.682120000000003</v>
       </c>
       <c r="G9" s="1">
-        <v>-27.360759999999999</v>
+        <v>-13.68038</v>
       </c>
       <c r="H9" s="1">
-        <v>-31.054899200000005</v>
+        <v>-15.527449600000002</v>
       </c>
       <c r="I9" s="1">
-        <v>-31.607116800000004</v>
+        <v>-15.803558400000002</v>
       </c>
       <c r="J9" s="1">
-        <v>-33.348689040000004</v>
+        <v>-16.674344520000002</v>
       </c>
       <c r="K9" s="1">
-        <v>-35.240329599999995</v>
+        <v>-17.620164799999998</v>
       </c>
       <c r="L9" s="1">
-        <v>-34.24545599999999</v>
+        <v>-17.122727999999995</v>
       </c>
       <c r="M9" s="1">
-        <v>-47.900889431999992</v>
+        <v>-23.950444715999996</v>
       </c>
       <c r="N9" s="1">
-        <v>-46.912123968000017</v>
+        <v>-23.456061984000009</v>
       </c>
       <c r="O9" s="1">
-        <v>-43.751756608000008</v>
+        <v>-21.875878304000004</v>
       </c>
       <c r="P9" s="1">
-        <v>-42.778973952000008</v>
+        <v>-21.389486976000004</v>
       </c>
       <c r="Q9" s="1">
-        <v>-41.699500919999998</v>
+        <v>-20.849750459999999</v>
       </c>
       <c r="R9" s="1">
-        <v>-38.930576256000009</v>
+        <v>-19.465288128000005</v>
       </c>
       <c r="S9" s="1">
-        <v>-34.408479999999997</v>
+        <v>-17.204239999999999</v>
       </c>
       <c r="T9" s="1">
-        <v>-31.215137184000003</v>
+        <v>-15.607568592000002</v>
       </c>
       <c r="U9" s="1">
-        <v>-28.746412032000002</v>
+        <v>-14.373206016000001</v>
       </c>
       <c r="V9" s="1">
-        <v>-18.823703200000001</v>
+        <v>-9.4118516000000003</v>
       </c>
       <c r="W9" s="1">
-        <v>-20.045946095999994</v>
+        <v>-10.022973047999997</v>
       </c>
       <c r="X9" s="1">
-        <v>-21.187286399999998</v>
+        <v>-10.593643199999999</v>
       </c>
       <c r="Y9" s="1">
-        <v>-21.388752199999999</v>
+        <v>-10.694376099999999</v>
       </c>
       <c r="Z9" s="1">
-        <v>-18.986647680000001</v>
+        <v>-9.4933238400000004</v>
       </c>
       <c r="AA9" s="1">
-        <v>-19.751961600000001</v>
+        <v>-9.8759808000000007</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.2">
@@ -70032,76 +70096,76 @@
         <v>3</v>
       </c>
       <c r="D10" s="1">
-        <v>20.72411928</v>
+        <v>10.36205964</v>
       </c>
       <c r="E10" s="1">
-        <v>22.388706239999998</v>
+        <v>11.194353119999999</v>
       </c>
       <c r="F10" s="1">
-        <v>24.628300799999998</v>
+        <v>12.314150399999999</v>
       </c>
       <c r="G10" s="1">
-        <v>25.437896920000004</v>
+        <v>12.718948460000002</v>
       </c>
       <c r="H10" s="1">
-        <v>27.076250199999993</v>
+        <v>13.538125099999997</v>
       </c>
       <c r="I10" s="1">
-        <v>31.394194000000006</v>
+        <v>15.697097000000003</v>
       </c>
       <c r="J10" s="1">
-        <v>27.896255999999997</v>
+        <v>13.948127999999999</v>
       </c>
       <c r="K10" s="1">
-        <v>31.480707840000004</v>
+        <v>15.740353920000002</v>
       </c>
       <c r="L10" s="1">
-        <v>31.295813136000007</v>
+        <v>15.647906568000003</v>
       </c>
       <c r="M10" s="1">
-        <v>35.696443872000003</v>
+        <v>17.848221936000002</v>
       </c>
       <c r="N10" s="1">
-        <v>37.0902192</v>
+        <v>18.5451096</v>
       </c>
       <c r="O10" s="1">
-        <v>32.98406232</v>
+        <v>16.49203116</v>
       </c>
       <c r="P10" s="1">
-        <v>32.839372800000007</v>
+        <v>16.419686400000003</v>
       </c>
       <c r="Q10" s="1">
-        <v>33.014366111999998</v>
+        <v>16.507183055999999</v>
       </c>
       <c r="R10" s="1">
-        <v>32.164957440000009</v>
+        <v>16.082478720000005</v>
       </c>
       <c r="S10" s="1">
-        <v>27.036718848000007</v>
+        <v>13.518359424000003</v>
       </c>
       <c r="T10" s="1">
-        <v>25.696234303999994</v>
+        <v>12.848117151999997</v>
       </c>
       <c r="U10" s="1">
-        <v>22.729334783999999</v>
+        <v>11.364667391999999</v>
       </c>
       <c r="V10" s="1">
-        <v>19.645138799999998</v>
+        <v>9.822569399999999</v>
       </c>
       <c r="W10" s="1">
-        <v>20.143763200000002</v>
+        <v>10.071881600000001</v>
       </c>
       <c r="X10" s="1">
-        <v>20.938802560000003</v>
+        <v>10.469401280000001</v>
       </c>
       <c r="Y10" s="1">
-        <v>24.689693280000007</v>
+        <v>12.344846640000004</v>
       </c>
       <c r="Z10" s="1">
-        <v>17.762223599999999</v>
+        <v>8.8811117999999993</v>
       </c>
       <c r="AA10" s="1">
-        <v>19.834080000000007</v>
+        <v>9.9170400000000036</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.2">
@@ -70115,76 +70179,76 @@
         <v>1</v>
       </c>
       <c r="D11" s="1">
-        <v>9.3411600000000021</v>
+        <v>4.6705800000000011</v>
       </c>
       <c r="E11" s="1">
-        <v>9.6527600000000007</v>
+        <v>4.8263800000000003</v>
       </c>
       <c r="F11" s="1">
-        <v>8.6434800000000003</v>
+        <v>4.3217400000000001</v>
       </c>
       <c r="G11" s="1">
-        <v>8.1927999999999983</v>
+        <v>4.0963999999999992</v>
       </c>
       <c r="H11" s="1">
-        <v>6.7123200000000001</v>
+        <v>3.35616</v>
       </c>
       <c r="I11" s="1">
-        <v>5.6969600000000007</v>
+        <v>2.8484800000000003</v>
       </c>
       <c r="J11" s="1">
-        <v>6.96692</v>
+        <v>3.48346</v>
       </c>
       <c r="K11" s="1">
-        <v>1.2099200000000001</v>
+        <v>0.60496000000000005</v>
       </c>
       <c r="L11" s="1">
-        <v>1.0640000000000001</v>
+        <v>0.53200000000000003</v>
       </c>
       <c r="M11" s="1">
-        <v>1.5511599999999997</v>
+        <v>0.77557999999999983</v>
       </c>
       <c r="N11" s="1">
-        <v>0.91352000000000011</v>
+        <v>0.45676000000000005</v>
       </c>
       <c r="O11" s="1">
-        <v>1.1415199999999999</v>
+        <v>0.57075999999999993</v>
       </c>
       <c r="P11" s="1">
-        <v>1.8186800000000005</v>
+        <v>0.90934000000000026</v>
       </c>
       <c r="Q11" s="1">
-        <v>3.3508400000000003</v>
+        <v>1.6754200000000001</v>
       </c>
       <c r="R11" s="1">
-        <v>3.5750399999999996</v>
+        <v>1.7875199999999998</v>
       </c>
       <c r="S11" s="1">
-        <v>3.5157599999999993</v>
+        <v>1.7578799999999997</v>
       </c>
       <c r="T11" s="1">
-        <v>1.9722</v>
+        <v>0.98609999999999998</v>
       </c>
       <c r="U11" s="1">
-        <v>4.0173599999999992</v>
+        <v>2.0086799999999996</v>
       </c>
       <c r="V11" s="1">
-        <v>2.3575200000000001</v>
+        <v>1.17876</v>
       </c>
       <c r="W11" s="1">
-        <v>1.6575599999999997</v>
+        <v>0.82877999999999985</v>
       </c>
       <c r="X11" s="1">
-        <v>2.5171200000000002</v>
+        <v>1.2585600000000001</v>
       </c>
       <c r="Y11" s="1">
-        <v>1.55572</v>
+        <v>0.77786</v>
       </c>
       <c r="Z11" s="1">
-        <v>7.1006800000000005</v>
+        <v>3.5503400000000003</v>
       </c>
       <c r="AA11" s="1">
-        <v>8.5598799999999997</v>
+        <v>4.2799399999999999</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.2">
@@ -70198,76 +70262,76 @@
         <v>1</v>
       </c>
       <c r="D12" s="1">
-        <v>-21.933600000000006</v>
+        <v>-10.966800000000003</v>
       </c>
       <c r="E12" s="1">
-        <v>-23.501808</v>
+        <v>-11.750904</v>
       </c>
       <c r="F12" s="1">
-        <v>-24.096028000000004</v>
+        <v>-12.048014000000002</v>
       </c>
       <c r="G12" s="1">
-        <v>-27.360759999999999</v>
+        <v>-13.68038</v>
       </c>
       <c r="H12" s="1">
-        <v>-30.744350208000004</v>
+        <v>-15.372175104000002</v>
       </c>
       <c r="I12" s="1">
-        <v>-32.871401472000002</v>
+        <v>-16.435700736000001</v>
       </c>
       <c r="J12" s="1">
-        <v>-32.348228368800008</v>
+        <v>-16.174114184400004</v>
       </c>
       <c r="K12" s="1">
-        <v>-34.88792630399999</v>
+        <v>-17.443963151999995</v>
       </c>
       <c r="L12" s="1">
-        <v>-34.93036511999999</v>
+        <v>-17.465182559999995</v>
       </c>
       <c r="M12" s="1">
-        <v>-45.984853854719994</v>
+        <v>-22.992426927359997</v>
       </c>
       <c r="N12" s="1">
-        <v>-47.381245207680024</v>
+        <v>-23.690622603840012</v>
       </c>
       <c r="O12" s="1">
-        <v>-45.064309306240013</v>
+        <v>-22.532154653120006</v>
       </c>
       <c r="P12" s="1">
-        <v>-41.495604733440004</v>
+        <v>-20.747802366720002</v>
       </c>
       <c r="Q12" s="1">
-        <v>-39.614525873999995</v>
+        <v>-19.807262936999997</v>
       </c>
       <c r="R12" s="1">
-        <v>-38.54127049344001</v>
+        <v>-19.270635246720005</v>
       </c>
       <c r="S12" s="1">
-        <v>-34.408479999999997</v>
+        <v>-17.204239999999999</v>
       </c>
       <c r="T12" s="1">
-        <v>-32.463742671360002</v>
+        <v>-16.231871335680001</v>
       </c>
       <c r="U12" s="1">
-        <v>-28.17148379136</v>
+        <v>-14.08574189568</v>
       </c>
       <c r="V12" s="1">
-        <v>-18.070755072000001</v>
+        <v>-9.0353775360000004</v>
       </c>
       <c r="W12" s="1">
-        <v>-20.246405556959996</v>
+        <v>-10.123202778479998</v>
       </c>
       <c r="X12" s="1">
-        <v>-22.246650719999998</v>
+        <v>-11.123325359999999</v>
       </c>
       <c r="Y12" s="1">
-        <v>-21.388752199999999</v>
+        <v>-10.694376099999999</v>
       </c>
       <c r="Z12" s="1">
-        <v>-18.417048249600001</v>
+        <v>-9.2085241248000003</v>
       </c>
       <c r="AA12" s="1">
-        <v>-19.356922367999999</v>
+        <v>-9.6784611839999997</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.2">
@@ -70281,76 +70345,76 @@
         <v>1</v>
       </c>
       <c r="D13" s="1">
-        <v>19.687913315999999</v>
+        <v>9.8439566579999997</v>
       </c>
       <c r="E13" s="1">
-        <v>21.7170450528</v>
+        <v>10.8585225264</v>
       </c>
       <c r="F13" s="1">
-        <v>24.874583807999997</v>
+        <v>12.437291903999999</v>
       </c>
       <c r="G13" s="1">
-        <v>24.929138981600005</v>
+        <v>12.464569490800002</v>
       </c>
       <c r="H13" s="1">
-        <v>26.805487697999993</v>
+        <v>13.402743848999997</v>
       </c>
       <c r="I13" s="1">
-        <v>31.708135940000005</v>
+        <v>15.854067970000003</v>
       </c>
       <c r="J13" s="1">
-        <v>27.896255999999997</v>
+        <v>13.948127999999999</v>
       </c>
       <c r="K13" s="1">
-        <v>31.795514918400002</v>
+        <v>15.897757459200001</v>
       </c>
       <c r="L13" s="1">
-        <v>31.295813136000007</v>
+        <v>15.647906568000003</v>
       </c>
       <c r="M13" s="1">
-        <v>36.767337188160006</v>
+        <v>18.383668594080003</v>
       </c>
       <c r="N13" s="1">
-        <v>35.235708240000001</v>
+        <v>17.617854120000001</v>
       </c>
       <c r="O13" s="1">
-        <v>31.334859204000001</v>
+        <v>15.667429602</v>
       </c>
       <c r="P13" s="1">
-        <v>33.824553984000005</v>
+        <v>16.912276992000002</v>
       </c>
       <c r="Q13" s="1">
-        <v>32.68422245088</v>
+        <v>16.34211122544</v>
       </c>
       <c r="R13" s="1">
-        <v>31.521658291200012</v>
+        <v>15.760829145600006</v>
       </c>
       <c r="S13" s="1">
-        <v>25.684882905600006</v>
+        <v>12.842441452800003</v>
       </c>
       <c r="T13" s="1">
-        <v>26.981046019199994</v>
+        <v>13.490523009599997</v>
       </c>
       <c r="U13" s="1">
-        <v>23.638508175359998</v>
+        <v>11.819254087679999</v>
       </c>
       <c r="V13" s="1">
-        <v>19.841590187999998</v>
+        <v>9.9207950939999989</v>
       </c>
       <c r="W13" s="1">
-        <v>20.748076096000005</v>
+        <v>10.374038048000003</v>
       </c>
       <c r="X13" s="1">
-        <v>20.729414534400004</v>
+        <v>10.364707267200002</v>
       </c>
       <c r="Y13" s="1">
-        <v>25.677281011200009</v>
+        <v>12.838640505600004</v>
       </c>
       <c r="Z13" s="1">
-        <v>17.762223599999999</v>
+        <v>8.8811117999999993</v>
       </c>
       <c r="AA13" s="1">
-        <v>20.230761600000008</v>
+        <v>10.115380800000004</v>
       </c>
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.2">
@@ -70364,76 +70428,76 @@
         <v>2</v>
       </c>
       <c r="D14" s="1">
-        <v>9.7148064000000023</v>
+        <v>4.8574032000000011</v>
       </c>
       <c r="E14" s="1">
-        <v>9.7492876000000006</v>
+        <v>4.8746438000000003</v>
       </c>
       <c r="F14" s="1">
-        <v>8.6434800000000003</v>
+        <v>4.3217400000000001</v>
       </c>
       <c r="G14" s="1">
-        <v>8.3566559999999974</v>
+        <v>4.1783279999999987</v>
       </c>
       <c r="H14" s="1">
-        <v>6.7794432000000002</v>
+        <v>3.3897216000000001</v>
       </c>
       <c r="I14" s="1">
-        <v>5.5260512000000004</v>
+        <v>2.7630256000000002</v>
       </c>
       <c r="J14" s="1">
-        <v>7.2455967999999995</v>
+        <v>3.6227983999999998</v>
       </c>
       <c r="K14" s="1">
-        <v>1.1978208000000001</v>
+        <v>0.59891040000000006</v>
       </c>
       <c r="L14" s="1">
-        <v>1.0959200000000002</v>
+        <v>0.54796000000000011</v>
       </c>
       <c r="M14" s="1">
-        <v>1.5356483999999997</v>
+        <v>0.76782419999999985</v>
       </c>
       <c r="N14" s="1">
-        <v>0.94092560000000003</v>
+        <v>0.47046280000000001</v>
       </c>
       <c r="O14" s="1">
-        <v>1.084444</v>
+        <v>0.54222199999999998</v>
       </c>
       <c r="P14" s="1">
-        <v>1.8186800000000005</v>
+        <v>0.90934000000000026</v>
       </c>
       <c r="Q14" s="1">
-        <v>3.4513652000000001</v>
+        <v>1.7256826000000001</v>
       </c>
       <c r="R14" s="1">
-        <v>3.5035391999999996</v>
+        <v>1.7517695999999998</v>
       </c>
       <c r="S14" s="1">
-        <v>3.5860751999999989</v>
+        <v>1.7930375999999995</v>
       </c>
       <c r="T14" s="1">
-        <v>1.8933119999999999</v>
+        <v>0.94665599999999994</v>
       </c>
       <c r="U14" s="1">
-        <v>3.856665599999999</v>
+        <v>1.9283327999999995</v>
       </c>
       <c r="V14" s="1">
-        <v>2.2632192</v>
+        <v>1.1316096</v>
       </c>
       <c r="W14" s="1">
-        <v>1.7404379999999997</v>
+        <v>0.87021899999999985</v>
       </c>
       <c r="X14" s="1">
-        <v>2.4416064000000004</v>
+        <v>1.2208032000000002</v>
       </c>
       <c r="Y14" s="1">
-        <v>1.6023916</v>
+        <v>0.80119580000000001</v>
       </c>
       <c r="Z14" s="1">
-        <v>7.1716868000000007</v>
+        <v>3.5858434000000003</v>
       </c>
       <c r="AA14" s="1">
-        <v>8.3886824000000004</v>
+        <v>4.1943412000000002</v>
       </c>
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.2">
@@ -70447,76 +70511,76 @@
         <v>2</v>
       </c>
       <c r="D15" s="1">
-        <v>-22.152936000000004</v>
+        <v>-11.076468000000002</v>
       </c>
       <c r="E15" s="1">
-        <v>-23.031771840000001</v>
+        <v>-11.515885920000001</v>
       </c>
       <c r="F15" s="1">
-        <v>-23.132186880000003</v>
+        <v>-11.566093440000001</v>
       </c>
       <c r="G15" s="1">
-        <v>-26.266329599999999</v>
+        <v>-13.133164799999999</v>
       </c>
       <c r="H15" s="1">
-        <v>-31.974124216320007</v>
+        <v>-15.987062108160004</v>
       </c>
       <c r="I15" s="1">
-        <v>-32.213973442559997</v>
+        <v>-16.106986721279998</v>
       </c>
       <c r="J15" s="1">
-        <v>-31.701263801424005</v>
+        <v>-15.850631900712003</v>
       </c>
       <c r="K15" s="1">
-        <v>-33.492409251839987</v>
+        <v>-16.746204625919994</v>
       </c>
       <c r="L15" s="1">
-        <v>-35.279668771199994</v>
+        <v>-17.639834385599997</v>
       </c>
       <c r="M15" s="1">
-        <v>-45.525005316172795</v>
+        <v>-22.762502658086397</v>
       </c>
       <c r="N15" s="1">
-        <v>-49.276495015987223</v>
+        <v>-24.638247507993611</v>
       </c>
       <c r="O15" s="1">
-        <v>-44.163023120115213</v>
+        <v>-22.081511560057606</v>
       </c>
       <c r="P15" s="1">
-        <v>-41.080648686105604</v>
+        <v>-20.540324343052802</v>
       </c>
       <c r="Q15" s="1">
-        <v>-38.029944839039992</v>
+        <v>-19.014972419519996</v>
       </c>
       <c r="R15" s="1">
-        <v>-37.770445083571211</v>
+        <v>-18.885222541785605</v>
       </c>
       <c r="S15" s="1">
-        <v>-32.688055999999996</v>
+        <v>-16.344027999999998</v>
       </c>
       <c r="T15" s="1">
-        <v>-32.463742671360002</v>
+        <v>-16.231871335680001</v>
       </c>
       <c r="U15" s="1">
-        <v>-27.889768953446399</v>
+        <v>-13.9448844767232</v>
       </c>
       <c r="V15" s="1">
-        <v>-18.070755072000001</v>
+        <v>-9.0353775360000004</v>
       </c>
       <c r="W15" s="1">
-        <v>-20.651333668099195</v>
+        <v>-10.325666834049597</v>
       </c>
       <c r="X15" s="1">
-        <v>-22.469117227199998</v>
+        <v>-11.234558613599999</v>
       </c>
       <c r="Y15" s="1">
-        <v>-21.602639721999999</v>
+        <v>-10.801319861</v>
       </c>
       <c r="Z15" s="1">
-        <v>-17.680366319615999</v>
+        <v>-8.8401831598079994</v>
       </c>
       <c r="AA15" s="1">
-        <v>-20.131199262719999</v>
+        <v>-10.06559963136</v>
       </c>
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.2">
@@ -70530,76 +70594,76 @@
         <v>2</v>
       </c>
       <c r="D16" s="1">
-        <v>18.703517650199998</v>
+        <v>9.3517588250999992</v>
       </c>
       <c r="E16" s="1">
-        <v>20.848363250687999</v>
+        <v>10.424181625344</v>
       </c>
       <c r="F16" s="1">
-        <v>26.118312998399997</v>
+        <v>13.059156499199998</v>
       </c>
       <c r="G16" s="1">
-        <v>23.931973422336004</v>
+        <v>11.965986711168002</v>
       </c>
       <c r="H16" s="1">
-        <v>28.145762082899992</v>
+        <v>14.072881041449996</v>
       </c>
       <c r="I16" s="1">
-        <v>30.439810502400004</v>
+        <v>15.219905251200002</v>
       </c>
       <c r="J16" s="1">
-        <v>28.175218559999998</v>
+        <v>14.087609279999999</v>
       </c>
       <c r="K16" s="1">
-        <v>31.795514918400002</v>
+        <v>15.897757459200001</v>
       </c>
       <c r="L16" s="1">
-        <v>29.731022479200007</v>
+        <v>14.865511239600004</v>
       </c>
       <c r="M16" s="1">
-        <v>37.502683931923208</v>
+        <v>18.751341965961604</v>
       </c>
       <c r="N16" s="1">
-        <v>34.530994075199999</v>
+        <v>17.265497037599999</v>
       </c>
       <c r="O16" s="1">
-        <v>32.588253572159999</v>
+        <v>16.29412678608</v>
       </c>
       <c r="P16" s="1">
-        <v>32.471571824640002</v>
+        <v>16.235785912320001</v>
       </c>
       <c r="Q16" s="1">
-        <v>33.664749124406399</v>
+        <v>16.832374562203199</v>
       </c>
       <c r="R16" s="1">
-        <v>32.152091457024014</v>
+        <v>16.076045728512007</v>
       </c>
       <c r="S16" s="1">
-        <v>25.941731734656006</v>
+        <v>12.970865867328003</v>
       </c>
       <c r="T16" s="1">
-        <v>27.520666939583993</v>
+        <v>13.760333469791997</v>
       </c>
       <c r="U16" s="1">
-        <v>23.165738011852799</v>
+        <v>11.582869005926399</v>
       </c>
       <c r="V16" s="1">
-        <v>20.040006089879999</v>
+        <v>10.020003044939999</v>
       </c>
       <c r="W16" s="1">
-        <v>20.748076096000005</v>
+        <v>10.374038048000003</v>
       </c>
       <c r="X16" s="1">
-        <v>21.558591115776004</v>
+        <v>10.779295557888002</v>
       </c>
       <c r="Y16" s="1">
-        <v>26.190826631424009</v>
+        <v>13.095413315712005</v>
       </c>
       <c r="Z16" s="1">
-        <v>17.939845836</v>
+        <v>8.969922918</v>
       </c>
       <c r="AA16" s="1">
-        <v>19.421531136000009</v>
+        <v>9.7107655680000047</v>
       </c>
     </row>
     <row r="17" spans="1:27" x14ac:dyDescent="0.2">
@@ -70613,76 +70677,76 @@
         <v>3</v>
       </c>
       <c r="D17" s="1">
-        <v>9.2290660800000026</v>
+        <v>4.6145330400000013</v>
       </c>
       <c r="E17" s="1">
-        <v>10.139259104000001</v>
+        <v>5.0696295520000003</v>
       </c>
       <c r="F17" s="1">
-        <v>8.5570451999999992</v>
+        <v>4.2785225999999996</v>
       </c>
       <c r="G17" s="1">
-        <v>8.7744887999999968</v>
+        <v>4.3872443999999984</v>
       </c>
       <c r="H17" s="1">
-        <v>6.8472376319999997</v>
+        <v>3.4236188159999998</v>
       </c>
       <c r="I17" s="1">
-        <v>5.470790688000001</v>
+        <v>2.7353953440000005</v>
       </c>
       <c r="J17" s="1">
-        <v>7.028228895999999</v>
+        <v>3.5141144479999995</v>
       </c>
       <c r="K17" s="1">
-        <v>1.2097990080000001</v>
+        <v>0.60489950400000003</v>
       </c>
       <c r="L17" s="1">
-        <v>1.0959200000000002</v>
+        <v>0.54796000000000011</v>
       </c>
       <c r="M17" s="1">
-        <v>1.4895789479999997</v>
+        <v>0.74478947399999984</v>
       </c>
       <c r="N17" s="1">
-        <v>0.93151634400000005</v>
+        <v>0.46575817200000003</v>
       </c>
       <c r="O17" s="1">
-        <v>1.0735995599999999</v>
+        <v>0.53679977999999995</v>
       </c>
       <c r="P17" s="1">
-        <v>1.8186800000000005</v>
+        <v>0.90934000000000026</v>
       </c>
       <c r="Q17" s="1">
-        <v>3.4858788520000004</v>
+        <v>1.7429394260000002</v>
       </c>
       <c r="R17" s="1">
-        <v>3.6787161599999996</v>
+        <v>1.8393580799999998</v>
       </c>
       <c r="S17" s="1">
-        <v>3.4067714399999987</v>
+        <v>1.7033857199999993</v>
       </c>
       <c r="T17" s="1">
-        <v>1.83651264</v>
+        <v>0.91825632000000001</v>
       </c>
       <c r="U17" s="1">
-        <v>3.8180989439999991</v>
+        <v>1.9090494719999995</v>
       </c>
       <c r="V17" s="1">
-        <v>2.3084835839999998</v>
+        <v>1.1542417919999999</v>
       </c>
       <c r="W17" s="1">
-        <v>1.7404379999999997</v>
+        <v>0.87021899999999985</v>
       </c>
       <c r="X17" s="1">
-        <v>2.3927742720000005</v>
+        <v>1.1963871360000002</v>
       </c>
       <c r="Y17" s="1">
-        <v>1.6023916</v>
+        <v>0.80119580000000001</v>
       </c>
       <c r="Z17" s="1">
-        <v>6.8848193280000007</v>
+        <v>3.4424096640000004</v>
       </c>
       <c r="AA17" s="1">
-        <v>8.2209087519999997</v>
+        <v>4.1104543759999999</v>
       </c>
     </row>
     <row r="18" spans="1:27" x14ac:dyDescent="0.2">
@@ -70696,76 +70760,76 @@
         <v>3</v>
       </c>
       <c r="D18" s="1">
-        <v>-21.931406640000006</v>
+        <v>-10.965703320000003</v>
       </c>
       <c r="E18" s="1">
-        <v>-23.953042713600002</v>
+        <v>-11.976521356800001</v>
       </c>
       <c r="F18" s="1">
-        <v>-21.975577535999999</v>
+        <v>-10.987788768</v>
       </c>
       <c r="G18" s="1">
-        <v>-26.528992895999998</v>
+        <v>-13.264496447999999</v>
       </c>
       <c r="H18" s="1">
-        <v>-32.933347942809604</v>
+        <v>-16.466673971404802</v>
       </c>
       <c r="I18" s="1">
-        <v>-32.536113176985594</v>
+        <v>-16.268056588492797</v>
       </c>
       <c r="J18" s="1">
-        <v>-30.433213249367046</v>
+        <v>-15.216606624683523</v>
       </c>
       <c r="K18" s="1">
-        <v>-34.162257436876786</v>
+        <v>-17.081128718438393</v>
       </c>
       <c r="L18" s="1">
-        <v>-35.632465458911994</v>
+        <v>-17.816232729455997</v>
       </c>
       <c r="M18" s="1">
-        <v>-43.704005103525887</v>
+        <v>-21.852002551762943</v>
       </c>
       <c r="N18" s="1">
-        <v>-50.262024916306963</v>
+        <v>-25.131012458153482</v>
       </c>
       <c r="O18" s="1">
-        <v>-43.72139288891406</v>
+        <v>-21.86069644445703</v>
       </c>
       <c r="P18" s="1">
-        <v>-42.313068146688778</v>
+        <v>-21.156534073344389</v>
       </c>
       <c r="Q18" s="1">
-        <v>-39.170843184211186</v>
+        <v>-19.585421592105593</v>
       </c>
       <c r="R18" s="1">
-        <v>-39.658967337749772</v>
+        <v>-19.829483668874886</v>
       </c>
       <c r="S18" s="1">
-        <v>-33.995578239999993</v>
+        <v>-16.997789119999997</v>
       </c>
       <c r="T18" s="1">
-        <v>-31.489830391219201</v>
+        <v>-15.7449151956096</v>
       </c>
       <c r="U18" s="1">
-        <v>-28.726462022049791</v>
+        <v>-14.363231011024896</v>
       </c>
       <c r="V18" s="1">
-        <v>-17.167217318400002</v>
+        <v>-8.5836086592000012</v>
       </c>
       <c r="W18" s="1">
-        <v>-20.238306994737211</v>
+        <v>-10.119153497368606</v>
       </c>
       <c r="X18" s="1">
-        <v>-22.244426054927999</v>
+        <v>-11.122213027463999</v>
       </c>
       <c r="Y18" s="1">
-        <v>-20.95456053034</v>
+        <v>-10.47728026517</v>
       </c>
       <c r="Z18" s="1">
-        <v>-17.326758993223681</v>
+        <v>-8.6633794966118405</v>
       </c>
       <c r="AA18" s="1">
-        <v>-20.131199262719999</v>
+        <v>-10.06559963136</v>
       </c>
     </row>
     <row r="19" spans="1:27" x14ac:dyDescent="0.2">
@@ -70779,76 +70843,76 @@
         <v>3</v>
       </c>
       <c r="D19" s="1">
-        <v>17.76834176769</v>
+        <v>8.884170883845</v>
       </c>
       <c r="E19" s="1">
-        <v>21.265330515701759</v>
+        <v>10.63266525785088</v>
       </c>
       <c r="F19" s="1">
-        <v>27.163045518335998</v>
+        <v>13.581522759167999</v>
       </c>
       <c r="G19" s="1">
-        <v>25.128572093452803</v>
+        <v>12.564286046726401</v>
       </c>
       <c r="H19" s="1">
-        <v>29.27159256621599</v>
+        <v>14.635796283107995</v>
       </c>
       <c r="I19" s="1">
-        <v>29.526616187328003</v>
+        <v>14.763308093664001</v>
       </c>
       <c r="J19" s="1">
-        <v>29.583979487999997</v>
+        <v>14.791989743999999</v>
       </c>
       <c r="K19" s="1">
-        <v>33.385290664320003</v>
+        <v>16.692645332160001</v>
       </c>
       <c r="L19" s="1">
-        <v>28.839091804824008</v>
+        <v>14.419545902412004</v>
       </c>
       <c r="M19" s="1">
-        <v>37.502683931923208</v>
+        <v>18.751341965961604</v>
       </c>
       <c r="N19" s="1">
-        <v>34.876304015952002</v>
+        <v>17.438152007976001</v>
       </c>
       <c r="O19" s="1">
-        <v>31.936488500716802</v>
+        <v>15.968244250358401</v>
       </c>
       <c r="P19" s="1">
-        <v>34.095150415872006</v>
+        <v>17.047575207936003</v>
       </c>
       <c r="Q19" s="1">
-        <v>32.65480665067421</v>
+        <v>16.327403325337105</v>
       </c>
       <c r="R19" s="1">
-        <v>30.544486884172812</v>
+        <v>15.272243442086406</v>
       </c>
       <c r="S19" s="1">
-        <v>25.682314417309446</v>
+        <v>12.841157208654723</v>
       </c>
       <c r="T19" s="1">
-        <v>27.520666939583993</v>
+        <v>13.760333469791997</v>
       </c>
       <c r="U19" s="1">
-        <v>23.629052772089853</v>
+        <v>11.814526386044927</v>
       </c>
       <c r="V19" s="1">
-        <v>20.841606333475198</v>
+        <v>10.420803166737599</v>
       </c>
       <c r="W19" s="1">
-        <v>21.370518378880007</v>
+        <v>10.685259189440004</v>
       </c>
       <c r="X19" s="1">
-        <v>21.558591115776004</v>
+        <v>10.779295557888002</v>
       </c>
       <c r="Y19" s="1">
-        <v>25.667010098795529</v>
+        <v>12.833505049397765</v>
       </c>
       <c r="Z19" s="1">
-        <v>17.222252002559998</v>
+        <v>8.6111260012799988</v>
       </c>
       <c r="AA19" s="1">
-        <v>18.838885201920007</v>
+        <v>9.4194426009600036</v>
       </c>
     </row>
     <row r="20" spans="1:27" x14ac:dyDescent="0.2">
@@ -70862,76 +70926,76 @@
         <v>1</v>
       </c>
       <c r="D20" s="1">
-        <v>10.275276000000003</v>
+        <v>5.1376380000000017</v>
       </c>
       <c r="E20" s="1">
-        <v>10.618036000000002</v>
+        <v>5.3090180000000009</v>
       </c>
       <c r="F20" s="1">
-        <v>9.5078280000000017</v>
+        <v>4.7539140000000009</v>
       </c>
       <c r="G20" s="1">
-        <v>9.0120799999999992</v>
+        <v>4.5060399999999996</v>
       </c>
       <c r="H20" s="1">
-        <v>7.3835520000000008</v>
+        <v>3.6917760000000004</v>
       </c>
       <c r="I20" s="1">
-        <v>6.2666560000000011</v>
+        <v>3.1333280000000006</v>
       </c>
       <c r="J20" s="1">
-        <v>7.6636120000000005</v>
+        <v>3.8318060000000003</v>
       </c>
       <c r="K20" s="1">
-        <v>1.3309120000000003</v>
+        <v>0.66545600000000016</v>
       </c>
       <c r="L20" s="1">
-        <v>1.1704000000000001</v>
+        <v>0.58520000000000005</v>
       </c>
       <c r="M20" s="1">
-        <v>1.7062759999999997</v>
+        <v>0.85313799999999984</v>
       </c>
       <c r="N20" s="1">
-        <v>1.0048720000000002</v>
+        <v>0.5024360000000001</v>
       </c>
       <c r="O20" s="1">
-        <v>1.2556719999999999</v>
+        <v>0.62783599999999995</v>
       </c>
       <c r="P20" s="1">
-        <v>2.0005480000000007</v>
+        <v>1.0002740000000003</v>
       </c>
       <c r="Q20" s="1">
-        <v>3.6859240000000004</v>
+        <v>1.8429620000000002</v>
       </c>
       <c r="R20" s="1">
-        <v>3.932544</v>
+        <v>1.966272</v>
       </c>
       <c r="S20" s="1">
-        <v>3.8673359999999994</v>
+        <v>1.9336679999999997</v>
       </c>
       <c r="T20" s="1">
-        <v>2.1694200000000001</v>
+        <v>1.0847100000000001</v>
       </c>
       <c r="U20" s="1">
-        <v>4.4190959999999997</v>
+        <v>2.2095479999999998</v>
       </c>
       <c r="V20" s="1">
-        <v>2.5932720000000002</v>
+        <v>1.2966360000000001</v>
       </c>
       <c r="W20" s="1">
-        <v>1.8233159999999997</v>
+        <v>0.91165799999999986</v>
       </c>
       <c r="X20" s="1">
-        <v>2.7688320000000006</v>
+        <v>1.3844160000000003</v>
       </c>
       <c r="Y20" s="1">
-        <v>1.711292</v>
+        <v>0.85564600000000002</v>
       </c>
       <c r="Z20" s="1">
-        <v>7.8107480000000011</v>
+        <v>3.9053740000000006</v>
       </c>
       <c r="AA20" s="1">
-        <v>9.4158679999999997</v>
+        <v>4.7079339999999998</v>
       </c>
     </row>
     <row r="21" spans="1:27" x14ac:dyDescent="0.2">
@@ -70945,76 +71009,76 @@
         <v>1</v>
       </c>
       <c r="D21" s="1">
-        <v>-21.273464440800009</v>
+        <v>-10.636732220400004</v>
       </c>
       <c r="E21" s="1">
-        <v>-25.150694849280004</v>
+        <v>-12.575347424640002</v>
       </c>
       <c r="F21" s="1">
-        <v>-21.316310209919997</v>
+        <v>-10.658155104959999</v>
       </c>
       <c r="G21" s="1">
-        <v>-27.059572753919998</v>
+        <v>-13.529786376959999</v>
       </c>
       <c r="H21" s="1">
-        <v>-34.250681860521993</v>
+        <v>-17.125340930260997</v>
       </c>
       <c r="I21" s="1">
-        <v>-32.536113176985594</v>
+        <v>-16.268056588492797</v>
       </c>
       <c r="J21" s="1">
-        <v>-30.73754538186072</v>
+        <v>-15.36877269093036</v>
       </c>
       <c r="K21" s="1">
-        <v>-33.820634862508015</v>
+        <v>-16.910317431254008</v>
       </c>
       <c r="L21" s="1">
-        <v>-35.988790113501111</v>
+        <v>-17.994395056750555</v>
       </c>
       <c r="M21" s="1">
-        <v>-43.704005103525887</v>
+        <v>-21.852002551762943</v>
       </c>
       <c r="N21" s="1">
-        <v>-49.75940466714389</v>
+        <v>-24.879702333571945</v>
       </c>
       <c r="O21" s="1">
-        <v>-45.470248604470626</v>
+        <v>-22.735124302235313</v>
       </c>
       <c r="P21" s="1">
-        <v>-42.313068146688778</v>
+        <v>-21.156534073344389</v>
       </c>
       <c r="Q21" s="1">
-        <v>-40.345968479737522</v>
+        <v>-20.172984239868761</v>
       </c>
       <c r="R21" s="1">
-        <v>-38.469198317617277</v>
+        <v>-19.234599158808638</v>
       </c>
       <c r="S21" s="1">
-        <v>-33.315666675199992</v>
+        <v>-16.657833337599996</v>
       </c>
       <c r="T21" s="1">
-        <v>-29.915338871658243</v>
+        <v>-14.957669435829121</v>
       </c>
       <c r="U21" s="1">
-        <v>-28.726462022049791</v>
+        <v>-14.363231011024896</v>
       </c>
       <c r="V21" s="1">
-        <v>-17.510561664768002</v>
+        <v>-8.7552808323840008</v>
       </c>
       <c r="W21" s="1">
-        <v>-20.845456204579328</v>
+        <v>-10.422728102289664</v>
       </c>
       <c r="X21" s="1">
-        <v>-23.13420309712512</v>
+        <v>-11.56710154856256</v>
       </c>
       <c r="Y21" s="1">
-        <v>-20.535469319733203</v>
+        <v>-10.267734659866601</v>
       </c>
       <c r="Z21" s="1">
-        <v>-17.326758993223681</v>
+        <v>-8.6633794966118405</v>
       </c>
       <c r="AA21" s="1">
-        <v>-20.735135240601597</v>
+        <v>-10.367567620300798</v>
       </c>
     </row>
     <row r="22" spans="1:27" x14ac:dyDescent="0.2">
@@ -71028,76 +71092,76 @@
         <v>1</v>
       </c>
       <c r="D22" s="1">
-        <v>16.8799246793055</v>
+        <v>8.4399623396527499</v>
       </c>
       <c r="E22" s="1">
-        <v>21.690637126015794</v>
+        <v>10.845318563007897</v>
       </c>
       <c r="F22" s="1">
-        <v>27.977936883886077</v>
+        <v>13.988968441943038</v>
       </c>
       <c r="G22" s="1">
-        <v>24.626000651583745</v>
+        <v>12.313000325791872</v>
       </c>
       <c r="H22" s="1">
-        <v>29.857024417540309</v>
+        <v>14.928512208770155</v>
       </c>
       <c r="I22" s="1">
-        <v>29.23135002545472</v>
+        <v>14.61567501272736</v>
       </c>
       <c r="J22" s="1">
-        <v>28.696460103359996</v>
+        <v>14.348230051679998</v>
       </c>
       <c r="K22" s="1">
-        <v>34.386849384249601</v>
+        <v>17.1934246921248</v>
       </c>
       <c r="L22" s="1">
-        <v>30.281046395065211</v>
+        <v>15.140523197532605</v>
       </c>
       <c r="M22" s="1">
-        <v>38.627764449880907</v>
+        <v>19.313882224940453</v>
       </c>
       <c r="N22" s="1">
-        <v>34.178777935632958</v>
+        <v>17.089388967816479</v>
       </c>
       <c r="O22" s="1">
-        <v>32.575218270731142</v>
+        <v>16.287609135365571</v>
       </c>
       <c r="P22" s="1">
-        <v>35.458956432506881</v>
+        <v>17.72947821625344</v>
       </c>
       <c r="Q22" s="1">
-        <v>33.634450850194433</v>
+        <v>16.817225425097217</v>
       </c>
       <c r="R22" s="1">
-        <v>29.628152277647629</v>
+        <v>14.814076138823815</v>
       </c>
       <c r="S22" s="1">
-        <v>25.425491273136348</v>
+        <v>12.712745636568174</v>
       </c>
       <c r="T22" s="1">
-        <v>28.071080278375671</v>
+        <v>14.035540139187836</v>
       </c>
       <c r="U22" s="1">
-        <v>22.92018118892716</v>
+        <v>11.46009059446358</v>
       </c>
       <c r="V22" s="1">
-        <v>21.466854523479455</v>
+        <v>10.733427261739727</v>
       </c>
       <c r="W22" s="1">
-        <v>22.225339114035204</v>
+        <v>11.112669557017602</v>
       </c>
       <c r="X22" s="1">
-        <v>21.343005204618244</v>
+        <v>10.671502602309122</v>
       </c>
       <c r="Y22" s="1">
-        <v>25.410339997807572</v>
+        <v>12.705169998903786</v>
       </c>
       <c r="Z22" s="1">
-        <v>17.566697042611196</v>
+        <v>8.783348521305598</v>
       </c>
       <c r="AA22" s="1">
-        <v>19.027274053939205</v>
+        <v>9.5136370269696027</v>
       </c>
     </row>
     <row r="23" spans="1:27" x14ac:dyDescent="0.2">
@@ -71111,76 +71175,76 @@
         <v>2</v>
       </c>
       <c r="D23" s="1">
-        <v>10.789039800000003</v>
+        <v>5.3945199000000015</v>
       </c>
       <c r="E23" s="1">
-        <v>11.148937800000001</v>
+        <v>5.5744689000000003</v>
       </c>
       <c r="F23" s="1">
-        <v>9.1275148800000014</v>
+        <v>4.5637574400000007</v>
       </c>
       <c r="G23" s="1">
-        <v>8.7417175999999994</v>
+        <v>4.3708587999999997</v>
       </c>
       <c r="H23" s="1">
-        <v>7.3097164800000005</v>
+        <v>3.6548582400000003</v>
       </c>
       <c r="I23" s="1">
-        <v>6.1413228800000015</v>
+        <v>3.0706614400000007</v>
       </c>
       <c r="J23" s="1">
-        <v>7.5869758799999998</v>
+        <v>3.7934879399999999</v>
       </c>
       <c r="K23" s="1">
-        <v>1.3442211200000003</v>
+        <v>0.67211056000000013</v>
       </c>
       <c r="L23" s="1">
-        <v>1.146992</v>
+        <v>0.57349600000000001</v>
       </c>
       <c r="M23" s="1">
-        <v>1.7233387599999999</v>
+        <v>0.86166937999999993</v>
       </c>
       <c r="N23" s="1">
-        <v>1.0450668800000003</v>
+        <v>0.52253344000000013</v>
       </c>
       <c r="O23" s="1">
-        <v>1.30589888</v>
+        <v>0.65294943999999999</v>
       </c>
       <c r="P23" s="1">
-        <v>1.9605370400000006</v>
+        <v>0.98026852000000031</v>
       </c>
       <c r="Q23" s="1">
-        <v>3.8333609600000007</v>
+        <v>1.9166804800000004</v>
       </c>
       <c r="R23" s="1">
-        <v>4.1291712</v>
+        <v>2.0645856</v>
       </c>
       <c r="S23" s="1">
-        <v>3.6739691999999997</v>
+        <v>1.8369845999999999</v>
       </c>
       <c r="T23" s="1">
-        <v>2.2345026000000003</v>
+        <v>1.1172513000000002</v>
       </c>
       <c r="U23" s="1">
-        <v>4.5958598399999993</v>
+        <v>2.2979299199999996</v>
       </c>
       <c r="V23" s="1">
-        <v>2.5414065600000004</v>
+        <v>1.2707032800000002</v>
       </c>
       <c r="W23" s="1">
-        <v>1.8050828399999999</v>
+        <v>0.90254141999999993</v>
       </c>
       <c r="X23" s="1">
-        <v>2.7688320000000006</v>
+        <v>1.3844160000000003</v>
       </c>
       <c r="Y23" s="1">
-        <v>1.7626307600000002</v>
+        <v>0.88131538000000009</v>
       </c>
       <c r="Z23" s="1">
-        <v>8.2012854000000015</v>
+        <v>4.1006427000000008</v>
       </c>
       <c r="AA23" s="1">
-        <v>9.6041853600000007</v>
+        <v>4.8020926800000003</v>
       </c>
     </row>
     <row r="24" spans="1:27" x14ac:dyDescent="0.2">
@@ -71194,76 +71258,76 @@
         <v>2</v>
       </c>
       <c r="D24" s="1">
-        <v>-21.48619908520801</v>
+        <v>-10.743099542604005</v>
       </c>
       <c r="E24" s="1">
-        <v>-25.905215694758404</v>
+        <v>-12.952607847379202</v>
       </c>
       <c r="F24" s="1">
-        <v>-20.889984005721598</v>
+        <v>-10.444992002860799</v>
       </c>
       <c r="G24" s="1">
-        <v>-26.518381298841597</v>
+        <v>-13.259190649420798</v>
       </c>
       <c r="H24" s="1">
-        <v>-34.593188679127216</v>
+        <v>-17.296594339563608</v>
       </c>
       <c r="I24" s="1">
-        <v>-31.560029781676025</v>
+        <v>-15.780014890838013</v>
       </c>
       <c r="J24" s="1">
-        <v>-30.122794474223507</v>
+        <v>-15.061397237111754</v>
       </c>
       <c r="K24" s="1">
-        <v>-34.497047559758172</v>
+        <v>-17.248523779879086</v>
       </c>
       <c r="L24" s="1">
-        <v>-37.428341718041153</v>
+        <v>-18.714170859020577</v>
       </c>
       <c r="M24" s="1">
-        <v>-45.015125256631663</v>
+        <v>-22.507562628315831</v>
       </c>
       <c r="N24" s="1">
-        <v>-47.76902848045814</v>
+        <v>-23.88451424022907</v>
       </c>
       <c r="O24" s="1">
-        <v>-46.834356062604748</v>
+        <v>-23.417178031302374</v>
       </c>
       <c r="P24" s="1">
-        <v>-41.043676102288117</v>
+        <v>-20.521838051144059</v>
       </c>
       <c r="Q24" s="1">
-        <v>-39.53904911014277</v>
+        <v>-19.769524555071385</v>
       </c>
       <c r="R24" s="1">
-        <v>-38.469198317617277</v>
+        <v>-19.234599158808638</v>
       </c>
       <c r="S24" s="1">
-        <v>-31.983040008191992</v>
+        <v>-15.991520004095996</v>
       </c>
       <c r="T24" s="1">
-        <v>-30.214492260374826</v>
+        <v>-15.107246130187413</v>
       </c>
       <c r="U24" s="1">
-        <v>-27.290138920947303</v>
+        <v>-13.645069460473652</v>
       </c>
       <c r="V24" s="1">
-        <v>-16.810139198177282</v>
+        <v>-8.405069599088641</v>
       </c>
       <c r="W24" s="1">
-        <v>-20.845456204579328</v>
+        <v>-10.422728102289664</v>
       </c>
       <c r="X24" s="1">
-        <v>-24.059571221010124</v>
+        <v>-12.029785610505062</v>
       </c>
       <c r="Y24" s="1">
-        <v>-19.919405240141206</v>
+        <v>-9.9597026200706029</v>
       </c>
       <c r="Z24" s="1">
-        <v>-17.673294173088156</v>
+        <v>-8.8366470865440778</v>
       </c>
       <c r="AA24" s="1">
-        <v>-20.527783888195582</v>
+        <v>-10.263891944097791</v>
       </c>
     </row>
     <row r="25" spans="1:27" x14ac:dyDescent="0.2">
@@ -71277,76 +71341,76 @@
         <v>2</v>
       </c>
       <c r="D25" s="1">
-        <v>16.711125432512446</v>
+        <v>8.3555627162562232</v>
       </c>
       <c r="E25" s="1">
-        <v>21.690637126015794</v>
+        <v>10.845318563007897</v>
       </c>
       <c r="F25" s="1">
-        <v>26.579040039691773</v>
+        <v>13.289520019845886</v>
       </c>
       <c r="G25" s="1">
-        <v>25.118520664615421</v>
+        <v>12.55926033230771</v>
       </c>
       <c r="H25" s="1">
-        <v>30.454164905891115</v>
+        <v>15.227082452945558</v>
       </c>
       <c r="I25" s="1">
-        <v>30.108290526218362</v>
+        <v>15.054145263109181</v>
       </c>
       <c r="J25" s="1">
-        <v>28.983424704393595</v>
+        <v>14.491712352196798</v>
       </c>
       <c r="K25" s="1">
-        <v>34.386849384249601</v>
+        <v>17.1934246921248</v>
       </c>
       <c r="L25" s="1">
-        <v>28.766994075311949</v>
+        <v>14.383497037655975</v>
       </c>
       <c r="M25" s="1">
-        <v>40.172875027876145</v>
+        <v>20.086437513938073</v>
       </c>
       <c r="N25" s="1">
-        <v>35.20414127370195</v>
+        <v>17.602070636850975</v>
       </c>
       <c r="O25" s="1">
-        <v>32.900970453438454</v>
+        <v>16.450485226719227</v>
       </c>
       <c r="P25" s="1">
-        <v>35.458956432506881</v>
+        <v>17.72947821625344</v>
       </c>
       <c r="Q25" s="1">
-        <v>33.298106341692488</v>
+        <v>16.649053170846244</v>
       </c>
       <c r="R25" s="1">
-        <v>28.146744663765247</v>
+        <v>14.073372331882624</v>
       </c>
       <c r="S25" s="1">
-        <v>24.154216709479527</v>
+        <v>12.077108354739764</v>
       </c>
       <c r="T25" s="1">
-        <v>27.228947870024399</v>
+        <v>13.614473935012199</v>
       </c>
       <c r="U25" s="1">
-        <v>22.461777565148619</v>
+        <v>11.23088878257431</v>
       </c>
       <c r="V25" s="1">
-        <v>21.466854523479455</v>
+        <v>10.733427261739727</v>
       </c>
       <c r="W25" s="1">
-        <v>22.892099287456261</v>
+        <v>11.446049643728131</v>
       </c>
       <c r="X25" s="1">
-        <v>20.27585494438733</v>
+        <v>10.137927472193665</v>
       </c>
       <c r="Y25" s="1">
-        <v>26.680856997697951</v>
+        <v>13.340428498848976</v>
       </c>
       <c r="Z25" s="1">
-        <v>17.215363101758971</v>
+        <v>8.6076815508794855</v>
       </c>
       <c r="AA25" s="1">
-        <v>19.598092275557381</v>
+        <v>9.7990461377786904</v>
       </c>
     </row>
     <row r="26" spans="1:27" x14ac:dyDescent="0.2">
@@ -71360,76 +71424,76 @@
         <v>3</v>
       </c>
       <c r="D26" s="1">
-        <v>11.112710994000004</v>
+        <v>5.556355497000002</v>
       </c>
       <c r="E26" s="1">
-        <v>11.260427178</v>
+        <v>5.6302135890000002</v>
       </c>
       <c r="F26" s="1">
-        <v>9.036239731200002</v>
+        <v>4.518119865600001</v>
       </c>
       <c r="G26" s="1">
-        <v>9.1788034799999991</v>
+        <v>4.5894017399999996</v>
       </c>
       <c r="H26" s="1">
-        <v>7.3828136448000006</v>
+        <v>3.6914068224000003</v>
       </c>
       <c r="I26" s="1">
-        <v>6.1413228800000015</v>
+        <v>3.0706614400000007</v>
       </c>
       <c r="J26" s="1">
-        <v>7.2076270859999996</v>
+        <v>3.6038135429999998</v>
       </c>
       <c r="K26" s="1">
-        <v>1.2770100640000002</v>
+        <v>0.63850503200000008</v>
       </c>
       <c r="L26" s="1">
-        <v>1.0896424</v>
+        <v>0.54482120000000001</v>
       </c>
       <c r="M26" s="1">
-        <v>1.6716385971999999</v>
+        <v>0.83581929859999993</v>
       </c>
       <c r="N26" s="1">
-        <v>1.0346162112000001</v>
+        <v>0.51730810560000007</v>
       </c>
       <c r="O26" s="1">
-        <v>1.3320168576</v>
+        <v>0.6660084288</v>
       </c>
       <c r="P26" s="1">
-        <v>1.9213262992000006</v>
+        <v>0.96066314960000032</v>
       </c>
       <c r="Q26" s="1">
-        <v>4.0250290080000006</v>
+        <v>2.0125145040000003</v>
       </c>
       <c r="R26" s="1">
-        <v>4.3356297599999998</v>
+        <v>2.1678148799999999</v>
       </c>
       <c r="S26" s="1">
-        <v>3.8576676599999997</v>
+        <v>1.9288338299999999</v>
       </c>
       <c r="T26" s="1">
-        <v>2.2568476260000003</v>
+        <v>1.1284238130000002</v>
       </c>
       <c r="U26" s="1">
-        <v>4.5958598399999993</v>
+        <v>2.2979299199999996</v>
       </c>
       <c r="V26" s="1">
-        <v>2.5414065600000004</v>
+        <v>1.2707032800000002</v>
       </c>
       <c r="W26" s="1">
-        <v>1.7328795263999999</v>
+        <v>0.86643976319999993</v>
       </c>
       <c r="X26" s="1">
-        <v>2.6857670400000004</v>
+        <v>1.3428835200000002</v>
       </c>
       <c r="Y26" s="1">
-        <v>1.7802570676000002</v>
+        <v>0.89012853380000012</v>
       </c>
       <c r="Z26" s="1">
-        <v>7.9552468380000017</v>
+        <v>3.9776234190000008</v>
       </c>
       <c r="AA26" s="1">
-        <v>9.8923109208</v>
+        <v>4.9461554604</v>
       </c>
     </row>
     <row r="27" spans="1:27" x14ac:dyDescent="0.2">
@@ -71443,76 +71507,76 @@
         <v>3</v>
       </c>
       <c r="D27" s="1">
-        <v>-22.56050903946841</v>
+        <v>-11.280254519734205</v>
       </c>
       <c r="E27" s="1">
-        <v>-25.646163537810821</v>
+        <v>-12.823081768905411</v>
       </c>
       <c r="F27" s="1">
-        <v>-20.681084165664384</v>
+        <v>-10.340542082832192</v>
       </c>
       <c r="G27" s="1">
-        <v>-25.722829859876345</v>
+        <v>-12.861414929938173</v>
       </c>
       <c r="H27" s="1">
-        <v>-34.247256792335946</v>
+        <v>-17.123628396167973</v>
       </c>
       <c r="I27" s="1">
-        <v>-32.506830675126309</v>
+        <v>-16.253415337563155</v>
       </c>
       <c r="J27" s="1">
-        <v>-28.616654750512328</v>
+        <v>-14.308327375256164</v>
       </c>
       <c r="K27" s="1">
-        <v>-34.152077084160595</v>
+        <v>-17.076038542080298</v>
       </c>
       <c r="L27" s="1">
-        <v>-36.305491466499923</v>
+        <v>-18.152745733249962</v>
       </c>
       <c r="M27" s="1">
-        <v>-46.365579014330613</v>
+        <v>-23.182789507165307</v>
       </c>
       <c r="N27" s="1">
-        <v>-47.76902848045814</v>
+        <v>-23.88451424022907</v>
       </c>
       <c r="O27" s="1">
-        <v>-46.834356062604748</v>
+        <v>-23.417178031302374</v>
       </c>
       <c r="P27" s="1">
-        <v>-40.222802580242359</v>
+        <v>-20.111401290121179</v>
       </c>
       <c r="Q27" s="1">
-        <v>-39.53904911014277</v>
+        <v>-19.769524555071385</v>
       </c>
       <c r="R27" s="1">
-        <v>-39.23858228396962</v>
+        <v>-19.61929114198481</v>
       </c>
       <c r="S27" s="1">
-        <v>-32.62270080835583</v>
+        <v>-16.311350404177915</v>
       </c>
       <c r="T27" s="1">
-        <v>-31.12092702818607</v>
+        <v>-15.560463514093035</v>
       </c>
       <c r="U27" s="1">
-        <v>-27.290138920947303</v>
+        <v>-13.645069460473652</v>
       </c>
       <c r="V27" s="1">
-        <v>-17.146341982140829</v>
+        <v>-8.5731709910704144</v>
       </c>
       <c r="W27" s="1">
-        <v>-21.679274452762503</v>
+        <v>-10.839637226381251</v>
       </c>
       <c r="X27" s="1">
-        <v>-23.33778408437982</v>
+        <v>-11.66889204218991</v>
       </c>
       <c r="Y27" s="1">
-        <v>-20.118599292542616</v>
+        <v>-10.059299646271308</v>
       </c>
       <c r="Z27" s="1">
-        <v>-16.789629464433748</v>
+        <v>-8.394814732216874</v>
       </c>
       <c r="AA27" s="1">
-        <v>-20.938339565959495</v>
+        <v>-10.469169782979748</v>
       </c>
     </row>
     <row r="28" spans="1:27" x14ac:dyDescent="0.2">
@@ -71526,76 +71590,76 @@
         <v>3</v>
       </c>
       <c r="D28" s="1">
-        <v>16.209791669537072</v>
+        <v>8.104895834768536</v>
       </c>
       <c r="E28" s="1">
-        <v>21.039918012235322</v>
+        <v>10.519959006117661</v>
       </c>
       <c r="F28" s="1">
-        <v>26.579040039691773</v>
+        <v>13.289520019845886</v>
       </c>
       <c r="G28" s="1">
-        <v>25.872076284553881</v>
+        <v>12.93603814227694</v>
       </c>
       <c r="H28" s="1">
-        <v>31.976873151185671</v>
+        <v>15.988436575592836</v>
       </c>
       <c r="I28" s="1">
-        <v>29.807207620956177</v>
+        <v>14.903603810478089</v>
       </c>
       <c r="J28" s="1">
-        <v>30.432595939613275</v>
+        <v>15.216297969806638</v>
       </c>
       <c r="K28" s="1">
-        <v>33.699112396564608</v>
+        <v>16.849556198282304</v>
       </c>
       <c r="L28" s="1">
-        <v>28.47932413455883</v>
+        <v>14.239662067279415</v>
       </c>
       <c r="M28" s="1">
-        <v>42.181518779269958</v>
+        <v>21.090759389634979</v>
       </c>
       <c r="N28" s="1">
-        <v>36.612306924650028</v>
+        <v>18.306153462325014</v>
       </c>
       <c r="O28" s="1">
-        <v>31.913941339835301</v>
+        <v>15.95697066991765</v>
       </c>
       <c r="P28" s="1">
-        <v>35.458956432506881</v>
+        <v>17.72947821625344</v>
       </c>
       <c r="Q28" s="1">
-        <v>34.630030595360182</v>
+        <v>17.315015297680091</v>
       </c>
       <c r="R28" s="1">
-        <v>28.146744663765247</v>
+        <v>14.073372331882624</v>
       </c>
       <c r="S28" s="1">
-        <v>23.671132375289936</v>
+        <v>11.835566187644968</v>
       </c>
       <c r="T28" s="1">
-        <v>26.412079433923669</v>
+        <v>13.206039716961834</v>
       </c>
       <c r="U28" s="1">
-        <v>23.58486644340605</v>
+        <v>11.792433221703025</v>
       </c>
       <c r="V28" s="1">
-        <v>21.466854523479455</v>
+        <v>10.733427261739727</v>
       </c>
       <c r="W28" s="1">
-        <v>22.663178294581698</v>
+        <v>11.331589147290849</v>
       </c>
       <c r="X28" s="1">
-        <v>21.086889142162821</v>
+        <v>10.543444571081411</v>
       </c>
       <c r="Y28" s="1">
-        <v>25.880431287767014</v>
+        <v>12.940215643883507</v>
       </c>
       <c r="Z28" s="1">
-        <v>17.731823994811741</v>
+        <v>8.8659119974058704</v>
       </c>
       <c r="AA28" s="1">
-        <v>19.010149507290659</v>
+        <v>9.5050747536453297</v>
       </c>
     </row>
     <row r="29" spans="1:27" x14ac:dyDescent="0.2">
@@ -71609,76 +71673,76 @@
         <v>1</v>
       </c>
       <c r="D29" s="1">
-        <v>9.7615122000000021</v>
+        <v>4.880756100000001</v>
       </c>
       <c r="E29" s="1">
-        <v>10.087134200000001</v>
+        <v>5.0435671000000006</v>
       </c>
       <c r="F29" s="1">
-        <v>9.0324366000000005</v>
+        <v>4.5162183000000002</v>
       </c>
       <c r="G29" s="1">
-        <v>8.561475999999999</v>
+        <v>4.2807379999999995</v>
       </c>
       <c r="H29" s="1">
-        <v>7.0143744000000003</v>
+        <v>3.5071872000000002</v>
       </c>
       <c r="I29" s="1">
-        <v>5.9533232000000007</v>
+        <v>2.9766616000000004</v>
       </c>
       <c r="J29" s="1">
-        <v>7.2804314000000003</v>
+        <v>3.6402157000000002</v>
       </c>
       <c r="K29" s="1">
-        <v>1.2643664000000003</v>
+        <v>0.63218320000000017</v>
       </c>
       <c r="L29" s="1">
-        <v>1.11188</v>
+        <v>0.55593999999999999</v>
       </c>
       <c r="M29" s="1">
-        <v>1.6209621999999997</v>
+        <v>0.81048109999999984</v>
       </c>
       <c r="N29" s="1">
-        <v>0.95462840000000015</v>
+        <v>0.47731420000000008</v>
       </c>
       <c r="O29" s="1">
-        <v>1.1928883999999997</v>
+        <v>0.59644419999999987</v>
       </c>
       <c r="P29" s="1">
-        <v>1.9005206000000006</v>
+        <v>0.95026030000000028</v>
       </c>
       <c r="Q29" s="1">
-        <v>3.5016278000000001</v>
+        <v>1.7508139</v>
       </c>
       <c r="R29" s="1">
-        <v>3.7359168</v>
+        <v>1.8679584</v>
       </c>
       <c r="S29" s="1">
-        <v>3.6739691999999993</v>
+        <v>1.8369845999999996</v>
       </c>
       <c r="T29" s="1">
-        <v>2.0609489999999999</v>
+        <v>1.0304745</v>
       </c>
       <c r="U29" s="1">
-        <v>4.1981411999999994</v>
+        <v>2.0990705999999997</v>
       </c>
       <c r="V29" s="1">
-        <v>2.4636084</v>
+        <v>1.2318042</v>
       </c>
       <c r="W29" s="1">
-        <v>1.7321501999999998</v>
+        <v>0.86607509999999988</v>
       </c>
       <c r="X29" s="1">
-        <v>2.6303904000000005</v>
+        <v>1.3151952000000002</v>
       </c>
       <c r="Y29" s="1">
-        <v>1.6257273999999999</v>
+        <v>0.81286369999999997</v>
       </c>
       <c r="Z29" s="1">
-        <v>7.4202106000000008</v>
+        <v>3.7101053000000004</v>
       </c>
       <c r="AA29" s="1">
-        <v>8.9450745999999999</v>
+        <v>4.4725372999999999</v>
       </c>
     </row>
     <row r="30" spans="1:27" x14ac:dyDescent="0.2">
@@ -71692,76 +71756,76 @@
         <v>1</v>
       </c>
       <c r="D30" s="1">
-        <v>-22.334903949073727</v>
+        <v>-11.167451974536863</v>
       </c>
       <c r="E30" s="1">
-        <v>-25.646163537810821</v>
+        <v>-12.823081768905411</v>
       </c>
       <c r="F30" s="1">
-        <v>-20.060651640694452</v>
+        <v>-10.030325820347226</v>
       </c>
       <c r="G30" s="1">
-        <v>-26.751743054271401</v>
+        <v>-13.3758715271357</v>
       </c>
       <c r="H30" s="1">
-        <v>-35.617147064029389</v>
+        <v>-17.808573532014695</v>
       </c>
       <c r="I30" s="1">
-        <v>-33.80710390213136</v>
+        <v>-16.90355195106568</v>
       </c>
       <c r="J30" s="1">
-        <v>-30.047487488037945</v>
+        <v>-15.023743744018972</v>
       </c>
       <c r="K30" s="1">
-        <v>-35.518160167527022</v>
+        <v>-17.759080083763511</v>
       </c>
       <c r="L30" s="1">
-        <v>-37.394656210494922</v>
+        <v>-18.697328105247461</v>
       </c>
       <c r="M30" s="1">
-        <v>-47.292890594617226</v>
+        <v>-23.646445297308613</v>
       </c>
       <c r="N30" s="1">
-        <v>-48.24671876526272</v>
+        <v>-24.12335938263136</v>
       </c>
       <c r="O30" s="1">
-        <v>-47.302699623230794</v>
+        <v>-23.651349811615397</v>
       </c>
       <c r="P30" s="1">
-        <v>-38.613890477032662</v>
+        <v>-19.306945238516331</v>
       </c>
       <c r="Q30" s="1">
-        <v>-37.957487145737062</v>
+        <v>-18.978743572868531</v>
       </c>
       <c r="R30" s="1">
-        <v>-40.023353929649012</v>
+        <v>-20.011676964824506</v>
       </c>
       <c r="S30" s="1">
-        <v>-32.948927816439394</v>
+        <v>-16.474463908219697</v>
       </c>
       <c r="T30" s="1">
-        <v>-31.432136298467931</v>
+        <v>-15.716068149233966</v>
       </c>
       <c r="U30" s="1">
-        <v>-28.108843088575721</v>
+        <v>-14.054421544287861</v>
       </c>
       <c r="V30" s="1">
-        <v>-16.289024883033786</v>
+        <v>-8.144512441516893</v>
       </c>
       <c r="W30" s="1">
-        <v>-21.896067197290126</v>
+        <v>-10.948033598645063</v>
       </c>
       <c r="X30" s="1">
-        <v>-22.404272721004627</v>
+        <v>-11.202136360502314</v>
       </c>
       <c r="Y30" s="1">
-        <v>-20.722157271318892</v>
+        <v>-10.361078635659446</v>
       </c>
       <c r="Z30" s="1">
-        <v>-17.125422053722424</v>
+        <v>-8.5627110268612121</v>
       </c>
       <c r="AA30" s="1">
-        <v>-21.985256544257471</v>
+        <v>-10.992628272128735</v>
       </c>
     </row>
     <row r="31" spans="1:27" x14ac:dyDescent="0.2">
@@ -71775,76 +71839,76 @@
         <v>1</v>
       </c>
       <c r="D31" s="1">
-        <v>16.858183336318554</v>
+        <v>8.4290916681592769</v>
       </c>
       <c r="E31" s="1">
-        <v>21.250317192357674</v>
+        <v>10.625158596178837</v>
       </c>
       <c r="F31" s="1">
-        <v>27.642201641279442</v>
+        <v>13.821100820639721</v>
       </c>
       <c r="G31" s="1">
-        <v>26.389517810244957</v>
+        <v>13.194758905122479</v>
       </c>
       <c r="H31" s="1">
-        <v>32.936179345721243</v>
+        <v>16.468089672860621</v>
       </c>
       <c r="I31" s="1">
-        <v>29.211063468537056</v>
+        <v>14.605531734268528</v>
       </c>
       <c r="J31" s="1">
-        <v>28.91096614263261</v>
+        <v>14.455483071316305</v>
       </c>
       <c r="K31" s="1">
-        <v>33.699112396564608</v>
+        <v>16.849556198282304</v>
       </c>
       <c r="L31" s="1">
-        <v>29.048910617250009</v>
+        <v>14.524455308625004</v>
       </c>
       <c r="M31" s="1">
-        <v>44.29059471823345</v>
+        <v>22.145297359116725</v>
       </c>
       <c r="N31" s="1">
-        <v>35.880060786157031</v>
+        <v>17.940030393078516</v>
       </c>
       <c r="O31" s="1">
-        <v>31.913941339835301</v>
+        <v>15.95697066991765</v>
       </c>
       <c r="P31" s="1">
-        <v>36.87731468980715</v>
+        <v>18.438657344903575</v>
       </c>
       <c r="Q31" s="1">
-        <v>32.898529065592172</v>
+        <v>16.449264532796086</v>
       </c>
       <c r="R31" s="1">
-        <v>28.146744663765247</v>
+        <v>14.073372331882624</v>
       </c>
       <c r="S31" s="1">
-        <v>24.854688994054431</v>
+        <v>12.427344497027216</v>
       </c>
       <c r="T31" s="1">
-        <v>26.147958639584431</v>
+        <v>13.073979319792215</v>
       </c>
       <c r="U31" s="1">
-        <v>23.113169114537929</v>
+        <v>11.556584557268964</v>
       </c>
       <c r="V31" s="1">
-        <v>21.896191613949046</v>
+        <v>10.948095806974523</v>
       </c>
       <c r="W31" s="1">
-        <v>23.343073643419146</v>
+        <v>11.671536821709573</v>
       </c>
       <c r="X31" s="1">
-        <v>21.50862692500608</v>
+        <v>10.75431346250304</v>
       </c>
       <c r="Y31" s="1">
-        <v>25.104018349134002</v>
+        <v>12.552009174567001</v>
       </c>
       <c r="Z31" s="1">
-        <v>17.909142234759859</v>
+        <v>8.9545711173799294</v>
       </c>
       <c r="AA31" s="1">
-        <v>19.200251002363565</v>
+        <v>9.6001255011817825</v>
       </c>
     </row>
     <row r="32" spans="1:27" x14ac:dyDescent="0.2">
@@ -71858,76 +71922,76 @@
         <v>2</v>
       </c>
       <c r="D32" s="1">
-        <v>9.6638970780000015</v>
+        <v>4.8319485390000008</v>
       </c>
       <c r="E32" s="1">
-        <v>10.591490910000003</v>
+        <v>5.2957454550000014</v>
       </c>
       <c r="F32" s="1">
-        <v>9.0324366000000005</v>
+        <v>4.5162183000000002</v>
       </c>
       <c r="G32" s="1">
-        <v>8.133402199999999</v>
+        <v>4.0667010999999995</v>
       </c>
       <c r="H32" s="1">
-        <v>6.9442306560000011</v>
+        <v>3.4721153280000006</v>
       </c>
       <c r="I32" s="1">
-        <v>5.6556570400000012</v>
+        <v>2.8278285200000006</v>
       </c>
       <c r="J32" s="1">
-        <v>6.989214144</v>
+        <v>3.494607072</v>
       </c>
       <c r="K32" s="1">
-        <v>1.3022973920000005</v>
+        <v>0.65114869600000025</v>
       </c>
       <c r="L32" s="1">
-        <v>1.11188</v>
+        <v>0.55593999999999999</v>
       </c>
       <c r="M32" s="1">
-        <v>1.5885429559999997</v>
+        <v>0.79427147799999986</v>
       </c>
       <c r="N32" s="1">
-        <v>0.94508211600000014</v>
+        <v>0.47254105800000007</v>
       </c>
       <c r="O32" s="1">
-        <v>1.2048172839999998</v>
+        <v>0.60240864199999988</v>
       </c>
       <c r="P32" s="1">
-        <v>1.8815153940000005</v>
+        <v>0.94075769700000023</v>
       </c>
       <c r="Q32" s="1">
-        <v>3.466611522</v>
+        <v>1.733305761</v>
       </c>
       <c r="R32" s="1">
-        <v>3.7732759679999996</v>
+        <v>1.8866379839999998</v>
       </c>
       <c r="S32" s="1">
-        <v>3.5270104319999995</v>
+        <v>1.7635052159999998</v>
       </c>
       <c r="T32" s="1">
-        <v>2.0609489999999999</v>
+        <v>1.0304745</v>
       </c>
       <c r="U32" s="1">
-        <v>4.4080482599999993</v>
+        <v>2.2040241299999996</v>
       </c>
       <c r="V32" s="1">
-        <v>2.3650640640000002</v>
+        <v>1.1825320320000001</v>
       </c>
       <c r="W32" s="1">
-        <v>1.7667932039999996</v>
+        <v>0.88339660199999981</v>
       </c>
       <c r="X32" s="1">
-        <v>2.5251747840000003</v>
+        <v>1.2625873920000001</v>
       </c>
       <c r="Y32" s="1">
-        <v>1.560698304</v>
+        <v>0.78034915199999999</v>
       </c>
       <c r="Z32" s="1">
-        <v>7.3460084940000012</v>
+        <v>3.6730042470000006</v>
       </c>
       <c r="AA32" s="1">
-        <v>8.9450745999999999</v>
+        <v>4.4725372999999999</v>
       </c>
     </row>
     <row r="33" spans="1:27" x14ac:dyDescent="0.2">
@@ -71941,76 +72005,76 @@
         <v>2</v>
       </c>
       <c r="D33" s="1">
-        <v>-21.88820587009225</v>
+        <v>-10.944102935046125</v>
       </c>
       <c r="E33" s="1">
-        <v>-25.133240267054607</v>
+        <v>-12.566620133527303</v>
       </c>
       <c r="F33" s="1">
-        <v>-19.659438607880563</v>
+        <v>-9.8297193039402817</v>
       </c>
       <c r="G33" s="1">
-        <v>-25.949190762643255</v>
+        <v>-12.974595381321627</v>
       </c>
       <c r="H33" s="1">
-        <v>-37.398004417230858</v>
+        <v>-18.699002208615429</v>
       </c>
       <c r="I33" s="1">
-        <v>-32.792890785067421</v>
+        <v>-16.39644539253371</v>
       </c>
       <c r="J33" s="1">
-        <v>-30.648437237798703</v>
+        <v>-15.324218618899351</v>
       </c>
       <c r="K33" s="1">
-        <v>-35.162978565851752</v>
+        <v>-17.581489282925876</v>
       </c>
       <c r="L33" s="1">
-        <v>-36.272816524180072</v>
+        <v>-18.136408262090036</v>
       </c>
       <c r="M33" s="1">
-        <v>-45.874103876778712</v>
+        <v>-22.937051938389356</v>
       </c>
       <c r="N33" s="1">
-        <v>-45.83438282699958</v>
+        <v>-22.91719141349979</v>
       </c>
       <c r="O33" s="1">
-        <v>-49.66783460439234</v>
+        <v>-24.83391730219617</v>
       </c>
       <c r="P33" s="1">
-        <v>-39.772307191343643</v>
+        <v>-19.886153595671821</v>
       </c>
       <c r="Q33" s="1">
-        <v>-38.716636888651799</v>
+        <v>-19.358318444325899</v>
       </c>
       <c r="R33" s="1">
-        <v>-41.62428808683498</v>
+        <v>-20.81214404341749</v>
       </c>
       <c r="S33" s="1">
-        <v>-34.266884929096967</v>
+        <v>-17.133442464548484</v>
       </c>
       <c r="T33" s="1">
-        <v>-31.117814935483253</v>
+        <v>-15.558907467741626</v>
       </c>
       <c r="U33" s="1">
-        <v>-27.827754657689965</v>
+        <v>-13.913877328844983</v>
       </c>
       <c r="V33" s="1">
-        <v>-16.451915131864123</v>
+        <v>-8.2259575659320614</v>
       </c>
       <c r="W33" s="1">
-        <v>-21.896067197290126</v>
+        <v>-10.948033598645063</v>
       </c>
       <c r="X33" s="1">
-        <v>-22.852358175424719</v>
+        <v>-11.426179087712359</v>
       </c>
       <c r="Y33" s="1">
-        <v>-21.758265134884837</v>
+        <v>-10.879132567442419</v>
       </c>
       <c r="Z33" s="1">
-        <v>-17.981693156408546</v>
+        <v>-8.9908465782042732</v>
       </c>
       <c r="AA33" s="1">
-        <v>-21.105846282487175</v>
+        <v>-10.552923141243587</v>
       </c>
     </row>
     <row r="34" spans="1:27" x14ac:dyDescent="0.2">
@@ -72024,76 +72088,76 @@
         <v>2</v>
       </c>
       <c r="D34" s="1">
-        <v>16.015274169502629</v>
+        <v>8.0076370847513143</v>
       </c>
       <c r="E34" s="1">
-        <v>21.887826708128404</v>
+        <v>10.943913354064202</v>
       </c>
       <c r="F34" s="1">
-        <v>26.260091559215471</v>
+        <v>13.130045779607736</v>
       </c>
       <c r="G34" s="1">
-        <v>25.333937097835161</v>
+        <v>12.666968548917581</v>
       </c>
       <c r="H34" s="1">
-        <v>31.289370378435184</v>
+        <v>15.644685189217592</v>
       </c>
       <c r="I34" s="1">
-        <v>30.087395372593168</v>
+        <v>15.043697686296584</v>
       </c>
       <c r="J34" s="1">
-        <v>27.754527496927302</v>
+        <v>13.877263748463651</v>
       </c>
       <c r="K34" s="1">
-        <v>32.014156776736378</v>
+        <v>16.007078388368189</v>
       </c>
       <c r="L34" s="1">
-        <v>30.210867041940009</v>
+        <v>15.105433520970005</v>
       </c>
       <c r="M34" s="1">
-        <v>42.076064982321775</v>
+        <v>21.038032491160887</v>
       </c>
       <c r="N34" s="1">
-        <v>34.086057746849178</v>
+        <v>17.043028873424589</v>
       </c>
       <c r="O34" s="1">
-        <v>33.509638406827065</v>
+        <v>16.754819203413533</v>
       </c>
       <c r="P34" s="1">
-        <v>37.614860983603293</v>
+        <v>18.807430491801647</v>
       </c>
       <c r="Q34" s="1">
-        <v>33.556499646904015</v>
+        <v>16.778249823452008</v>
       </c>
       <c r="R34" s="1">
-        <v>28.709679557040555</v>
+        <v>14.354839778520278</v>
       </c>
       <c r="S34" s="1">
-        <v>24.854688994054431</v>
+        <v>12.427344497027216</v>
       </c>
       <c r="T34" s="1">
-        <v>26.409438225980274</v>
+        <v>13.204719112990137</v>
       </c>
       <c r="U34" s="1">
-        <v>22.419774041101793</v>
+        <v>11.209887020550896</v>
       </c>
       <c r="V34" s="1">
-        <v>22.553077362367517</v>
+        <v>11.276538681183759</v>
       </c>
       <c r="W34" s="1">
-        <v>23.80993511628753</v>
+        <v>11.904967558143765</v>
       </c>
       <c r="X34" s="1">
-        <v>20.433195578755775</v>
+        <v>10.216597789377888</v>
       </c>
       <c r="Y34" s="1">
-        <v>24.852978165642661</v>
+        <v>12.42648908282133</v>
       </c>
       <c r="Z34" s="1">
-        <v>17.013685123021865</v>
+        <v>8.5068425615109327</v>
       </c>
       <c r="AA34" s="1">
-        <v>19.776258532434472</v>
+        <v>9.888129266217236</v>
       </c>
     </row>
     <row r="35" spans="1:27" x14ac:dyDescent="0.2">
@@ -72107,76 +72171,76 @@
         <v>3</v>
       </c>
       <c r="D35" s="1">
-        <v>9.6638970780000015</v>
+        <v>4.8319485390000008</v>
       </c>
       <c r="E35" s="1">
-        <v>11.015150546400003</v>
+        <v>5.5075752732000014</v>
       </c>
       <c r="F35" s="1">
-        <v>9.0324366000000005</v>
+        <v>4.5162183000000002</v>
       </c>
       <c r="G35" s="1">
-        <v>7.9707341559999989</v>
+        <v>3.9853670779999995</v>
       </c>
       <c r="H35" s="1">
-        <v>6.5970191232000017</v>
+        <v>3.2985095616000009</v>
       </c>
       <c r="I35" s="1">
-        <v>5.5425438992000009</v>
+        <v>2.7712719496000005</v>
       </c>
       <c r="J35" s="1">
-        <v>6.6397534368000004</v>
+        <v>3.3198767184000002</v>
       </c>
       <c r="K35" s="1">
-        <v>1.2762514441600006</v>
+        <v>0.63812572208000029</v>
       </c>
       <c r="L35" s="1">
-        <v>1.11188</v>
+        <v>0.55593999999999999</v>
       </c>
       <c r="M35" s="1">
-        <v>1.6044283855599997</v>
+        <v>0.80221419277999984</v>
       </c>
       <c r="N35" s="1">
-        <v>0.99233622180000014</v>
+        <v>0.49616811090000007</v>
       </c>
       <c r="O35" s="1">
-        <v>1.1927691111599998</v>
+        <v>0.59638455557999992</v>
       </c>
       <c r="P35" s="1">
-        <v>1.9755911637000005</v>
+        <v>0.98779558185000027</v>
       </c>
       <c r="Q35" s="1">
-        <v>3.5359437524399997</v>
+        <v>1.7679718762199998</v>
       </c>
       <c r="R35" s="1">
-        <v>3.8487414873599994</v>
+        <v>1.9243707436799997</v>
       </c>
       <c r="S35" s="1">
-        <v>3.4212001190399999</v>
+        <v>1.7106000595199999</v>
       </c>
       <c r="T35" s="1">
-        <v>2.1227774699999999</v>
+        <v>1.061388735</v>
       </c>
       <c r="U35" s="1">
-        <v>4.275806812199999</v>
+        <v>2.1379034060999995</v>
       </c>
       <c r="V35" s="1">
-        <v>2.4596666265600002</v>
+        <v>1.2298333132800001</v>
       </c>
       <c r="W35" s="1">
-        <v>1.7137894078799996</v>
+        <v>0.85689470393999978</v>
       </c>
       <c r="X35" s="1">
-        <v>2.3989160448000004</v>
+        <v>1.1994580224000002</v>
       </c>
       <c r="Y35" s="1">
-        <v>1.5450913209600001</v>
+        <v>0.77254566048000006</v>
       </c>
       <c r="Z35" s="1">
-        <v>7.4929286638800008</v>
+        <v>3.7464643319400004</v>
       </c>
       <c r="AA35" s="1">
-        <v>8.855623854000001</v>
+        <v>4.4278119270000005</v>
       </c>
     </row>
     <row r="36" spans="1:27" x14ac:dyDescent="0.2">
@@ -72190,76 +72254,76 @@
         <v>3</v>
       </c>
       <c r="D36" s="1">
-        <v>-22.982616163596862</v>
+        <v>-11.491308081798431</v>
       </c>
       <c r="E36" s="1">
-        <v>-26.389902280407338</v>
+        <v>-13.194951140203669</v>
       </c>
       <c r="F36" s="1">
-        <v>-20.249221766116978</v>
+        <v>-10.124610883058489</v>
       </c>
       <c r="G36" s="1">
-        <v>-26.468174577896121</v>
+        <v>-13.234087288948061</v>
       </c>
       <c r="H36" s="1">
-        <v>-38.145964505575478</v>
+        <v>-19.072982252787739</v>
       </c>
       <c r="I36" s="1">
-        <v>-34.432535324320796</v>
+        <v>-17.216267662160398</v>
       </c>
       <c r="J36" s="1">
-        <v>-29.728984120664741</v>
+        <v>-14.86449206033237</v>
       </c>
       <c r="K36" s="1">
-        <v>-35.866238137168786</v>
+        <v>-17.933119068584393</v>
       </c>
       <c r="L36" s="1">
-        <v>-35.910088358938275</v>
+        <v>-17.955044179469137</v>
       </c>
       <c r="M36" s="1">
-        <v>-44.497880760475354</v>
+        <v>-22.248940380237677</v>
       </c>
       <c r="N36" s="1">
-        <v>-43.542663685649607</v>
+        <v>-21.771331842824804</v>
       </c>
       <c r="O36" s="1">
-        <v>-48.674477912304489</v>
+        <v>-24.337238956152245</v>
       </c>
       <c r="P36" s="1">
-        <v>-37.783691831776459</v>
+        <v>-18.891845915888229</v>
       </c>
       <c r="Q36" s="1">
-        <v>-38.32947051976528</v>
+        <v>-19.16473525988264</v>
       </c>
       <c r="R36" s="1">
-        <v>-43.70550249117673</v>
+        <v>-21.852751245588365</v>
       </c>
       <c r="S36" s="1">
-        <v>-35.29489147696988</v>
+        <v>-17.64744573848494</v>
       </c>
       <c r="T36" s="1">
-        <v>-29.561924188709089</v>
+        <v>-14.780962094354544</v>
       </c>
       <c r="U36" s="1">
-        <v>-29.219142390574461</v>
+        <v>-14.609571195287231</v>
       </c>
       <c r="V36" s="1">
-        <v>-16.616434283182762</v>
+        <v>-8.3082171415913812</v>
       </c>
       <c r="W36" s="1">
-        <v>-22.333988541235925</v>
+        <v>-11.166994270617963</v>
       </c>
       <c r="X36" s="1">
-        <v>-22.166787430161975</v>
+        <v>-11.083393715080987</v>
       </c>
       <c r="Y36" s="1">
-        <v>-20.887934529489442</v>
+        <v>-10.443967264744721</v>
       </c>
       <c r="Z36" s="1">
-        <v>-18.700960882664887</v>
+        <v>-9.3504804413324436</v>
       </c>
       <c r="AA36" s="1">
-        <v>-20.683729356837429</v>
+        <v>-10.341864678418714</v>
       </c>
     </row>
     <row r="37" spans="1:27" x14ac:dyDescent="0.2">
@@ -72273,76 +72337,76 @@
         <v>3</v>
       </c>
       <c r="D37" s="1">
-        <v>16.015274169502629</v>
+        <v>8.0076370847513143</v>
       </c>
       <c r="E37" s="1">
-        <v>21.450070173965837</v>
+        <v>10.725035086982919</v>
       </c>
       <c r="F37" s="1">
-        <v>26.260091559215471</v>
+        <v>13.130045779607736</v>
       </c>
       <c r="G37" s="1">
-        <v>24.067240242943402</v>
+        <v>12.033620121471701</v>
       </c>
       <c r="H37" s="1">
-        <v>32.228051489788243</v>
+        <v>16.114025744894121</v>
       </c>
       <c r="I37" s="1">
-        <v>31.591765141222826</v>
+        <v>15.795882570611413</v>
       </c>
       <c r="J37" s="1">
-        <v>28.864708596804395</v>
+        <v>14.432354298402197</v>
       </c>
       <c r="K37" s="1">
-        <v>32.654439912271101</v>
+        <v>16.327219956135551</v>
       </c>
       <c r="L37" s="1">
-        <v>30.210867041940009</v>
+        <v>15.105433520970005</v>
       </c>
       <c r="M37" s="1">
-        <v>42.917586281968205</v>
+        <v>21.458793140984103</v>
       </c>
       <c r="N37" s="1">
-        <v>35.449500056723146</v>
+        <v>17.724750028361573</v>
       </c>
       <c r="O37" s="1">
-        <v>34.514927559031875</v>
+        <v>17.257463779515938</v>
       </c>
       <c r="P37" s="1">
-        <v>35.734117934423132</v>
+        <v>17.867058967211566</v>
       </c>
       <c r="Q37" s="1">
-        <v>31.878674664558815</v>
+        <v>15.939337332279408</v>
       </c>
       <c r="R37" s="1">
-        <v>29.283873148181364</v>
+        <v>14.641936574090682</v>
       </c>
       <c r="S37" s="1">
-        <v>24.357595214173344</v>
+        <v>12.178797607086672</v>
       </c>
       <c r="T37" s="1">
-        <v>26.937626990499879</v>
+        <v>13.46881349524994</v>
       </c>
       <c r="U37" s="1">
-        <v>21.747180819868742</v>
+        <v>10.873590409934371</v>
       </c>
       <c r="V37" s="1">
-        <v>23.455200456862215</v>
+        <v>11.727600228431108</v>
       </c>
       <c r="W37" s="1">
-        <v>23.333736413961777</v>
+        <v>11.666868206980888</v>
       </c>
       <c r="X37" s="1">
-        <v>20.228863622968216</v>
+        <v>10.114431811484108</v>
       </c>
       <c r="Y37" s="1">
-        <v>24.852978165642661</v>
+        <v>12.42648908282133</v>
       </c>
       <c r="Z37" s="1">
-        <v>16.333137718100989</v>
+        <v>8.1665688590504946</v>
       </c>
       <c r="AA37" s="1">
-        <v>19.776258532434472</v>
+        <v>9.888129266217236</v>
       </c>
     </row>
   </sheetData>

--- a/data/OP1/case33_2/case33_2_operational_data.xlsx
+++ b/data/OP1/case33_2/case33_2_operational_data.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/micaelsimoes/PycharmProjects/shared-resources-planning/data/CS7/case33_2/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/micaelsimoes/PycharmProjects/shared-resources-planning/data/OP1/case33_2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22A33D5E-48B4-484F-BD94-44F8DCA9BB97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0063B4B5-7359-A141-B3F8-B41F1F042D2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1120" yWindow="620" windowWidth="29400" windowHeight="19120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -473,12 +473,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1">
-        <f>E2*1</f>
         <v>4</v>
       </c>
       <c r="C2" s="1">
-        <f>-F2*1</f>
-        <v>-2.4</v>
+        <v>2.4</v>
       </c>
       <c r="D2" s="2">
         <v>2.6917900403768499E-2</v>
@@ -495,11 +493,9 @@
         <v>2</v>
       </c>
       <c r="B3" s="1">
-        <f t="shared" ref="B3:B33" si="0">E3*1</f>
         <v>3.5999999999999996</v>
       </c>
       <c r="C3" s="1">
-        <f t="shared" ref="C3:C33" si="1">-F3*1</f>
         <v>-1.6</v>
       </c>
       <c r="D3" s="2">
@@ -517,12 +513,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1">
-        <f t="shared" si="0"/>
         <v>4.8</v>
       </c>
       <c r="C4" s="1">
-        <f t="shared" si="1"/>
-        <v>-3.2</v>
+        <v>3.2</v>
       </c>
       <c r="D4" s="2">
         <v>3.2301480484522194E-2</v>
@@ -539,11 +533,9 @@
         <v>4</v>
       </c>
       <c r="B5" s="1">
-        <f t="shared" si="0"/>
         <v>2.4</v>
       </c>
       <c r="C5" s="1">
-        <f t="shared" si="1"/>
         <v>-1.2</v>
       </c>
       <c r="D5" s="2">
@@ -561,12 +553,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1">
-        <f t="shared" si="0"/>
         <v>2.4</v>
       </c>
       <c r="C6" s="1">
-        <f t="shared" si="1"/>
-        <v>-0.8</v>
+        <v>0.8</v>
       </c>
       <c r="D6" s="2">
         <v>1.6150740242261097E-2</v>
@@ -583,11 +573,9 @@
         <v>6</v>
       </c>
       <c r="B7" s="1">
-        <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="C7" s="1">
-        <f t="shared" si="1"/>
         <v>-4</v>
       </c>
       <c r="D7" s="2">
@@ -605,12 +593,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1">
-        <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="C8" s="1">
-        <f t="shared" si="1"/>
-        <v>-4</v>
+        <v>4</v>
       </c>
       <c r="D8" s="2">
         <v>5.3835800807536999E-2</v>
@@ -627,11 +613,9 @@
         <v>8</v>
       </c>
       <c r="B9" s="1">
-        <f t="shared" si="0"/>
         <v>2.4</v>
       </c>
       <c r="C9" s="1">
-        <f t="shared" si="1"/>
         <v>-0.8</v>
       </c>
       <c r="D9" s="2">
@@ -649,12 +633,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1">
-        <f t="shared" si="0"/>
         <v>2.4</v>
       </c>
       <c r="C10" s="1">
-        <f t="shared" si="1"/>
-        <v>-0.8</v>
+        <v>0.8</v>
       </c>
       <c r="D10" s="2">
         <v>1.6150740242261097E-2</v>
@@ -671,11 +653,9 @@
         <v>10</v>
       </c>
       <c r="B11" s="1">
-        <f t="shared" si="0"/>
         <v>1.7999999999999998</v>
       </c>
       <c r="C11" s="1">
-        <f t="shared" si="1"/>
         <v>-1.2</v>
       </c>
       <c r="D11" s="2">
@@ -693,12 +673,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1">
-        <f t="shared" si="0"/>
         <v>2.4</v>
       </c>
       <c r="C12" s="1">
-        <f t="shared" si="1"/>
-        <v>-1.4000000000000001</v>
+        <v>1.4000000000000001</v>
       </c>
       <c r="D12" s="2">
         <v>1.6150740242261097E-2</v>
@@ -715,11 +693,9 @@
         <v>12</v>
       </c>
       <c r="B13" s="1">
-        <f t="shared" si="0"/>
         <v>2.4</v>
       </c>
       <c r="C13" s="1">
-        <f t="shared" si="1"/>
         <v>-1.4000000000000001</v>
       </c>
       <c r="D13" s="2">
@@ -737,12 +713,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1">
-        <f t="shared" si="0"/>
         <v>4.8</v>
       </c>
       <c r="C14" s="1">
-        <f t="shared" si="1"/>
-        <v>-3.2</v>
+        <v>3.2</v>
       </c>
       <c r="D14" s="2">
         <v>3.2301480484522194E-2</v>
@@ -759,11 +733,9 @@
         <v>14</v>
       </c>
       <c r="B15" s="1">
-        <f t="shared" si="0"/>
         <v>2.4</v>
       </c>
       <c r="C15" s="1">
-        <f t="shared" si="1"/>
         <v>-0.4</v>
       </c>
       <c r="D15" s="2">
@@ -781,12 +753,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="1">
-        <f t="shared" si="0"/>
         <v>2.4</v>
       </c>
       <c r="C16" s="1">
-        <f t="shared" si="1"/>
-        <v>-0.8</v>
+        <v>0.8</v>
       </c>
       <c r="D16" s="2">
         <v>1.6150740242261097E-2</v>
@@ -803,11 +773,9 @@
         <v>16</v>
       </c>
       <c r="B17" s="1">
-        <f t="shared" si="0"/>
         <v>2.4</v>
       </c>
       <c r="C17" s="1">
-        <f t="shared" si="1"/>
         <v>-0.8</v>
       </c>
       <c r="D17" s="2">
@@ -825,12 +793,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="1">
-        <f t="shared" si="0"/>
-        <v>3.5999999999999996</v>
+        <v>5.3999999999999995</v>
       </c>
       <c r="C18" s="1">
-        <f t="shared" si="1"/>
-        <v>-1.6</v>
+        <v>1.6</v>
       </c>
       <c r="D18" s="2">
         <v>2.4226110363391645E-2</v>
@@ -847,11 +813,9 @@
         <v>18</v>
       </c>
       <c r="B19" s="1">
-        <f t="shared" si="0"/>
-        <v>3.5999999999999996</v>
+        <v>5.3999999999999995</v>
       </c>
       <c r="C19" s="1">
-        <f t="shared" si="1"/>
         <v>-1.6</v>
       </c>
       <c r="D19" s="2">
@@ -869,12 +833,10 @@
         <v>19</v>
       </c>
       <c r="B20" s="1">
-        <f t="shared" si="0"/>
-        <v>3.5999999999999996</v>
+        <v>5.3999999999999995</v>
       </c>
       <c r="C20" s="1">
-        <f t="shared" si="1"/>
-        <v>-1.6</v>
+        <v>1.6</v>
       </c>
       <c r="D20" s="2">
         <v>2.4226110363391645E-2</v>
@@ -891,11 +853,9 @@
         <v>20</v>
       </c>
       <c r="B21" s="1">
-        <f t="shared" si="0"/>
-        <v>3.5999999999999996</v>
+        <v>5.3999999999999995</v>
       </c>
       <c r="C21" s="1">
-        <f t="shared" si="1"/>
         <v>-1.6</v>
       </c>
       <c r="D21" s="2">
@@ -913,12 +873,10 @@
         <v>21</v>
       </c>
       <c r="B22" s="1">
-        <f t="shared" si="0"/>
-        <v>3.5999999999999996</v>
+        <v>5.3999999999999995</v>
       </c>
       <c r="C22" s="1">
-        <f t="shared" si="1"/>
-        <v>-1.6</v>
+        <v>1.6</v>
       </c>
       <c r="D22" s="2">
         <v>2.4226110363391645E-2</v>
@@ -935,11 +893,9 @@
         <v>22</v>
       </c>
       <c r="B23" s="1">
-        <f t="shared" si="0"/>
-        <v>3.5999999999999996</v>
+        <v>5.3999999999999995</v>
       </c>
       <c r="C23" s="1">
-        <f t="shared" si="1"/>
         <v>-2</v>
       </c>
       <c r="D23" s="2">
@@ -957,12 +913,10 @@
         <v>23</v>
       </c>
       <c r="B24" s="1">
-        <f t="shared" si="0"/>
-        <v>16.8</v>
+        <v>25.2</v>
       </c>
       <c r="C24" s="1">
-        <f t="shared" si="1"/>
-        <v>-8</v>
+        <v>8</v>
       </c>
       <c r="D24" s="2">
         <v>0.11305518169582769</v>
@@ -979,11 +933,9 @@
         <v>24</v>
       </c>
       <c r="B25" s="1">
-        <f t="shared" si="0"/>
-        <v>16.8</v>
+        <v>25.2</v>
       </c>
       <c r="C25" s="1">
-        <f t="shared" si="1"/>
         <v>-8</v>
       </c>
       <c r="D25" s="2">
@@ -1001,12 +953,10 @@
         <v>25</v>
       </c>
       <c r="B26" s="1">
-        <f t="shared" si="0"/>
-        <v>2.4</v>
+        <v>3.5999999999999996</v>
       </c>
       <c r="C26" s="1">
-        <f t="shared" si="1"/>
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="D26" s="2">
         <v>1.6150740242261097E-2</v>
@@ -1023,11 +973,9 @@
         <v>26</v>
       </c>
       <c r="B27" s="1">
-        <f t="shared" si="0"/>
-        <v>2.4</v>
+        <v>3.5999999999999996</v>
       </c>
       <c r="C27" s="1">
-        <f t="shared" si="1"/>
         <v>-1</v>
       </c>
       <c r="D27" s="2">
@@ -1045,12 +993,10 @@
         <v>27</v>
       </c>
       <c r="B28" s="1">
-        <f t="shared" si="0"/>
-        <v>2.4</v>
+        <v>3.5999999999999996</v>
       </c>
       <c r="C28" s="1">
-        <f t="shared" si="1"/>
-        <v>-0.8</v>
+        <v>0.8</v>
       </c>
       <c r="D28" s="2">
         <v>1.6150740242261097E-2</v>
@@ -1067,11 +1013,9 @@
         <v>28</v>
       </c>
       <c r="B29" s="1">
-        <f t="shared" si="0"/>
-        <v>4.8</v>
+        <v>7.1999999999999993</v>
       </c>
       <c r="C29" s="1">
-        <f t="shared" si="1"/>
         <v>-2.8000000000000003</v>
       </c>
       <c r="D29" s="2">
@@ -1089,12 +1033,10 @@
         <v>29</v>
       </c>
       <c r="B30" s="1">
-        <f t="shared" si="0"/>
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C30" s="1">
-        <f t="shared" si="1"/>
-        <v>-24</v>
+        <v>24</v>
       </c>
       <c r="D30" s="2">
         <v>5.3835800807536999E-2</v>
@@ -1111,11 +1053,9 @@
         <v>30</v>
       </c>
       <c r="B31" s="1">
-        <f t="shared" si="0"/>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C31" s="1">
-        <f t="shared" si="1"/>
         <v>-2.8000000000000003</v>
       </c>
       <c r="D31" s="2">
@@ -1133,12 +1073,10 @@
         <v>31</v>
       </c>
       <c r="B32" s="1">
-        <f t="shared" si="0"/>
-        <v>8.4</v>
+        <v>12.6</v>
       </c>
       <c r="C32" s="1">
-        <f t="shared" si="1"/>
-        <v>-4</v>
+        <v>4</v>
       </c>
       <c r="D32" s="2">
         <v>5.6527590847913846E-2</v>
@@ -1155,11 +1093,9 @@
         <v>32</v>
       </c>
       <c r="B33" s="1">
-        <f t="shared" si="0"/>
-        <v>2.4</v>
+        <v>3.5999999999999996</v>
       </c>
       <c r="C33" s="1">
-        <f t="shared" si="1"/>
         <v>-1.6</v>
       </c>
       <c r="D33" s="2">

--- a/data/OP1/case33_2/case33_2_operational_data.xlsx
+++ b/data/OP1/case33_2/case33_2_operational_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/micaelsimoes/PycharmProjects/shared-resources-planning/data/OP1/case33_2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0063B4B5-7359-A141-B3F8-B41F1F042D2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3257B2F7-A476-5149-A743-EFF0E019D7F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1120" yWindow="620" windowWidth="29400" windowHeight="19120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1120" yWindow="620" windowWidth="50080" windowHeight="28180" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Characterization" sheetId="2" r:id="rId1"/>
@@ -69368,76 +69368,76 @@
         <v>1</v>
       </c>
       <c r="D2" s="1">
-        <v>4.9164000000000012</v>
+        <v>17.207400000000003</v>
       </c>
       <c r="E2" s="1">
-        <v>5.0804000000000009</v>
+        <v>17.781400000000005</v>
       </c>
       <c r="F2" s="1">
-        <v>4.5491999999999999</v>
+        <v>15.9222</v>
       </c>
       <c r="G2" s="1">
-        <v>4.3119999999999994</v>
+        <v>15.091999999999999</v>
       </c>
       <c r="H2" s="1">
-        <v>3.5328000000000004</v>
+        <v>12.364800000000001</v>
       </c>
       <c r="I2" s="1">
-        <v>2.9984000000000006</v>
+        <v>10.494400000000002</v>
       </c>
       <c r="J2" s="1">
-        <v>3.6668000000000003</v>
+        <v>12.8338</v>
       </c>
       <c r="K2" s="1">
-        <v>0.63680000000000003</v>
+        <v>2.2288000000000001</v>
       </c>
       <c r="L2" s="1">
-        <v>0.56000000000000005</v>
+        <v>1.9600000000000002</v>
       </c>
       <c r="M2" s="1">
-        <v>0.8163999999999999</v>
+        <v>2.8573999999999997</v>
       </c>
       <c r="N2" s="1">
-        <v>0.48080000000000006</v>
+        <v>1.6828000000000003</v>
       </c>
       <c r="O2" s="1">
-        <v>0.6008</v>
+        <v>2.1028000000000002</v>
       </c>
       <c r="P2" s="1">
-        <v>0.95720000000000027</v>
+        <v>3.350200000000001</v>
       </c>
       <c r="Q2" s="1">
-        <v>1.7636000000000003</v>
+        <v>6.172600000000001</v>
       </c>
       <c r="R2" s="1">
-        <v>1.8815999999999999</v>
+        <v>6.5855999999999995</v>
       </c>
       <c r="S2" s="1">
-        <v>1.8503999999999998</v>
+        <v>6.476399999999999</v>
       </c>
       <c r="T2" s="1">
-        <v>1.038</v>
+        <v>3.633</v>
       </c>
       <c r="U2" s="1">
-        <v>2.1143999999999998</v>
+        <v>7.4003999999999994</v>
       </c>
       <c r="V2" s="1">
-        <v>1.2408000000000001</v>
+        <v>4.3428000000000004</v>
       </c>
       <c r="W2" s="1">
-        <v>0.87239999999999984</v>
+        <v>3.0533999999999994</v>
       </c>
       <c r="X2" s="1">
-        <v>1.3248000000000002</v>
+        <v>4.6368000000000009</v>
       </c>
       <c r="Y2" s="1">
-        <v>0.81880000000000008</v>
+        <v>2.8658000000000001</v>
       </c>
       <c r="Z2" s="1">
-        <v>3.7372000000000005</v>
+        <v>13.080200000000001</v>
       </c>
       <c r="AA2" s="1">
-        <v>4.5052000000000003</v>
+        <v>15.7682</v>
       </c>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.2">
@@ -69451,76 +69451,76 @@
         <v>1</v>
       </c>
       <c r="D3" s="1">
-        <v>-11.100000000000001</v>
+        <v>-38.850000000000009</v>
       </c>
       <c r="E3" s="1">
-        <v>-11.8696</v>
+        <v>-41.543599999999998</v>
       </c>
       <c r="F3" s="1">
-        <v>-13.349600000000002</v>
+        <v>-46.723600000000005</v>
       </c>
       <c r="G3" s="1">
-        <v>-14.400400000000001</v>
+        <v>-50.401400000000002</v>
       </c>
       <c r="H3" s="1">
-        <v>-15.392000000000001</v>
+        <v>-53.872000000000007</v>
       </c>
       <c r="I3" s="1">
-        <v>-16.798000000000002</v>
+        <v>-58.793000000000006</v>
       </c>
       <c r="J3" s="1">
-        <v>-16.028400000000001</v>
+        <v>-56.099400000000003</v>
       </c>
       <c r="K3" s="1">
-        <v>-17.979759999999999</v>
+        <v>-62.929159999999996</v>
       </c>
       <c r="L3" s="1">
-        <v>-16.307359999999996</v>
+        <v>-57.075759999999988</v>
       </c>
       <c r="M3" s="1">
-        <v>-23.952839999999998</v>
+        <v>-83.834939999999989</v>
       </c>
       <c r="N3" s="1">
-        <v>-23.707360000000005</v>
+        <v>-82.975760000000022</v>
       </c>
       <c r="O3" s="1">
-        <v>-21.672160000000002</v>
+        <v>-75.852560000000011</v>
       </c>
       <c r="P3" s="1">
-        <v>-20.774560000000001</v>
+        <v>-72.71096</v>
       </c>
       <c r="Q3" s="1">
-        <v>-20.057480000000002</v>
+        <v>-70.201180000000008</v>
       </c>
       <c r="R3" s="1">
-        <v>-18.905680000000004</v>
+        <v>-66.169880000000006</v>
       </c>
       <c r="S3" s="1">
-        <v>-17.204239999999999</v>
+        <v>-60.214839999999995</v>
       </c>
       <c r="T3" s="1">
-        <v>-16.086960000000001</v>
+        <v>-56.304360000000003</v>
       </c>
       <c r="U3" s="1">
-        <v>-14.396240000000002</v>
+        <v>-50.386840000000007</v>
       </c>
       <c r="V3" s="1">
-        <v>-9.1377199999999998</v>
+        <v>-31.982019999999999</v>
       </c>
       <c r="W3" s="1">
-        <v>-10.226479999999999</v>
+        <v>-35.792679999999997</v>
       </c>
       <c r="X3" s="1">
-        <v>-10.809839999999999</v>
+        <v>-37.834440000000001</v>
       </c>
       <c r="Y3" s="1">
-        <v>-11.605399999999999</v>
+        <v>-40.618899999999996</v>
       </c>
       <c r="Z3" s="1">
-        <v>-9.2204000000000015</v>
+        <v>-32.271400000000007</v>
       </c>
       <c r="AA3" s="1">
-        <v>-9.797600000000001</v>
+        <v>-34.291600000000003</v>
       </c>
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.2">
@@ -69534,76 +69534,76 @@
         <v>1</v>
       </c>
       <c r="D4" s="1">
-        <v>10.69356</v>
+        <v>37.427459999999996</v>
       </c>
       <c r="E4" s="1">
-        <v>11.440319999999996</v>
+        <v>40.041119999999985</v>
       </c>
       <c r="F4" s="1">
-        <v>12.82724</v>
+        <v>44.895339999999997</v>
       </c>
       <c r="G4" s="1">
-        <v>13.802440000000002</v>
+        <v>48.308540000000008</v>
       </c>
       <c r="H4" s="1">
-        <v>14.691399999999998</v>
+        <v>51.419899999999991</v>
       </c>
       <c r="I4" s="1">
-        <v>16.042000000000002</v>
+        <v>56.147000000000006</v>
       </c>
       <c r="J4" s="1">
-        <v>15.293999999999999</v>
+        <v>53.528999999999996</v>
       </c>
       <c r="K4" s="1">
-        <v>17.259160000000001</v>
+        <v>60.407060000000001</v>
       </c>
       <c r="L4" s="1">
-        <v>15.809160000000002</v>
+        <v>55.332060000000006</v>
       </c>
       <c r="M4" s="1">
-        <v>18.039439999999999</v>
+        <v>63.138039999999997</v>
       </c>
       <c r="N4" s="1">
-        <v>18.181480000000001</v>
+        <v>63.635180000000005</v>
       </c>
       <c r="O4" s="1">
-        <v>17.019639999999999</v>
+        <v>59.568739999999998</v>
       </c>
       <c r="P4" s="1">
-        <v>16.446000000000002</v>
+        <v>57.561000000000007</v>
       </c>
       <c r="Q4" s="1">
-        <v>16.02328</v>
+        <v>56.081479999999999</v>
       </c>
       <c r="R4" s="1">
-        <v>15.016320000000004</v>
+        <v>52.557120000000012</v>
       </c>
       <c r="S4" s="1">
-        <v>13.671480000000003</v>
+        <v>47.850180000000009</v>
       </c>
       <c r="T4" s="1">
-        <v>12.736039999999997</v>
+        <v>44.576139999999988</v>
       </c>
       <c r="U4" s="1">
-        <v>11.38288</v>
+        <v>39.84008</v>
       </c>
       <c r="V4" s="1">
-        <v>8.9093599999999995</v>
+        <v>31.182759999999998</v>
       </c>
       <c r="W4" s="1">
-        <v>9.9721600000000006</v>
+        <v>34.902560000000001</v>
       </c>
       <c r="X4" s="1">
-        <v>10.596560000000002</v>
+        <v>37.08796000000001</v>
       </c>
       <c r="Y4" s="1">
-        <v>11.414560000000002</v>
+        <v>39.950960000000009</v>
       </c>
       <c r="Z4" s="1">
-        <v>8.8819999999999997</v>
+        <v>31.087</v>
       </c>
       <c r="AA4" s="1">
-        <v>9.4448000000000025</v>
+        <v>33.05680000000001</v>
       </c>
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.2">
@@ -69617,76 +69617,76 @@
         <v>2</v>
       </c>
       <c r="D5" s="1">
-        <v>4.8672360000000019</v>
+        <v>17.035326000000005</v>
       </c>
       <c r="E5" s="1">
-        <v>5.0804000000000009</v>
+        <v>17.781400000000005</v>
       </c>
       <c r="F5" s="1">
-        <v>4.7311680000000003</v>
+        <v>16.559088000000003</v>
       </c>
       <c r="G5" s="1">
-        <v>4.3982399999999995</v>
+        <v>15.393839999999997</v>
       </c>
       <c r="H5" s="1">
-        <v>3.4621440000000003</v>
+        <v>12.117504</v>
       </c>
       <c r="I5" s="1">
-        <v>2.8784640000000006</v>
+        <v>10.074624000000002</v>
       </c>
       <c r="J5" s="1">
-        <v>3.7034680000000004</v>
+        <v>12.962138000000001</v>
       </c>
       <c r="K5" s="1">
-        <v>0.62406400000000006</v>
+        <v>2.1842240000000004</v>
       </c>
       <c r="L5" s="1">
-        <v>0.58240000000000014</v>
+        <v>2.0384000000000007</v>
       </c>
       <c r="M5" s="1">
-        <v>0.85721999999999998</v>
+        <v>3.00027</v>
       </c>
       <c r="N5" s="1">
-        <v>0.4711840000000001</v>
+        <v>1.6491440000000004</v>
       </c>
       <c r="O5" s="1">
-        <v>0.60680800000000001</v>
+        <v>2.123828</v>
       </c>
       <c r="P5" s="1">
-        <v>0.95720000000000027</v>
+        <v>3.350200000000001</v>
       </c>
       <c r="Q5" s="1">
-        <v>1.8517800000000002</v>
+        <v>6.4812300000000009</v>
       </c>
       <c r="R5" s="1">
-        <v>1.8815999999999999</v>
+        <v>6.5855999999999995</v>
       </c>
       <c r="S5" s="1">
-        <v>1.8874079999999998</v>
+        <v>6.6059279999999987</v>
       </c>
       <c r="T5" s="1">
-        <v>0.98609999999999998</v>
+        <v>3.4513499999999997</v>
       </c>
       <c r="U5" s="1">
-        <v>2.2201199999999996</v>
+        <v>7.7704199999999988</v>
       </c>
       <c r="V5" s="1">
-        <v>1.2532080000000001</v>
+        <v>4.386228</v>
       </c>
       <c r="W5" s="1">
-        <v>0.89857199999999982</v>
+        <v>3.1450019999999994</v>
       </c>
       <c r="X5" s="1">
-        <v>1.3380480000000003</v>
+        <v>4.6831680000000011</v>
       </c>
       <c r="Y5" s="1">
-        <v>0.77786</v>
+        <v>2.7225099999999998</v>
       </c>
       <c r="Z5" s="1">
-        <v>3.8119440000000004</v>
+        <v>13.341804000000002</v>
       </c>
       <c r="AA5" s="1">
-        <v>4.5052000000000003</v>
+        <v>15.7682</v>
       </c>
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.2">
@@ -69700,76 +69700,76 @@
         <v>2</v>
       </c>
       <c r="D6" s="1">
-        <v>-11.100000000000001</v>
+        <v>-38.850000000000009</v>
       </c>
       <c r="E6" s="1">
-        <v>-11.750904</v>
+        <v>-41.128163999999998</v>
       </c>
       <c r="F6" s="1">
-        <v>-13.349600000000002</v>
+        <v>-46.723600000000005</v>
       </c>
       <c r="G6" s="1">
-        <v>-13.68038</v>
+        <v>-47.881329999999998</v>
       </c>
       <c r="H6" s="1">
-        <v>-14.930240000000001</v>
+        <v>-52.255840000000006</v>
       </c>
       <c r="I6" s="1">
-        <v>-16.126080000000002</v>
+        <v>-56.441280000000006</v>
       </c>
       <c r="J6" s="1">
-        <v>-16.188684000000002</v>
+        <v>-56.660394000000011</v>
       </c>
       <c r="K6" s="1">
-        <v>-17.979759999999999</v>
+        <v>-62.929159999999996</v>
       </c>
       <c r="L6" s="1">
-        <v>-16.307359999999996</v>
+        <v>-57.075759999999988</v>
       </c>
       <c r="M6" s="1">
-        <v>-23.713311599999997</v>
+        <v>-82.99659059999999</v>
       </c>
       <c r="N6" s="1">
-        <v>-24.181507200000006</v>
+        <v>-84.635275200000024</v>
       </c>
       <c r="O6" s="1">
-        <v>-21.238716800000002</v>
+        <v>-74.335508800000014</v>
       </c>
       <c r="P6" s="1">
-        <v>-21.605542400000001</v>
+        <v>-75.619398400000009</v>
       </c>
       <c r="Q6" s="1">
-        <v>-19.8569052</v>
+        <v>-69.4991682</v>
       </c>
       <c r="R6" s="1">
-        <v>-19.661907200000005</v>
+        <v>-68.81667520000002</v>
       </c>
       <c r="S6" s="1">
-        <v>-17.204239999999999</v>
+        <v>-60.214839999999995</v>
       </c>
       <c r="T6" s="1">
-        <v>-15.765220800000002</v>
+        <v>-55.178272800000002</v>
       </c>
       <c r="U6" s="1">
-        <v>-13.820390400000001</v>
+        <v>-48.371366399999999</v>
       </c>
       <c r="V6" s="1">
-        <v>-9.1377199999999998</v>
+        <v>-31.982019999999999</v>
       </c>
       <c r="W6" s="1">
-        <v>-10.124215199999998</v>
+        <v>-35.434753199999996</v>
       </c>
       <c r="X6" s="1">
-        <v>-10.593643199999999</v>
+        <v>-37.077751199999994</v>
       </c>
       <c r="Y6" s="1">
-        <v>-11.257237999999999</v>
+        <v>-39.400332999999996</v>
       </c>
       <c r="Z6" s="1">
-        <v>-9.5892160000000004</v>
+        <v>-33.562256000000005</v>
       </c>
       <c r="AA6" s="1">
-        <v>-9.4056960000000007</v>
+        <v>-32.919936</v>
       </c>
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.2">
@@ -69783,76 +69783,76 @@
         <v>2</v>
       </c>
       <c r="D7" s="1">
-        <v>10.158882</v>
+        <v>35.556086999999998</v>
       </c>
       <c r="E7" s="1">
-        <v>11.783529599999998</v>
+        <v>41.242353599999994</v>
       </c>
       <c r="F7" s="1">
-        <v>12.314150399999999</v>
+        <v>43.099526399999995</v>
       </c>
       <c r="G7" s="1">
-        <v>13.112318000000002</v>
+        <v>45.893113000000007</v>
       </c>
       <c r="H7" s="1">
-        <v>14.250657999999998</v>
+        <v>49.877302999999991</v>
       </c>
       <c r="I7" s="1">
-        <v>16.523260000000004</v>
+        <v>57.831410000000012</v>
       </c>
       <c r="J7" s="1">
-        <v>14.68224</v>
+        <v>51.387839999999997</v>
       </c>
       <c r="K7" s="1">
-        <v>16.568793600000003</v>
+        <v>57.990777600000008</v>
       </c>
       <c r="L7" s="1">
-        <v>15.967251600000003</v>
+        <v>55.885380600000012</v>
       </c>
       <c r="M7" s="1">
-        <v>17.4982568</v>
+        <v>61.243898799999997</v>
       </c>
       <c r="N7" s="1">
-        <v>18.181480000000001</v>
+        <v>63.635180000000005</v>
       </c>
       <c r="O7" s="1">
-        <v>17.360032799999999</v>
+        <v>60.760114799999997</v>
       </c>
       <c r="P7" s="1">
-        <v>15.788160000000003</v>
+        <v>55.25856000000001</v>
       </c>
       <c r="Q7" s="1">
-        <v>16.343745599999998</v>
+        <v>57.203109599999991</v>
       </c>
       <c r="R7" s="1">
-        <v>15.767136000000004</v>
+        <v>55.184976000000013</v>
       </c>
       <c r="S7" s="1">
-        <v>14.081624400000003</v>
+        <v>49.285685400000006</v>
       </c>
       <c r="T7" s="1">
-        <v>12.353958799999997</v>
+        <v>43.238855799999989</v>
       </c>
       <c r="U7" s="1">
-        <v>11.838195199999999</v>
+        <v>41.433683199999997</v>
       </c>
       <c r="V7" s="1">
-        <v>9.3548279999999995</v>
+        <v>32.741897999999999</v>
       </c>
       <c r="W7" s="1">
-        <v>9.9721600000000006</v>
+        <v>34.902560000000001</v>
       </c>
       <c r="X7" s="1">
-        <v>10.066732000000002</v>
+        <v>35.233562000000006</v>
       </c>
       <c r="Y7" s="1">
-        <v>11.985288000000002</v>
+        <v>41.948508000000011</v>
       </c>
       <c r="Z7" s="1">
-        <v>8.7931799999999996</v>
+        <v>30.776129999999998</v>
       </c>
       <c r="AA7" s="1">
-        <v>9.4448000000000025</v>
+        <v>33.05680000000001</v>
       </c>
     </row>
     <row r="8" spans="1:27" x14ac:dyDescent="0.2">
@@ -69866,76 +69866,76 @@
         <v>3</v>
       </c>
       <c r="D8" s="1">
-        <v>4.7698912800000013</v>
+        <v>16.694619480000004</v>
       </c>
       <c r="E8" s="1">
-        <v>5.1820080000000006</v>
+        <v>18.137028000000001</v>
       </c>
       <c r="F8" s="1">
-        <v>4.7784796800000002</v>
+        <v>16.724678879999999</v>
       </c>
       <c r="G8" s="1">
-        <v>4.2223103999999996</v>
+        <v>14.778086399999999</v>
       </c>
       <c r="H8" s="1">
-        <v>3.2890367999999999</v>
+        <v>11.5116288</v>
       </c>
       <c r="I8" s="1">
-        <v>2.9072486400000006</v>
+        <v>10.175370240000003</v>
       </c>
       <c r="J8" s="1">
-        <v>3.6664333200000003</v>
+        <v>12.832516620000002</v>
       </c>
       <c r="K8" s="1">
-        <v>0.64902656000000003</v>
+        <v>2.27159296</v>
       </c>
       <c r="L8" s="1">
-        <v>0.58240000000000014</v>
+        <v>2.0384000000000007</v>
       </c>
       <c r="M8" s="1">
-        <v>0.81435900000000006</v>
+        <v>2.8502565000000004</v>
       </c>
       <c r="N8" s="1">
-        <v>0.47589584000000007</v>
+        <v>1.6656354400000002</v>
       </c>
       <c r="O8" s="1">
-        <v>0.60680800000000001</v>
+        <v>2.123828</v>
       </c>
       <c r="P8" s="1">
-        <v>0.94762800000000025</v>
+        <v>3.316698000000001</v>
       </c>
       <c r="Q8" s="1">
-        <v>1.7591910000000002</v>
+        <v>6.1571685000000009</v>
       </c>
       <c r="R8" s="1">
-        <v>1.8251519999999999</v>
+        <v>6.3880319999999999</v>
       </c>
       <c r="S8" s="1">
-        <v>1.8307857599999997</v>
+        <v>6.4077501599999991</v>
       </c>
       <c r="T8" s="1">
-        <v>0.98609999999999998</v>
+        <v>3.4513499999999997</v>
       </c>
       <c r="U8" s="1">
-        <v>2.1535163999999996</v>
+        <v>7.5373073999999987</v>
       </c>
       <c r="V8" s="1">
-        <v>1.22814384</v>
+        <v>4.2985034400000002</v>
       </c>
       <c r="W8" s="1">
-        <v>0.9435005999999998</v>
+        <v>3.3022520999999991</v>
       </c>
       <c r="X8" s="1">
-        <v>1.3380480000000003</v>
+        <v>4.6831680000000011</v>
       </c>
       <c r="Y8" s="1">
-        <v>0.80897439999999998</v>
+        <v>2.8314103999999998</v>
       </c>
       <c r="Z8" s="1">
-        <v>3.7357051200000004</v>
+        <v>13.074967920000002</v>
       </c>
       <c r="AA8" s="1">
-        <v>4.3249919999999999</v>
+        <v>15.137471999999999</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.2">
@@ -69949,76 +69949,76 @@
         <v>3</v>
       </c>
       <c r="D9" s="1">
-        <v>-10.545000000000002</v>
+        <v>-36.907500000000006</v>
       </c>
       <c r="E9" s="1">
-        <v>-11.750904</v>
+        <v>-41.128163999999998</v>
       </c>
       <c r="F9" s="1">
-        <v>-12.682120000000003</v>
+        <v>-44.387420000000013</v>
       </c>
       <c r="G9" s="1">
-        <v>-13.68038</v>
+        <v>-47.881329999999998</v>
       </c>
       <c r="H9" s="1">
-        <v>-15.527449600000002</v>
+        <v>-54.346073600000011</v>
       </c>
       <c r="I9" s="1">
-        <v>-15.803558400000002</v>
+        <v>-55.312454400000007</v>
       </c>
       <c r="J9" s="1">
-        <v>-16.674344520000002</v>
+        <v>-58.360205820000004</v>
       </c>
       <c r="K9" s="1">
-        <v>-17.620164799999998</v>
+        <v>-61.670576799999992</v>
       </c>
       <c r="L9" s="1">
-        <v>-17.122727999999995</v>
+        <v>-59.929547999999983</v>
       </c>
       <c r="M9" s="1">
-        <v>-23.950444715999996</v>
+        <v>-83.826556505999989</v>
       </c>
       <c r="N9" s="1">
-        <v>-23.456061984000009</v>
+        <v>-82.096216944000034</v>
       </c>
       <c r="O9" s="1">
-        <v>-21.875878304000004</v>
+        <v>-76.565574064000018</v>
       </c>
       <c r="P9" s="1">
-        <v>-21.389486976000004</v>
+        <v>-74.863204416000016</v>
       </c>
       <c r="Q9" s="1">
-        <v>-20.849750459999999</v>
+        <v>-72.974126609999999</v>
       </c>
       <c r="R9" s="1">
-        <v>-19.465288128000005</v>
+        <v>-68.128508448000019</v>
       </c>
       <c r="S9" s="1">
-        <v>-17.204239999999999</v>
+        <v>-60.214839999999995</v>
       </c>
       <c r="T9" s="1">
-        <v>-15.607568592000002</v>
+        <v>-54.626490072000003</v>
       </c>
       <c r="U9" s="1">
-        <v>-14.373206016000001</v>
+        <v>-50.306221056000005</v>
       </c>
       <c r="V9" s="1">
-        <v>-9.4118516000000003</v>
+        <v>-32.941480599999998</v>
       </c>
       <c r="W9" s="1">
-        <v>-10.022973047999997</v>
+        <v>-35.08040566799999</v>
       </c>
       <c r="X9" s="1">
-        <v>-10.593643199999999</v>
+        <v>-37.077751199999994</v>
       </c>
       <c r="Y9" s="1">
-        <v>-10.694376099999999</v>
+        <v>-37.430316349999998</v>
       </c>
       <c r="Z9" s="1">
-        <v>-9.4933238400000004</v>
+        <v>-33.226633440000001</v>
       </c>
       <c r="AA9" s="1">
-        <v>-9.8759808000000007</v>
+        <v>-34.565932799999999</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.2">
@@ -70032,76 +70032,76 @@
         <v>3</v>
       </c>
       <c r="D10" s="1">
-        <v>10.36205964</v>
+        <v>36.267208740000001</v>
       </c>
       <c r="E10" s="1">
-        <v>11.194353119999999</v>
+        <v>39.180235919999994</v>
       </c>
       <c r="F10" s="1">
-        <v>12.314150399999999</v>
+        <v>43.099526399999995</v>
       </c>
       <c r="G10" s="1">
-        <v>12.718948460000002</v>
+        <v>44.516319610000004</v>
       </c>
       <c r="H10" s="1">
-        <v>13.538125099999997</v>
+        <v>47.383437849999986</v>
       </c>
       <c r="I10" s="1">
-        <v>15.697097000000003</v>
+        <v>54.939839500000012</v>
       </c>
       <c r="J10" s="1">
-        <v>13.948127999999999</v>
+        <v>48.818447999999997</v>
       </c>
       <c r="K10" s="1">
-        <v>15.740353920000002</v>
+        <v>55.091238720000007</v>
       </c>
       <c r="L10" s="1">
-        <v>15.647906568000003</v>
+        <v>54.767672988000015</v>
       </c>
       <c r="M10" s="1">
-        <v>17.848221936000002</v>
+        <v>62.468776776000006</v>
       </c>
       <c r="N10" s="1">
-        <v>18.5451096</v>
+        <v>64.907883600000005</v>
       </c>
       <c r="O10" s="1">
-        <v>16.49203116</v>
+        <v>57.722109060000001</v>
       </c>
       <c r="P10" s="1">
-        <v>16.419686400000003</v>
+        <v>57.468902400000012</v>
       </c>
       <c r="Q10" s="1">
-        <v>16.507183055999999</v>
+        <v>57.775140695999994</v>
       </c>
       <c r="R10" s="1">
-        <v>16.082478720000005</v>
+        <v>56.288675520000012</v>
       </c>
       <c r="S10" s="1">
-        <v>13.518359424000003</v>
+        <v>47.314257984000008</v>
       </c>
       <c r="T10" s="1">
-        <v>12.848117151999997</v>
+        <v>44.968410031999987</v>
       </c>
       <c r="U10" s="1">
-        <v>11.364667391999999</v>
+        <v>39.776335871999997</v>
       </c>
       <c r="V10" s="1">
-        <v>9.822569399999999</v>
+        <v>34.3789929</v>
       </c>
       <c r="W10" s="1">
-        <v>10.071881600000001</v>
+        <v>35.251585600000006</v>
       </c>
       <c r="X10" s="1">
-        <v>10.469401280000001</v>
+        <v>36.642904480000006</v>
       </c>
       <c r="Y10" s="1">
-        <v>12.344846640000004</v>
+        <v>43.206963240000015</v>
       </c>
       <c r="Z10" s="1">
-        <v>8.8811117999999993</v>
+        <v>31.083891299999998</v>
       </c>
       <c r="AA10" s="1">
-        <v>9.9170400000000036</v>
+        <v>34.709640000000014</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.2">
@@ -70115,76 +70115,76 @@
         <v>1</v>
       </c>
       <c r="D11" s="1">
-        <v>4.6705800000000011</v>
+        <v>16.347030000000004</v>
       </c>
       <c r="E11" s="1">
-        <v>4.8263800000000003</v>
+        <v>16.892330000000001</v>
       </c>
       <c r="F11" s="1">
-        <v>4.3217400000000001</v>
+        <v>15.126090000000001</v>
       </c>
       <c r="G11" s="1">
-        <v>4.0963999999999992</v>
+        <v>14.337399999999997</v>
       </c>
       <c r="H11" s="1">
-        <v>3.35616</v>
+        <v>11.746560000000001</v>
       </c>
       <c r="I11" s="1">
-        <v>2.8484800000000003</v>
+        <v>9.9696800000000003</v>
       </c>
       <c r="J11" s="1">
-        <v>3.48346</v>
+        <v>12.19211</v>
       </c>
       <c r="K11" s="1">
-        <v>0.60496000000000005</v>
+        <v>2.1173600000000001</v>
       </c>
       <c r="L11" s="1">
-        <v>0.53200000000000003</v>
+        <v>1.8620000000000001</v>
       </c>
       <c r="M11" s="1">
-        <v>0.77557999999999983</v>
+        <v>2.7145299999999994</v>
       </c>
       <c r="N11" s="1">
-        <v>0.45676000000000005</v>
+        <v>1.5986600000000002</v>
       </c>
       <c r="O11" s="1">
-        <v>0.57075999999999993</v>
+        <v>1.9976599999999998</v>
       </c>
       <c r="P11" s="1">
-        <v>0.90934000000000026</v>
+        <v>3.1826900000000009</v>
       </c>
       <c r="Q11" s="1">
-        <v>1.6754200000000001</v>
+        <v>5.8639700000000001</v>
       </c>
       <c r="R11" s="1">
-        <v>1.7875199999999998</v>
+        <v>6.2563199999999988</v>
       </c>
       <c r="S11" s="1">
-        <v>1.7578799999999997</v>
+        <v>6.1525799999999986</v>
       </c>
       <c r="T11" s="1">
-        <v>0.98609999999999998</v>
+        <v>3.4513499999999997</v>
       </c>
       <c r="U11" s="1">
-        <v>2.0086799999999996</v>
+        <v>7.0303799999999983</v>
       </c>
       <c r="V11" s="1">
-        <v>1.17876</v>
+        <v>4.1256599999999999</v>
       </c>
       <c r="W11" s="1">
-        <v>0.82877999999999985</v>
+        <v>2.9007299999999994</v>
       </c>
       <c r="X11" s="1">
-        <v>1.2585600000000001</v>
+        <v>4.4049600000000009</v>
       </c>
       <c r="Y11" s="1">
-        <v>0.77786</v>
+        <v>2.7225099999999998</v>
       </c>
       <c r="Z11" s="1">
-        <v>3.5503400000000003</v>
+        <v>12.426190000000002</v>
       </c>
       <c r="AA11" s="1">
-        <v>4.2799399999999999</v>
+        <v>14.979789999999999</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.2">
@@ -70198,76 +70198,76 @@
         <v>1</v>
       </c>
       <c r="D12" s="1">
-        <v>-10.966800000000003</v>
+        <v>-38.383800000000008</v>
       </c>
       <c r="E12" s="1">
-        <v>-11.750904</v>
+        <v>-41.128163999999998</v>
       </c>
       <c r="F12" s="1">
-        <v>-12.048014000000002</v>
+        <v>-42.168049000000011</v>
       </c>
       <c r="G12" s="1">
-        <v>-13.68038</v>
+        <v>-47.881329999999998</v>
       </c>
       <c r="H12" s="1">
-        <v>-15.372175104000002</v>
+        <v>-53.802612864000004</v>
       </c>
       <c r="I12" s="1">
-        <v>-16.435700736000001</v>
+        <v>-57.524952576000004</v>
       </c>
       <c r="J12" s="1">
-        <v>-16.174114184400004</v>
+        <v>-56.609399645400018</v>
       </c>
       <c r="K12" s="1">
-        <v>-17.443963151999995</v>
+        <v>-61.053871031999982</v>
       </c>
       <c r="L12" s="1">
-        <v>-17.465182559999995</v>
+        <v>-61.128138959999987</v>
       </c>
       <c r="M12" s="1">
-        <v>-22.992426927359997</v>
+        <v>-80.473494245759994</v>
       </c>
       <c r="N12" s="1">
-        <v>-23.690622603840012</v>
+        <v>-82.917179113440042</v>
       </c>
       <c r="O12" s="1">
-        <v>-22.532154653120006</v>
+        <v>-78.862541285920017</v>
       </c>
       <c r="P12" s="1">
-        <v>-20.747802366720002</v>
+        <v>-72.617308283520003</v>
       </c>
       <c r="Q12" s="1">
-        <v>-19.807262936999997</v>
+        <v>-69.325420279499994</v>
       </c>
       <c r="R12" s="1">
-        <v>-19.270635246720005</v>
+        <v>-67.44722336352001</v>
       </c>
       <c r="S12" s="1">
-        <v>-17.204239999999999</v>
+        <v>-60.214839999999995</v>
       </c>
       <c r="T12" s="1">
-        <v>-16.231871335680001</v>
+        <v>-56.811549674880006</v>
       </c>
       <c r="U12" s="1">
-        <v>-14.08574189568</v>
+        <v>-49.300096634879999</v>
       </c>
       <c r="V12" s="1">
-        <v>-9.0353775360000004</v>
+        <v>-31.623821376000002</v>
       </c>
       <c r="W12" s="1">
-        <v>-10.123202778479998</v>
+        <v>-35.431209724679995</v>
       </c>
       <c r="X12" s="1">
-        <v>-11.123325359999999</v>
+        <v>-38.931638759999998</v>
       </c>
       <c r="Y12" s="1">
-        <v>-10.694376099999999</v>
+        <v>-37.430316349999998</v>
       </c>
       <c r="Z12" s="1">
-        <v>-9.2085241248000003</v>
+        <v>-32.229834436800004</v>
       </c>
       <c r="AA12" s="1">
-        <v>-9.6784611839999997</v>
+        <v>-33.874614143999999</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.2">
@@ -70281,76 +70281,76 @@
         <v>1</v>
       </c>
       <c r="D13" s="1">
-        <v>9.8439566579999997</v>
+        <v>34.453848303000001</v>
       </c>
       <c r="E13" s="1">
-        <v>10.8585225264</v>
+        <v>38.004828842400002</v>
       </c>
       <c r="F13" s="1">
-        <v>12.437291903999999</v>
+        <v>43.530521663999991</v>
       </c>
       <c r="G13" s="1">
-        <v>12.464569490800002</v>
+        <v>43.625993217800008</v>
       </c>
       <c r="H13" s="1">
-        <v>13.402743848999997</v>
+        <v>46.909603471499992</v>
       </c>
       <c r="I13" s="1">
-        <v>15.854067970000003</v>
+        <v>55.489237895000009</v>
       </c>
       <c r="J13" s="1">
-        <v>13.948127999999999</v>
+        <v>48.818447999999997</v>
       </c>
       <c r="K13" s="1">
-        <v>15.897757459200001</v>
+        <v>55.642151107200007</v>
       </c>
       <c r="L13" s="1">
-        <v>15.647906568000003</v>
+        <v>54.767672988000015</v>
       </c>
       <c r="M13" s="1">
-        <v>18.383668594080003</v>
+        <v>64.342840079280009</v>
       </c>
       <c r="N13" s="1">
-        <v>17.617854120000001</v>
+        <v>61.66248942</v>
       </c>
       <c r="O13" s="1">
-        <v>15.667429602</v>
+        <v>54.836003607000002</v>
       </c>
       <c r="P13" s="1">
-        <v>16.912276992000002</v>
+        <v>59.192969472000009</v>
       </c>
       <c r="Q13" s="1">
-        <v>16.34211122544</v>
+        <v>57.197389289040004</v>
       </c>
       <c r="R13" s="1">
-        <v>15.760829145600006</v>
+        <v>55.162902009600018</v>
       </c>
       <c r="S13" s="1">
-        <v>12.842441452800003</v>
+        <v>44.94854508480001</v>
       </c>
       <c r="T13" s="1">
-        <v>13.490523009599997</v>
+        <v>47.216830533599989</v>
       </c>
       <c r="U13" s="1">
-        <v>11.819254087679999</v>
+        <v>41.36738930688</v>
       </c>
       <c r="V13" s="1">
-        <v>9.9207950939999989</v>
+        <v>34.722782828999996</v>
       </c>
       <c r="W13" s="1">
-        <v>10.374038048000003</v>
+        <v>36.30913316800001</v>
       </c>
       <c r="X13" s="1">
-        <v>10.364707267200002</v>
+        <v>36.276475435200005</v>
       </c>
       <c r="Y13" s="1">
-        <v>12.838640505600004</v>
+        <v>44.935241769600012</v>
       </c>
       <c r="Z13" s="1">
-        <v>8.8811117999999993</v>
+        <v>31.083891299999998</v>
       </c>
       <c r="AA13" s="1">
-        <v>10.115380800000004</v>
+        <v>35.403832800000018</v>
       </c>
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.2">
@@ -70364,76 +70364,76 @@
         <v>2</v>
       </c>
       <c r="D14" s="1">
-        <v>4.8574032000000011</v>
+        <v>17.000911200000004</v>
       </c>
       <c r="E14" s="1">
-        <v>4.8746438000000003</v>
+        <v>17.061253300000001</v>
       </c>
       <c r="F14" s="1">
-        <v>4.3217400000000001</v>
+        <v>15.126090000000001</v>
       </c>
       <c r="G14" s="1">
-        <v>4.1783279999999987</v>
+        <v>14.624147999999995</v>
       </c>
       <c r="H14" s="1">
-        <v>3.3897216000000001</v>
+        <v>11.8640256</v>
       </c>
       <c r="I14" s="1">
-        <v>2.7630256000000002</v>
+        <v>9.6705896000000013</v>
       </c>
       <c r="J14" s="1">
-        <v>3.6227983999999998</v>
+        <v>12.679794399999999</v>
       </c>
       <c r="K14" s="1">
-        <v>0.59891040000000006</v>
+        <v>2.0961864000000001</v>
       </c>
       <c r="L14" s="1">
-        <v>0.54796000000000011</v>
+        <v>1.9178600000000003</v>
       </c>
       <c r="M14" s="1">
-        <v>0.76782419999999985</v>
+        <v>2.6873846999999995</v>
       </c>
       <c r="N14" s="1">
-        <v>0.47046280000000001</v>
+        <v>1.6466198000000001</v>
       </c>
       <c r="O14" s="1">
-        <v>0.54222199999999998</v>
+        <v>1.897777</v>
       </c>
       <c r="P14" s="1">
-        <v>0.90934000000000026</v>
+        <v>3.1826900000000009</v>
       </c>
       <c r="Q14" s="1">
-        <v>1.7256826000000001</v>
+        <v>6.0398890999999999</v>
       </c>
       <c r="R14" s="1">
-        <v>1.7517695999999998</v>
+        <v>6.1311935999999996</v>
       </c>
       <c r="S14" s="1">
-        <v>1.7930375999999995</v>
+        <v>6.2756315999999979</v>
       </c>
       <c r="T14" s="1">
-        <v>0.94665599999999994</v>
+        <v>3.3132959999999998</v>
       </c>
       <c r="U14" s="1">
-        <v>1.9283327999999995</v>
+        <v>6.7491647999999982</v>
       </c>
       <c r="V14" s="1">
-        <v>1.1316096</v>
+        <v>3.9606336</v>
       </c>
       <c r="W14" s="1">
-        <v>0.87021899999999985</v>
+        <v>3.0457664999999996</v>
       </c>
       <c r="X14" s="1">
-        <v>1.2208032000000002</v>
+        <v>4.2728112000000005</v>
       </c>
       <c r="Y14" s="1">
-        <v>0.80119580000000001</v>
+        <v>2.8041852999999999</v>
       </c>
       <c r="Z14" s="1">
-        <v>3.5858434000000003</v>
+        <v>12.550451900000001</v>
       </c>
       <c r="AA14" s="1">
-        <v>4.1943412000000002</v>
+        <v>14.680194200000001</v>
       </c>
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.2">
@@ -70447,76 +70447,76 @@
         <v>2</v>
       </c>
       <c r="D15" s="1">
-        <v>-11.076468000000002</v>
+        <v>-38.767638000000005</v>
       </c>
       <c r="E15" s="1">
-        <v>-11.515885920000001</v>
+        <v>-40.305600720000001</v>
       </c>
       <c r="F15" s="1">
-        <v>-11.566093440000001</v>
+        <v>-40.481327040000004</v>
       </c>
       <c r="G15" s="1">
-        <v>-13.133164799999999</v>
+        <v>-45.966076799999996</v>
       </c>
       <c r="H15" s="1">
-        <v>-15.987062108160004</v>
+        <v>-55.954717378560012</v>
       </c>
       <c r="I15" s="1">
-        <v>-16.106986721279998</v>
+        <v>-56.374453524479996</v>
       </c>
       <c r="J15" s="1">
-        <v>-15.850631900712003</v>
+        <v>-55.477211652492009</v>
       </c>
       <c r="K15" s="1">
-        <v>-16.746204625919994</v>
+        <v>-58.611716190719974</v>
       </c>
       <c r="L15" s="1">
-        <v>-17.639834385599997</v>
+        <v>-61.739420349599989</v>
       </c>
       <c r="M15" s="1">
-        <v>-22.762502658086397</v>
+        <v>-79.668759303302394</v>
       </c>
       <c r="N15" s="1">
-        <v>-24.638247507993611</v>
+        <v>-86.23386627797764</v>
       </c>
       <c r="O15" s="1">
-        <v>-22.081511560057606</v>
+        <v>-77.285290460201622</v>
       </c>
       <c r="P15" s="1">
-        <v>-20.540324343052802</v>
+        <v>-71.891135200684801</v>
       </c>
       <c r="Q15" s="1">
-        <v>-19.014972419519996</v>
+        <v>-66.55240346831998</v>
       </c>
       <c r="R15" s="1">
-        <v>-18.885222541785605</v>
+        <v>-66.098278896249624</v>
       </c>
       <c r="S15" s="1">
-        <v>-16.344027999999998</v>
+        <v>-57.204097999999995</v>
       </c>
       <c r="T15" s="1">
-        <v>-16.231871335680001</v>
+        <v>-56.811549674880006</v>
       </c>
       <c r="U15" s="1">
-        <v>-13.9448844767232</v>
+        <v>-48.807095668531197</v>
       </c>
       <c r="V15" s="1">
-        <v>-9.0353775360000004</v>
+        <v>-31.623821376000002</v>
       </c>
       <c r="W15" s="1">
-        <v>-10.325666834049597</v>
+        <v>-36.13983391917359</v>
       </c>
       <c r="X15" s="1">
-        <v>-11.234558613599999</v>
+        <v>-39.320955147599996</v>
       </c>
       <c r="Y15" s="1">
-        <v>-10.801319861</v>
+        <v>-37.8046195135</v>
       </c>
       <c r="Z15" s="1">
-        <v>-8.8401831598079994</v>
+        <v>-30.940641059327998</v>
       </c>
       <c r="AA15" s="1">
-        <v>-10.06559963136</v>
+        <v>-35.229598709759998</v>
       </c>
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.2">
@@ -70530,76 +70530,76 @@
         <v>2</v>
       </c>
       <c r="D16" s="1">
-        <v>9.3517588250999992</v>
+        <v>32.731155887849994</v>
       </c>
       <c r="E16" s="1">
-        <v>10.424181625344</v>
+        <v>36.484635688703996</v>
       </c>
       <c r="F16" s="1">
-        <v>13.059156499199998</v>
+        <v>45.707047747199994</v>
       </c>
       <c r="G16" s="1">
-        <v>11.965986711168002</v>
+        <v>41.880953489088007</v>
       </c>
       <c r="H16" s="1">
-        <v>14.072881041449996</v>
+        <v>49.25508364507499</v>
       </c>
       <c r="I16" s="1">
-        <v>15.219905251200002</v>
+        <v>53.269668379200006</v>
       </c>
       <c r="J16" s="1">
-        <v>14.087609279999999</v>
+        <v>49.306632479999998</v>
       </c>
       <c r="K16" s="1">
-        <v>15.897757459200001</v>
+        <v>55.642151107200007</v>
       </c>
       <c r="L16" s="1">
-        <v>14.865511239600004</v>
+        <v>52.029289338600009</v>
       </c>
       <c r="M16" s="1">
-        <v>18.751341965961604</v>
+        <v>65.629696880865609</v>
       </c>
       <c r="N16" s="1">
-        <v>17.265497037599999</v>
+        <v>60.429239631599998</v>
       </c>
       <c r="O16" s="1">
-        <v>16.29412678608</v>
+        <v>57.029443751279999</v>
       </c>
       <c r="P16" s="1">
-        <v>16.235785912320001</v>
+        <v>56.825250693120005</v>
       </c>
       <c r="Q16" s="1">
-        <v>16.832374562203199</v>
+        <v>58.913310967711197</v>
       </c>
       <c r="R16" s="1">
-        <v>16.076045728512007</v>
+        <v>56.26616004979202</v>
       </c>
       <c r="S16" s="1">
-        <v>12.970865867328003</v>
+        <v>45.398030535648012</v>
       </c>
       <c r="T16" s="1">
-        <v>13.760333469791997</v>
+        <v>48.161167144271985</v>
       </c>
       <c r="U16" s="1">
-        <v>11.582869005926399</v>
+        <v>40.540041520742399</v>
       </c>
       <c r="V16" s="1">
-        <v>10.020003044939999</v>
+        <v>35.070010657289998</v>
       </c>
       <c r="W16" s="1">
-        <v>10.374038048000003</v>
+        <v>36.30913316800001</v>
       </c>
       <c r="X16" s="1">
-        <v>10.779295557888002</v>
+        <v>37.727534452608005</v>
       </c>
       <c r="Y16" s="1">
-        <v>13.095413315712005</v>
+        <v>45.833946604992015</v>
       </c>
       <c r="Z16" s="1">
-        <v>8.969922918</v>
+        <v>31.394730212999999</v>
       </c>
       <c r="AA16" s="1">
-        <v>9.7107655680000047</v>
+        <v>33.987679488000019</v>
       </c>
     </row>
     <row r="17" spans="1:27" x14ac:dyDescent="0.2">
@@ -70613,76 +70613,76 @@
         <v>3</v>
       </c>
       <c r="D17" s="1">
-        <v>4.6145330400000013</v>
+        <v>16.150865640000006</v>
       </c>
       <c r="E17" s="1">
-        <v>5.0696295520000003</v>
+        <v>17.743703432</v>
       </c>
       <c r="F17" s="1">
-        <v>4.2785225999999996</v>
+        <v>14.974829099999999</v>
       </c>
       <c r="G17" s="1">
-        <v>4.3872443999999984</v>
+        <v>15.355355399999993</v>
       </c>
       <c r="H17" s="1">
-        <v>3.4236188159999998</v>
+        <v>11.982665855999999</v>
       </c>
       <c r="I17" s="1">
-        <v>2.7353953440000005</v>
+        <v>9.5738837040000018</v>
       </c>
       <c r="J17" s="1">
-        <v>3.5141144479999995</v>
+        <v>12.299400567999998</v>
       </c>
       <c r="K17" s="1">
-        <v>0.60489950400000003</v>
+        <v>2.1171482639999999</v>
       </c>
       <c r="L17" s="1">
-        <v>0.54796000000000011</v>
+        <v>1.9178600000000003</v>
       </c>
       <c r="M17" s="1">
-        <v>0.74478947399999984</v>
+        <v>2.6067631589999993</v>
       </c>
       <c r="N17" s="1">
-        <v>0.46575817200000003</v>
+        <v>1.630153602</v>
       </c>
       <c r="O17" s="1">
-        <v>0.53679977999999995</v>
+        <v>1.8787992299999998</v>
       </c>
       <c r="P17" s="1">
-        <v>0.90934000000000026</v>
+        <v>3.1826900000000009</v>
       </c>
       <c r="Q17" s="1">
-        <v>1.7429394260000002</v>
+        <v>6.100287991000001</v>
       </c>
       <c r="R17" s="1">
-        <v>1.8393580799999998</v>
+        <v>6.437753279999999</v>
       </c>
       <c r="S17" s="1">
-        <v>1.7033857199999993</v>
+        <v>5.9618500199999973</v>
       </c>
       <c r="T17" s="1">
-        <v>0.91825632000000001</v>
+        <v>3.2138971199999999</v>
       </c>
       <c r="U17" s="1">
-        <v>1.9090494719999995</v>
+        <v>6.6816731519999983</v>
       </c>
       <c r="V17" s="1">
-        <v>1.1542417919999999</v>
+        <v>4.0398462719999992</v>
       </c>
       <c r="W17" s="1">
-        <v>0.87021899999999985</v>
+        <v>3.0457664999999996</v>
       </c>
       <c r="X17" s="1">
-        <v>1.1963871360000002</v>
+        <v>4.1873549760000008</v>
       </c>
       <c r="Y17" s="1">
-        <v>0.80119580000000001</v>
+        <v>2.8041852999999999</v>
       </c>
       <c r="Z17" s="1">
-        <v>3.4424096640000004</v>
+        <v>12.048433824000002</v>
       </c>
       <c r="AA17" s="1">
-        <v>4.1104543759999999</v>
+        <v>14.386590315999999</v>
       </c>
     </row>
     <row r="18" spans="1:27" x14ac:dyDescent="0.2">
@@ -70696,76 +70696,76 @@
         <v>3</v>
       </c>
       <c r="D18" s="1">
-        <v>-10.965703320000003</v>
+        <v>-38.37996162000001</v>
       </c>
       <c r="E18" s="1">
-        <v>-11.976521356800001</v>
+        <v>-41.917824748800001</v>
       </c>
       <c r="F18" s="1">
-        <v>-10.987788768</v>
+        <v>-38.457260687999998</v>
       </c>
       <c r="G18" s="1">
-        <v>-13.264496447999999</v>
+        <v>-46.425737567999995</v>
       </c>
       <c r="H18" s="1">
-        <v>-16.466673971404802</v>
+        <v>-57.633358899916807</v>
       </c>
       <c r="I18" s="1">
-        <v>-16.268056588492797</v>
+        <v>-56.93819805972479</v>
       </c>
       <c r="J18" s="1">
-        <v>-15.216606624683523</v>
+        <v>-53.258123186392332</v>
       </c>
       <c r="K18" s="1">
-        <v>-17.081128718438393</v>
+        <v>-59.783950514534375</v>
       </c>
       <c r="L18" s="1">
-        <v>-17.816232729455997</v>
+        <v>-62.356814553095987</v>
       </c>
       <c r="M18" s="1">
-        <v>-21.852002551762943</v>
+        <v>-76.482008931170299</v>
       </c>
       <c r="N18" s="1">
-        <v>-25.131012458153482</v>
+        <v>-87.95854360353718</v>
       </c>
       <c r="O18" s="1">
-        <v>-21.86069644445703</v>
+        <v>-76.512437555599604</v>
       </c>
       <c r="P18" s="1">
-        <v>-21.156534073344389</v>
+        <v>-74.047869256705354</v>
       </c>
       <c r="Q18" s="1">
-        <v>-19.585421592105593</v>
+        <v>-68.548975572369571</v>
       </c>
       <c r="R18" s="1">
-        <v>-19.829483668874886</v>
+        <v>-69.403192841062094</v>
       </c>
       <c r="S18" s="1">
-        <v>-16.997789119999997</v>
+        <v>-59.49226191999999</v>
       </c>
       <c r="T18" s="1">
-        <v>-15.7449151956096</v>
+        <v>-55.107203184633605</v>
       </c>
       <c r="U18" s="1">
-        <v>-14.363231011024896</v>
+        <v>-50.271308538587135</v>
       </c>
       <c r="V18" s="1">
-        <v>-8.5836086592000012</v>
+        <v>-30.042630307200003</v>
       </c>
       <c r="W18" s="1">
-        <v>-10.119153497368606</v>
+        <v>-35.417037240790123</v>
       </c>
       <c r="X18" s="1">
-        <v>-11.122213027463999</v>
+        <v>-38.927745596123998</v>
       </c>
       <c r="Y18" s="1">
-        <v>-10.47728026517</v>
+        <v>-36.670480928095003</v>
       </c>
       <c r="Z18" s="1">
-        <v>-8.6633794966118405</v>
+        <v>-30.321828238141443</v>
       </c>
       <c r="AA18" s="1">
-        <v>-10.06559963136</v>
+        <v>-35.229598709759998</v>
       </c>
     </row>
     <row r="19" spans="1:27" x14ac:dyDescent="0.2">
@@ -70779,76 +70779,76 @@
         <v>3</v>
       </c>
       <c r="D19" s="1">
-        <v>8.884170883845</v>
+        <v>31.094598093457499</v>
       </c>
       <c r="E19" s="1">
-        <v>10.63266525785088</v>
+        <v>37.214328402478081</v>
       </c>
       <c r="F19" s="1">
-        <v>13.581522759167999</v>
+        <v>47.535329657087999</v>
       </c>
       <c r="G19" s="1">
-        <v>12.564286046726401</v>
+        <v>43.975001163542402</v>
       </c>
       <c r="H19" s="1">
-        <v>14.635796283107995</v>
+        <v>51.225286990877983</v>
       </c>
       <c r="I19" s="1">
-        <v>14.763308093664001</v>
+        <v>51.671578327824008</v>
       </c>
       <c r="J19" s="1">
-        <v>14.791989743999999</v>
+        <v>51.771964103999991</v>
       </c>
       <c r="K19" s="1">
-        <v>16.692645332160001</v>
+        <v>58.424258662560007</v>
       </c>
       <c r="L19" s="1">
-        <v>14.419545902412004</v>
+        <v>50.468410658442011</v>
       </c>
       <c r="M19" s="1">
-        <v>18.751341965961604</v>
+        <v>65.629696880865609</v>
       </c>
       <c r="N19" s="1">
-        <v>17.438152007976001</v>
+        <v>61.033532027916003</v>
       </c>
       <c r="O19" s="1">
-        <v>15.968244250358401</v>
+        <v>55.888854876254406</v>
       </c>
       <c r="P19" s="1">
-        <v>17.047575207936003</v>
+        <v>59.666513227776008</v>
       </c>
       <c r="Q19" s="1">
-        <v>16.327403325337105</v>
+        <v>57.14591163867987</v>
       </c>
       <c r="R19" s="1">
-        <v>15.272243442086406</v>
+        <v>53.452852047302422</v>
       </c>
       <c r="S19" s="1">
-        <v>12.841157208654723</v>
+        <v>44.944050230291531</v>
       </c>
       <c r="T19" s="1">
-        <v>13.760333469791997</v>
+        <v>48.161167144271985</v>
       </c>
       <c r="U19" s="1">
-        <v>11.814526386044927</v>
+        <v>41.35084235115724</v>
       </c>
       <c r="V19" s="1">
-        <v>10.420803166737599</v>
+        <v>36.472811083581597</v>
       </c>
       <c r="W19" s="1">
-        <v>10.685259189440004</v>
+        <v>37.398407163040012</v>
       </c>
       <c r="X19" s="1">
-        <v>10.779295557888002</v>
+        <v>37.727534452608005</v>
       </c>
       <c r="Y19" s="1">
-        <v>12.833505049397765</v>
+        <v>44.91726767289218</v>
       </c>
       <c r="Z19" s="1">
-        <v>8.6111260012799988</v>
+        <v>30.138941004479996</v>
       </c>
       <c r="AA19" s="1">
-        <v>9.4194426009600036</v>
+        <v>32.968049103360016</v>
       </c>
     </row>
     <row r="20" spans="1:27" x14ac:dyDescent="0.2">
@@ -70862,76 +70862,76 @@
         <v>1</v>
       </c>
       <c r="D20" s="1">
-        <v>5.1376380000000017</v>
+        <v>17.981733000000006</v>
       </c>
       <c r="E20" s="1">
-        <v>5.3090180000000009</v>
+        <v>18.581563000000003</v>
       </c>
       <c r="F20" s="1">
-        <v>4.7539140000000009</v>
+        <v>16.638699000000003</v>
       </c>
       <c r="G20" s="1">
-        <v>4.5060399999999996</v>
+        <v>15.771139999999999</v>
       </c>
       <c r="H20" s="1">
-        <v>3.6917760000000004</v>
+        <v>12.921216000000001</v>
       </c>
       <c r="I20" s="1">
-        <v>3.1333280000000006</v>
+        <v>10.966648000000003</v>
       </c>
       <c r="J20" s="1">
-        <v>3.8318060000000003</v>
+        <v>13.411321000000001</v>
       </c>
       <c r="K20" s="1">
-        <v>0.66545600000000016</v>
+        <v>2.3290960000000007</v>
       </c>
       <c r="L20" s="1">
-        <v>0.58520000000000005</v>
+        <v>2.0482</v>
       </c>
       <c r="M20" s="1">
-        <v>0.85313799999999984</v>
+        <v>2.9859829999999996</v>
       </c>
       <c r="N20" s="1">
-        <v>0.5024360000000001</v>
+        <v>1.7585260000000003</v>
       </c>
       <c r="O20" s="1">
-        <v>0.62783599999999995</v>
+        <v>2.1974259999999997</v>
       </c>
       <c r="P20" s="1">
-        <v>1.0002740000000003</v>
+        <v>3.5009590000000013</v>
       </c>
       <c r="Q20" s="1">
-        <v>1.8429620000000002</v>
+        <v>6.4503670000000008</v>
       </c>
       <c r="R20" s="1">
-        <v>1.966272</v>
+        <v>6.8819520000000001</v>
       </c>
       <c r="S20" s="1">
-        <v>1.9336679999999997</v>
+        <v>6.7678379999999994</v>
       </c>
       <c r="T20" s="1">
-        <v>1.0847100000000001</v>
+        <v>3.7964850000000001</v>
       </c>
       <c r="U20" s="1">
-        <v>2.2095479999999998</v>
+        <v>7.7334179999999995</v>
       </c>
       <c r="V20" s="1">
-        <v>1.2966360000000001</v>
+        <v>4.5382260000000008</v>
       </c>
       <c r="W20" s="1">
-        <v>0.91165799999999986</v>
+        <v>3.1908029999999994</v>
       </c>
       <c r="X20" s="1">
-        <v>1.3844160000000003</v>
+        <v>4.8454560000000013</v>
       </c>
       <c r="Y20" s="1">
-        <v>0.85564600000000002</v>
+        <v>2.994761</v>
       </c>
       <c r="Z20" s="1">
-        <v>3.9053740000000006</v>
+        <v>13.668809000000001</v>
       </c>
       <c r="AA20" s="1">
-        <v>4.7079339999999998</v>
+        <v>16.477768999999999</v>
       </c>
     </row>
     <row r="21" spans="1:27" x14ac:dyDescent="0.2">
@@ -70945,76 +70945,76 @@
         <v>1</v>
       </c>
       <c r="D21" s="1">
-        <v>-10.636732220400004</v>
+        <v>-37.228562771400014</v>
       </c>
       <c r="E21" s="1">
-        <v>-12.575347424640002</v>
+        <v>-44.013715986240008</v>
       </c>
       <c r="F21" s="1">
-        <v>-10.658155104959999</v>
+        <v>-37.303542867359994</v>
       </c>
       <c r="G21" s="1">
-        <v>-13.529786376959999</v>
+        <v>-47.354252319359993</v>
       </c>
       <c r="H21" s="1">
-        <v>-17.125340930260997</v>
+        <v>-59.938693255913492</v>
       </c>
       <c r="I21" s="1">
-        <v>-16.268056588492797</v>
+        <v>-56.93819805972479</v>
       </c>
       <c r="J21" s="1">
-        <v>-15.36877269093036</v>
+        <v>-53.790704418256261</v>
       </c>
       <c r="K21" s="1">
-        <v>-16.910317431254008</v>
+        <v>-59.186111009389023</v>
       </c>
       <c r="L21" s="1">
-        <v>-17.994395056750555</v>
+        <v>-62.98038269862694</v>
       </c>
       <c r="M21" s="1">
-        <v>-21.852002551762943</v>
+        <v>-76.482008931170299</v>
       </c>
       <c r="N21" s="1">
-        <v>-24.879702333571945</v>
+        <v>-87.07895816750181</v>
       </c>
       <c r="O21" s="1">
-        <v>-22.735124302235313</v>
+        <v>-79.572935057823599</v>
       </c>
       <c r="P21" s="1">
-        <v>-21.156534073344389</v>
+        <v>-74.047869256705354</v>
       </c>
       <c r="Q21" s="1">
-        <v>-20.172984239868761</v>
+        <v>-70.605444839540667</v>
       </c>
       <c r="R21" s="1">
-        <v>-19.234599158808638</v>
+        <v>-67.321097055830236</v>
       </c>
       <c r="S21" s="1">
-        <v>-16.657833337599996</v>
+        <v>-58.302416681599986</v>
       </c>
       <c r="T21" s="1">
-        <v>-14.957669435829121</v>
+        <v>-52.351843025401926</v>
       </c>
       <c r="U21" s="1">
-        <v>-14.363231011024896</v>
+        <v>-50.271308538587135</v>
       </c>
       <c r="V21" s="1">
-        <v>-8.7552808323840008</v>
+        <v>-30.643482913344002</v>
       </c>
       <c r="W21" s="1">
-        <v>-10.422728102289664</v>
+        <v>-36.479548358013822</v>
       </c>
       <c r="X21" s="1">
-        <v>-11.56710154856256</v>
+        <v>-40.484855419968959</v>
       </c>
       <c r="Y21" s="1">
-        <v>-10.267734659866601</v>
+        <v>-35.937071309533103</v>
       </c>
       <c r="Z21" s="1">
-        <v>-8.6633794966118405</v>
+        <v>-30.321828238141443</v>
       </c>
       <c r="AA21" s="1">
-        <v>-10.367567620300798</v>
+        <v>-36.286486671052792</v>
       </c>
     </row>
     <row r="22" spans="1:27" x14ac:dyDescent="0.2">
@@ -71028,76 +71028,76 @@
         <v>1</v>
       </c>
       <c r="D22" s="1">
-        <v>8.4399623396527499</v>
+        <v>29.539868188784624</v>
       </c>
       <c r="E22" s="1">
-        <v>10.845318563007897</v>
+        <v>37.958614970527641</v>
       </c>
       <c r="F22" s="1">
-        <v>13.988968441943038</v>
+        <v>48.961389546800632</v>
       </c>
       <c r="G22" s="1">
-        <v>12.313000325791872</v>
+        <v>43.095501140271551</v>
       </c>
       <c r="H22" s="1">
-        <v>14.928512208770155</v>
+        <v>52.249792730695539</v>
       </c>
       <c r="I22" s="1">
-        <v>14.61567501272736</v>
+        <v>51.154862544545757</v>
       </c>
       <c r="J22" s="1">
-        <v>14.348230051679998</v>
+        <v>50.218805180879997</v>
       </c>
       <c r="K22" s="1">
-        <v>17.1934246921248</v>
+        <v>60.176986422436798</v>
       </c>
       <c r="L22" s="1">
-        <v>15.140523197532605</v>
+        <v>52.99183119136412</v>
       </c>
       <c r="M22" s="1">
-        <v>19.313882224940453</v>
+        <v>67.598587787291592</v>
       </c>
       <c r="N22" s="1">
-        <v>17.089388967816479</v>
+        <v>59.812861387357678</v>
       </c>
       <c r="O22" s="1">
-        <v>16.287609135365571</v>
+        <v>57.006631973779498</v>
       </c>
       <c r="P22" s="1">
-        <v>17.72947821625344</v>
+        <v>62.053173756887041</v>
       </c>
       <c r="Q22" s="1">
-        <v>16.817225425097217</v>
+        <v>58.860288987840256</v>
       </c>
       <c r="R22" s="1">
-        <v>14.814076138823815</v>
+        <v>51.849266485883348</v>
       </c>
       <c r="S22" s="1">
-        <v>12.712745636568174</v>
+        <v>44.49460972798861</v>
       </c>
       <c r="T22" s="1">
-        <v>14.035540139187836</v>
+        <v>49.124390487157427</v>
       </c>
       <c r="U22" s="1">
-        <v>11.46009059446358</v>
+        <v>40.110317080622529</v>
       </c>
       <c r="V22" s="1">
-        <v>10.733427261739727</v>
+        <v>37.566995416089043</v>
       </c>
       <c r="W22" s="1">
-        <v>11.112669557017602</v>
+        <v>38.89434344956161</v>
       </c>
       <c r="X22" s="1">
-        <v>10.671502602309122</v>
+        <v>37.350259108081929</v>
       </c>
       <c r="Y22" s="1">
-        <v>12.705169998903786</v>
+        <v>44.468094996163252</v>
       </c>
       <c r="Z22" s="1">
-        <v>8.783348521305598</v>
+        <v>30.741719824569593</v>
       </c>
       <c r="AA22" s="1">
-        <v>9.5136370269696027</v>
+        <v>33.297729594393608</v>
       </c>
     </row>
     <row r="23" spans="1:27" x14ac:dyDescent="0.2">
@@ -71111,76 +71111,76 @@
         <v>2</v>
       </c>
       <c r="D23" s="1">
-        <v>5.3945199000000015</v>
+        <v>18.880819650000007</v>
       </c>
       <c r="E23" s="1">
-        <v>5.5744689000000003</v>
+        <v>19.510641150000001</v>
       </c>
       <c r="F23" s="1">
-        <v>4.5637574400000007</v>
+        <v>15.973151040000003</v>
       </c>
       <c r="G23" s="1">
-        <v>4.3708587999999997</v>
+        <v>15.298005799999999</v>
       </c>
       <c r="H23" s="1">
-        <v>3.6548582400000003</v>
+        <v>12.792003840000001</v>
       </c>
       <c r="I23" s="1">
-        <v>3.0706614400000007</v>
+        <v>10.747315040000002</v>
       </c>
       <c r="J23" s="1">
-        <v>3.7934879399999999</v>
+        <v>13.27720779</v>
       </c>
       <c r="K23" s="1">
-        <v>0.67211056000000013</v>
+        <v>2.3523869600000005</v>
       </c>
       <c r="L23" s="1">
-        <v>0.57349600000000001</v>
+        <v>2.0072359999999998</v>
       </c>
       <c r="M23" s="1">
-        <v>0.86166937999999993</v>
+        <v>3.0158428299999995</v>
       </c>
       <c r="N23" s="1">
-        <v>0.52253344000000013</v>
+        <v>1.8288670400000004</v>
       </c>
       <c r="O23" s="1">
-        <v>0.65294943999999999</v>
+        <v>2.2853230399999998</v>
       </c>
       <c r="P23" s="1">
-        <v>0.98026852000000031</v>
+        <v>3.4309398200000012</v>
       </c>
       <c r="Q23" s="1">
-        <v>1.9166804800000004</v>
+        <v>6.7083816800000013</v>
       </c>
       <c r="R23" s="1">
-        <v>2.0645856</v>
+        <v>7.2260495999999996</v>
       </c>
       <c r="S23" s="1">
-        <v>1.8369845999999999</v>
+        <v>6.4294460999999998</v>
       </c>
       <c r="T23" s="1">
-        <v>1.1172513000000002</v>
+        <v>3.9103795500000005</v>
       </c>
       <c r="U23" s="1">
-        <v>2.2979299199999996</v>
+        <v>8.0427547199999978</v>
       </c>
       <c r="V23" s="1">
-        <v>1.2707032800000002</v>
+        <v>4.4474614800000012</v>
       </c>
       <c r="W23" s="1">
-        <v>0.90254141999999993</v>
+        <v>3.1588949699999995</v>
       </c>
       <c r="X23" s="1">
-        <v>1.3844160000000003</v>
+        <v>4.8454560000000013</v>
       </c>
       <c r="Y23" s="1">
-        <v>0.88131538000000009</v>
+        <v>3.0846038300000003</v>
       </c>
       <c r="Z23" s="1">
-        <v>4.1006427000000008</v>
+        <v>14.352249450000002</v>
       </c>
       <c r="AA23" s="1">
-        <v>4.8020926800000003</v>
+        <v>16.807324380000001</v>
       </c>
     </row>
     <row r="24" spans="1:27" x14ac:dyDescent="0.2">
@@ -71194,76 +71194,76 @@
         <v>2</v>
       </c>
       <c r="D24" s="1">
-        <v>-10.743099542604005</v>
+        <v>-37.600848399114021</v>
       </c>
       <c r="E24" s="1">
-        <v>-12.952607847379202</v>
+        <v>-45.334127465827208</v>
       </c>
       <c r="F24" s="1">
-        <v>-10.444992002860799</v>
+        <v>-36.557472010012795</v>
       </c>
       <c r="G24" s="1">
-        <v>-13.259190649420798</v>
+        <v>-46.407167272972792</v>
       </c>
       <c r="H24" s="1">
-        <v>-17.296594339563608</v>
+        <v>-60.538080188472627</v>
       </c>
       <c r="I24" s="1">
-        <v>-15.780014890838013</v>
+        <v>-55.230052117933042</v>
       </c>
       <c r="J24" s="1">
-        <v>-15.061397237111754</v>
+        <v>-52.714890329891141</v>
       </c>
       <c r="K24" s="1">
-        <v>-17.248523779879086</v>
+        <v>-60.369833229576798</v>
       </c>
       <c r="L24" s="1">
-        <v>-18.714170859020577</v>
+        <v>-65.499598006572015</v>
       </c>
       <c r="M24" s="1">
-        <v>-22.507562628315831</v>
+        <v>-78.776469199105406</v>
       </c>
       <c r="N24" s="1">
-        <v>-23.88451424022907</v>
+        <v>-83.595799840801746</v>
       </c>
       <c r="O24" s="1">
-        <v>-23.417178031302374</v>
+        <v>-81.96012310955831</v>
       </c>
       <c r="P24" s="1">
-        <v>-20.521838051144059</v>
+        <v>-71.826433179004198</v>
       </c>
       <c r="Q24" s="1">
-        <v>-19.769524555071385</v>
+        <v>-69.193335942749854</v>
       </c>
       <c r="R24" s="1">
-        <v>-19.234599158808638</v>
+        <v>-67.321097055830236</v>
       </c>
       <c r="S24" s="1">
-        <v>-15.991520004095996</v>
+        <v>-55.970320014335982</v>
       </c>
       <c r="T24" s="1">
-        <v>-15.107246130187413</v>
+        <v>-52.875361455655948</v>
       </c>
       <c r="U24" s="1">
-        <v>-13.645069460473652</v>
+        <v>-47.757743111657781</v>
       </c>
       <c r="V24" s="1">
-        <v>-8.405069599088641</v>
+        <v>-29.417743596810244</v>
       </c>
       <c r="W24" s="1">
-        <v>-10.422728102289664</v>
+        <v>-36.479548358013822</v>
       </c>
       <c r="X24" s="1">
-        <v>-12.029785610505062</v>
+        <v>-42.104249636767719</v>
       </c>
       <c r="Y24" s="1">
-        <v>-9.9597026200706029</v>
+        <v>-34.858959170247111</v>
       </c>
       <c r="Z24" s="1">
-        <v>-8.8366470865440778</v>
+        <v>-30.928264802904273</v>
       </c>
       <c r="AA24" s="1">
-        <v>-10.263891944097791</v>
+        <v>-35.923621804342268</v>
       </c>
     </row>
     <row r="25" spans="1:27" x14ac:dyDescent="0.2">
@@ -71277,76 +71277,76 @@
         <v>2</v>
       </c>
       <c r="D25" s="1">
-        <v>8.3555627162562232</v>
+        <v>29.244469506896781</v>
       </c>
       <c r="E25" s="1">
-        <v>10.845318563007897</v>
+        <v>37.958614970527641</v>
       </c>
       <c r="F25" s="1">
-        <v>13.289520019845886</v>
+        <v>46.513320069460605</v>
       </c>
       <c r="G25" s="1">
-        <v>12.55926033230771</v>
+        <v>43.957411163076983</v>
       </c>
       <c r="H25" s="1">
-        <v>15.227082452945558</v>
+        <v>53.294788585309455</v>
       </c>
       <c r="I25" s="1">
-        <v>15.054145263109181</v>
+        <v>52.689508420882134</v>
       </c>
       <c r="J25" s="1">
-        <v>14.491712352196798</v>
+        <v>50.720993232688791</v>
       </c>
       <c r="K25" s="1">
-        <v>17.1934246921248</v>
+        <v>60.176986422436798</v>
       </c>
       <c r="L25" s="1">
-        <v>14.383497037655975</v>
+        <v>50.342239631795913</v>
       </c>
       <c r="M25" s="1">
-        <v>20.086437513938073</v>
+        <v>70.302531298783251</v>
       </c>
       <c r="N25" s="1">
-        <v>17.602070636850975</v>
+        <v>61.607247228978409</v>
       </c>
       <c r="O25" s="1">
-        <v>16.450485226719227</v>
+        <v>57.576698293517296</v>
       </c>
       <c r="P25" s="1">
-        <v>17.72947821625344</v>
+        <v>62.053173756887041</v>
       </c>
       <c r="Q25" s="1">
-        <v>16.649053170846244</v>
+        <v>58.271686097961855</v>
       </c>
       <c r="R25" s="1">
-        <v>14.073372331882624</v>
+        <v>49.256803161589183</v>
       </c>
       <c r="S25" s="1">
-        <v>12.077108354739764</v>
+        <v>42.269879241589173</v>
       </c>
       <c r="T25" s="1">
-        <v>13.614473935012199</v>
+        <v>47.650658772542698</v>
       </c>
       <c r="U25" s="1">
-        <v>11.23088878257431</v>
+        <v>39.308110739010083</v>
       </c>
       <c r="V25" s="1">
-        <v>10.733427261739727</v>
+        <v>37.566995416089043</v>
       </c>
       <c r="W25" s="1">
-        <v>11.446049643728131</v>
+        <v>40.061173753048458</v>
       </c>
       <c r="X25" s="1">
-        <v>10.137927472193665</v>
+        <v>35.482746152677827</v>
       </c>
       <c r="Y25" s="1">
-        <v>13.340428498848976</v>
+        <v>46.691499745971413</v>
       </c>
       <c r="Z25" s="1">
-        <v>8.6076815508794855</v>
+        <v>30.1268854280782</v>
       </c>
       <c r="AA25" s="1">
-        <v>9.7990461377786904</v>
+        <v>34.296661482225417</v>
       </c>
     </row>
     <row r="26" spans="1:27" x14ac:dyDescent="0.2">
@@ -71360,76 +71360,76 @@
         <v>3</v>
       </c>
       <c r="D26" s="1">
-        <v>5.556355497000002</v>
+        <v>19.447244239500009</v>
       </c>
       <c r="E26" s="1">
-        <v>5.6302135890000002</v>
+        <v>19.705747561500001</v>
       </c>
       <c r="F26" s="1">
-        <v>4.518119865600001</v>
+        <v>15.813419529600004</v>
       </c>
       <c r="G26" s="1">
-        <v>4.5894017399999996</v>
+        <v>16.062906089999998</v>
       </c>
       <c r="H26" s="1">
-        <v>3.6914068224000003</v>
+        <v>12.919923878400001</v>
       </c>
       <c r="I26" s="1">
-        <v>3.0706614400000007</v>
+        <v>10.747315040000002</v>
       </c>
       <c r="J26" s="1">
-        <v>3.6038135429999998</v>
+        <v>12.613347400499999</v>
       </c>
       <c r="K26" s="1">
-        <v>0.63850503200000008</v>
+        <v>2.2347676120000002</v>
       </c>
       <c r="L26" s="1">
-        <v>0.54482120000000001</v>
+        <v>1.9068742000000001</v>
       </c>
       <c r="M26" s="1">
-        <v>0.83581929859999993</v>
+        <v>2.9253675450999999</v>
       </c>
       <c r="N26" s="1">
-        <v>0.51730810560000007</v>
+        <v>1.8105783696000002</v>
       </c>
       <c r="O26" s="1">
-        <v>0.6660084288</v>
+        <v>2.3310295008000002</v>
       </c>
       <c r="P26" s="1">
-        <v>0.96066314960000032</v>
+        <v>3.3623210236000012</v>
       </c>
       <c r="Q26" s="1">
-        <v>2.0125145040000003</v>
+        <v>7.0438007640000011</v>
       </c>
       <c r="R26" s="1">
-        <v>2.1678148799999999</v>
+        <v>7.5873520799999996</v>
       </c>
       <c r="S26" s="1">
-        <v>1.9288338299999999</v>
+        <v>6.7509184049999993</v>
       </c>
       <c r="T26" s="1">
-        <v>1.1284238130000002</v>
+        <v>3.9494833455000005</v>
       </c>
       <c r="U26" s="1">
-        <v>2.2979299199999996</v>
+        <v>8.0427547199999978</v>
       </c>
       <c r="V26" s="1">
-        <v>1.2707032800000002</v>
+        <v>4.4474614800000012</v>
       </c>
       <c r="W26" s="1">
-        <v>0.86643976319999993</v>
+        <v>3.0325391711999998</v>
       </c>
       <c r="X26" s="1">
-        <v>1.3428835200000002</v>
+        <v>4.7000923200000004</v>
       </c>
       <c r="Y26" s="1">
-        <v>0.89012853380000012</v>
+        <v>3.1154498683000003</v>
       </c>
       <c r="Z26" s="1">
-        <v>3.9776234190000008</v>
+        <v>13.921681966500003</v>
       </c>
       <c r="AA26" s="1">
-        <v>4.9461554604</v>
+        <v>17.3115441114</v>
       </c>
     </row>
     <row r="27" spans="1:27" x14ac:dyDescent="0.2">
@@ -71443,76 +71443,76 @@
         <v>3</v>
       </c>
       <c r="D27" s="1">
-        <v>-11.280254519734205</v>
+        <v>-39.480890819069721</v>
       </c>
       <c r="E27" s="1">
-        <v>-12.823081768905411</v>
+        <v>-44.880786191168937</v>
       </c>
       <c r="F27" s="1">
-        <v>-10.340542082832192</v>
+        <v>-36.191897289912674</v>
       </c>
       <c r="G27" s="1">
-        <v>-12.861414929938173</v>
+        <v>-45.014952254783601</v>
       </c>
       <c r="H27" s="1">
-        <v>-17.123628396167973</v>
+        <v>-59.932699386587906</v>
       </c>
       <c r="I27" s="1">
-        <v>-16.253415337563155</v>
+        <v>-56.886953681471041</v>
       </c>
       <c r="J27" s="1">
-        <v>-14.308327375256164</v>
+        <v>-50.079145813396572</v>
       </c>
       <c r="K27" s="1">
-        <v>-17.076038542080298</v>
+        <v>-59.766134897281042</v>
       </c>
       <c r="L27" s="1">
-        <v>-18.152745733249962</v>
+        <v>-63.534610066374867</v>
       </c>
       <c r="M27" s="1">
-        <v>-23.182789507165307</v>
+        <v>-81.139763275078579</v>
       </c>
       <c r="N27" s="1">
-        <v>-23.88451424022907</v>
+        <v>-83.595799840801746</v>
       </c>
       <c r="O27" s="1">
-        <v>-23.417178031302374</v>
+        <v>-81.96012310955831</v>
       </c>
       <c r="P27" s="1">
-        <v>-20.111401290121179</v>
+        <v>-70.389904515424121</v>
       </c>
       <c r="Q27" s="1">
-        <v>-19.769524555071385</v>
+        <v>-69.193335942749854</v>
       </c>
       <c r="R27" s="1">
-        <v>-19.61929114198481</v>
+        <v>-68.667518996946839</v>
       </c>
       <c r="S27" s="1">
-        <v>-16.311350404177915</v>
+        <v>-57.089726414622703</v>
       </c>
       <c r="T27" s="1">
-        <v>-15.560463514093035</v>
+        <v>-54.461622299325626</v>
       </c>
       <c r="U27" s="1">
-        <v>-13.645069460473652</v>
+        <v>-47.757743111657781</v>
       </c>
       <c r="V27" s="1">
-        <v>-8.5731709910704144</v>
+        <v>-30.006098468746451</v>
       </c>
       <c r="W27" s="1">
-        <v>-10.839637226381251</v>
+        <v>-37.938730292334377</v>
       </c>
       <c r="X27" s="1">
-        <v>-11.66889204218991</v>
+        <v>-40.841122147664684</v>
       </c>
       <c r="Y27" s="1">
-        <v>-10.059299646271308</v>
+        <v>-35.207548761949575</v>
       </c>
       <c r="Z27" s="1">
-        <v>-8.394814732216874</v>
+        <v>-29.38185156275906</v>
       </c>
       <c r="AA27" s="1">
-        <v>-10.469169782979748</v>
+        <v>-36.642094240429117</v>
       </c>
     </row>
     <row r="28" spans="1:27" x14ac:dyDescent="0.2">
@@ -71526,76 +71526,76 @@
         <v>3</v>
       </c>
       <c r="D28" s="1">
-        <v>8.104895834768536</v>
+        <v>28.367135421689877</v>
       </c>
       <c r="E28" s="1">
-        <v>10.519959006117661</v>
+        <v>36.819856521411815</v>
       </c>
       <c r="F28" s="1">
-        <v>13.289520019845886</v>
+        <v>46.513320069460605</v>
       </c>
       <c r="G28" s="1">
-        <v>12.93603814227694</v>
+        <v>45.27613349796929</v>
       </c>
       <c r="H28" s="1">
-        <v>15.988436575592836</v>
+        <v>55.959528014574929</v>
       </c>
       <c r="I28" s="1">
-        <v>14.903603810478089</v>
+        <v>52.16261333667331</v>
       </c>
       <c r="J28" s="1">
-        <v>15.216297969806638</v>
+        <v>53.257042894323234</v>
       </c>
       <c r="K28" s="1">
-        <v>16.849556198282304</v>
+        <v>58.973446693988066</v>
       </c>
       <c r="L28" s="1">
-        <v>14.239662067279415</v>
+        <v>49.838817235477954</v>
       </c>
       <c r="M28" s="1">
-        <v>21.090759389634979</v>
+        <v>73.817657863722431</v>
       </c>
       <c r="N28" s="1">
-        <v>18.306153462325014</v>
+        <v>64.071537118137542</v>
       </c>
       <c r="O28" s="1">
-        <v>15.95697066991765</v>
+        <v>55.849397344711775</v>
       </c>
       <c r="P28" s="1">
-        <v>17.72947821625344</v>
+        <v>62.053173756887041</v>
       </c>
       <c r="Q28" s="1">
-        <v>17.315015297680091</v>
+        <v>60.602553541880319</v>
       </c>
       <c r="R28" s="1">
-        <v>14.073372331882624</v>
+        <v>49.256803161589183</v>
       </c>
       <c r="S28" s="1">
-        <v>11.835566187644968</v>
+        <v>41.424481656757386</v>
       </c>
       <c r="T28" s="1">
-        <v>13.206039716961834</v>
+        <v>46.221139009366418</v>
       </c>
       <c r="U28" s="1">
-        <v>11.792433221703025</v>
+        <v>41.273516275960588</v>
       </c>
       <c r="V28" s="1">
-        <v>10.733427261739727</v>
+        <v>37.566995416089043</v>
       </c>
       <c r="W28" s="1">
-        <v>11.331589147290849</v>
+        <v>39.660562015517968</v>
       </c>
       <c r="X28" s="1">
-        <v>10.543444571081411</v>
+        <v>36.902055998784938</v>
       </c>
       <c r="Y28" s="1">
-        <v>12.940215643883507</v>
+        <v>45.290754753592275</v>
       </c>
       <c r="Z28" s="1">
-        <v>8.8659119974058704</v>
+        <v>31.030691990920545</v>
       </c>
       <c r="AA28" s="1">
-        <v>9.5050747536453297</v>
+        <v>33.267761637758653</v>
       </c>
     </row>
     <row r="29" spans="1:27" x14ac:dyDescent="0.2">
@@ -71609,76 +71609,76 @@
         <v>1</v>
       </c>
       <c r="D29" s="1">
-        <v>4.880756100000001</v>
+        <v>17.082646350000005</v>
       </c>
       <c r="E29" s="1">
-        <v>5.0435671000000006</v>
+        <v>17.65248485</v>
       </c>
       <c r="F29" s="1">
-        <v>4.5162183000000002</v>
+        <v>15.806764050000002</v>
       </c>
       <c r="G29" s="1">
-        <v>4.2807379999999995</v>
+        <v>14.982582999999998</v>
       </c>
       <c r="H29" s="1">
-        <v>3.5071872000000002</v>
+        <v>12.2751552</v>
       </c>
       <c r="I29" s="1">
-        <v>2.9766616000000004</v>
+        <v>10.418315600000001</v>
       </c>
       <c r="J29" s="1">
-        <v>3.6402157000000002</v>
+        <v>12.740754950000001</v>
       </c>
       <c r="K29" s="1">
-        <v>0.63218320000000017</v>
+        <v>2.2126412000000006</v>
       </c>
       <c r="L29" s="1">
-        <v>0.55593999999999999</v>
+        <v>1.9457899999999999</v>
       </c>
       <c r="M29" s="1">
-        <v>0.81048109999999984</v>
+        <v>2.8366838499999996</v>
       </c>
       <c r="N29" s="1">
-        <v>0.47731420000000008</v>
+        <v>1.6705997000000004</v>
       </c>
       <c r="O29" s="1">
-        <v>0.59644419999999987</v>
+        <v>2.0875546999999997</v>
       </c>
       <c r="P29" s="1">
-        <v>0.95026030000000028</v>
+        <v>3.3259110500000011</v>
       </c>
       <c r="Q29" s="1">
-        <v>1.7508139</v>
+        <v>6.1278486499999998</v>
       </c>
       <c r="R29" s="1">
-        <v>1.8679584</v>
+        <v>6.5378544000000005</v>
       </c>
       <c r="S29" s="1">
-        <v>1.8369845999999996</v>
+        <v>6.4294460999999989</v>
       </c>
       <c r="T29" s="1">
-        <v>1.0304745</v>
+        <v>3.6066607499999996</v>
       </c>
       <c r="U29" s="1">
-        <v>2.0990705999999997</v>
+        <v>7.3467470999999991</v>
       </c>
       <c r="V29" s="1">
-        <v>1.2318042</v>
+        <v>4.3113147000000005</v>
       </c>
       <c r="W29" s="1">
-        <v>0.86607509999999988</v>
+        <v>3.0312628499999996</v>
       </c>
       <c r="X29" s="1">
-        <v>1.3151952000000002</v>
+        <v>4.603183200000001</v>
       </c>
       <c r="Y29" s="1">
-        <v>0.81286369999999997</v>
+        <v>2.8450229499999997</v>
       </c>
       <c r="Z29" s="1">
-        <v>3.7101053000000004</v>
+        <v>12.98536855</v>
       </c>
       <c r="AA29" s="1">
-        <v>4.4725372999999999</v>
+        <v>15.65388055</v>
       </c>
     </row>
     <row r="30" spans="1:27" x14ac:dyDescent="0.2">
@@ -71692,76 +71692,76 @@
         <v>1</v>
       </c>
       <c r="D30" s="1">
-        <v>-11.167451974536863</v>
+        <v>-39.086081910879024</v>
       </c>
       <c r="E30" s="1">
-        <v>-12.823081768905411</v>
+        <v>-44.880786191168937</v>
       </c>
       <c r="F30" s="1">
-        <v>-10.030325820347226</v>
+        <v>-35.10614037121529</v>
       </c>
       <c r="G30" s="1">
-        <v>-13.3758715271357</v>
+        <v>-46.815550344974952</v>
       </c>
       <c r="H30" s="1">
-        <v>-17.808573532014695</v>
+        <v>-62.330007362051433</v>
       </c>
       <c r="I30" s="1">
-        <v>-16.90355195106568</v>
+        <v>-59.162431828729879</v>
       </c>
       <c r="J30" s="1">
-        <v>-15.023743744018972</v>
+        <v>-52.583103104066403</v>
       </c>
       <c r="K30" s="1">
-        <v>-17.759080083763511</v>
+        <v>-62.156780293172289</v>
       </c>
       <c r="L30" s="1">
-        <v>-18.697328105247461</v>
+        <v>-65.440648368366112</v>
       </c>
       <c r="M30" s="1">
-        <v>-23.646445297308613</v>
+        <v>-82.762558540580144</v>
       </c>
       <c r="N30" s="1">
-        <v>-24.12335938263136</v>
+        <v>-84.431757839209766</v>
       </c>
       <c r="O30" s="1">
-        <v>-23.651349811615397</v>
+        <v>-82.779724340653885</v>
       </c>
       <c r="P30" s="1">
-        <v>-19.306945238516331</v>
+        <v>-67.574308334807156</v>
       </c>
       <c r="Q30" s="1">
-        <v>-18.978743572868531</v>
+        <v>-66.425602505039862</v>
       </c>
       <c r="R30" s="1">
-        <v>-20.011676964824506</v>
+        <v>-70.040869376885766</v>
       </c>
       <c r="S30" s="1">
-        <v>-16.474463908219697</v>
+        <v>-57.660623678768943</v>
       </c>
       <c r="T30" s="1">
-        <v>-15.716068149233966</v>
+        <v>-55.006238522318881</v>
       </c>
       <c r="U30" s="1">
-        <v>-14.054421544287861</v>
+        <v>-49.190475405007511</v>
       </c>
       <c r="V30" s="1">
-        <v>-8.144512441516893</v>
+        <v>-28.505793545309125</v>
       </c>
       <c r="W30" s="1">
-        <v>-10.948033598645063</v>
+        <v>-38.318117595257718</v>
       </c>
       <c r="X30" s="1">
-        <v>-11.202136360502314</v>
+        <v>-39.2074772617581</v>
       </c>
       <c r="Y30" s="1">
-        <v>-10.361078635659446</v>
+        <v>-36.263775224808057</v>
       </c>
       <c r="Z30" s="1">
-        <v>-8.5627110268612121</v>
+        <v>-29.969488594014244</v>
       </c>
       <c r="AA30" s="1">
-        <v>-10.992628272128735</v>
+        <v>-38.474198952450571</v>
       </c>
     </row>
     <row r="31" spans="1:27" x14ac:dyDescent="0.2">
@@ -71775,76 +71775,76 @@
         <v>1</v>
       </c>
       <c r="D31" s="1">
-        <v>8.4290916681592769</v>
+        <v>29.501820838557471</v>
       </c>
       <c r="E31" s="1">
-        <v>10.625158596178837</v>
+        <v>37.18805508662593</v>
       </c>
       <c r="F31" s="1">
-        <v>13.821100820639721</v>
+        <v>48.373852872239027</v>
       </c>
       <c r="G31" s="1">
-        <v>13.194758905122479</v>
+        <v>46.181656167928672</v>
       </c>
       <c r="H31" s="1">
-        <v>16.468089672860621</v>
+        <v>57.638313855012171</v>
       </c>
       <c r="I31" s="1">
-        <v>14.605531734268528</v>
+        <v>51.119361069939849</v>
       </c>
       <c r="J31" s="1">
-        <v>14.455483071316305</v>
+        <v>50.594190749607066</v>
       </c>
       <c r="K31" s="1">
-        <v>16.849556198282304</v>
+        <v>58.973446693988066</v>
       </c>
       <c r="L31" s="1">
-        <v>14.524455308625004</v>
+        <v>50.835593580187513</v>
       </c>
       <c r="M31" s="1">
-        <v>22.145297359116725</v>
+        <v>77.508540756908531</v>
       </c>
       <c r="N31" s="1">
-        <v>17.940030393078516</v>
+        <v>62.790106375774805</v>
       </c>
       <c r="O31" s="1">
-        <v>15.95697066991765</v>
+        <v>55.849397344711775</v>
       </c>
       <c r="P31" s="1">
-        <v>18.438657344903575</v>
+        <v>64.53530070716252</v>
       </c>
       <c r="Q31" s="1">
-        <v>16.449264532796086</v>
+        <v>57.572425864786297</v>
       </c>
       <c r="R31" s="1">
-        <v>14.073372331882624</v>
+        <v>49.256803161589183</v>
       </c>
       <c r="S31" s="1">
-        <v>12.427344497027216</v>
+        <v>43.495705739595252</v>
       </c>
       <c r="T31" s="1">
-        <v>13.073979319792215</v>
+        <v>45.758927619272754</v>
       </c>
       <c r="U31" s="1">
-        <v>11.556584557268964</v>
+        <v>40.448045950441376</v>
       </c>
       <c r="V31" s="1">
-        <v>10.948095806974523</v>
+        <v>38.318335324410832</v>
       </c>
       <c r="W31" s="1">
-        <v>11.671536821709573</v>
+        <v>40.850378875983509</v>
       </c>
       <c r="X31" s="1">
-        <v>10.75431346250304</v>
+        <v>37.640097118760643</v>
       </c>
       <c r="Y31" s="1">
-        <v>12.552009174567001</v>
+        <v>43.932032110984501</v>
       </c>
       <c r="Z31" s="1">
-        <v>8.9545711173799294</v>
+        <v>31.340998910829754</v>
       </c>
       <c r="AA31" s="1">
-        <v>9.6001255011817825</v>
+        <v>33.600439254136241</v>
       </c>
     </row>
     <row r="32" spans="1:27" x14ac:dyDescent="0.2">
@@ -71858,76 +71858,76 @@
         <v>2</v>
       </c>
       <c r="D32" s="1">
-        <v>4.8319485390000008</v>
+        <v>16.911819886500002</v>
       </c>
       <c r="E32" s="1">
-        <v>5.2957454550000014</v>
+        <v>18.535109092500004</v>
       </c>
       <c r="F32" s="1">
-        <v>4.5162183000000002</v>
+        <v>15.806764050000002</v>
       </c>
       <c r="G32" s="1">
-        <v>4.0667010999999995</v>
+        <v>14.233453849999998</v>
       </c>
       <c r="H32" s="1">
-        <v>3.4721153280000006</v>
+        <v>12.152403648000002</v>
       </c>
       <c r="I32" s="1">
-        <v>2.8278285200000006</v>
+        <v>9.8973998200000022</v>
       </c>
       <c r="J32" s="1">
-        <v>3.494607072</v>
+        <v>12.231124751999999</v>
       </c>
       <c r="K32" s="1">
-        <v>0.65114869600000025</v>
+        <v>2.279020436000001</v>
       </c>
       <c r="L32" s="1">
-        <v>0.55593999999999999</v>
+        <v>1.9457899999999999</v>
       </c>
       <c r="M32" s="1">
-        <v>0.79427147799999986</v>
+        <v>2.7799501729999996</v>
       </c>
       <c r="N32" s="1">
-        <v>0.47254105800000007</v>
+        <v>1.6538937030000003</v>
       </c>
       <c r="O32" s="1">
-        <v>0.60240864199999988</v>
+        <v>2.1084302469999994</v>
       </c>
       <c r="P32" s="1">
-        <v>0.94075769700000023</v>
+        <v>3.2926519395000007</v>
       </c>
       <c r="Q32" s="1">
-        <v>1.733305761</v>
+        <v>6.0665701634999998</v>
       </c>
       <c r="R32" s="1">
-        <v>1.8866379839999998</v>
+        <v>6.6032329439999993</v>
       </c>
       <c r="S32" s="1">
-        <v>1.7635052159999998</v>
+        <v>6.1722682559999988</v>
       </c>
       <c r="T32" s="1">
-        <v>1.0304745</v>
+        <v>3.6066607499999996</v>
       </c>
       <c r="U32" s="1">
-        <v>2.2040241299999996</v>
+        <v>7.7140844549999983</v>
       </c>
       <c r="V32" s="1">
-        <v>1.1825320320000001</v>
+        <v>4.138862112</v>
       </c>
       <c r="W32" s="1">
-        <v>0.88339660199999981</v>
+        <v>3.0918881069999995</v>
       </c>
       <c r="X32" s="1">
-        <v>1.2625873920000001</v>
+        <v>4.4190558720000004</v>
       </c>
       <c r="Y32" s="1">
-        <v>0.78034915199999999</v>
+        <v>2.7312220319999998</v>
       </c>
       <c r="Z32" s="1">
-        <v>3.6730042470000006</v>
+        <v>12.855514864500002</v>
       </c>
       <c r="AA32" s="1">
-        <v>4.4725372999999999</v>
+        <v>15.65388055</v>
       </c>
     </row>
     <row r="33" spans="1:27" x14ac:dyDescent="0.2">
@@ -71941,76 +71941,76 @@
         <v>2</v>
       </c>
       <c r="D33" s="1">
-        <v>-10.944102935046125</v>
+        <v>-38.304360272661441</v>
       </c>
       <c r="E33" s="1">
-        <v>-12.566620133527303</v>
+        <v>-43.983170467345559</v>
       </c>
       <c r="F33" s="1">
-        <v>-9.8297193039402817</v>
+        <v>-34.404017563790987</v>
       </c>
       <c r="G33" s="1">
-        <v>-12.974595381321627</v>
+        <v>-45.4110838346257</v>
       </c>
       <c r="H33" s="1">
-        <v>-18.699002208615429</v>
+        <v>-65.446507730153996</v>
       </c>
       <c r="I33" s="1">
-        <v>-16.39644539253371</v>
+        <v>-57.387558873867988</v>
       </c>
       <c r="J33" s="1">
-        <v>-15.324218618899351</v>
+        <v>-53.63476516614773</v>
       </c>
       <c r="K33" s="1">
-        <v>-17.581489282925876</v>
+        <v>-61.535212490240568</v>
       </c>
       <c r="L33" s="1">
-        <v>-18.136408262090036</v>
+        <v>-63.477428917315123</v>
       </c>
       <c r="M33" s="1">
-        <v>-22.937051938389356</v>
+        <v>-80.279681784362751</v>
       </c>
       <c r="N33" s="1">
-        <v>-22.91719141349979</v>
+        <v>-80.21016994724927</v>
       </c>
       <c r="O33" s="1">
-        <v>-24.83391730219617</v>
+        <v>-86.918710557686595</v>
       </c>
       <c r="P33" s="1">
-        <v>-19.886153595671821</v>
+        <v>-69.601537584851371</v>
       </c>
       <c r="Q33" s="1">
-        <v>-19.358318444325899</v>
+        <v>-67.754114555140646</v>
       </c>
       <c r="R33" s="1">
-        <v>-20.81214404341749</v>
+        <v>-72.842504151961208</v>
       </c>
       <c r="S33" s="1">
-        <v>-17.133442464548484</v>
+        <v>-59.967048625919695</v>
       </c>
       <c r="T33" s="1">
-        <v>-15.558907467741626</v>
+        <v>-54.456176137095696</v>
       </c>
       <c r="U33" s="1">
-        <v>-13.913877328844983</v>
+        <v>-48.698570650957436</v>
       </c>
       <c r="V33" s="1">
-        <v>-8.2259575659320614</v>
+        <v>-28.790851480762214</v>
       </c>
       <c r="W33" s="1">
-        <v>-10.948033598645063</v>
+        <v>-38.318117595257718</v>
       </c>
       <c r="X33" s="1">
-        <v>-11.426179087712359</v>
+        <v>-39.99162680699326</v>
       </c>
       <c r="Y33" s="1">
-        <v>-10.879132567442419</v>
+        <v>-38.076963986048469</v>
       </c>
       <c r="Z33" s="1">
-        <v>-8.9908465782042732</v>
+        <v>-31.467963023714958</v>
       </c>
       <c r="AA33" s="1">
-        <v>-10.552923141243587</v>
+        <v>-36.935230994352558</v>
       </c>
     </row>
     <row r="34" spans="1:27" x14ac:dyDescent="0.2">
@@ -72024,76 +72024,76 @@
         <v>2</v>
       </c>
       <c r="D34" s="1">
-        <v>8.0076370847513143</v>
+        <v>28.026729796629599</v>
       </c>
       <c r="E34" s="1">
-        <v>10.943913354064202</v>
+        <v>38.303696739224705</v>
       </c>
       <c r="F34" s="1">
-        <v>13.130045779607736</v>
+        <v>45.955160228627072</v>
       </c>
       <c r="G34" s="1">
-        <v>12.666968548917581</v>
+        <v>44.334389921211532</v>
       </c>
       <c r="H34" s="1">
-        <v>15.644685189217592</v>
+        <v>54.756398162261569</v>
       </c>
       <c r="I34" s="1">
-        <v>15.043697686296584</v>
+        <v>52.652941902038044</v>
       </c>
       <c r="J34" s="1">
-        <v>13.877263748463651</v>
+        <v>48.570423119622781</v>
       </c>
       <c r="K34" s="1">
-        <v>16.007078388368189</v>
+        <v>56.024774359288664</v>
       </c>
       <c r="L34" s="1">
-        <v>15.105433520970005</v>
+        <v>52.869017323395013</v>
       </c>
       <c r="M34" s="1">
-        <v>21.038032491160887</v>
+        <v>73.633113719063104</v>
       </c>
       <c r="N34" s="1">
-        <v>17.043028873424589</v>
+        <v>59.650601056986062</v>
       </c>
       <c r="O34" s="1">
-        <v>16.754819203413533</v>
+        <v>58.641867211947364</v>
       </c>
       <c r="P34" s="1">
-        <v>18.807430491801647</v>
+        <v>65.82600672130576</v>
       </c>
       <c r="Q34" s="1">
-        <v>16.778249823452008</v>
+        <v>58.72387438208203</v>
       </c>
       <c r="R34" s="1">
-        <v>14.354839778520278</v>
+        <v>50.241939224820975</v>
       </c>
       <c r="S34" s="1">
-        <v>12.427344497027216</v>
+        <v>43.495705739595252</v>
       </c>
       <c r="T34" s="1">
-        <v>13.204719112990137</v>
+        <v>46.216516895465482</v>
       </c>
       <c r="U34" s="1">
-        <v>11.209887020550896</v>
+        <v>39.234604571928138</v>
       </c>
       <c r="V34" s="1">
-        <v>11.276538681183759</v>
+        <v>39.467885384143159</v>
       </c>
       <c r="W34" s="1">
-        <v>11.904967558143765</v>
+        <v>41.667386453503177</v>
       </c>
       <c r="X34" s="1">
-        <v>10.216597789377888</v>
+        <v>35.758092262822608</v>
       </c>
       <c r="Y34" s="1">
-        <v>12.42648908282133</v>
+        <v>43.492711789874654</v>
       </c>
       <c r="Z34" s="1">
-        <v>8.5068425615109327</v>
+        <v>29.773948965288263</v>
       </c>
       <c r="AA34" s="1">
-        <v>9.888129266217236</v>
+        <v>34.608452431760327</v>
       </c>
     </row>
     <row r="35" spans="1:27" x14ac:dyDescent="0.2">
@@ -72107,76 +72107,76 @@
         <v>3</v>
       </c>
       <c r="D35" s="1">
-        <v>4.8319485390000008</v>
+        <v>16.911819886500002</v>
       </c>
       <c r="E35" s="1">
-        <v>5.5075752732000014</v>
+        <v>19.276513456200004</v>
       </c>
       <c r="F35" s="1">
-        <v>4.5162183000000002</v>
+        <v>15.806764050000002</v>
       </c>
       <c r="G35" s="1">
-        <v>3.9853670779999995</v>
+        <v>13.948784772999998</v>
       </c>
       <c r="H35" s="1">
-        <v>3.2985095616000009</v>
+        <v>11.544783465600004</v>
       </c>
       <c r="I35" s="1">
-        <v>2.7712719496000005</v>
+        <v>9.6994518236000022</v>
       </c>
       <c r="J35" s="1">
-        <v>3.3198767184000002</v>
+        <v>11.619568514400001</v>
       </c>
       <c r="K35" s="1">
-        <v>0.63812572208000029</v>
+        <v>2.2334400272800012</v>
       </c>
       <c r="L35" s="1">
-        <v>0.55593999999999999</v>
+        <v>1.9457899999999999</v>
       </c>
       <c r="M35" s="1">
-        <v>0.80221419277999984</v>
+        <v>2.8077496747299993</v>
       </c>
       <c r="N35" s="1">
-        <v>0.49616811090000007</v>
+        <v>1.7365883881500002</v>
       </c>
       <c r="O35" s="1">
-        <v>0.59638455557999992</v>
+        <v>2.0873459445299996</v>
       </c>
       <c r="P35" s="1">
-        <v>0.98779558185000027</v>
+        <v>3.4572845364750009</v>
       </c>
       <c r="Q35" s="1">
-        <v>1.7679718762199998</v>
+        <v>6.1879015667699999</v>
       </c>
       <c r="R35" s="1">
-        <v>1.9243707436799997</v>
+        <v>6.7352976028799993</v>
       </c>
       <c r="S35" s="1">
-        <v>1.7106000595199999</v>
+        <v>5.9871002083199993</v>
       </c>
       <c r="T35" s="1">
-        <v>1.061388735</v>
+        <v>3.7148605725000001</v>
       </c>
       <c r="U35" s="1">
-        <v>2.1379034060999995</v>
+        <v>7.4826619213499983</v>
       </c>
       <c r="V35" s="1">
-        <v>1.2298333132800001</v>
+        <v>4.3044165964800003</v>
       </c>
       <c r="W35" s="1">
-        <v>0.85689470393999978</v>
+        <v>2.9991314637899991</v>
       </c>
       <c r="X35" s="1">
-        <v>1.1994580224000002</v>
+        <v>4.1981030784000009</v>
       </c>
       <c r="Y35" s="1">
-        <v>0.77254566048000006</v>
+        <v>2.70390981168</v>
       </c>
       <c r="Z35" s="1">
-        <v>3.7464643319400004</v>
+        <v>13.112625161790001</v>
       </c>
       <c r="AA35" s="1">
-        <v>4.4278119270000005</v>
+        <v>15.497341744500002</v>
       </c>
     </row>
     <row r="36" spans="1:27" x14ac:dyDescent="0.2">
@@ -72190,76 +72190,76 @@
         <v>3</v>
       </c>
       <c r="D36" s="1">
-        <v>-11.491308081798431</v>
+        <v>-40.219578286294507</v>
       </c>
       <c r="E36" s="1">
-        <v>-13.194951140203669</v>
+        <v>-46.18232899071284</v>
       </c>
       <c r="F36" s="1">
-        <v>-10.124610883058489</v>
+        <v>-35.436138090704709</v>
       </c>
       <c r="G36" s="1">
-        <v>-13.234087288948061</v>
+        <v>-46.319305511318213</v>
       </c>
       <c r="H36" s="1">
-        <v>-19.072982252787739</v>
+        <v>-66.755437884757086</v>
       </c>
       <c r="I36" s="1">
-        <v>-17.216267662160398</v>
+        <v>-60.256936817561396</v>
       </c>
       <c r="J36" s="1">
-        <v>-14.86449206033237</v>
+        <v>-52.025722211163298</v>
       </c>
       <c r="K36" s="1">
-        <v>-17.933119068584393</v>
+        <v>-62.765916740045377</v>
       </c>
       <c r="L36" s="1">
-        <v>-17.955044179469137</v>
+        <v>-62.842654628141979</v>
       </c>
       <c r="M36" s="1">
-        <v>-22.248940380237677</v>
+        <v>-77.871291330831866</v>
       </c>
       <c r="N36" s="1">
-        <v>-21.771331842824804</v>
+        <v>-76.199661449886818</v>
       </c>
       <c r="O36" s="1">
-        <v>-24.337238956152245</v>
+        <v>-85.180336346532854</v>
       </c>
       <c r="P36" s="1">
-        <v>-18.891845915888229</v>
+        <v>-66.121460705608797</v>
       </c>
       <c r="Q36" s="1">
-        <v>-19.16473525988264</v>
+        <v>-67.076573409589244</v>
       </c>
       <c r="R36" s="1">
-        <v>-21.852751245588365</v>
+        <v>-76.484629359559278</v>
       </c>
       <c r="S36" s="1">
-        <v>-17.64744573848494</v>
+        <v>-61.766060084697287</v>
       </c>
       <c r="T36" s="1">
-        <v>-14.780962094354544</v>
+        <v>-51.733367330240903</v>
       </c>
       <c r="U36" s="1">
-        <v>-14.609571195287231</v>
+        <v>-51.133499183505307</v>
       </c>
       <c r="V36" s="1">
-        <v>-8.3082171415913812</v>
+        <v>-29.078759995569833</v>
       </c>
       <c r="W36" s="1">
-        <v>-11.166994270617963</v>
+        <v>-39.084479947162869</v>
       </c>
       <c r="X36" s="1">
-        <v>-11.083393715080987</v>
+        <v>-38.791878002783456</v>
       </c>
       <c r="Y36" s="1">
-        <v>-10.443967264744721</v>
+        <v>-36.553885426606527</v>
       </c>
       <c r="Z36" s="1">
-        <v>-9.3504804413324436</v>
+        <v>-32.726681544663549</v>
       </c>
       <c r="AA36" s="1">
-        <v>-10.341864678418714</v>
+        <v>-36.196526374465499</v>
       </c>
     </row>
     <row r="37" spans="1:27" x14ac:dyDescent="0.2">
@@ -72273,76 +72273,76 @@
         <v>3</v>
       </c>
       <c r="D37" s="1">
-        <v>8.0076370847513143</v>
+        <v>28.026729796629599</v>
       </c>
       <c r="E37" s="1">
-        <v>10.725035086982919</v>
+        <v>37.537622804440218</v>
       </c>
       <c r="F37" s="1">
-        <v>13.130045779607736</v>
+        <v>45.955160228627072</v>
       </c>
       <c r="G37" s="1">
-        <v>12.033620121471701</v>
+        <v>42.117670425150955</v>
       </c>
       <c r="H37" s="1">
-        <v>16.114025744894121</v>
+        <v>56.399090107129425</v>
       </c>
       <c r="I37" s="1">
-        <v>15.795882570611413</v>
+        <v>55.285588997139946</v>
       </c>
       <c r="J37" s="1">
-        <v>14.432354298402197</v>
+        <v>50.513240044407688</v>
       </c>
       <c r="K37" s="1">
-        <v>16.327219956135551</v>
+        <v>57.145269846474427</v>
       </c>
       <c r="L37" s="1">
-        <v>15.105433520970005</v>
+        <v>52.869017323395013</v>
       </c>
       <c r="M37" s="1">
-        <v>21.458793140984103</v>
+        <v>75.105775993444354</v>
       </c>
       <c r="N37" s="1">
-        <v>17.724750028361573</v>
+        <v>62.036625099265507</v>
       </c>
       <c r="O37" s="1">
-        <v>17.257463779515938</v>
+        <v>60.401123228305778</v>
       </c>
       <c r="P37" s="1">
-        <v>17.867058967211566</v>
+        <v>62.534706385240483</v>
       </c>
       <c r="Q37" s="1">
-        <v>15.939337332279408</v>
+        <v>55.787680662977927</v>
       </c>
       <c r="R37" s="1">
-        <v>14.641936574090682</v>
+        <v>51.246778009317389</v>
       </c>
       <c r="S37" s="1">
-        <v>12.178797607086672</v>
+        <v>42.625791624803355</v>
       </c>
       <c r="T37" s="1">
-        <v>13.46881349524994</v>
+        <v>47.140847233374785</v>
       </c>
       <c r="U37" s="1">
-        <v>10.873590409934371</v>
+        <v>38.057566434770301</v>
       </c>
       <c r="V37" s="1">
-        <v>11.727600228431108</v>
+        <v>41.04660079950888</v>
       </c>
       <c r="W37" s="1">
-        <v>11.666868206980888</v>
+        <v>40.834038724433107</v>
       </c>
       <c r="X37" s="1">
-        <v>10.114431811484108</v>
+        <v>35.400511340194377</v>
       </c>
       <c r="Y37" s="1">
-        <v>12.42648908282133</v>
+        <v>43.492711789874654</v>
       </c>
       <c r="Z37" s="1">
-        <v>8.1665688590504946</v>
+        <v>28.582991006676732</v>
       </c>
       <c r="AA37" s="1">
-        <v>9.888129266217236</v>
+        <v>34.608452431760327</v>
       </c>
     </row>
   </sheetData>
